--- a/web/EXCEL_TEMPLATE/KHNV/NV_QT.xlsx
+++ b/web/EXCEL_TEMPLATE/KHNV/NV_QT.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Project\IMS_REPORTS\IMS_REPORTS\web\EXCEL_TEMPLATE\KHNV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Cap nhat CN\IMS_REPORT NEW_27DEC21\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -92,7 +92,7 @@
     <definedName name="ZZZ" localSheetId="0">#REF!</definedName>
     <definedName name="ZZZ">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1530,9 +1530,6 @@
     <xf numFmtId="3" fontId="15" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1581,6 +1578,77 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1608,19 +1676,8 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1628,63 +1685,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -3185,12 +3185,11 @@
   <cols>
     <col min="1" max="1" width="8.3984375" style="77" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.3984375" customWidth="1"/>
-    <col min="3" max="3" width="56.8984375" customWidth="1"/>
-    <col min="4" max="4" width="10.59765625" customWidth="1"/>
-    <col min="5" max="5" width="8.5" customWidth="1"/>
-    <col min="6" max="6" width="11.19921875" customWidth="1"/>
-    <col min="7" max="7" width="8.19921875" customWidth="1"/>
-    <col min="8" max="8" width="9.09765625" customWidth="1"/>
+    <col min="3" max="3" width="59.796875" customWidth="1"/>
+    <col min="4" max="5" width="18.5" customWidth="1"/>
+    <col min="6" max="6" width="20.8984375" customWidth="1"/>
+    <col min="7" max="7" width="20.59765625" customWidth="1"/>
+    <col min="8" max="8" width="14.5" customWidth="1"/>
     <col min="9" max="9" width="10.8984375" customWidth="1"/>
     <col min="10" max="27" width="9.09765625" customWidth="1"/>
   </cols>
@@ -3198,13 +3197,13 @@
     <row r="1" spans="1:27" ht="17.25" customHeight="1">
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
-      <c r="D1" s="115" t="s">
+      <c r="D1" s="140" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="114"/>
-      <c r="F1" s="114"/>
-      <c r="G1" s="114"/>
-      <c r="H1" s="114"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
+      <c r="H1" s="139"/>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
@@ -3230,13 +3229,13 @@
         <v>1</v>
       </c>
       <c r="C2" s="2"/>
-      <c r="D2" s="116" t="s">
+      <c r="D2" s="141" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="114"/>
-      <c r="F2" s="114"/>
-      <c r="G2" s="114"/>
-      <c r="H2" s="114"/>
+      <c r="E2" s="139"/>
+      <c r="F2" s="139"/>
+      <c r="G2" s="139"/>
+      <c r="H2" s="139"/>
       <c r="I2" s="4"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
@@ -3290,7 +3289,7 @@
       <c r="AA3" s="3"/>
     </row>
     <row r="4" spans="1:27" ht="17.25" customHeight="1">
-      <c r="B4" s="112" t="s">
+      <c r="B4" s="111" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="2"/>
@@ -3320,15 +3319,15 @@
       <c r="AA4" s="3"/>
     </row>
     <row r="5" spans="1:27" ht="17.25" customHeight="1">
-      <c r="B5" s="117" t="s">
+      <c r="B5" s="142" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="114"/>
-      <c r="D5" s="114"/>
-      <c r="E5" s="114"/>
-      <c r="F5" s="114"/>
-      <c r="G5" s="114"/>
-      <c r="H5" s="114"/>
+      <c r="C5" s="139"/>
+      <c r="D5" s="139"/>
+      <c r="E5" s="139"/>
+      <c r="F5" s="139"/>
+      <c r="G5" s="139"/>
+      <c r="H5" s="139"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
@@ -3350,15 +3349,15 @@
       <c r="AA5" s="3"/>
     </row>
     <row r="6" spans="1:27" ht="21" customHeight="1">
-      <c r="B6" s="118" t="s">
+      <c r="B6" s="143" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="119"/>
-      <c r="D6" s="119"/>
-      <c r="E6" s="119"/>
-      <c r="F6" s="119"/>
-      <c r="G6" s="119"/>
-      <c r="H6" s="119"/>
+      <c r="C6" s="144"/>
+      <c r="D6" s="144"/>
+      <c r="E6" s="144"/>
+      <c r="F6" s="144"/>
+      <c r="G6" s="144"/>
+      <c r="H6" s="144"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
@@ -3380,13 +3379,13 @@
       <c r="AA6" s="3"/>
     </row>
     <row r="7" spans="1:27" ht="13.5" customHeight="1">
-      <c r="B7" s="120"/>
-      <c r="C7" s="114"/>
-      <c r="D7" s="114"/>
-      <c r="E7" s="114"/>
-      <c r="F7" s="114"/>
-      <c r="G7" s="114"/>
-      <c r="H7" s="114"/>
+      <c r="B7" s="145"/>
+      <c r="C7" s="139"/>
+      <c r="D7" s="139"/>
+      <c r="E7" s="139"/>
+      <c r="F7" s="139"/>
+      <c r="G7" s="139"/>
+      <c r="H7" s="139"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
@@ -3408,15 +3407,15 @@
       <c r="AA7" s="3"/>
     </row>
     <row r="8" spans="1:27" ht="15.75" customHeight="1">
-      <c r="B8" s="121" t="s">
+      <c r="B8" s="146" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="122"/>
-      <c r="D8" s="122"/>
-      <c r="E8" s="122"/>
-      <c r="F8" s="122"/>
-      <c r="G8" s="122"/>
-      <c r="H8" s="122"/>
+      <c r="C8" s="147"/>
+      <c r="D8" s="147"/>
+      <c r="E8" s="147"/>
+      <c r="F8" s="147"/>
+      <c r="G8" s="147"/>
+      <c r="H8" s="147"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
@@ -3438,27 +3437,27 @@
       <c r="AA8" s="3"/>
     </row>
     <row r="9" spans="1:27" ht="21.75" customHeight="1">
-      <c r="A9" s="123"/>
-      <c r="B9" s="123" t="s">
+      <c r="A9" s="121"/>
+      <c r="B9" s="121" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="123" t="s">
+      <c r="C9" s="121" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="126" t="s">
+      <c r="D9" s="148" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="129" t="s">
+      <c r="E9" s="149" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="130"/>
-      <c r="G9" s="131" t="s">
+      <c r="F9" s="150"/>
+      <c r="G9" s="127" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="131" t="s">
+      <c r="H9" s="127" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="113"/>
+      <c r="I9" s="138"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
@@ -3479,19 +3478,19 @@
       <c r="AA9" s="3"/>
     </row>
     <row r="10" spans="1:27" ht="18" customHeight="1">
-      <c r="A10" s="124"/>
-      <c r="B10" s="124"/>
-      <c r="C10" s="124"/>
-      <c r="D10" s="127"/>
-      <c r="E10" s="126" t="s">
+      <c r="A10" s="122"/>
+      <c r="B10" s="122"/>
+      <c r="C10" s="122"/>
+      <c r="D10" s="128"/>
+      <c r="E10" s="148" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="126" t="s">
+      <c r="F10" s="148" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="127"/>
-      <c r="H10" s="127"/>
-      <c r="I10" s="114"/>
+      <c r="G10" s="128"/>
+      <c r="H10" s="128"/>
+      <c r="I10" s="139"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
@@ -3512,15 +3511,15 @@
       <c r="AA10" s="3"/>
     </row>
     <row r="11" spans="1:27" ht="167.25" customHeight="1">
-      <c r="A11" s="125"/>
-      <c r="B11" s="125"/>
-      <c r="C11" s="125"/>
-      <c r="D11" s="128"/>
-      <c r="E11" s="128"/>
-      <c r="F11" s="128"/>
-      <c r="G11" s="128"/>
-      <c r="H11" s="128"/>
-      <c r="I11" s="114"/>
+      <c r="A11" s="123"/>
+      <c r="B11" s="123"/>
+      <c r="C11" s="123"/>
+      <c r="D11" s="129"/>
+      <c r="E11" s="129"/>
+      <c r="F11" s="129"/>
+      <c r="G11" s="129"/>
+      <c r="H11" s="129"/>
+      <c r="I11" s="139"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3" t="s">
         <v>17</v>
@@ -3599,23 +3598,23 @@
       </c>
       <c r="D13" s="13">
         <f t="shared" ref="D13:F13" si="0">SUM(D14,D22)</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E13" s="13">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F13" s="13">
         <f t="shared" si="0"/>
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="G13" s="14">
         <f>IF(AND(D13="",F13=""),"",F13*1-D13*1)</f>
-        <v>90</v>
-      </c>
-      <c r="H13" s="109">
+        <v>0</v>
+      </c>
+      <c r="H13" s="108" t="str">
         <f>IFERROR(G13/E13,"")</f>
-        <v>0.9</v>
+        <v/>
       </c>
       <c r="J13" s="11"/>
       <c r="K13" s="11"/>
@@ -3648,23 +3647,23 @@
       </c>
       <c r="D14" s="19">
         <f t="shared" ref="D14:F14" si="1">D15+D16</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E14" s="20">
         <f t="shared" si="1"/>
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F14" s="20">
         <f t="shared" si="1"/>
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="G14" s="21">
         <f t="shared" ref="G14:G77" si="2">IF(AND(D14="",F14=""),"",F14*1-D14*1)</f>
-        <v>70</v>
-      </c>
-      <c r="H14" s="110">
+        <v>0</v>
+      </c>
+      <c r="H14" s="109" t="str">
         <f t="shared" ref="H14:H77" si="3">IFERROR(G14/E14,"")</f>
-        <v>0.875</v>
+        <v/>
       </c>
       <c r="J14" s="11"/>
       <c r="K14" s="11"/>
@@ -3697,23 +3696,23 @@
       </c>
       <c r="D15" s="94">
         <f t="shared" ref="D15:F15" si="4">D25-D22-D16</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E15" s="94">
         <f t="shared" si="4"/>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F15" s="95">
         <f t="shared" si="4"/>
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G15" s="43">
         <f t="shared" si="2"/>
-        <v>70</v>
-      </c>
-      <c r="H15" s="108">
+        <v>0</v>
+      </c>
+      <c r="H15" s="107" t="str">
         <f t="shared" si="3"/>
-        <v>1.75</v>
+        <v/>
       </c>
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
@@ -3738,31 +3737,28 @@
       <c r="A16" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="96">
+      <c r="B16" s="120">
         <v>2</v>
       </c>
-      <c r="C16" s="93" t="s">
+      <c r="C16" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="94">
-        <f t="shared" ref="D16:F16" si="5">D17+D21</f>
-        <v>40</v>
-      </c>
-      <c r="E16" s="94">
-        <f t="shared" si="5"/>
-        <v>40</v>
-      </c>
-      <c r="F16" s="94">
-        <f t="shared" si="5"/>
-        <v>40</v>
+      <c r="D16" s="82">
+        <v>0</v>
+      </c>
+      <c r="E16" s="82">
+        <v>0</v>
+      </c>
+      <c r="F16" s="82">
+        <v>0</v>
       </c>
       <c r="G16" s="43">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H16" s="108">
+      <c r="H16" s="107" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J16" s="11"/>
       <c r="K16" s="11"/>
@@ -3793,22 +3789,16 @@
       <c r="C17" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="D17" s="79">
-        <v>30</v>
-      </c>
-      <c r="E17" s="80">
-        <v>30</v>
-      </c>
-      <c r="F17" s="80">
-        <v>30</v>
-      </c>
-      <c r="G17" s="22">
+      <c r="D17" s="79"/>
+      <c r="E17" s="80"/>
+      <c r="F17" s="80"/>
+      <c r="G17" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H17" s="108">
+        <v/>
+      </c>
+      <c r="H17" s="107" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J17" s="11"/>
       <c r="K17" s="11"/>
@@ -3839,22 +3829,16 @@
       <c r="C18" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="D18" s="81">
-        <v>10</v>
-      </c>
-      <c r="E18" s="82">
-        <v>10</v>
-      </c>
-      <c r="F18" s="82">
-        <v>10</v>
-      </c>
-      <c r="G18" s="22">
+      <c r="D18" s="81"/>
+      <c r="E18" s="82"/>
+      <c r="F18" s="82"/>
+      <c r="G18" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H18" s="108">
+        <v/>
+      </c>
+      <c r="H18" s="107" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -3883,20 +3867,14 @@
       <c r="C19" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="D19" s="81">
-        <v>0</v>
-      </c>
-      <c r="E19" s="82">
-        <v>0</v>
-      </c>
-      <c r="F19" s="82">
-        <v>0</v>
-      </c>
-      <c r="G19" s="22">
+      <c r="D19" s="81"/>
+      <c r="E19" s="82"/>
+      <c r="F19" s="82"/>
+      <c r="G19" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H19" s="108" t="str">
+        <v/>
+      </c>
+      <c r="H19" s="107" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3927,22 +3905,16 @@
       <c r="C20" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="D20" s="81">
-        <v>10</v>
-      </c>
-      <c r="E20" s="82">
-        <v>10</v>
-      </c>
-      <c r="F20" s="82">
-        <v>10</v>
-      </c>
-      <c r="G20" s="22">
+      <c r="D20" s="81"/>
+      <c r="E20" s="82"/>
+      <c r="F20" s="82"/>
+      <c r="G20" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H20" s="108">
+        <v/>
+      </c>
+      <c r="H20" s="107" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J20" s="11"/>
       <c r="K20" s="11"/>
@@ -3973,22 +3945,16 @@
       <c r="C21" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="D21" s="81">
-        <v>10</v>
-      </c>
-      <c r="E21" s="82">
-        <v>10</v>
-      </c>
-      <c r="F21" s="82">
-        <v>10</v>
-      </c>
-      <c r="G21" s="22">
+      <c r="D21" s="81"/>
+      <c r="E21" s="82"/>
+      <c r="F21" s="82"/>
+      <c r="G21" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H21" s="108">
+        <v/>
+      </c>
+      <c r="H21" s="107" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J21" s="11"/>
       <c r="K21" s="11"/>
@@ -4020,24 +3986,24 @@
         <v>42</v>
       </c>
       <c r="D22" s="19">
-        <f t="shared" ref="D22:F22" si="6">D23+D24</f>
-        <v>50</v>
+        <f t="shared" ref="D22:F22" si="5">D23+D24</f>
+        <v>0</v>
       </c>
       <c r="E22" s="19">
-        <f t="shared" si="6"/>
-        <v>20</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="F22" s="19">
-        <f t="shared" si="6"/>
-        <v>70</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="G22" s="32">
         <f t="shared" si="2"/>
-        <v>20</v>
-      </c>
-      <c r="H22" s="110">
+        <v>0</v>
+      </c>
+      <c r="H22" s="109" t="str">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="J22" s="11"/>
       <c r="K22" s="11"/>
@@ -4068,22 +4034,16 @@
       <c r="C23" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D23" s="81">
-        <v>40</v>
-      </c>
-      <c r="E23" s="82">
-        <v>10</v>
-      </c>
-      <c r="F23" s="82">
-        <v>50</v>
-      </c>
-      <c r="G23" s="35">
+      <c r="D23" s="81"/>
+      <c r="E23" s="82"/>
+      <c r="F23" s="82"/>
+      <c r="G23" s="35" t="str">
         <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="H23" s="108">
+        <v/>
+      </c>
+      <c r="H23" s="107" t="str">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
@@ -4112,22 +4072,16 @@
       <c r="C24" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="81">
-        <v>10</v>
-      </c>
-      <c r="E24" s="82">
-        <v>10</v>
-      </c>
-      <c r="F24" s="82">
-        <v>20</v>
-      </c>
-      <c r="G24" s="35">
+      <c r="D24" s="81"/>
+      <c r="E24" s="82"/>
+      <c r="F24" s="82"/>
+      <c r="G24" s="35" t="str">
         <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="H24" s="108">
+        <v/>
+      </c>
+      <c r="H24" s="107" t="str">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="J24" s="11"/>
       <c r="K24" s="11"/>
@@ -4152,31 +4106,31 @@
       <c r="A25" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="97" t="s">
+      <c r="B25" s="96" t="s">
         <v>48</v>
       </c>
-      <c r="C25" s="97" t="s">
+      <c r="C25" s="96" t="s">
         <v>49</v>
       </c>
-      <c r="D25" s="98">
-        <f t="shared" ref="D25:F25" si="7">D26+D63+D90</f>
-        <v>100</v>
-      </c>
-      <c r="E25" s="98">
-        <f t="shared" si="7"/>
-        <v>100</v>
-      </c>
-      <c r="F25" s="98">
-        <f t="shared" si="7"/>
-        <v>190</v>
+      <c r="D25" s="97">
+        <f t="shared" ref="D25:F25" si="6">D26+D63+D90</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="97">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F25" s="97">
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="G25" s="14">
         <f t="shared" si="2"/>
-        <v>90</v>
-      </c>
-      <c r="H25" s="109">
+        <v>0</v>
+      </c>
+      <c r="H25" s="108" t="str">
         <f t="shared" si="3"/>
-        <v>0.9</v>
+        <v/>
       </c>
       <c r="J25" s="11"/>
       <c r="K25" s="11"/>
@@ -4201,31 +4155,31 @@
       <c r="A26" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="B26" s="99" t="s">
+      <c r="B26" s="98" t="s">
         <v>23</v>
       </c>
-      <c r="C26" s="100" t="s">
+      <c r="C26" s="99" t="s">
         <v>51</v>
       </c>
-      <c r="D26" s="101">
-        <f t="shared" ref="D26:F26" si="8">SUM(D27:D54)+D62-D34-D49</f>
-        <v>60</v>
-      </c>
-      <c r="E26" s="101">
-        <f t="shared" si="8"/>
-        <v>60</v>
-      </c>
-      <c r="F26" s="101">
-        <f t="shared" si="8"/>
-        <v>120</v>
+      <c r="D26" s="100">
+        <f t="shared" ref="D26:F26" si="7">SUM(D27:D54)+D62-D34-D49</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="100">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F26" s="100">
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="G26" s="32">
         <f t="shared" si="2"/>
-        <v>60</v>
-      </c>
-      <c r="H26" s="110">
+        <v>0</v>
+      </c>
+      <c r="H26" s="109" t="str">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="J26" s="11"/>
       <c r="K26" s="11"/>
@@ -4256,22 +4210,16 @@
       <c r="C27" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="D27" s="81">
-        <v>10</v>
-      </c>
-      <c r="E27" s="82">
-        <v>10</v>
-      </c>
-      <c r="F27" s="82">
-        <v>20</v>
-      </c>
-      <c r="G27" s="35">
+      <c r="D27" s="81"/>
+      <c r="E27" s="82"/>
+      <c r="F27" s="82"/>
+      <c r="G27" s="35" t="str">
         <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="H27" s="108">
+        <v/>
+      </c>
+      <c r="H27" s="107" t="str">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="J27" s="11"/>
       <c r="K27" s="11"/>
@@ -4302,22 +4250,16 @@
       <c r="C28" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="D28" s="81">
-        <v>10</v>
-      </c>
-      <c r="E28" s="82">
-        <v>10</v>
-      </c>
-      <c r="F28" s="82">
-        <v>20</v>
-      </c>
-      <c r="G28" s="35">
+      <c r="D28" s="81"/>
+      <c r="E28" s="82"/>
+      <c r="F28" s="82"/>
+      <c r="G28" s="35" t="str">
         <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="H28" s="108">
+        <v/>
+      </c>
+      <c r="H28" s="107" t="str">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="J28" s="11"/>
       <c r="K28" s="11"/>
@@ -4348,22 +4290,16 @@
       <c r="C29" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="D29" s="81">
-        <v>10</v>
-      </c>
-      <c r="E29" s="82">
-        <v>10</v>
-      </c>
-      <c r="F29" s="82">
-        <v>20</v>
-      </c>
-      <c r="G29" s="35">
+      <c r="D29" s="81"/>
+      <c r="E29" s="82"/>
+      <c r="F29" s="82"/>
+      <c r="G29" s="35" t="str">
         <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="H29" s="108">
+        <v/>
+      </c>
+      <c r="H29" s="107" t="str">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="J29" s="11"/>
       <c r="K29" s="11"/>
@@ -4401,7 +4337,7 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H30" s="108" t="str">
+      <c r="H30" s="107" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4441,7 +4377,7 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H31" s="108" t="str">
+      <c r="H31" s="107" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4481,7 +4417,7 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H32" s="108" t="str">
+      <c r="H32" s="107" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4514,22 +4450,16 @@
       <c r="C33" s="44" t="s">
         <v>65</v>
       </c>
-      <c r="D33" s="83">
-        <v>10</v>
-      </c>
-      <c r="E33" s="84">
-        <v>10</v>
-      </c>
-      <c r="F33" s="84">
-        <v>20</v>
-      </c>
-      <c r="G33" s="22">
+      <c r="D33" s="83"/>
+      <c r="E33" s="84"/>
+      <c r="F33" s="84"/>
+      <c r="G33" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="H33" s="108">
+        <v/>
+      </c>
+      <c r="H33" s="107" t="str">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="J33" s="11"/>
       <c r="K33" s="11"/>
@@ -4560,22 +4490,16 @@
       <c r="C34" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="D34" s="83">
-        <v>5</v>
-      </c>
-      <c r="E34" s="84">
-        <v>5</v>
-      </c>
-      <c r="F34" s="84">
-        <v>5</v>
-      </c>
-      <c r="G34" s="22">
+      <c r="D34" s="83"/>
+      <c r="E34" s="84"/>
+      <c r="F34" s="84"/>
+      <c r="G34" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H34" s="108">
+        <v/>
+      </c>
+      <c r="H34" s="107" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J34" s="11"/>
       <c r="K34" s="11"/>
@@ -4613,7 +4537,7 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H35" s="108" t="str">
+      <c r="H35" s="107" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4653,7 +4577,7 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H36" s="108" t="str">
+      <c r="H36" s="107" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4693,7 +4617,7 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H37" s="108" t="str">
+      <c r="H37" s="107" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4733,7 +4657,7 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H38" s="108" t="str">
+      <c r="H38" s="107" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4773,7 +4697,7 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H39" s="108" t="str">
+      <c r="H39" s="107" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4813,7 +4737,7 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H40" s="108" t="str">
+      <c r="H40" s="107" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4853,7 +4777,7 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H41" s="108" t="str">
+      <c r="H41" s="107" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4893,7 +4817,7 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H42" s="108" t="str">
+      <c r="H42" s="107" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4933,7 +4857,7 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H43" s="108" t="str">
+      <c r="H43" s="107" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -4973,7 +4897,7 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H44" s="108" t="str">
+      <c r="H44" s="107" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5013,7 +4937,7 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H45" s="108" t="str">
+      <c r="H45" s="107" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5053,7 +4977,7 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H46" s="108" t="str">
+      <c r="H46" s="107" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5093,7 +5017,7 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H47" s="108" t="str">
+      <c r="H47" s="107" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5126,22 +5050,16 @@
       <c r="C48" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="D48" s="83">
-        <v>10</v>
-      </c>
-      <c r="E48" s="84">
-        <v>10</v>
-      </c>
-      <c r="F48" s="84">
-        <v>20</v>
-      </c>
-      <c r="G48" s="35">
+      <c r="D48" s="83"/>
+      <c r="E48" s="84"/>
+      <c r="F48" s="84"/>
+      <c r="G48" s="35" t="str">
         <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="H48" s="108">
+        <v/>
+      </c>
+      <c r="H48" s="107" t="str">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="J48" s="11"/>
       <c r="K48" s="11"/>
@@ -5170,22 +5088,16 @@
       <c r="C49" s="47" t="s">
         <v>97</v>
       </c>
-      <c r="D49" s="81">
-        <v>1</v>
-      </c>
-      <c r="E49" s="82">
-        <v>1</v>
-      </c>
-      <c r="F49" s="82">
-        <v>1</v>
-      </c>
-      <c r="G49" s="35">
+      <c r="D49" s="81"/>
+      <c r="E49" s="82"/>
+      <c r="F49" s="82"/>
+      <c r="G49" s="35" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H49" s="108">
+        <v/>
+      </c>
+      <c r="H49" s="107" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J49" s="11"/>
       <c r="K49" s="11"/>
@@ -5223,7 +5135,7 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H50" s="108" t="str">
+      <c r="H50" s="107" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5263,7 +5175,7 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H51" s="108" t="str">
+      <c r="H51" s="107" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5303,7 +5215,7 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H52" s="108" t="str">
+      <c r="H52" s="107" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5343,7 +5255,7 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H53" s="108" t="str">
+      <c r="H53" s="107" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5370,31 +5282,31 @@
       <c r="A54" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="B54" s="102">
+      <c r="B54" s="101">
         <v>26</v>
       </c>
-      <c r="C54" s="103" t="s">
+      <c r="C54" s="102" t="s">
         <v>107</v>
       </c>
-      <c r="D54" s="104">
-        <f t="shared" ref="D54:F54" si="9">SUM(D55:D61)</f>
-        <v>10</v>
-      </c>
-      <c r="E54" s="104">
-        <f t="shared" si="9"/>
-        <v>10</v>
-      </c>
-      <c r="F54" s="104">
-        <f t="shared" si="9"/>
-        <v>20</v>
+      <c r="D54" s="103">
+        <f t="shared" ref="D54:F54" si="8">SUM(D55:D61)</f>
+        <v>0</v>
+      </c>
+      <c r="E54" s="103">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F54" s="103">
+        <f t="shared" si="8"/>
+        <v>0</v>
       </c>
       <c r="G54" s="49">
         <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="H54" s="108">
+        <v>0</v>
+      </c>
+      <c r="H54" s="107" t="str">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="J54" s="11"/>
       <c r="K54" s="11"/>
@@ -5425,22 +5337,16 @@
       <c r="C55" s="50" t="s">
         <v>109</v>
       </c>
-      <c r="D55" s="81">
-        <v>5</v>
-      </c>
-      <c r="E55" s="82">
-        <v>5</v>
-      </c>
-      <c r="F55" s="82">
-        <v>10</v>
-      </c>
-      <c r="G55" s="35">
+      <c r="D55" s="81"/>
+      <c r="E55" s="82"/>
+      <c r="F55" s="82"/>
+      <c r="G55" s="35" t="str">
         <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="H55" s="108">
+        <v/>
+      </c>
+      <c r="H55" s="107" t="str">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="J55" s="11"/>
       <c r="K55" s="11"/>
@@ -5476,7 +5382,7 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H56" s="108" t="str">
+      <c r="H56" s="107" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5507,22 +5413,16 @@
       <c r="C57" s="47" t="s">
         <v>113</v>
       </c>
-      <c r="D57" s="81">
-        <v>5</v>
-      </c>
-      <c r="E57" s="82">
-        <v>5</v>
-      </c>
-      <c r="F57" s="82">
-        <v>10</v>
-      </c>
-      <c r="G57" s="35">
+      <c r="D57" s="81"/>
+      <c r="E57" s="82"/>
+      <c r="F57" s="82"/>
+      <c r="G57" s="35" t="str">
         <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="H57" s="108">
+        <v/>
+      </c>
+      <c r="H57" s="107" t="str">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="J57" s="11"/>
       <c r="K57" s="11"/>
@@ -5558,7 +5458,7 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H58" s="108" t="str">
+      <c r="H58" s="107" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5596,7 +5496,7 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H59" s="108" t="str">
+      <c r="H59" s="107" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5634,7 +5534,7 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H60" s="108" t="str">
+      <c r="H60" s="107" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5672,7 +5572,7 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H61" s="108" t="str">
+      <c r="H61" s="107" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5712,7 +5612,7 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H62" s="108" t="str">
+      <c r="H62" s="107" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5739,31 +5639,31 @@
       <c r="A63" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="B63" s="105" t="s">
+      <c r="B63" s="104" t="s">
         <v>41</v>
       </c>
-      <c r="C63" s="106" t="s">
+      <c r="C63" s="105" t="s">
         <v>125</v>
       </c>
-      <c r="D63" s="107">
-        <f t="shared" ref="D63:F63" si="10">SUM(D64:D89)-D70-D85</f>
-        <v>30</v>
-      </c>
-      <c r="E63" s="107">
-        <f t="shared" si="10"/>
-        <v>30</v>
-      </c>
-      <c r="F63" s="107">
-        <f t="shared" si="10"/>
-        <v>60</v>
+      <c r="D63" s="106">
+        <f t="shared" ref="D63:F63" si="9">SUM(D64:D89)-D70-D85</f>
+        <v>0</v>
+      </c>
+      <c r="E63" s="106">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="F63" s="106">
+        <f t="shared" si="9"/>
+        <v>0</v>
       </c>
       <c r="G63" s="54">
         <f t="shared" si="2"/>
-        <v>30</v>
-      </c>
-      <c r="H63" s="109">
+        <v>0</v>
+      </c>
+      <c r="H63" s="108" t="str">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="J63" s="11"/>
       <c r="K63" s="11"/>
@@ -5795,22 +5695,16 @@
         <f>C27</f>
         <v>Cho vay hộ nghèo theo Nghị định số 78/2002/NĐ-CP</v>
       </c>
-      <c r="D64" s="81">
-        <v>10</v>
-      </c>
-      <c r="E64" s="82">
-        <v>10</v>
-      </c>
-      <c r="F64" s="82">
-        <v>20</v>
-      </c>
-      <c r="G64" s="35">
+      <c r="D64" s="81"/>
+      <c r="E64" s="82"/>
+      <c r="F64" s="82"/>
+      <c r="G64" s="35" t="str">
         <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="H64" s="108">
+        <v/>
+      </c>
+      <c r="H64" s="107" t="str">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="J64" s="11"/>
       <c r="K64" s="11"/>
@@ -5848,7 +5742,7 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H65" s="108" t="str">
+      <c r="H65" s="107" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5889,7 +5783,7 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H66" s="108" t="str">
+      <c r="H66" s="107" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5929,7 +5823,7 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H67" s="108" t="str">
+      <c r="H67" s="107" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -5969,7 +5863,7 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H68" s="108" t="str">
+      <c r="H68" s="107" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -6003,22 +5897,16 @@
         <f>C33</f>
         <v>Cho vay người lao động đi làm việc ở nước ngoài theo Quyết định số 365/QĐ-NHNN, Quyết định số 1465/QĐ-TTg, Quyết định số 63/2015/QĐ-TTg và Nghị định số 61/2015/NĐ-CP</v>
       </c>
-      <c r="D69" s="83">
-        <v>10</v>
-      </c>
-      <c r="E69" s="84">
-        <v>10</v>
-      </c>
-      <c r="F69" s="84">
-        <v>20</v>
-      </c>
-      <c r="G69" s="22">
+      <c r="D69" s="83"/>
+      <c r="E69" s="84"/>
+      <c r="F69" s="84"/>
+      <c r="G69" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="H69" s="108">
+        <v/>
+      </c>
+      <c r="H69" s="107" t="str">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="J69" s="11"/>
       <c r="K69" s="11"/>
@@ -6049,22 +5937,16 @@
       <c r="C70" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="D70" s="83">
-        <v>5</v>
-      </c>
-      <c r="E70" s="84">
-        <v>5</v>
-      </c>
-      <c r="F70" s="84">
-        <v>5</v>
-      </c>
-      <c r="G70" s="22">
+      <c r="D70" s="83"/>
+      <c r="E70" s="84"/>
+      <c r="F70" s="84"/>
+      <c r="G70" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H70" s="108">
+        <v/>
+      </c>
+      <c r="H70" s="107" t="str">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J70" s="11"/>
       <c r="K70" s="11"/>
@@ -6102,7 +5984,7 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H71" s="108" t="str">
+      <c r="H71" s="107" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -6143,7 +6025,7 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H72" s="108" t="str">
+      <c r="H72" s="107" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -6183,7 +6065,7 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H73" s="108" t="str">
+      <c r="H73" s="107" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -6224,7 +6106,7 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H74" s="108" t="str">
+      <c r="H74" s="107" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -6264,7 +6146,7 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H75" s="108" t="str">
+      <c r="H75" s="107" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -6304,7 +6186,7 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H76" s="108" t="str">
+      <c r="H76" s="107" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -6344,7 +6226,7 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="H77" s="108" t="str">
+      <c r="H77" s="107" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -6381,11 +6263,11 @@
       <c r="E78" s="84"/>
       <c r="F78" s="84"/>
       <c r="G78" s="22" t="str">
-        <f t="shared" ref="G78:G92" si="11">IF(AND(D78="",F78=""),"",F78*1-D78*1)</f>
+        <f t="shared" ref="G78:G92" si="10">IF(AND(D78="",F78=""),"",F78*1-D78*1)</f>
         <v/>
       </c>
-      <c r="H78" s="108" t="str">
-        <f t="shared" ref="H78:H92" si="12">IFERROR(G78/E78,"")</f>
+      <c r="H78" s="107" t="str">
+        <f t="shared" ref="H78:H92" si="11">IFERROR(G78/E78,"")</f>
         <v/>
       </c>
       <c r="J78" s="11"/>
@@ -6415,18 +6297,18 @@
         <v>15</v>
       </c>
       <c r="C79" s="42" t="str">
-        <f t="shared" ref="C79:C84" si="13">C43</f>
+        <f t="shared" ref="C79:C84" si="12">C43</f>
         <v>Cho vay hỗ trợ hộ nghèo về nhà ở (QĐ 167/2008/QĐ-TTg)</v>
       </c>
       <c r="D79" s="83"/>
       <c r="E79" s="84"/>
       <c r="F79" s="84"/>
       <c r="G79" s="22" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H79" s="107" t="str">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="H79" s="108" t="str">
-        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J79" s="11"/>
@@ -6456,18 +6338,18 @@
         <v>16</v>
       </c>
       <c r="C80" s="42" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">Cho vay hỗ trợ hộ nghèo về nhà ở theo QĐ 33/2015/QĐ-TTg </v>
       </c>
       <c r="D80" s="83"/>
       <c r="E80" s="84"/>
       <c r="F80" s="84"/>
       <c r="G80" s="22" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H80" s="107" t="str">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="H80" s="108" t="str">
-        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J80" s="11"/>
@@ -6497,18 +6379,18 @@
         <v>17</v>
       </c>
       <c r="C81" s="42" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>Cho vay thương nhân tại VKK (QĐ 92/2009/QĐ-TTg)</v>
       </c>
       <c r="D81" s="83"/>
       <c r="E81" s="84"/>
       <c r="F81" s="84"/>
       <c r="G81" s="22" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H81" s="107" t="str">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="H81" s="108" t="str">
-        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J81" s="11"/>
@@ -6538,18 +6420,18 @@
         <v>18</v>
       </c>
       <c r="C82" s="42" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">Cho vay hỗ trợ hộ nghèo xây dựng nhà ở phòng, tránh bão, lụt khu vực miền Trung theo QĐ 716, 48/2014/QĐ-TTg </v>
       </c>
       <c r="D82" s="83"/>
       <c r="E82" s="84"/>
       <c r="F82" s="84"/>
       <c r="G82" s="22" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H82" s="107" t="str">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="H82" s="108" t="str">
-        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J82" s="11"/>
@@ -6579,18 +6461,18 @@
         <v>19</v>
       </c>
       <c r="C83" s="41" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v xml:space="preserve">Cho vay đối với hộ gia đình và người nhiễm HIV, người sau cai nghiện ma túy, người điều trị nghiện các chất dạng thuốc phiện bằng thuốc thay thế, người bán dâm hoàn lương theo Quyết định số 29/2014/QĐ-TTg </v>
       </c>
       <c r="D83" s="81"/>
       <c r="E83" s="82"/>
       <c r="F83" s="82"/>
       <c r="G83" s="22" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H83" s="107" t="str">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="H83" s="108" t="str">
-        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J83" s="11"/>
@@ -6620,25 +6502,19 @@
         <v>20</v>
       </c>
       <c r="C84" s="46" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>Cho vay nhà ở xã hội theo NĐ 100/2015/NĐ-CP</v>
       </c>
-      <c r="D84" s="83">
-        <v>10</v>
-      </c>
-      <c r="E84" s="84">
-        <v>10</v>
-      </c>
-      <c r="F84" s="84">
-        <v>20</v>
-      </c>
-      <c r="G84" s="35">
+      <c r="D84" s="83"/>
+      <c r="E84" s="84"/>
+      <c r="F84" s="84"/>
+      <c r="G84" s="35" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H84" s="107" t="str">
         <f t="shared" si="11"/>
-        <v>10</v>
-      </c>
-      <c r="H84" s="108">
-        <f t="shared" si="12"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="J84" s="11"/>
       <c r="K84" s="11"/>
@@ -6667,22 +6543,16 @@
       <c r="C85" s="58" t="s">
         <v>97</v>
       </c>
-      <c r="D85" s="83">
-        <v>5</v>
-      </c>
-      <c r="E85" s="84">
-        <v>5</v>
-      </c>
-      <c r="F85" s="84">
-        <v>5</v>
-      </c>
-      <c r="G85" s="35">
+      <c r="D85" s="83"/>
+      <c r="E85" s="84"/>
+      <c r="F85" s="84"/>
+      <c r="G85" s="35" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H85" s="107" t="str">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H85" s="108">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J85" s="11"/>
       <c r="K85" s="11"/>
@@ -6717,11 +6587,11 @@
       <c r="E86" s="82"/>
       <c r="F86" s="82"/>
       <c r="G86" s="35" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H86" s="107" t="str">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="H86" s="108" t="str">
-        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J86" s="11"/>
@@ -6751,18 +6621,18 @@
         <v>22</v>
       </c>
       <c r="C87" s="41" t="str">
-        <f t="shared" ref="C87:C88" si="14">C52</f>
+        <f t="shared" ref="C87:C88" si="13">C52</f>
         <v xml:space="preserve">Cho vay trồng rừng sản xuất, phát triển chăn nuôi theo NĐ 75/2015/NĐ-CP </v>
       </c>
       <c r="D87" s="81"/>
       <c r="E87" s="82"/>
       <c r="F87" s="82"/>
       <c r="G87" s="35" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H87" s="107" t="str">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="H87" s="108" t="str">
-        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J87" s="11"/>
@@ -6792,18 +6662,18 @@
         <v>23</v>
       </c>
       <c r="C88" s="41" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>Cho vay hỗ trợ phát triển kinh tế - xã hội vùng dân tộc thiểu số và miền núi giai đoạn 2017 - 2020 theo Quyết định số 2085/QĐ-TTg</v>
       </c>
       <c r="D88" s="81"/>
       <c r="E88" s="82"/>
       <c r="F88" s="82"/>
       <c r="G88" s="35" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H88" s="107" t="str">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="H88" s="108" t="str">
-        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J88" s="11"/>
@@ -6839,11 +6709,11 @@
       <c r="E89" s="82"/>
       <c r="F89" s="82"/>
       <c r="G89" s="35" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H89" s="107" t="str">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="H89" s="108" t="str">
-        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J89" s="11"/>
@@ -6876,24 +6746,24 @@
         <v>160</v>
       </c>
       <c r="D90" s="54">
-        <f t="shared" ref="D90:F90" si="15">D92+D91</f>
-        <v>10</v>
+        <f t="shared" ref="D90:F90" si="14">D92+D91</f>
+        <v>0</v>
       </c>
       <c r="E90" s="54">
-        <f t="shared" si="15"/>
-        <v>10</v>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="F90" s="54">
-        <f t="shared" si="15"/>
-        <v>10</v>
+        <f t="shared" si="14"/>
+        <v>0</v>
       </c>
       <c r="G90" s="54">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="H90" s="108" t="str">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H90" s="109">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J90" s="11"/>
       <c r="K90" s="11"/>
@@ -6924,22 +6794,16 @@
       <c r="C91" s="62" t="s">
         <v>162</v>
       </c>
-      <c r="D91" s="81">
-        <v>1</v>
-      </c>
-      <c r="E91" s="82">
-        <v>1</v>
-      </c>
-      <c r="F91" s="82">
-        <v>1</v>
-      </c>
-      <c r="G91" s="35">
+      <c r="D91" s="81"/>
+      <c r="E91" s="82"/>
+      <c r="F91" s="82"/>
+      <c r="G91" s="35" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H91" s="107" t="str">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H91" s="108">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J91" s="11"/>
       <c r="K91" s="11"/>
@@ -6968,22 +6832,16 @@
       <c r="C92" s="65" t="s">
         <v>164</v>
       </c>
-      <c r="D92" s="85">
-        <v>9</v>
-      </c>
-      <c r="E92" s="86">
-        <v>9</v>
-      </c>
-      <c r="F92" s="86">
-        <v>9</v>
-      </c>
-      <c r="G92" s="66">
+      <c r="D92" s="85"/>
+      <c r="E92" s="86"/>
+      <c r="F92" s="86"/>
+      <c r="G92" s="66" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="H92" s="110" t="str">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H92" s="111">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="J92" s="11"/>
       <c r="K92" s="11"/>
@@ -7011,14 +6869,14 @@
       <c r="B93" s="67" t="s">
         <v>166</v>
       </c>
-      <c r="C93" s="140" t="s">
+      <c r="C93" s="124" t="s">
         <v>167</v>
       </c>
-      <c r="D93" s="141"/>
-      <c r="E93" s="141"/>
-      <c r="F93" s="141"/>
-      <c r="G93" s="141"/>
-      <c r="H93" s="142"/>
+      <c r="D93" s="125"/>
+      <c r="E93" s="125"/>
+      <c r="F93" s="125"/>
+      <c r="G93" s="125"/>
+      <c r="H93" s="126"/>
       <c r="J93" s="11"/>
       <c r="K93" s="11"/>
       <c r="L93" s="38"/>
@@ -7050,7 +6908,7 @@
       </c>
       <c r="D94" s="43"/>
       <c r="E94" s="43"/>
-      <c r="F94" s="146"/>
+      <c r="F94" s="115"/>
       <c r="G94" s="43"/>
       <c r="H94" s="43"/>
       <c r="J94" s="11"/>
@@ -7084,7 +6942,7 @@
       </c>
       <c r="D95" s="43"/>
       <c r="E95" s="43"/>
-      <c r="F95" s="147"/>
+      <c r="F95" s="116"/>
       <c r="G95" s="43"/>
       <c r="H95" s="43"/>
       <c r="J95" s="11"/>
@@ -7116,7 +6974,7 @@
       </c>
       <c r="D96" s="43"/>
       <c r="E96" s="43"/>
-      <c r="F96" s="148"/>
+      <c r="F96" s="117"/>
       <c r="G96" s="43"/>
       <c r="H96" s="43"/>
       <c r="J96" s="11"/>
@@ -7150,7 +7008,7 @@
       </c>
       <c r="D97" s="43"/>
       <c r="E97" s="43"/>
-      <c r="F97" s="149"/>
+      <c r="F97" s="118"/>
       <c r="G97" s="43"/>
       <c r="H97" s="43"/>
       <c r="J97" s="11"/>
@@ -7177,12 +7035,12 @@
         <v>178</v>
       </c>
       <c r="B98" s="45"/>
-      <c r="C98" s="143" t="s">
+      <c r="C98" s="112" t="s">
         <v>177</v>
       </c>
       <c r="D98" s="43"/>
       <c r="E98" s="43"/>
-      <c r="F98" s="149"/>
+      <c r="F98" s="118"/>
       <c r="G98" s="43"/>
       <c r="H98" s="43"/>
       <c r="J98" s="11"/>
@@ -7216,7 +7074,7 @@
       </c>
       <c r="D99" s="43"/>
       <c r="E99" s="43"/>
-      <c r="F99" s="149"/>
+      <c r="F99" s="118"/>
       <c r="G99" s="43"/>
       <c r="H99" s="43"/>
       <c r="J99" s="11"/>
@@ -7245,12 +7103,12 @@
       <c r="B100" s="39">
         <v>5</v>
       </c>
-      <c r="C100" s="144" t="s">
+      <c r="C100" s="113" t="s">
         <v>181</v>
       </c>
       <c r="D100" s="43"/>
       <c r="E100" s="43"/>
-      <c r="F100" s="149"/>
+      <c r="F100" s="118"/>
       <c r="G100" s="43"/>
       <c r="H100" s="43"/>
       <c r="J100" s="11"/>
@@ -7284,7 +7142,7 @@
       </c>
       <c r="D101" s="43"/>
       <c r="E101" s="43"/>
-      <c r="F101" s="149"/>
+      <c r="F101" s="118"/>
       <c r="G101" s="43"/>
       <c r="H101" s="43"/>
       <c r="J101" s="11"/>
@@ -7311,12 +7169,12 @@
         <v>186</v>
       </c>
       <c r="B102" s="45"/>
-      <c r="C102" s="143" t="s">
+      <c r="C102" s="112" t="s">
         <v>185</v>
       </c>
       <c r="D102" s="43"/>
       <c r="E102" s="43"/>
-      <c r="F102" s="149"/>
+      <c r="F102" s="118"/>
       <c r="G102" s="43"/>
       <c r="H102" s="43"/>
       <c r="J102" s="11"/>
@@ -7343,12 +7201,12 @@
         <v>188</v>
       </c>
       <c r="B103" s="71"/>
-      <c r="C103" s="145" t="s">
+      <c r="C103" s="114" t="s">
         <v>187</v>
       </c>
       <c r="D103" s="43"/>
       <c r="E103" s="43"/>
-      <c r="F103" s="150"/>
+      <c r="F103" s="119"/>
       <c r="G103" s="43"/>
       <c r="H103" s="43"/>
       <c r="J103" s="11"/>
@@ -7374,17 +7232,17 @@
       <c r="A104" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="B104" s="137" t="s">
+      <c r="B104" s="135" t="s">
         <v>195</v>
       </c>
-      <c r="C104" s="138"/>
-      <c r="D104" s="138"/>
-      <c r="E104" s="138"/>
-      <c r="F104" s="139"/>
-      <c r="G104" s="135" t="s">
+      <c r="C104" s="136"/>
+      <c r="D104" s="136"/>
+      <c r="E104" s="136"/>
+      <c r="F104" s="137"/>
+      <c r="G104" s="133" t="s">
         <v>194</v>
       </c>
-      <c r="H104" s="136"/>
+      <c r="H104" s="134"/>
       <c r="J104" s="11"/>
       <c r="K104" s="11"/>
       <c r="L104" s="3"/>
@@ -7435,12 +7293,12 @@
       <c r="B106" s="72"/>
       <c r="C106" s="72"/>
       <c r="D106" s="72"/>
-      <c r="E106" s="132" t="s">
+      <c r="E106" s="130" t="s">
         <v>189</v>
       </c>
-      <c r="F106" s="133"/>
-      <c r="G106" s="133"/>
-      <c r="H106" s="134"/>
+      <c r="F106" s="131"/>
+      <c r="G106" s="131"/>
+      <c r="H106" s="132"/>
       <c r="I106" s="3"/>
       <c r="J106" s="3"/>
       <c r="K106" s="3"/>
@@ -32360,14 +32218,8 @@
       <c r="AA995" s="3"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="VLoLPhKlQvmAvCh6O2N18hyTyDgBrwYoHmcuR4WxTylRvbN/VyCZGdUjDwymTuDfPt5es7TFUunHBoBNyU7WGw==" saltValue="EHXnnL/PeRnIYaWI5apQFw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="2O9r7hVlFQT0p8D5FD8kvmpTuyDyIepwcAg10qdUNtnPToY5T4vGZgT/VFW2Ngi8JMPxCIIH/rPXBa6rNmv23Q==" saltValue="2xblJYER5Pi8Y5oa/s72Kg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="20">
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="C93:H93"/>
-    <mergeCell ref="H9:H11"/>
-    <mergeCell ref="E106:H106"/>
-    <mergeCell ref="G104:H104"/>
-    <mergeCell ref="B104:F104"/>
     <mergeCell ref="I9:I11"/>
     <mergeCell ref="D1:H1"/>
     <mergeCell ref="D2:H2"/>
@@ -32382,6 +32234,12 @@
     <mergeCell ref="G9:G11"/>
     <mergeCell ref="E10:E11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="C93:H93"/>
+    <mergeCell ref="H9:H11"/>
+    <mergeCell ref="E106:H106"/>
+    <mergeCell ref="G104:H104"/>
+    <mergeCell ref="B104:F104"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.39370078740157483" bottom="0.23622047244094491" header="0" footer="0"/>

--- a/web/EXCEL_TEMPLATE/KHNV/NV_QT.xlsx
+++ b/web/EXCEL_TEMPLATE/KHNV/NV_QT.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DucAnh\Desktop\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11040"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040"/>
   </bookViews>
   <sheets>
     <sheet name="Biểu số 11" sheetId="1" r:id="rId1"/>
@@ -87,7 +92,7 @@
     <definedName name="ZZZ" localSheetId="0">#REF!</definedName>
     <definedName name="ZZZ">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="" roundtripDataSignature="AMtx7miiPYpftlC0kKdav03lF3/fCfpDfg=="/>
@@ -97,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="188">
   <si>
     <t>Biểu số: 11/NHCS-KH</t>
   </si>
@@ -117,9 +122,6 @@
     <t>BÁO CÁO</t>
   </si>
   <si>
-    <t>KẾT QUẢ THỰC HIỆN  KẾ HOẠCH TÍN DỤNG NĂM 2022</t>
-  </si>
-  <si>
     <t>Đơn vị: Triệu đồng, hộ, người</t>
   </si>
   <si>
@@ -129,21 +131,12 @@
     <t>CHỈ TIÊU</t>
   </si>
   <si>
-    <t>Số thực hiện đến 31/12/2021</t>
-  </si>
-  <si>
     <t>Năm báo cáo</t>
-  </si>
-  <si>
-    <t>Tăng/giảm so với năm 2021</t>
   </si>
   <si>
     <t>Tỷ lệ 
 hoàn thành 
 kế hoạch giao tăng trưởng (%)</t>
-  </si>
-  <si>
-    <t>Kế hoạch giao tăng trưởng năm 2022</t>
   </si>
   <si>
     <t>Số thực hiện đến 31/12/2022</t>
@@ -386,9 +379,6 @@
     <t>Cho vay nhà ở xã hội theo NĐ 100/2015/NĐ-CP (không bao gồm cho vay theo Nghị quyết số 11/NQ-CP)</t>
   </si>
   <si>
-    <t>sửa lại tên</t>
-  </si>
-  <si>
     <t>KH0037</t>
   </si>
   <si>
@@ -396,9 +386,6 @@
   </si>
   <si>
     <t>KH0038</t>
-  </si>
-  <si>
-    <t>Cho vay trả lương ngừng việc theo QĐ 15/2020/QĐ-TTg</t>
   </si>
   <si>
     <t>KH0039</t>
@@ -594,9 +581,6 @@
     <t>KH0073</t>
   </si>
   <si>
-    <t>Sửa tên</t>
-  </si>
-  <si>
     <t>KH0074</t>
   </si>
   <si>
@@ -693,11 +677,29 @@
   <si>
     <t>………., ngày       tháng     năm 2023</t>
   </si>
+  <si>
+    <t>KH0086</t>
+  </si>
+  <si>
+    <t>Cho vay đối với người chấp hành xong án phạt tù theo QĐ số 22/2023/QĐ-TTg</t>
+  </si>
+  <si>
+    <t>KẾT QUẢ THỰC HIỆN  KẾ HOẠCH TÍN DỤNG NĂM 2023</t>
+  </si>
+  <si>
+    <t>Kế hoạch giao tăng trưởng năm 2023</t>
+  </si>
+  <si>
+    <t>Số thực hiện đến 31/12/2023</t>
+  </si>
+  <si>
+    <t>Tăng/giảm so với năm 2022</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -820,7 +822,7 @@
       <charset val="163"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -831,12 +833,6 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor theme="0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
     <fill>
@@ -1037,7 +1033,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1067,7 +1063,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1076,47 +1072,47 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="14" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="14" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="14" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="14" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="13" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="13" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1137,36 +1133,30 @@
     <xf numFmtId="3" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="14" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="14" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1177,10 +1167,10 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="13" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1192,23 +1182,13 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1217,29 +1197,10 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1248,28 +1209,16 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1285,7 +1234,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1297,6 +1246,86 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1311,43 +1340,15 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1372,7 +1373,7 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1162050</xdr:colOff>
-      <xdr:row>99</xdr:row>
+      <xdr:row>100</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="238125" cy="38100"/>
@@ -1381,7 +1382,7 @@
         <xdr:cNvPr id="3" name="Shape 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1427,7 +1428,7 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>2886075</xdr:colOff>
-      <xdr:row>99</xdr:row>
+      <xdr:row>100</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="38100" cy="38100"/>
@@ -1436,7 +1437,7 @@
         <xdr:cNvPr id="4" name="Shape 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1482,7 +1483,7 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1162050</xdr:colOff>
-      <xdr:row>99</xdr:row>
+      <xdr:row>100</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="238125" cy="38100"/>
@@ -1491,7 +1492,7 @@
         <xdr:cNvPr id="2" name="Shape 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1537,7 +1538,7 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>2886075</xdr:colOff>
-      <xdr:row>99</xdr:row>
+      <xdr:row>100</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="38100" cy="38100"/>
@@ -1546,7 +1547,7 @@
         <xdr:cNvPr id="5" name="Shape 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1592,7 +1593,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1038225</xdr:colOff>
-      <xdr:row>98</xdr:row>
+      <xdr:row>99</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="38100" cy="38100"/>
@@ -1601,7 +1602,7 @@
         <xdr:cNvPr id="6" name="Shape 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1647,7 +1648,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1790700</xdr:colOff>
-      <xdr:row>98</xdr:row>
+      <xdr:row>99</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="38100" cy="38100"/>
@@ -1656,7 +1657,7 @@
         <xdr:cNvPr id="7" name="Shape 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1702,7 +1703,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1038225</xdr:colOff>
-      <xdr:row>98</xdr:row>
+      <xdr:row>99</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="38100" cy="38100"/>
@@ -1711,7 +1712,7 @@
         <xdr:cNvPr id="8" name="Shape 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1757,7 +1758,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1790700</xdr:colOff>
-      <xdr:row>98</xdr:row>
+      <xdr:row>99</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="38100" cy="38100"/>
@@ -1766,7 +1767,7 @@
         <xdr:cNvPr id="9" name="Shape 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1812,7 +1813,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>96</xdr:row>
+      <xdr:row>97</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="85725" cy="238125"/>
@@ -1821,7 +1822,7 @@
         <xdr:cNvPr id="10" name="Shape 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1867,7 +1868,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>96</xdr:row>
+      <xdr:row>97</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="85725" cy="238125"/>
@@ -1876,7 +1877,7 @@
         <xdr:cNvPr id="11" name="Shape 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1922,7 +1923,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>96</xdr:row>
+      <xdr:row>97</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="85725" cy="238125"/>
@@ -1931,7 +1932,7 @@
         <xdr:cNvPr id="12" name="Shape 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1977,7 +1978,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>96</xdr:row>
+      <xdr:row>97</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="85725" cy="238125"/>
@@ -1986,7 +1987,7 @@
         <xdr:cNvPr id="13" name="Shape 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2041,7 +2042,7 @@
         <xdr:cNvPr id="14" name="Shape 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2096,7 +2097,7 @@
         <xdr:cNvPr id="15" name="Shape 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000F000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2142,7 +2143,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>96</xdr:row>
+      <xdr:row>97</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="85725" cy="238125"/>
@@ -2151,7 +2152,7 @@
         <xdr:cNvPr id="16" name="Shape 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000010000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000010000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2197,7 +2198,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>96</xdr:row>
+      <xdr:row>97</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="85725" cy="238125"/>
@@ -2206,7 +2207,7 @@
         <xdr:cNvPr id="17" name="Shape 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000011000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000011000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2252,7 +2253,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>96</xdr:row>
+      <xdr:row>97</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="85725" cy="238125"/>
@@ -2261,7 +2262,7 @@
         <xdr:cNvPr id="18" name="Shape 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000012000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000012000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2307,7 +2308,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>96</xdr:row>
+      <xdr:row>97</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="85725" cy="238125"/>
@@ -2316,7 +2317,7 @@
         <xdr:cNvPr id="19" name="Shape 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000013000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000013000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2362,7 +2363,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>96</xdr:row>
+      <xdr:row>97</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="85725" cy="238125"/>
@@ -2371,7 +2372,7 @@
         <xdr:cNvPr id="20" name="Shape 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000014000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000014000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2417,7 +2418,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>96</xdr:row>
+      <xdr:row>97</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="85725" cy="238125"/>
@@ -2426,7 +2427,7 @@
         <xdr:cNvPr id="21" name="Shape 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000015000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000015000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2472,7 +2473,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>96</xdr:row>
+      <xdr:row>97</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="85725" cy="238125"/>
@@ -2481,7 +2482,7 @@
         <xdr:cNvPr id="22" name="Shape 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000016000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000016000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2527,7 +2528,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>96</xdr:row>
+      <xdr:row>97</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="85725" cy="238125"/>
@@ -2536,7 +2537,7 @@
         <xdr:cNvPr id="23" name="Shape 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000017000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000017000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2582,7 +2583,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>96</xdr:row>
+      <xdr:row>97</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="85725" cy="238125"/>
@@ -2591,7 +2592,7 @@
         <xdr:cNvPr id="24" name="Shape 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000018000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000018000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2637,7 +2638,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>96</xdr:row>
+      <xdr:row>97</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="85725" cy="238125"/>
@@ -2646,7 +2647,7 @@
         <xdr:cNvPr id="25" name="Shape 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000019000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000019000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2889,12 +2890,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AA993"/>
+  <dimension ref="A1:AA994"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="3" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="65" style="3" customWidth="1"/>
+    <col min="3" max="3" width="79.5703125" style="3" customWidth="1"/>
     <col min="4" max="4" width="13.28515625" style="3" customWidth="1"/>
     <col min="5" max="5" width="11.140625" style="3" customWidth="1"/>
     <col min="6" max="6" width="12.85546875" style="3" customWidth="1"/>
@@ -2908,13 +2909,13 @@
     <row r="1" spans="1:27" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
-      <c r="D1" s="96" t="s">
+      <c r="D1" s="115" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
-      <c r="H1" s="95"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="114"/>
       <c r="I1" s="4"/>
       <c r="J1" s="4"/>
       <c r="K1" s="4"/>
@@ -2939,13 +2940,13 @@
         <v>1</v>
       </c>
       <c r="C2" s="2"/>
-      <c r="D2" s="97" t="s">
+      <c r="D2" s="116" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
-      <c r="H2" s="95"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="114"/>
       <c r="I2" s="5"/>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
@@ -2973,7 +2974,7 @@
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
       <c r="F3" s="8" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="G3" s="8"/>
       <c r="H3" s="9"/>
@@ -3026,15 +3027,15 @@
       <c r="Z4" s="4"/>
     </row>
     <row r="5" spans="1:27" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="98" t="s">
+      <c r="B5" s="117" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="95"/>
-      <c r="D5" s="95"/>
-      <c r="E5" s="95"/>
-      <c r="F5" s="95"/>
-      <c r="G5" s="95"/>
-      <c r="H5" s="95"/>
+      <c r="C5" s="114"/>
+      <c r="D5" s="114"/>
+      <c r="E5" s="114"/>
+      <c r="F5" s="114"/>
+      <c r="G5" s="114"/>
+      <c r="H5" s="114"/>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
@@ -3055,15 +3056,15 @@
       <c r="Z5" s="4"/>
     </row>
     <row r="6" spans="1:27" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="99" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="95"/>
-      <c r="D6" s="95"/>
-      <c r="E6" s="95"/>
-      <c r="F6" s="95"/>
-      <c r="G6" s="95"/>
-      <c r="H6" s="95"/>
+      <c r="B6" s="118" t="s">
+        <v>184</v>
+      </c>
+      <c r="C6" s="119"/>
+      <c r="D6" s="119"/>
+      <c r="E6" s="119"/>
+      <c r="F6" s="119"/>
+      <c r="G6" s="119"/>
+      <c r="H6" s="119"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
@@ -3084,13 +3085,13 @@
       <c r="Z6" s="4"/>
     </row>
     <row r="7" spans="1:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="100"/>
-      <c r="C7" s="95"/>
-      <c r="D7" s="95"/>
-      <c r="E7" s="95"/>
-      <c r="F7" s="95"/>
-      <c r="G7" s="95"/>
-      <c r="H7" s="95"/>
+      <c r="B7" s="120"/>
+      <c r="C7" s="114"/>
+      <c r="D7" s="114"/>
+      <c r="E7" s="114"/>
+      <c r="F7" s="114"/>
+      <c r="G7" s="114"/>
+      <c r="H7" s="114"/>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
@@ -3111,15 +3112,15 @@
       <c r="Z7" s="4"/>
     </row>
     <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="109" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="110"/>
-      <c r="D8" s="110"/>
-      <c r="E8" s="110"/>
-      <c r="F8" s="110"/>
-      <c r="G8" s="110"/>
-      <c r="H8" s="110"/>
+      <c r="B8" s="102" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="103"/>
+      <c r="D8" s="103"/>
+      <c r="E8" s="103"/>
+      <c r="F8" s="103"/>
+      <c r="G8" s="103"/>
+      <c r="H8" s="103"/>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
@@ -3140,27 +3141,27 @@
       <c r="Z8" s="4"/>
     </row>
     <row r="9" spans="1:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="111"/>
-      <c r="B9" s="111" t="s">
+      <c r="A9" s="104"/>
+      <c r="B9" s="104" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="104" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="111" t="s">
+      <c r="D9" s="107" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="110" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="114" t="s">
+      <c r="F9" s="111"/>
+      <c r="G9" s="107" t="s">
+        <v>187</v>
+      </c>
+      <c r="H9" s="112" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="115" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="103"/>
-      <c r="G9" s="114" t="s">
-        <v>12</v>
-      </c>
-      <c r="H9" s="116" t="s">
-        <v>13</v>
-      </c>
-      <c r="I9" s="94"/>
+      <c r="I9" s="113"/>
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -3181,19 +3182,19 @@
       <c r="AA9" s="4"/>
     </row>
     <row r="10" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="112"/>
-      <c r="B10" s="112"/>
-      <c r="C10" s="112"/>
-      <c r="D10" s="112"/>
-      <c r="E10" s="114" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="114" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" s="112"/>
-      <c r="H10" s="112"/>
-      <c r="I10" s="95"/>
+      <c r="A10" s="105"/>
+      <c r="B10" s="105"/>
+      <c r="C10" s="105"/>
+      <c r="D10" s="108"/>
+      <c r="E10" s="107" t="s">
+        <v>185</v>
+      </c>
+      <c r="F10" s="107" t="s">
+        <v>186</v>
+      </c>
+      <c r="G10" s="108"/>
+      <c r="H10" s="105"/>
+      <c r="I10" s="114"/>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -3214,18 +3215,18 @@
       <c r="AA10" s="4"/>
     </row>
     <row r="11" spans="1:27" ht="120" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="113"/>
-      <c r="B11" s="113"/>
-      <c r="C11" s="113"/>
-      <c r="D11" s="113"/>
-      <c r="E11" s="113"/>
-      <c r="F11" s="113"/>
-      <c r="G11" s="113"/>
-      <c r="H11" s="113"/>
-      <c r="I11" s="95"/>
+      <c r="A11" s="106"/>
+      <c r="B11" s="106"/>
+      <c r="C11" s="106"/>
+      <c r="D11" s="109"/>
+      <c r="E11" s="109"/>
+      <c r="F11" s="109"/>
+      <c r="G11" s="109"/>
+      <c r="H11" s="106"/>
+      <c r="I11" s="114"/>
       <c r="J11" s="4"/>
       <c r="K11" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
@@ -3264,10 +3265,10 @@
         <v>5</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I12" s="15"/>
       <c r="J12" s="4"/>
@@ -3291,11 +3292,11 @@
     </row>
     <row r="13" spans="1:27" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B13" s="17"/>
       <c r="C13" s="17" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D13" s="18">
         <f>SUM(D14,D19)</f>
@@ -3338,13 +3339,13 @@
     </row>
     <row r="14" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D14" s="23">
         <f t="shared" ref="D14:G14" si="0">D15+D16</f>
@@ -3387,13 +3388,13 @@
     </row>
     <row r="15" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D15" s="28">
         <f>D22-D19-D16</f>
@@ -3436,13 +3437,13 @@
     </row>
     <row r="16" spans="1:27" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B16" s="30" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D16" s="28">
         <f>D17+D18</f>
@@ -3485,13 +3486,13 @@
     </row>
     <row r="17" spans="1:27" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B17" s="31">
         <v>1</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D17" s="33"/>
       <c r="E17" s="33"/>
@@ -3525,13 +3526,13 @@
     </row>
     <row r="18" spans="1:27" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B18" s="34">
         <v>2</v>
       </c>
       <c r="C18" s="35" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D18" s="36"/>
       <c r="E18" s="36"/>
@@ -3565,13 +3566,13 @@
     </row>
     <row r="19" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D19" s="23">
         <f t="shared" ref="D19:G19" si="2">D20+D21</f>
@@ -3614,13 +3615,13 @@
     </row>
     <row r="20" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C20" s="39" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D20" s="36"/>
       <c r="E20" s="36"/>
@@ -3654,11 +3655,11 @@
     </row>
     <row r="21" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B21" s="38"/>
       <c r="C21" s="39" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D21" s="36"/>
       <c r="E21" s="36"/>
@@ -3692,26 +3693,26 @@
     </row>
     <row r="22" spans="1:27" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B22" s="40"/>
       <c r="C22" s="40" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D22" s="41">
-        <f>D23+D68+D94</f>
+        <f>D23+D68+D95</f>
         <v>0</v>
       </c>
       <c r="E22" s="41">
-        <f>E23+E68+E94</f>
+        <f>E23+E68+E95</f>
         <v>0</v>
       </c>
       <c r="F22" s="41">
-        <f>F23+F68+F94</f>
+        <f>F23+F68+F95</f>
         <v>0</v>
       </c>
       <c r="G22" s="41">
-        <f>G23+G68+G94</f>
+        <f>G23+G68+G95</f>
         <v>0</v>
       </c>
       <c r="H22" s="25">
@@ -3739,13 +3740,13 @@
     </row>
     <row r="23" spans="1:27" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B23" s="42" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C23" s="43" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D23" s="44">
         <f t="shared" ref="D23:G23" si="4">D24+D61</f>
@@ -3788,13 +3789,13 @@
     </row>
     <row r="24" spans="1:27" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24" s="46" t="s">
-        <v>49</v>
-      </c>
-      <c r="C24" s="47" t="s">
-        <v>50</v>
+        <v>39</v>
+      </c>
+      <c r="B24" s="82" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="83" t="s">
+        <v>46</v>
       </c>
       <c r="D24" s="41">
         <f t="shared" ref="D24:G24" si="5">SUM(D25:D52)+D60-D32-D47</f>
@@ -3818,32 +3819,32 @@
       </c>
       <c r="J24" s="15"/>
       <c r="K24" s="15"/>
-      <c r="L24" s="48"/>
-      <c r="M24" s="48"/>
-      <c r="N24" s="48"/>
-      <c r="O24" s="48"/>
-      <c r="P24" s="48"/>
-      <c r="Q24" s="48"/>
-      <c r="R24" s="48"/>
-      <c r="S24" s="48"/>
-      <c r="T24" s="48"/>
-      <c r="U24" s="48"/>
-      <c r="V24" s="48"/>
-      <c r="W24" s="48"/>
-      <c r="X24" s="48"/>
-      <c r="Y24" s="48"/>
-      <c r="Z24" s="48"/>
-      <c r="AA24" s="48"/>
+      <c r="L24" s="46"/>
+      <c r="M24" s="46"/>
+      <c r="N24" s="46"/>
+      <c r="O24" s="46"/>
+      <c r="P24" s="46"/>
+      <c r="Q24" s="46"/>
+      <c r="R24" s="46"/>
+      <c r="S24" s="46"/>
+      <c r="T24" s="46"/>
+      <c r="U24" s="46"/>
+      <c r="V24" s="46"/>
+      <c r="W24" s="46"/>
+      <c r="X24" s="46"/>
+      <c r="Y24" s="46"/>
+      <c r="Z24" s="46"/>
+      <c r="AA24" s="46"/>
     </row>
     <row r="25" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="B25" s="49">
+        <v>41</v>
+      </c>
+      <c r="B25" s="47">
         <v>1</v>
       </c>
       <c r="C25" s="35" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D25" s="36"/>
       <c r="E25" s="36"/>
@@ -3858,32 +3859,32 @@
       </c>
       <c r="J25" s="15"/>
       <c r="K25" s="15"/>
-      <c r="L25" s="48"/>
-      <c r="M25" s="48"/>
-      <c r="N25" s="48"/>
-      <c r="O25" s="48"/>
-      <c r="P25" s="48"/>
-      <c r="Q25" s="48"/>
-      <c r="R25" s="48"/>
-      <c r="S25" s="48"/>
-      <c r="T25" s="48"/>
-      <c r="U25" s="48"/>
-      <c r="V25" s="48"/>
-      <c r="W25" s="48"/>
-      <c r="X25" s="48"/>
-      <c r="Y25" s="48"/>
-      <c r="Z25" s="48"/>
-      <c r="AA25" s="48"/>
+      <c r="L25" s="46"/>
+      <c r="M25" s="46"/>
+      <c r="N25" s="46"/>
+      <c r="O25" s="46"/>
+      <c r="P25" s="46"/>
+      <c r="Q25" s="46"/>
+      <c r="R25" s="46"/>
+      <c r="S25" s="46"/>
+      <c r="T25" s="46"/>
+      <c r="U25" s="46"/>
+      <c r="V25" s="46"/>
+      <c r="W25" s="46"/>
+      <c r="X25" s="46"/>
+      <c r="Y25" s="46"/>
+      <c r="Z25" s="46"/>
+      <c r="AA25" s="46"/>
     </row>
     <row r="26" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="B26" s="49">
+        <v>43</v>
+      </c>
+      <c r="B26" s="47">
         <v>2</v>
       </c>
-      <c r="C26" s="50" t="s">
-        <v>54</v>
+      <c r="C26" s="48" t="s">
+        <v>50</v>
       </c>
       <c r="D26" s="36"/>
       <c r="E26" s="36"/>
@@ -3898,32 +3899,32 @@
       </c>
       <c r="J26" s="15"/>
       <c r="K26" s="15"/>
-      <c r="L26" s="48"/>
-      <c r="M26" s="48"/>
-      <c r="N26" s="48"/>
-      <c r="O26" s="48"/>
-      <c r="P26" s="48"/>
-      <c r="Q26" s="48"/>
-      <c r="R26" s="48"/>
-      <c r="S26" s="48"/>
-      <c r="T26" s="48"/>
-      <c r="U26" s="48"/>
-      <c r="V26" s="48"/>
-      <c r="W26" s="48"/>
-      <c r="X26" s="48"/>
-      <c r="Y26" s="48"/>
-      <c r="Z26" s="48"/>
-      <c r="AA26" s="48"/>
+      <c r="L26" s="46"/>
+      <c r="M26" s="46"/>
+      <c r="N26" s="46"/>
+      <c r="O26" s="46"/>
+      <c r="P26" s="46"/>
+      <c r="Q26" s="46"/>
+      <c r="R26" s="46"/>
+      <c r="S26" s="46"/>
+      <c r="T26" s="46"/>
+      <c r="U26" s="46"/>
+      <c r="V26" s="46"/>
+      <c r="W26" s="46"/>
+      <c r="X26" s="46"/>
+      <c r="Y26" s="46"/>
+      <c r="Z26" s="46"/>
+      <c r="AA26" s="46"/>
     </row>
     <row r="27" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="B27" s="49">
+        <v>47</v>
+      </c>
+      <c r="B27" s="47">
         <v>3</v>
       </c>
-      <c r="C27" s="51" t="s">
-        <v>56</v>
+      <c r="C27" s="49" t="s">
+        <v>52</v>
       </c>
       <c r="D27" s="36"/>
       <c r="E27" s="36"/>
@@ -3938,36 +3939,36 @@
       </c>
       <c r="J27" s="15"/>
       <c r="K27" s="15"/>
-      <c r="L27" s="48"/>
-      <c r="M27" s="48"/>
-      <c r="N27" s="48"/>
-      <c r="O27" s="48"/>
-      <c r="P27" s="48"/>
-      <c r="Q27" s="48"/>
-      <c r="R27" s="48"/>
-      <c r="S27" s="48"/>
-      <c r="T27" s="48"/>
-      <c r="U27" s="48"/>
-      <c r="V27" s="48"/>
-      <c r="W27" s="48"/>
-      <c r="X27" s="48"/>
-      <c r="Y27" s="48"/>
-      <c r="Z27" s="48"/>
-      <c r="AA27" s="48"/>
+      <c r="L27" s="46"/>
+      <c r="M27" s="46"/>
+      <c r="N27" s="46"/>
+      <c r="O27" s="46"/>
+      <c r="P27" s="46"/>
+      <c r="Q27" s="46"/>
+      <c r="R27" s="46"/>
+      <c r="S27" s="46"/>
+      <c r="T27" s="46"/>
+      <c r="U27" s="46"/>
+      <c r="V27" s="46"/>
+      <c r="W27" s="46"/>
+      <c r="X27" s="46"/>
+      <c r="Y27" s="46"/>
+      <c r="Z27" s="46"/>
+      <c r="AA27" s="46"/>
     </row>
     <row r="28" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="B28" s="49">
+        <v>49</v>
+      </c>
+      <c r="B28" s="47">
         <v>4</v>
       </c>
-      <c r="C28" s="51" t="s">
-        <v>58</v>
-      </c>
-      <c r="D28" s="52"/>
-      <c r="E28" s="52"/>
-      <c r="F28" s="52"/>
+      <c r="C28" s="49" t="s">
+        <v>54</v>
+      </c>
+      <c r="D28" s="50"/>
+      <c r="E28" s="50"/>
+      <c r="F28" s="50"/>
       <c r="G28" s="29">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -3978,36 +3979,36 @@
       </c>
       <c r="J28" s="15"/>
       <c r="K28" s="15"/>
-      <c r="L28" s="48"/>
-      <c r="M28" s="48"/>
-      <c r="N28" s="48"/>
-      <c r="O28" s="48"/>
-      <c r="P28" s="48"/>
-      <c r="Q28" s="48"/>
-      <c r="R28" s="48"/>
-      <c r="S28" s="48"/>
-      <c r="T28" s="48"/>
-      <c r="U28" s="48"/>
-      <c r="V28" s="48"/>
-      <c r="W28" s="48"/>
-      <c r="X28" s="48"/>
-      <c r="Y28" s="48"/>
-      <c r="Z28" s="48"/>
-      <c r="AA28" s="48"/>
+      <c r="L28" s="46"/>
+      <c r="M28" s="46"/>
+      <c r="N28" s="46"/>
+      <c r="O28" s="46"/>
+      <c r="P28" s="46"/>
+      <c r="Q28" s="46"/>
+      <c r="R28" s="46"/>
+      <c r="S28" s="46"/>
+      <c r="T28" s="46"/>
+      <c r="U28" s="46"/>
+      <c r="V28" s="46"/>
+      <c r="W28" s="46"/>
+      <c r="X28" s="46"/>
+      <c r="Y28" s="46"/>
+      <c r="Z28" s="46"/>
+      <c r="AA28" s="46"/>
     </row>
     <row r="29" spans="1:27" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="B29" s="49">
+        <v>51</v>
+      </c>
+      <c r="B29" s="47">
         <v>5</v>
       </c>
-      <c r="C29" s="53" t="s">
-        <v>60</v>
-      </c>
-      <c r="D29" s="52"/>
-      <c r="E29" s="52"/>
-      <c r="F29" s="52"/>
+      <c r="C29" s="51" t="s">
+        <v>56</v>
+      </c>
+      <c r="D29" s="50"/>
+      <c r="E29" s="50"/>
+      <c r="F29" s="50"/>
       <c r="G29" s="29">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -4018,36 +4019,36 @@
       </c>
       <c r="J29" s="15"/>
       <c r="K29" s="15"/>
-      <c r="L29" s="48"/>
-      <c r="M29" s="48"/>
-      <c r="N29" s="48"/>
-      <c r="O29" s="48"/>
-      <c r="P29" s="48"/>
-      <c r="Q29" s="48"/>
-      <c r="R29" s="48"/>
-      <c r="S29" s="48"/>
-      <c r="T29" s="48"/>
-      <c r="U29" s="48"/>
-      <c r="V29" s="48"/>
-      <c r="W29" s="48"/>
-      <c r="X29" s="48"/>
-      <c r="Y29" s="48"/>
-      <c r="Z29" s="48"/>
-      <c r="AA29" s="48"/>
+      <c r="L29" s="46"/>
+      <c r="M29" s="46"/>
+      <c r="N29" s="46"/>
+      <c r="O29" s="46"/>
+      <c r="P29" s="46"/>
+      <c r="Q29" s="46"/>
+      <c r="R29" s="46"/>
+      <c r="S29" s="46"/>
+      <c r="T29" s="46"/>
+      <c r="U29" s="46"/>
+      <c r="V29" s="46"/>
+      <c r="W29" s="46"/>
+      <c r="X29" s="46"/>
+      <c r="Y29" s="46"/>
+      <c r="Z29" s="46"/>
+      <c r="AA29" s="46"/>
     </row>
     <row r="30" spans="1:27" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="B30" s="49">
+        <v>53</v>
+      </c>
+      <c r="B30" s="47">
         <v>6</v>
       </c>
-      <c r="C30" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="D30" s="52"/>
-      <c r="E30" s="52"/>
-      <c r="F30" s="52"/>
+      <c r="C30" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30" s="50"/>
+      <c r="E30" s="50"/>
+      <c r="F30" s="50"/>
       <c r="G30" s="29">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -4058,36 +4059,36 @@
       </c>
       <c r="J30" s="15"/>
       <c r="K30" s="15"/>
-      <c r="L30" s="48"/>
-      <c r="M30" s="48"/>
-      <c r="N30" s="48"/>
-      <c r="O30" s="48"/>
-      <c r="P30" s="48"/>
-      <c r="Q30" s="48"/>
-      <c r="R30" s="48"/>
-      <c r="S30" s="48"/>
-      <c r="T30" s="48"/>
-      <c r="U30" s="48"/>
-      <c r="V30" s="48"/>
-      <c r="W30" s="48"/>
-      <c r="X30" s="48"/>
-      <c r="Y30" s="48"/>
-      <c r="Z30" s="48"/>
-      <c r="AA30" s="48"/>
+      <c r="L30" s="46"/>
+      <c r="M30" s="46"/>
+      <c r="N30" s="46"/>
+      <c r="O30" s="46"/>
+      <c r="P30" s="46"/>
+      <c r="Q30" s="46"/>
+      <c r="R30" s="46"/>
+      <c r="S30" s="46"/>
+      <c r="T30" s="46"/>
+      <c r="U30" s="46"/>
+      <c r="V30" s="46"/>
+      <c r="W30" s="46"/>
+      <c r="X30" s="46"/>
+      <c r="Y30" s="46"/>
+      <c r="Z30" s="46"/>
+      <c r="AA30" s="46"/>
     </row>
     <row r="31" spans="1:27" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="B31" s="49">
+        <v>55</v>
+      </c>
+      <c r="B31" s="47">
         <v>7</v>
       </c>
-      <c r="C31" s="53" t="s">
-        <v>64</v>
-      </c>
-      <c r="D31" s="52"/>
-      <c r="E31" s="52"/>
-      <c r="F31" s="52"/>
+      <c r="C31" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="D31" s="50"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="50"/>
       <c r="G31" s="29">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -4098,36 +4099,36 @@
       </c>
       <c r="J31" s="15"/>
       <c r="K31" s="15"/>
-      <c r="L31" s="48"/>
-      <c r="M31" s="48"/>
-      <c r="N31" s="48"/>
-      <c r="O31" s="48"/>
-      <c r="P31" s="48"/>
-      <c r="Q31" s="48"/>
-      <c r="R31" s="48"/>
-      <c r="S31" s="48"/>
-      <c r="T31" s="48"/>
-      <c r="U31" s="48"/>
-      <c r="V31" s="48"/>
-      <c r="W31" s="48"/>
-      <c r="X31" s="48"/>
-      <c r="Y31" s="48"/>
-      <c r="Z31" s="48"/>
-      <c r="AA31" s="48"/>
+      <c r="L31" s="46"/>
+      <c r="M31" s="46"/>
+      <c r="N31" s="46"/>
+      <c r="O31" s="46"/>
+      <c r="P31" s="46"/>
+      <c r="Q31" s="46"/>
+      <c r="R31" s="46"/>
+      <c r="S31" s="46"/>
+      <c r="T31" s="46"/>
+      <c r="U31" s="46"/>
+      <c r="V31" s="46"/>
+      <c r="W31" s="46"/>
+      <c r="X31" s="46"/>
+      <c r="Y31" s="46"/>
+      <c r="Z31" s="46"/>
+      <c r="AA31" s="46"/>
     </row>
     <row r="32" spans="1:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="B32" s="54" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32" s="55" t="s">
-        <v>66</v>
-      </c>
-      <c r="D32" s="52"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="52"/>
+        <v>57</v>
+      </c>
+      <c r="B32" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32" s="53" t="s">
+        <v>62</v>
+      </c>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
+      <c r="F32" s="50"/>
       <c r="G32" s="29">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -4138,36 +4139,36 @@
       </c>
       <c r="J32" s="15"/>
       <c r="K32" s="15"/>
-      <c r="L32" s="48"/>
-      <c r="M32" s="48"/>
-      <c r="N32" s="48"/>
-      <c r="O32" s="48"/>
-      <c r="P32" s="48"/>
-      <c r="Q32" s="48"/>
-      <c r="R32" s="48"/>
-      <c r="S32" s="48"/>
-      <c r="T32" s="48"/>
-      <c r="U32" s="48"/>
-      <c r="V32" s="48"/>
-      <c r="W32" s="48"/>
-      <c r="X32" s="48"/>
-      <c r="Y32" s="48"/>
-      <c r="Z32" s="48"/>
-      <c r="AA32" s="48"/>
+      <c r="L32" s="46"/>
+      <c r="M32" s="46"/>
+      <c r="N32" s="46"/>
+      <c r="O32" s="46"/>
+      <c r="P32" s="46"/>
+      <c r="Q32" s="46"/>
+      <c r="R32" s="46"/>
+      <c r="S32" s="46"/>
+      <c r="T32" s="46"/>
+      <c r="U32" s="46"/>
+      <c r="V32" s="46"/>
+      <c r="W32" s="46"/>
+      <c r="X32" s="46"/>
+      <c r="Y32" s="46"/>
+      <c r="Z32" s="46"/>
+      <c r="AA32" s="46"/>
     </row>
     <row r="33" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="B33" s="49">
+        <v>59</v>
+      </c>
+      <c r="B33" s="47">
         <v>8</v>
       </c>
-      <c r="C33" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="D33" s="52"/>
-      <c r="E33" s="52"/>
-      <c r="F33" s="52"/>
+      <c r="C33" s="51" t="s">
+        <v>64</v>
+      </c>
+      <c r="D33" s="50"/>
+      <c r="E33" s="50"/>
+      <c r="F33" s="50"/>
       <c r="G33" s="29">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -4178,36 +4179,36 @@
       </c>
       <c r="J33" s="15"/>
       <c r="K33" s="15"/>
-      <c r="L33" s="48"/>
-      <c r="M33" s="48"/>
-      <c r="N33" s="48"/>
-      <c r="O33" s="48"/>
-      <c r="P33" s="48"/>
-      <c r="Q33" s="48"/>
-      <c r="R33" s="48"/>
-      <c r="S33" s="48"/>
-      <c r="T33" s="48"/>
-      <c r="U33" s="48"/>
-      <c r="V33" s="48"/>
-      <c r="W33" s="48"/>
-      <c r="X33" s="48"/>
-      <c r="Y33" s="48"/>
-      <c r="Z33" s="48"/>
-      <c r="AA33" s="48"/>
+      <c r="L33" s="46"/>
+      <c r="M33" s="46"/>
+      <c r="N33" s="46"/>
+      <c r="O33" s="46"/>
+      <c r="P33" s="46"/>
+      <c r="Q33" s="46"/>
+      <c r="R33" s="46"/>
+      <c r="S33" s="46"/>
+      <c r="T33" s="46"/>
+      <c r="U33" s="46"/>
+      <c r="V33" s="46"/>
+      <c r="W33" s="46"/>
+      <c r="X33" s="46"/>
+      <c r="Y33" s="46"/>
+      <c r="Z33" s="46"/>
+      <c r="AA33" s="46"/>
     </row>
     <row r="34" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="B34" s="49">
+        <v>61</v>
+      </c>
+      <c r="B34" s="47">
         <v>9</v>
       </c>
-      <c r="C34" s="53" t="s">
-        <v>70</v>
-      </c>
-      <c r="D34" s="52"/>
-      <c r="E34" s="52"/>
-      <c r="F34" s="52"/>
+      <c r="C34" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="D34" s="50"/>
+      <c r="E34" s="50"/>
+      <c r="F34" s="50"/>
       <c r="G34" s="29">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -4218,36 +4219,36 @@
       </c>
       <c r="J34" s="15"/>
       <c r="K34" s="15"/>
-      <c r="L34" s="48"/>
-      <c r="M34" s="48"/>
-      <c r="N34" s="48"/>
-      <c r="O34" s="48"/>
-      <c r="P34" s="48"/>
-      <c r="Q34" s="48"/>
-      <c r="R34" s="48"/>
-      <c r="S34" s="48"/>
-      <c r="T34" s="48"/>
-      <c r="U34" s="48"/>
-      <c r="V34" s="48"/>
-      <c r="W34" s="48"/>
-      <c r="X34" s="48"/>
-      <c r="Y34" s="48"/>
-      <c r="Z34" s="48"/>
-      <c r="AA34" s="48"/>
+      <c r="L34" s="46"/>
+      <c r="M34" s="46"/>
+      <c r="N34" s="46"/>
+      <c r="O34" s="46"/>
+      <c r="P34" s="46"/>
+      <c r="Q34" s="46"/>
+      <c r="R34" s="46"/>
+      <c r="S34" s="46"/>
+      <c r="T34" s="46"/>
+      <c r="U34" s="46"/>
+      <c r="V34" s="46"/>
+      <c r="W34" s="46"/>
+      <c r="X34" s="46"/>
+      <c r="Y34" s="46"/>
+      <c r="Z34" s="46"/>
+      <c r="AA34" s="46"/>
     </row>
     <row r="35" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="B35" s="49">
+        <v>63</v>
+      </c>
+      <c r="B35" s="47">
         <v>10</v>
       </c>
-      <c r="C35" s="53" t="s">
-        <v>72</v>
-      </c>
-      <c r="D35" s="52"/>
-      <c r="E35" s="52"/>
-      <c r="F35" s="52"/>
+      <c r="C35" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D35" s="50"/>
+      <c r="E35" s="50"/>
+      <c r="F35" s="50"/>
       <c r="G35" s="29">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -4258,36 +4259,36 @@
       </c>
       <c r="J35" s="15"/>
       <c r="K35" s="15"/>
-      <c r="L35" s="48"/>
-      <c r="M35" s="48"/>
-      <c r="N35" s="48"/>
-      <c r="O35" s="48"/>
-      <c r="P35" s="48"/>
-      <c r="Q35" s="48"/>
-      <c r="R35" s="48"/>
-      <c r="S35" s="48"/>
-      <c r="T35" s="48"/>
-      <c r="U35" s="48"/>
-      <c r="V35" s="48"/>
-      <c r="W35" s="48"/>
-      <c r="X35" s="48"/>
-      <c r="Y35" s="48"/>
-      <c r="Z35" s="48"/>
-      <c r="AA35" s="48"/>
+      <c r="L35" s="46"/>
+      <c r="M35" s="46"/>
+      <c r="N35" s="46"/>
+      <c r="O35" s="46"/>
+      <c r="P35" s="46"/>
+      <c r="Q35" s="46"/>
+      <c r="R35" s="46"/>
+      <c r="S35" s="46"/>
+      <c r="T35" s="46"/>
+      <c r="U35" s="46"/>
+      <c r="V35" s="46"/>
+      <c r="W35" s="46"/>
+      <c r="X35" s="46"/>
+      <c r="Y35" s="46"/>
+      <c r="Z35" s="46"/>
+      <c r="AA35" s="46"/>
     </row>
     <row r="36" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="B36" s="49">
+        <v>65</v>
+      </c>
+      <c r="B36" s="47">
         <v>11</v>
       </c>
-      <c r="C36" s="53" t="s">
-        <v>74</v>
-      </c>
-      <c r="D36" s="52"/>
-      <c r="E36" s="52"/>
-      <c r="F36" s="52"/>
+      <c r="C36" s="51" t="s">
+        <v>70</v>
+      </c>
+      <c r="D36" s="50"/>
+      <c r="E36" s="50"/>
+      <c r="F36" s="50"/>
       <c r="G36" s="29">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -4298,36 +4299,36 @@
       </c>
       <c r="J36" s="15"/>
       <c r="K36" s="15"/>
-      <c r="L36" s="48"/>
-      <c r="M36" s="48"/>
-      <c r="N36" s="48"/>
-      <c r="O36" s="48"/>
-      <c r="P36" s="48"/>
-      <c r="Q36" s="48"/>
-      <c r="R36" s="48"/>
-      <c r="S36" s="48"/>
-      <c r="T36" s="48"/>
-      <c r="U36" s="48"/>
-      <c r="V36" s="48"/>
-      <c r="W36" s="48"/>
-      <c r="X36" s="48"/>
-      <c r="Y36" s="48"/>
-      <c r="Z36" s="48"/>
-      <c r="AA36" s="48"/>
+      <c r="L36" s="46"/>
+      <c r="M36" s="46"/>
+      <c r="N36" s="46"/>
+      <c r="O36" s="46"/>
+      <c r="P36" s="46"/>
+      <c r="Q36" s="46"/>
+      <c r="R36" s="46"/>
+      <c r="S36" s="46"/>
+      <c r="T36" s="46"/>
+      <c r="U36" s="46"/>
+      <c r="V36" s="46"/>
+      <c r="W36" s="46"/>
+      <c r="X36" s="46"/>
+      <c r="Y36" s="46"/>
+      <c r="Z36" s="46"/>
+      <c r="AA36" s="46"/>
     </row>
     <row r="37" spans="1:27" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="B37" s="49">
+        <v>67</v>
+      </c>
+      <c r="B37" s="47">
         <v>12</v>
       </c>
-      <c r="C37" s="51" t="s">
-        <v>76</v>
-      </c>
-      <c r="D37" s="52"/>
-      <c r="E37" s="52"/>
-      <c r="F37" s="52"/>
+      <c r="C37" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="D37" s="50"/>
+      <c r="E37" s="50"/>
+      <c r="F37" s="50"/>
       <c r="G37" s="29">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -4338,36 +4339,36 @@
       </c>
       <c r="J37" s="15"/>
       <c r="K37" s="15"/>
-      <c r="L37" s="48"/>
-      <c r="M37" s="48"/>
-      <c r="N37" s="48"/>
-      <c r="O37" s="48"/>
-      <c r="P37" s="48"/>
-      <c r="Q37" s="48"/>
-      <c r="R37" s="48"/>
-      <c r="S37" s="48"/>
-      <c r="T37" s="48"/>
-      <c r="U37" s="48"/>
-      <c r="V37" s="48"/>
-      <c r="W37" s="48"/>
-      <c r="X37" s="48"/>
-      <c r="Y37" s="48"/>
-      <c r="Z37" s="48"/>
-      <c r="AA37" s="48"/>
+      <c r="L37" s="46"/>
+      <c r="M37" s="46"/>
+      <c r="N37" s="46"/>
+      <c r="O37" s="46"/>
+      <c r="P37" s="46"/>
+      <c r="Q37" s="46"/>
+      <c r="R37" s="46"/>
+      <c r="S37" s="46"/>
+      <c r="T37" s="46"/>
+      <c r="U37" s="46"/>
+      <c r="V37" s="46"/>
+      <c r="W37" s="46"/>
+      <c r="X37" s="46"/>
+      <c r="Y37" s="46"/>
+      <c r="Z37" s="46"/>
+      <c r="AA37" s="46"/>
     </row>
     <row r="38" spans="1:27" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B38" s="49">
+        <v>69</v>
+      </c>
+      <c r="B38" s="47">
         <v>13</v>
       </c>
-      <c r="C38" s="51" t="s">
-        <v>78</v>
-      </c>
-      <c r="D38" s="52"/>
-      <c r="E38" s="52"/>
-      <c r="F38" s="52"/>
+      <c r="C38" s="49" t="s">
+        <v>74</v>
+      </c>
+      <c r="D38" s="50"/>
+      <c r="E38" s="50"/>
+      <c r="F38" s="50"/>
       <c r="G38" s="29">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -4378,36 +4379,36 @@
       </c>
       <c r="J38" s="15"/>
       <c r="K38" s="15"/>
-      <c r="L38" s="48"/>
-      <c r="M38" s="48"/>
-      <c r="N38" s="48"/>
-      <c r="O38" s="48"/>
-      <c r="P38" s="48"/>
-      <c r="Q38" s="48"/>
-      <c r="R38" s="48"/>
-      <c r="S38" s="48"/>
-      <c r="T38" s="48"/>
-      <c r="U38" s="48"/>
-      <c r="V38" s="48"/>
-      <c r="W38" s="48"/>
-      <c r="X38" s="48"/>
-      <c r="Y38" s="48"/>
-      <c r="Z38" s="48"/>
-      <c r="AA38" s="48"/>
+      <c r="L38" s="46"/>
+      <c r="M38" s="46"/>
+      <c r="N38" s="46"/>
+      <c r="O38" s="46"/>
+      <c r="P38" s="46"/>
+      <c r="Q38" s="46"/>
+      <c r="R38" s="46"/>
+      <c r="S38" s="46"/>
+      <c r="T38" s="46"/>
+      <c r="U38" s="46"/>
+      <c r="V38" s="46"/>
+      <c r="W38" s="46"/>
+      <c r="X38" s="46"/>
+      <c r="Y38" s="46"/>
+      <c r="Z38" s="46"/>
+      <c r="AA38" s="46"/>
     </row>
     <row r="39" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="B39" s="49">
+        <v>71</v>
+      </c>
+      <c r="B39" s="47">
         <v>14</v>
       </c>
-      <c r="C39" s="51" t="s">
-        <v>80</v>
-      </c>
-      <c r="D39" s="52"/>
-      <c r="E39" s="52"/>
-      <c r="F39" s="52"/>
+      <c r="C39" s="49" t="s">
+        <v>76</v>
+      </c>
+      <c r="D39" s="50"/>
+      <c r="E39" s="50"/>
+      <c r="F39" s="50"/>
       <c r="G39" s="29">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -4418,32 +4419,32 @@
       </c>
       <c r="J39" s="15"/>
       <c r="K39" s="15"/>
-      <c r="L39" s="48"/>
-      <c r="M39" s="48"/>
-      <c r="N39" s="48"/>
-      <c r="O39" s="48"/>
-      <c r="P39" s="48"/>
-      <c r="Q39" s="48"/>
-      <c r="R39" s="48"/>
-      <c r="S39" s="48"/>
-      <c r="T39" s="48"/>
-      <c r="U39" s="48"/>
-      <c r="V39" s="48"/>
-      <c r="W39" s="48"/>
-      <c r="X39" s="48"/>
-      <c r="Y39" s="48"/>
-      <c r="Z39" s="48"/>
-      <c r="AA39" s="48"/>
+      <c r="L39" s="46"/>
+      <c r="M39" s="46"/>
+      <c r="N39" s="46"/>
+      <c r="O39" s="46"/>
+      <c r="P39" s="46"/>
+      <c r="Q39" s="46"/>
+      <c r="R39" s="46"/>
+      <c r="S39" s="46"/>
+      <c r="T39" s="46"/>
+      <c r="U39" s="46"/>
+      <c r="V39" s="46"/>
+      <c r="W39" s="46"/>
+      <c r="X39" s="46"/>
+      <c r="Y39" s="46"/>
+      <c r="Z39" s="46"/>
+      <c r="AA39" s="46"/>
     </row>
     <row r="40" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="B40" s="49">
+        <v>73</v>
+      </c>
+      <c r="B40" s="47">
         <v>15</v>
       </c>
-      <c r="C40" s="53" t="s">
-        <v>82</v>
+      <c r="C40" s="51" t="s">
+        <v>78</v>
       </c>
       <c r="D40" s="36"/>
       <c r="E40" s="36"/>
@@ -4458,36 +4459,36 @@
       </c>
       <c r="J40" s="15"/>
       <c r="K40" s="15"/>
-      <c r="L40" s="48"/>
-      <c r="M40" s="48"/>
-      <c r="N40" s="48"/>
-      <c r="O40" s="48"/>
-      <c r="P40" s="48"/>
-      <c r="Q40" s="48"/>
-      <c r="R40" s="48"/>
-      <c r="S40" s="48"/>
-      <c r="T40" s="48"/>
-      <c r="U40" s="48"/>
-      <c r="V40" s="48"/>
-      <c r="W40" s="48"/>
-      <c r="X40" s="48"/>
-      <c r="Y40" s="48"/>
-      <c r="Z40" s="48"/>
-      <c r="AA40" s="48"/>
+      <c r="L40" s="46"/>
+      <c r="M40" s="46"/>
+      <c r="N40" s="46"/>
+      <c r="O40" s="46"/>
+      <c r="P40" s="46"/>
+      <c r="Q40" s="46"/>
+      <c r="R40" s="46"/>
+      <c r="S40" s="46"/>
+      <c r="T40" s="46"/>
+      <c r="U40" s="46"/>
+      <c r="V40" s="46"/>
+      <c r="W40" s="46"/>
+      <c r="X40" s="46"/>
+      <c r="Y40" s="46"/>
+      <c r="Z40" s="46"/>
+      <c r="AA40" s="46"/>
     </row>
     <row r="41" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="B41" s="49">
+        <v>75</v>
+      </c>
+      <c r="B41" s="47">
         <v>16</v>
       </c>
-      <c r="C41" s="53" t="s">
-        <v>84</v>
-      </c>
-      <c r="D41" s="52"/>
-      <c r="E41" s="52"/>
-      <c r="F41" s="52"/>
+      <c r="C41" s="51" t="s">
+        <v>80</v>
+      </c>
+      <c r="D41" s="50"/>
+      <c r="E41" s="50"/>
+      <c r="F41" s="50"/>
       <c r="G41" s="29">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -4498,36 +4499,36 @@
       </c>
       <c r="J41" s="15"/>
       <c r="K41" s="15"/>
-      <c r="L41" s="48"/>
-      <c r="M41" s="48"/>
-      <c r="N41" s="48"/>
-      <c r="O41" s="48"/>
-      <c r="P41" s="48"/>
-      <c r="Q41" s="48"/>
-      <c r="R41" s="48"/>
-      <c r="S41" s="48"/>
-      <c r="T41" s="48"/>
-      <c r="U41" s="48"/>
-      <c r="V41" s="48"/>
-      <c r="W41" s="48"/>
-      <c r="X41" s="48"/>
-      <c r="Y41" s="48"/>
-      <c r="Z41" s="48"/>
-      <c r="AA41" s="48"/>
+      <c r="L41" s="46"/>
+      <c r="M41" s="46"/>
+      <c r="N41" s="46"/>
+      <c r="O41" s="46"/>
+      <c r="P41" s="46"/>
+      <c r="Q41" s="46"/>
+      <c r="R41" s="46"/>
+      <c r="S41" s="46"/>
+      <c r="T41" s="46"/>
+      <c r="U41" s="46"/>
+      <c r="V41" s="46"/>
+      <c r="W41" s="46"/>
+      <c r="X41" s="46"/>
+      <c r="Y41" s="46"/>
+      <c r="Z41" s="46"/>
+      <c r="AA41" s="46"/>
     </row>
     <row r="42" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="B42" s="49">
+        <v>77</v>
+      </c>
+      <c r="B42" s="47">
         <v>17</v>
       </c>
-      <c r="C42" s="51" t="s">
-        <v>86</v>
-      </c>
-      <c r="D42" s="52"/>
-      <c r="E42" s="52"/>
-      <c r="F42" s="52"/>
+      <c r="C42" s="49" t="s">
+        <v>82</v>
+      </c>
+      <c r="D42" s="50"/>
+      <c r="E42" s="50"/>
+      <c r="F42" s="50"/>
       <c r="G42" s="29">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -4538,36 +4539,36 @@
       </c>
       <c r="J42" s="15"/>
       <c r="K42" s="15"/>
-      <c r="L42" s="48"/>
-      <c r="M42" s="48"/>
-      <c r="N42" s="48"/>
-      <c r="O42" s="48"/>
-      <c r="P42" s="48"/>
-      <c r="Q42" s="48"/>
-      <c r="R42" s="48"/>
-      <c r="S42" s="48"/>
-      <c r="T42" s="48"/>
-      <c r="U42" s="48"/>
-      <c r="V42" s="48"/>
-      <c r="W42" s="48"/>
-      <c r="X42" s="48"/>
-      <c r="Y42" s="48"/>
-      <c r="Z42" s="48"/>
-      <c r="AA42" s="48"/>
+      <c r="L42" s="46"/>
+      <c r="M42" s="46"/>
+      <c r="N42" s="46"/>
+      <c r="O42" s="46"/>
+      <c r="P42" s="46"/>
+      <c r="Q42" s="46"/>
+      <c r="R42" s="46"/>
+      <c r="S42" s="46"/>
+      <c r="T42" s="46"/>
+      <c r="U42" s="46"/>
+      <c r="V42" s="46"/>
+      <c r="W42" s="46"/>
+      <c r="X42" s="46"/>
+      <c r="Y42" s="46"/>
+      <c r="Z42" s="46"/>
+      <c r="AA42" s="46"/>
     </row>
     <row r="43" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="B43" s="49">
+        <v>79</v>
+      </c>
+      <c r="B43" s="47">
         <v>18</v>
       </c>
-      <c r="C43" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="D43" s="52"/>
-      <c r="E43" s="52"/>
-      <c r="F43" s="52"/>
+      <c r="C43" s="51" t="s">
+        <v>84</v>
+      </c>
+      <c r="D43" s="50"/>
+      <c r="E43" s="50"/>
+      <c r="F43" s="50"/>
       <c r="G43" s="29">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -4578,36 +4579,36 @@
       </c>
       <c r="J43" s="15"/>
       <c r="K43" s="15"/>
-      <c r="L43" s="48"/>
-      <c r="M43" s="48"/>
-      <c r="N43" s="48"/>
-      <c r="O43" s="48"/>
-      <c r="P43" s="48"/>
-      <c r="Q43" s="48"/>
-      <c r="R43" s="48"/>
-      <c r="S43" s="48"/>
-      <c r="T43" s="48"/>
-      <c r="U43" s="48"/>
-      <c r="V43" s="48"/>
-      <c r="W43" s="48"/>
-      <c r="X43" s="48"/>
-      <c r="Y43" s="48"/>
-      <c r="Z43" s="48"/>
-      <c r="AA43" s="48"/>
+      <c r="L43" s="46"/>
+      <c r="M43" s="46"/>
+      <c r="N43" s="46"/>
+      <c r="O43" s="46"/>
+      <c r="P43" s="46"/>
+      <c r="Q43" s="46"/>
+      <c r="R43" s="46"/>
+      <c r="S43" s="46"/>
+      <c r="T43" s="46"/>
+      <c r="U43" s="46"/>
+      <c r="V43" s="46"/>
+      <c r="W43" s="46"/>
+      <c r="X43" s="46"/>
+      <c r="Y43" s="46"/>
+      <c r="Z43" s="46"/>
+      <c r="AA43" s="46"/>
     </row>
     <row r="44" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="B44" s="49">
+        <v>81</v>
+      </c>
+      <c r="B44" s="47">
         <v>19</v>
       </c>
-      <c r="C44" s="51" t="s">
-        <v>90</v>
-      </c>
-      <c r="D44" s="52"/>
-      <c r="E44" s="52"/>
-      <c r="F44" s="52"/>
+      <c r="C44" s="49" t="s">
+        <v>86</v>
+      </c>
+      <c r="D44" s="50"/>
+      <c r="E44" s="50"/>
+      <c r="F44" s="50"/>
       <c r="G44" s="29">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -4618,32 +4619,32 @@
       </c>
       <c r="J44" s="15"/>
       <c r="K44" s="15"/>
-      <c r="L44" s="48"/>
-      <c r="M44" s="48"/>
-      <c r="N44" s="48"/>
-      <c r="O44" s="48"/>
-      <c r="P44" s="48"/>
-      <c r="Q44" s="48"/>
-      <c r="R44" s="48"/>
-      <c r="S44" s="48"/>
-      <c r="T44" s="48"/>
-      <c r="U44" s="48"/>
-      <c r="V44" s="48"/>
-      <c r="W44" s="48"/>
-      <c r="X44" s="48"/>
-      <c r="Y44" s="48"/>
-      <c r="Z44" s="48"/>
-      <c r="AA44" s="48"/>
+      <c r="L44" s="46"/>
+      <c r="M44" s="46"/>
+      <c r="N44" s="46"/>
+      <c r="O44" s="46"/>
+      <c r="P44" s="46"/>
+      <c r="Q44" s="46"/>
+      <c r="R44" s="46"/>
+      <c r="S44" s="46"/>
+      <c r="T44" s="46"/>
+      <c r="U44" s="46"/>
+      <c r="V44" s="46"/>
+      <c r="W44" s="46"/>
+      <c r="X44" s="46"/>
+      <c r="Y44" s="46"/>
+      <c r="Z44" s="46"/>
+      <c r="AA44" s="46"/>
     </row>
     <row r="45" spans="1:27" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="B45" s="49">
+        <v>83</v>
+      </c>
+      <c r="B45" s="47">
         <v>20</v>
       </c>
-      <c r="C45" s="50" t="s">
-        <v>92</v>
+      <c r="C45" s="48" t="s">
+        <v>88</v>
       </c>
       <c r="D45" s="36"/>
       <c r="E45" s="36"/>
@@ -4658,36 +4659,36 @@
       </c>
       <c r="J45" s="15"/>
       <c r="K45" s="15"/>
-      <c r="L45" s="48"/>
-      <c r="M45" s="48"/>
-      <c r="N45" s="48"/>
-      <c r="O45" s="48"/>
-      <c r="P45" s="48"/>
-      <c r="Q45" s="48"/>
-      <c r="R45" s="48"/>
-      <c r="S45" s="48"/>
-      <c r="T45" s="48"/>
-      <c r="U45" s="48"/>
-      <c r="V45" s="48"/>
-      <c r="W45" s="48"/>
-      <c r="X45" s="48"/>
-      <c r="Y45" s="48"/>
-      <c r="Z45" s="48"/>
-      <c r="AA45" s="48"/>
+      <c r="L45" s="46"/>
+      <c r="M45" s="46"/>
+      <c r="N45" s="46"/>
+      <c r="O45" s="46"/>
+      <c r="P45" s="46"/>
+      <c r="Q45" s="46"/>
+      <c r="R45" s="46"/>
+      <c r="S45" s="46"/>
+      <c r="T45" s="46"/>
+      <c r="U45" s="46"/>
+      <c r="V45" s="46"/>
+      <c r="W45" s="46"/>
+      <c r="X45" s="46"/>
+      <c r="Y45" s="46"/>
+      <c r="Z45" s="46"/>
+      <c r="AA45" s="46"/>
     </row>
     <row r="46" spans="1:27" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="B46" s="49">
+        <v>85</v>
+      </c>
+      <c r="B46" s="79">
         <v>21</v>
       </c>
-      <c r="C46" s="56" t="s">
-        <v>94</v>
-      </c>
-      <c r="D46" s="52"/>
-      <c r="E46" s="52"/>
-      <c r="F46" s="52"/>
+      <c r="C46" s="84" t="s">
+        <v>90</v>
+      </c>
+      <c r="D46" s="50"/>
+      <c r="E46" s="50"/>
+      <c r="F46" s="50"/>
       <c r="G46" s="29">
         <f t="shared" si="6"/>
         <v>0</v>
@@ -4696,35 +4697,33 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I46" s="57" t="s">
-        <v>95</v>
-      </c>
+      <c r="I46" s="81"/>
       <c r="J46" s="15"/>
       <c r="K46" s="15"/>
-      <c r="L46" s="48"/>
-      <c r="M46" s="48"/>
-      <c r="N46" s="48"/>
-      <c r="O46" s="48"/>
-      <c r="P46" s="48"/>
-      <c r="Q46" s="48"/>
-      <c r="R46" s="48"/>
-      <c r="S46" s="48"/>
-      <c r="T46" s="48"/>
-      <c r="U46" s="48"/>
-      <c r="V46" s="48"/>
-      <c r="W46" s="48"/>
-      <c r="X46" s="48"/>
-      <c r="Y46" s="48"/>
-      <c r="Z46" s="48"/>
-      <c r="AA46" s="48"/>
+      <c r="L46" s="46"/>
+      <c r="M46" s="46"/>
+      <c r="N46" s="46"/>
+      <c r="O46" s="46"/>
+      <c r="P46" s="46"/>
+      <c r="Q46" s="46"/>
+      <c r="R46" s="46"/>
+      <c r="S46" s="46"/>
+      <c r="T46" s="46"/>
+      <c r="U46" s="46"/>
+      <c r="V46" s="46"/>
+      <c r="W46" s="46"/>
+      <c r="X46" s="46"/>
+      <c r="Y46" s="46"/>
+      <c r="Z46" s="46"/>
+      <c r="AA46" s="46"/>
     </row>
     <row r="47" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="B47" s="49"/>
-      <c r="C47" s="58" t="s">
-        <v>97</v>
+        <v>87</v>
+      </c>
+      <c r="B47" s="79"/>
+      <c r="C47" s="80" t="s">
+        <v>92</v>
       </c>
       <c r="D47" s="36"/>
       <c r="E47" s="36"/>
@@ -4734,37 +4733,38 @@
         <v>0</v>
       </c>
       <c r="H47" s="25">
-        <f t="shared" ref="H47:H96" si="7">IFERROR(G47/E47,0)</f>
+        <f t="shared" ref="H47:H97" si="7">IFERROR(G47/E47,0)</f>
         <v>0</v>
       </c>
+      <c r="I47" s="81"/>
       <c r="J47" s="15"/>
       <c r="K47" s="15"/>
-      <c r="L47" s="48"/>
-      <c r="M47" s="48"/>
-      <c r="N47" s="48"/>
-      <c r="O47" s="48"/>
-      <c r="P47" s="48"/>
-      <c r="Q47" s="48"/>
-      <c r="R47" s="48"/>
-      <c r="S47" s="48"/>
-      <c r="T47" s="48"/>
-      <c r="U47" s="48"/>
-      <c r="V47" s="48"/>
-      <c r="W47" s="48"/>
-      <c r="X47" s="48"/>
-      <c r="Y47" s="48"/>
-      <c r="Z47" s="48"/>
-      <c r="AA47" s="48"/>
+      <c r="L47" s="46"/>
+      <c r="M47" s="46"/>
+      <c r="N47" s="46"/>
+      <c r="O47" s="46"/>
+      <c r="P47" s="46"/>
+      <c r="Q47" s="46"/>
+      <c r="R47" s="46"/>
+      <c r="S47" s="46"/>
+      <c r="T47" s="46"/>
+      <c r="U47" s="46"/>
+      <c r="V47" s="46"/>
+      <c r="W47" s="46"/>
+      <c r="X47" s="46"/>
+      <c r="Y47" s="46"/>
+      <c r="Z47" s="46"/>
+      <c r="AA47" s="46"/>
     </row>
     <row r="48" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="B48" s="49">
+        <v>89</v>
+      </c>
+      <c r="B48" s="79">
         <v>22</v>
       </c>
-      <c r="C48" s="59" t="s">
-        <v>99</v>
+      <c r="C48" s="121" t="s">
+        <v>183</v>
       </c>
       <c r="D48" s="36"/>
       <c r="E48" s="36"/>
@@ -4777,37 +4777,35 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="I48" s="57" t="s">
-        <v>95</v>
-      </c>
+      <c r="I48" s="81"/>
       <c r="J48" s="15"/>
       <c r="K48" s="15"/>
-      <c r="L48" s="48"/>
-      <c r="M48" s="48"/>
-      <c r="N48" s="48"/>
-      <c r="O48" s="48"/>
-      <c r="P48" s="48"/>
-      <c r="Q48" s="48"/>
-      <c r="R48" s="48"/>
-      <c r="S48" s="48"/>
-      <c r="T48" s="48"/>
-      <c r="U48" s="48"/>
-      <c r="V48" s="48"/>
-      <c r="W48" s="48"/>
-      <c r="X48" s="48"/>
-      <c r="Y48" s="48"/>
-      <c r="Z48" s="48"/>
-      <c r="AA48" s="48"/>
+      <c r="L48" s="46"/>
+      <c r="M48" s="46"/>
+      <c r="N48" s="46"/>
+      <c r="O48" s="46"/>
+      <c r="P48" s="46"/>
+      <c r="Q48" s="46"/>
+      <c r="R48" s="46"/>
+      <c r="S48" s="46"/>
+      <c r="T48" s="46"/>
+      <c r="U48" s="46"/>
+      <c r="V48" s="46"/>
+      <c r="W48" s="46"/>
+      <c r="X48" s="46"/>
+      <c r="Y48" s="46"/>
+      <c r="Z48" s="46"/>
+      <c r="AA48" s="46"/>
     </row>
     <row r="49" spans="1:27" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B49" s="49">
+        <v>91</v>
+      </c>
+      <c r="B49" s="79">
         <v>23</v>
       </c>
-      <c r="C49" s="60" t="s">
-        <v>101</v>
+      <c r="C49" s="85" t="s">
+        <v>95</v>
       </c>
       <c r="D49" s="36"/>
       <c r="E49" s="36"/>
@@ -4820,37 +4818,35 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="I49" s="57" t="s">
-        <v>95</v>
-      </c>
+      <c r="I49" s="81"/>
       <c r="J49" s="15"/>
       <c r="K49" s="15"/>
-      <c r="L49" s="48"/>
-      <c r="M49" s="48"/>
-      <c r="N49" s="48"/>
-      <c r="O49" s="48"/>
-      <c r="P49" s="48"/>
-      <c r="Q49" s="48"/>
-      <c r="R49" s="48"/>
-      <c r="S49" s="48"/>
-      <c r="T49" s="48"/>
-      <c r="U49" s="48"/>
-      <c r="V49" s="48"/>
-      <c r="W49" s="48"/>
-      <c r="X49" s="48"/>
-      <c r="Y49" s="48"/>
-      <c r="Z49" s="48"/>
-      <c r="AA49" s="48"/>
+      <c r="L49" s="46"/>
+      <c r="M49" s="46"/>
+      <c r="N49" s="46"/>
+      <c r="O49" s="46"/>
+      <c r="P49" s="46"/>
+      <c r="Q49" s="46"/>
+      <c r="R49" s="46"/>
+      <c r="S49" s="46"/>
+      <c r="T49" s="46"/>
+      <c r="U49" s="46"/>
+      <c r="V49" s="46"/>
+      <c r="W49" s="46"/>
+      <c r="X49" s="46"/>
+      <c r="Y49" s="46"/>
+      <c r="Z49" s="46"/>
+      <c r="AA49" s="46"/>
     </row>
     <row r="50" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="B50" s="49">
+        <v>93</v>
+      </c>
+      <c r="B50" s="47">
         <v>24</v>
       </c>
-      <c r="C50" s="50" t="s">
-        <v>103</v>
+      <c r="C50" s="48" t="s">
+        <v>97</v>
       </c>
       <c r="D50" s="36"/>
       <c r="E50" s="36"/>
@@ -4865,32 +4861,32 @@
       </c>
       <c r="J50" s="15"/>
       <c r="K50" s="15"/>
-      <c r="L50" s="48"/>
-      <c r="M50" s="48"/>
-      <c r="N50" s="48"/>
-      <c r="O50" s="48"/>
-      <c r="P50" s="48"/>
-      <c r="Q50" s="48"/>
-      <c r="R50" s="48"/>
-      <c r="S50" s="48"/>
-      <c r="T50" s="48"/>
-      <c r="U50" s="48"/>
-      <c r="V50" s="48"/>
-      <c r="W50" s="48"/>
-      <c r="X50" s="48"/>
-      <c r="Y50" s="48"/>
-      <c r="Z50" s="48"/>
-      <c r="AA50" s="48"/>
+      <c r="L50" s="46"/>
+      <c r="M50" s="46"/>
+      <c r="N50" s="46"/>
+      <c r="O50" s="46"/>
+      <c r="P50" s="46"/>
+      <c r="Q50" s="46"/>
+      <c r="R50" s="46"/>
+      <c r="S50" s="46"/>
+      <c r="T50" s="46"/>
+      <c r="U50" s="46"/>
+      <c r="V50" s="46"/>
+      <c r="W50" s="46"/>
+      <c r="X50" s="46"/>
+      <c r="Y50" s="46"/>
+      <c r="Z50" s="46"/>
+      <c r="AA50" s="46"/>
     </row>
     <row r="51" spans="1:27" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A51" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="B51" s="49">
+        <v>94</v>
+      </c>
+      <c r="B51" s="47">
         <v>25</v>
       </c>
-      <c r="C51" s="50" t="s">
-        <v>105</v>
+      <c r="C51" s="48" t="s">
+        <v>99</v>
       </c>
       <c r="D51" s="36"/>
       <c r="E51" s="36"/>
@@ -4905,32 +4901,32 @@
       </c>
       <c r="J51" s="15"/>
       <c r="K51" s="15"/>
-      <c r="L51" s="48"/>
-      <c r="M51" s="48"/>
-      <c r="N51" s="48"/>
-      <c r="O51" s="48"/>
-      <c r="P51" s="48"/>
-      <c r="Q51" s="48"/>
-      <c r="R51" s="48"/>
-      <c r="S51" s="48"/>
-      <c r="T51" s="48"/>
-      <c r="U51" s="48"/>
-      <c r="V51" s="48"/>
-      <c r="W51" s="48"/>
-      <c r="X51" s="48"/>
-      <c r="Y51" s="48"/>
-      <c r="Z51" s="48"/>
-      <c r="AA51" s="48"/>
+      <c r="L51" s="46"/>
+      <c r="M51" s="46"/>
+      <c r="N51" s="46"/>
+      <c r="O51" s="46"/>
+      <c r="P51" s="46"/>
+      <c r="Q51" s="46"/>
+      <c r="R51" s="46"/>
+      <c r="S51" s="46"/>
+      <c r="T51" s="46"/>
+      <c r="U51" s="46"/>
+      <c r="V51" s="46"/>
+      <c r="W51" s="46"/>
+      <c r="X51" s="46"/>
+      <c r="Y51" s="46"/>
+      <c r="Z51" s="46"/>
+      <c r="AA51" s="46"/>
     </row>
     <row r="52" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="B52" s="61">
+        <v>96</v>
+      </c>
+      <c r="B52" s="55">
         <v>26</v>
       </c>
-      <c r="C52" s="62" t="s">
-        <v>107</v>
+      <c r="C52" s="56" t="s">
+        <v>101</v>
       </c>
       <c r="D52" s="28">
         <f t="shared" ref="D52:G52" si="8">SUM(D53:D59)</f>
@@ -4954,32 +4950,32 @@
       </c>
       <c r="J52" s="15"/>
       <c r="K52" s="15"/>
-      <c r="L52" s="48"/>
-      <c r="M52" s="48"/>
-      <c r="N52" s="48"/>
-      <c r="O52" s="48"/>
-      <c r="P52" s="48"/>
-      <c r="Q52" s="48"/>
-      <c r="R52" s="48"/>
-      <c r="S52" s="48"/>
-      <c r="T52" s="48"/>
-      <c r="U52" s="48"/>
-      <c r="V52" s="48"/>
-      <c r="W52" s="48"/>
-      <c r="X52" s="48"/>
-      <c r="Y52" s="48"/>
-      <c r="Z52" s="48"/>
-      <c r="AA52" s="48"/>
+      <c r="L52" s="46"/>
+      <c r="M52" s="46"/>
+      <c r="N52" s="46"/>
+      <c r="O52" s="46"/>
+      <c r="P52" s="46"/>
+      <c r="Q52" s="46"/>
+      <c r="R52" s="46"/>
+      <c r="S52" s="46"/>
+      <c r="T52" s="46"/>
+      <c r="U52" s="46"/>
+      <c r="V52" s="46"/>
+      <c r="W52" s="46"/>
+      <c r="X52" s="46"/>
+      <c r="Y52" s="46"/>
+      <c r="Z52" s="46"/>
+      <c r="AA52" s="46"/>
     </row>
     <row r="53" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="B53" s="54" t="s">
-        <v>33</v>
-      </c>
-      <c r="C53" s="63" t="s">
-        <v>109</v>
+        <v>98</v>
+      </c>
+      <c r="B53" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="C53" s="57" t="s">
+        <v>103</v>
       </c>
       <c r="D53" s="36"/>
       <c r="E53" s="36"/>
@@ -4994,30 +4990,30 @@
       </c>
       <c r="J53" s="15"/>
       <c r="K53" s="15"/>
-      <c r="L53" s="64"/>
-      <c r="M53" s="64"/>
-      <c r="N53" s="64"/>
-      <c r="O53" s="64"/>
-      <c r="P53" s="64"/>
-      <c r="Q53" s="64"/>
-      <c r="R53" s="64"/>
-      <c r="S53" s="64"/>
-      <c r="T53" s="64"/>
-      <c r="U53" s="64"/>
-      <c r="V53" s="64"/>
-      <c r="W53" s="64"/>
-      <c r="X53" s="64"/>
-      <c r="Y53" s="64"/>
-      <c r="Z53" s="64"/>
-      <c r="AA53" s="64"/>
+      <c r="L53" s="58"/>
+      <c r="M53" s="58"/>
+      <c r="N53" s="58"/>
+      <c r="O53" s="58"/>
+      <c r="P53" s="58"/>
+      <c r="Q53" s="58"/>
+      <c r="R53" s="58"/>
+      <c r="S53" s="58"/>
+      <c r="T53" s="58"/>
+      <c r="U53" s="58"/>
+      <c r="V53" s="58"/>
+      <c r="W53" s="58"/>
+      <c r="X53" s="58"/>
+      <c r="Y53" s="58"/>
+      <c r="Z53" s="58"/>
+      <c r="AA53" s="58"/>
     </row>
     <row r="54" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="B54" s="54"/>
-      <c r="C54" s="63" t="s">
-        <v>111</v>
+        <v>100</v>
+      </c>
+      <c r="B54" s="52"/>
+      <c r="C54" s="57" t="s">
+        <v>105</v>
       </c>
       <c r="D54" s="36"/>
       <c r="E54" s="36"/>
@@ -5032,30 +5028,30 @@
       </c>
       <c r="J54" s="15"/>
       <c r="K54" s="15"/>
-      <c r="L54" s="64"/>
-      <c r="M54" s="64"/>
-      <c r="N54" s="64"/>
-      <c r="O54" s="64"/>
-      <c r="P54" s="64"/>
-      <c r="Q54" s="64"/>
-      <c r="R54" s="64"/>
-      <c r="S54" s="64"/>
-      <c r="T54" s="64"/>
-      <c r="U54" s="64"/>
-      <c r="V54" s="64"/>
-      <c r="W54" s="64"/>
-      <c r="X54" s="64"/>
-      <c r="Y54" s="64"/>
-      <c r="Z54" s="64"/>
-      <c r="AA54" s="64"/>
+      <c r="L54" s="58"/>
+      <c r="M54" s="58"/>
+      <c r="N54" s="58"/>
+      <c r="O54" s="58"/>
+      <c r="P54" s="58"/>
+      <c r="Q54" s="58"/>
+      <c r="R54" s="58"/>
+      <c r="S54" s="58"/>
+      <c r="T54" s="58"/>
+      <c r="U54" s="58"/>
+      <c r="V54" s="58"/>
+      <c r="W54" s="58"/>
+      <c r="X54" s="58"/>
+      <c r="Y54" s="58"/>
+      <c r="Z54" s="58"/>
+      <c r="AA54" s="58"/>
     </row>
     <row r="55" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="B55" s="54"/>
-      <c r="C55" s="58" t="s">
-        <v>113</v>
+        <v>102</v>
+      </c>
+      <c r="B55" s="52"/>
+      <c r="C55" s="54" t="s">
+        <v>107</v>
       </c>
       <c r="D55" s="36"/>
       <c r="E55" s="36"/>
@@ -5070,30 +5066,30 @@
       </c>
       <c r="J55" s="15"/>
       <c r="K55" s="15"/>
-      <c r="L55" s="64"/>
-      <c r="M55" s="64"/>
-      <c r="N55" s="64"/>
-      <c r="O55" s="64"/>
-      <c r="P55" s="64"/>
-      <c r="Q55" s="64"/>
-      <c r="R55" s="64"/>
-      <c r="S55" s="64"/>
-      <c r="T55" s="64"/>
-      <c r="U55" s="64"/>
-      <c r="V55" s="64"/>
-      <c r="W55" s="64"/>
-      <c r="X55" s="64"/>
-      <c r="Y55" s="64"/>
-      <c r="Z55" s="64"/>
-      <c r="AA55" s="64"/>
+      <c r="L55" s="58"/>
+      <c r="M55" s="58"/>
+      <c r="N55" s="58"/>
+      <c r="O55" s="58"/>
+      <c r="P55" s="58"/>
+      <c r="Q55" s="58"/>
+      <c r="R55" s="58"/>
+      <c r="S55" s="58"/>
+      <c r="T55" s="58"/>
+      <c r="U55" s="58"/>
+      <c r="V55" s="58"/>
+      <c r="W55" s="58"/>
+      <c r="X55" s="58"/>
+      <c r="Y55" s="58"/>
+      <c r="Z55" s="58"/>
+      <c r="AA55" s="58"/>
     </row>
     <row r="56" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="B56" s="54"/>
-      <c r="C56" s="58" t="s">
-        <v>115</v>
+        <v>104</v>
+      </c>
+      <c r="B56" s="52"/>
+      <c r="C56" s="54" t="s">
+        <v>109</v>
       </c>
       <c r="D56" s="36"/>
       <c r="E56" s="36"/>
@@ -5108,34 +5104,34 @@
       </c>
       <c r="J56" s="15"/>
       <c r="K56" s="15"/>
-      <c r="L56" s="64"/>
-      <c r="M56" s="64"/>
-      <c r="N56" s="64"/>
-      <c r="O56" s="64"/>
-      <c r="P56" s="64"/>
-      <c r="Q56" s="64"/>
-      <c r="R56" s="64"/>
-      <c r="S56" s="64"/>
-      <c r="T56" s="64"/>
-      <c r="U56" s="64"/>
-      <c r="V56" s="64"/>
-      <c r="W56" s="64"/>
-      <c r="X56" s="64"/>
-      <c r="Y56" s="64"/>
-      <c r="Z56" s="64"/>
-      <c r="AA56" s="64"/>
+      <c r="L56" s="58"/>
+      <c r="M56" s="58"/>
+      <c r="N56" s="58"/>
+      <c r="O56" s="58"/>
+      <c r="P56" s="58"/>
+      <c r="Q56" s="58"/>
+      <c r="R56" s="58"/>
+      <c r="S56" s="58"/>
+      <c r="T56" s="58"/>
+      <c r="U56" s="58"/>
+      <c r="V56" s="58"/>
+      <c r="W56" s="58"/>
+      <c r="X56" s="58"/>
+      <c r="Y56" s="58"/>
+      <c r="Z56" s="58"/>
+      <c r="AA56" s="58"/>
     </row>
     <row r="57" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="B57" s="54"/>
-      <c r="C57" s="65" t="s">
-        <v>117</v>
-      </c>
-      <c r="D57" s="52"/>
-      <c r="E57" s="52"/>
-      <c r="F57" s="52"/>
+        <v>106</v>
+      </c>
+      <c r="B57" s="52"/>
+      <c r="C57" s="59" t="s">
+        <v>111</v>
+      </c>
+      <c r="D57" s="50"/>
+      <c r="E57" s="50"/>
+      <c r="F57" s="50"/>
       <c r="G57" s="29">
         <f t="shared" si="9"/>
         <v>0</v>
@@ -5146,34 +5142,34 @@
       </c>
       <c r="J57" s="15"/>
       <c r="K57" s="15"/>
-      <c r="L57" s="64"/>
-      <c r="M57" s="64"/>
-      <c r="N57" s="64"/>
-      <c r="O57" s="64"/>
-      <c r="P57" s="64"/>
-      <c r="Q57" s="64"/>
-      <c r="R57" s="64"/>
-      <c r="S57" s="64"/>
-      <c r="T57" s="64"/>
-      <c r="U57" s="64"/>
-      <c r="V57" s="64"/>
-      <c r="W57" s="64"/>
-      <c r="X57" s="64"/>
-      <c r="Y57" s="64"/>
-      <c r="Z57" s="64"/>
-      <c r="AA57" s="64"/>
+      <c r="L57" s="58"/>
+      <c r="M57" s="58"/>
+      <c r="N57" s="58"/>
+      <c r="O57" s="58"/>
+      <c r="P57" s="58"/>
+      <c r="Q57" s="58"/>
+      <c r="R57" s="58"/>
+      <c r="S57" s="58"/>
+      <c r="T57" s="58"/>
+      <c r="U57" s="58"/>
+      <c r="V57" s="58"/>
+      <c r="W57" s="58"/>
+      <c r="X57" s="58"/>
+      <c r="Y57" s="58"/>
+      <c r="Z57" s="58"/>
+      <c r="AA57" s="58"/>
     </row>
     <row r="58" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="B58" s="54"/>
-      <c r="C58" s="65" t="s">
-        <v>119</v>
-      </c>
-      <c r="D58" s="52"/>
-      <c r="E58" s="52"/>
-      <c r="F58" s="52"/>
+        <v>108</v>
+      </c>
+      <c r="B58" s="52"/>
+      <c r="C58" s="59" t="s">
+        <v>113</v>
+      </c>
+      <c r="D58" s="50"/>
+      <c r="E58" s="50"/>
+      <c r="F58" s="50"/>
       <c r="G58" s="29">
         <f t="shared" si="9"/>
         <v>0</v>
@@ -5184,34 +5180,34 @@
       </c>
       <c r="J58" s="15"/>
       <c r="K58" s="15"/>
-      <c r="L58" s="64"/>
-      <c r="M58" s="64"/>
-      <c r="N58" s="64"/>
-      <c r="O58" s="64"/>
-      <c r="P58" s="64"/>
-      <c r="Q58" s="64"/>
-      <c r="R58" s="64"/>
-      <c r="S58" s="64"/>
-      <c r="T58" s="64"/>
-      <c r="U58" s="64"/>
-      <c r="V58" s="64"/>
-      <c r="W58" s="64"/>
-      <c r="X58" s="64"/>
-      <c r="Y58" s="64"/>
-      <c r="Z58" s="64"/>
-      <c r="AA58" s="64"/>
+      <c r="L58" s="58"/>
+      <c r="M58" s="58"/>
+      <c r="N58" s="58"/>
+      <c r="O58" s="58"/>
+      <c r="P58" s="58"/>
+      <c r="Q58" s="58"/>
+      <c r="R58" s="58"/>
+      <c r="S58" s="58"/>
+      <c r="T58" s="58"/>
+      <c r="U58" s="58"/>
+      <c r="V58" s="58"/>
+      <c r="W58" s="58"/>
+      <c r="X58" s="58"/>
+      <c r="Y58" s="58"/>
+      <c r="Z58" s="58"/>
+      <c r="AA58" s="58"/>
     </row>
     <row r="59" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="B59" s="54"/>
-      <c r="C59" s="65" t="s">
-        <v>121</v>
-      </c>
-      <c r="D59" s="52"/>
-      <c r="E59" s="52"/>
-      <c r="F59" s="52"/>
+        <v>110</v>
+      </c>
+      <c r="B59" s="52"/>
+      <c r="C59" s="59" t="s">
+        <v>115</v>
+      </c>
+      <c r="D59" s="50"/>
+      <c r="E59" s="50"/>
+      <c r="F59" s="50"/>
       <c r="G59" s="29">
         <f t="shared" si="9"/>
         <v>0</v>
@@ -5222,32 +5218,32 @@
       </c>
       <c r="J59" s="15"/>
       <c r="K59" s="15"/>
-      <c r="L59" s="64"/>
-      <c r="M59" s="64"/>
-      <c r="N59" s="64"/>
-      <c r="O59" s="64"/>
-      <c r="P59" s="64"/>
-      <c r="Q59" s="64"/>
-      <c r="R59" s="64"/>
-      <c r="S59" s="64"/>
-      <c r="T59" s="64"/>
-      <c r="U59" s="64"/>
-      <c r="V59" s="64"/>
-      <c r="W59" s="64"/>
-      <c r="X59" s="64"/>
-      <c r="Y59" s="64"/>
-      <c r="Z59" s="64"/>
-      <c r="AA59" s="64"/>
+      <c r="L59" s="58"/>
+      <c r="M59" s="58"/>
+      <c r="N59" s="58"/>
+      <c r="O59" s="58"/>
+      <c r="P59" s="58"/>
+      <c r="Q59" s="58"/>
+      <c r="R59" s="58"/>
+      <c r="S59" s="58"/>
+      <c r="T59" s="58"/>
+      <c r="U59" s="58"/>
+      <c r="V59" s="58"/>
+      <c r="W59" s="58"/>
+      <c r="X59" s="58"/>
+      <c r="Y59" s="58"/>
+      <c r="Z59" s="58"/>
+      <c r="AA59" s="58"/>
     </row>
     <row r="60" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="B60" s="49">
+        <v>112</v>
+      </c>
+      <c r="B60" s="47">
         <v>27</v>
       </c>
       <c r="C60" s="35" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D60" s="36"/>
       <c r="E60" s="36"/>
@@ -5262,46 +5258,46 @@
       </c>
       <c r="J60" s="15"/>
       <c r="K60" s="15"/>
-      <c r="L60" s="64"/>
-      <c r="M60" s="64"/>
-      <c r="N60" s="64"/>
-      <c r="O60" s="64"/>
-      <c r="P60" s="64"/>
-      <c r="Q60" s="64"/>
-      <c r="R60" s="64"/>
-      <c r="S60" s="64"/>
-      <c r="T60" s="64"/>
-      <c r="U60" s="64"/>
-      <c r="V60" s="64"/>
-      <c r="W60" s="64"/>
-      <c r="X60" s="64"/>
-      <c r="Y60" s="64"/>
-      <c r="Z60" s="64"/>
-      <c r="AA60" s="64"/>
+      <c r="L60" s="58"/>
+      <c r="M60" s="58"/>
+      <c r="N60" s="58"/>
+      <c r="O60" s="58"/>
+      <c r="P60" s="58"/>
+      <c r="Q60" s="58"/>
+      <c r="R60" s="58"/>
+      <c r="S60" s="58"/>
+      <c r="T60" s="58"/>
+      <c r="U60" s="58"/>
+      <c r="V60" s="58"/>
+      <c r="W60" s="58"/>
+      <c r="X60" s="58"/>
+      <c r="Y60" s="58"/>
+      <c r="Z60" s="58"/>
+      <c r="AA60" s="58"/>
     </row>
     <row r="61" spans="1:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="B61" s="46" t="s">
-        <v>124</v>
-      </c>
-      <c r="C61" s="66" t="s">
-        <v>125</v>
-      </c>
-      <c r="D61" s="67">
+        <v>114</v>
+      </c>
+      <c r="B61" s="82" t="s">
+        <v>118</v>
+      </c>
+      <c r="C61" s="86" t="s">
+        <v>119</v>
+      </c>
+      <c r="D61" s="87">
         <f>D62+D63+D65+D66+D67</f>
         <v>0</v>
       </c>
-      <c r="E61" s="67">
-        <f t="shared" ref="D61:G61" si="10">E62+E63+E65+E66+E67</f>
+      <c r="E61" s="87">
+        <f t="shared" ref="E61:G61" si="10">E62+E63+E65+E66+E67</f>
         <v>0</v>
       </c>
-      <c r="F61" s="67">
+      <c r="F61" s="87">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G61" s="67">
+      <c r="G61" s="87">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
@@ -5330,17 +5326,17 @@
     </row>
     <row r="62" spans="1:27" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="B62" s="68">
+        <v>116</v>
+      </c>
+      <c r="B62" s="79">
         <v>1</v>
       </c>
-      <c r="C62" s="60" t="s">
-        <v>62</v>
-      </c>
-      <c r="D62" s="69"/>
-      <c r="E62" s="69"/>
-      <c r="F62" s="69"/>
+      <c r="C62" s="85" t="s">
+        <v>58</v>
+      </c>
+      <c r="D62" s="88"/>
+      <c r="E62" s="88"/>
+      <c r="F62" s="88"/>
       <c r="G62" s="19">
         <f t="shared" ref="G62:G67" si="11">F62-D62</f>
         <v>0</v>
@@ -5370,17 +5366,17 @@
     </row>
     <row r="63" spans="1:27" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="B63" s="68">
+        <v>125</v>
+      </c>
+      <c r="B63" s="79">
         <v>2</v>
       </c>
-      <c r="C63" s="70" t="s">
-        <v>126</v>
-      </c>
-      <c r="D63" s="69"/>
-      <c r="E63" s="69"/>
-      <c r="F63" s="69"/>
+      <c r="C63" s="89" t="s">
+        <v>120</v>
+      </c>
+      <c r="D63" s="88"/>
+      <c r="E63" s="88"/>
+      <c r="F63" s="88"/>
       <c r="G63" s="19">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -5410,17 +5406,17 @@
     </row>
     <row r="64" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="B64" s="71" t="s">
-        <v>33</v>
-      </c>
-      <c r="C64" s="72" t="s">
         <v>127</v>
       </c>
-      <c r="D64" s="69"/>
-      <c r="E64" s="69"/>
-      <c r="F64" s="69"/>
+      <c r="B64" s="90" t="s">
+        <v>29</v>
+      </c>
+      <c r="C64" s="91" t="s">
+        <v>121</v>
+      </c>
+      <c r="D64" s="88"/>
+      <c r="E64" s="88"/>
+      <c r="F64" s="88"/>
       <c r="G64" s="19">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -5450,17 +5446,17 @@
     </row>
     <row r="65" spans="1:27" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="B65" s="68">
+        <v>128</v>
+      </c>
+      <c r="B65" s="79">
         <v>3</v>
       </c>
-      <c r="C65" s="60" t="s">
-        <v>128</v>
-      </c>
-      <c r="D65" s="69"/>
-      <c r="E65" s="69"/>
-      <c r="F65" s="69"/>
+      <c r="C65" s="85" t="s">
+        <v>122</v>
+      </c>
+      <c r="D65" s="88"/>
+      <c r="E65" s="88"/>
+      <c r="F65" s="88"/>
       <c r="G65" s="19">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -5490,17 +5486,17 @@
     </row>
     <row r="66" spans="1:27" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="B66" s="68">
+        <v>129</v>
+      </c>
+      <c r="B66" s="79">
         <v>4</v>
       </c>
-      <c r="C66" s="70" t="s">
-        <v>129</v>
-      </c>
-      <c r="D66" s="69"/>
-      <c r="E66" s="69"/>
-      <c r="F66" s="69"/>
+      <c r="C66" s="89" t="s">
+        <v>123</v>
+      </c>
+      <c r="D66" s="88"/>
+      <c r="E66" s="88"/>
+      <c r="F66" s="88"/>
       <c r="G66" s="19">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -5530,17 +5526,17 @@
     </row>
     <row r="67" spans="1:27" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="B67" s="68">
+        <v>130</v>
+      </c>
+      <c r="B67" s="79">
         <v>5</v>
       </c>
-      <c r="C67" s="70" t="s">
-        <v>130</v>
-      </c>
-      <c r="D67" s="69"/>
-      <c r="E67" s="69"/>
-      <c r="F67" s="69"/>
+      <c r="C67" s="89" t="s">
+        <v>124</v>
+      </c>
+      <c r="D67" s="88"/>
+      <c r="E67" s="88"/>
+      <c r="F67" s="88"/>
       <c r="G67" s="19">
         <f t="shared" si="11"/>
         <v>0</v>
@@ -5570,28 +5566,28 @@
     </row>
     <row r="68" spans="1:27" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="16" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B68" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="C68" s="73" t="s">
-        <v>132</v>
+        <v>35</v>
+      </c>
+      <c r="C68" s="60" t="s">
+        <v>126</v>
       </c>
       <c r="D68" s="41">
-        <f>SUM(D69:D93)-D74-D76-D87-D88</f>
+        <f>SUM(D69:D94)-D74-D76-D87-D88</f>
         <v>0</v>
       </c>
       <c r="E68" s="41">
-        <f>SUM(E69:E93)-E74-E76-E87-E88</f>
+        <f>SUM(E69:E94)-E74-E76-E87-E88</f>
         <v>0</v>
       </c>
       <c r="F68" s="41">
-        <f>SUM(F69:F93)-F74-F76-F87-F88</f>
+        <f>SUM(F69:F94)-F74-F76-F87-F88</f>
         <v>0</v>
       </c>
       <c r="G68" s="41">
-        <f>SUM(G69:G93)-G74-G76-G87-G88</f>
+        <f>SUM(G69:G94)-G74-G76-G87-G88</f>
         <v>0</v>
       </c>
       <c r="H68" s="25">
@@ -5619,9 +5615,9 @@
     </row>
     <row r="69" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="16" t="s">
-        <v>141</v>
-      </c>
-      <c r="B69" s="49">
+        <v>135</v>
+      </c>
+      <c r="B69" s="47">
         <v>1</v>
       </c>
       <c r="C69" s="35" t="str">
@@ -5632,7 +5628,7 @@
       <c r="E69" s="36"/>
       <c r="F69" s="36"/>
       <c r="G69" s="29">
-        <f t="shared" ref="G69:G96" si="12">F69-D69</f>
+        <f t="shared" ref="G69:G97" si="12">F69-D69</f>
         <v>0</v>
       </c>
       <c r="H69" s="25">
@@ -5641,32 +5637,32 @@
       </c>
       <c r="J69" s="15"/>
       <c r="K69" s="15"/>
-      <c r="L69" s="74"/>
-      <c r="M69" s="74"/>
-      <c r="N69" s="74"/>
-      <c r="O69" s="74"/>
-      <c r="P69" s="74"/>
-      <c r="Q69" s="74"/>
-      <c r="R69" s="74"/>
-      <c r="S69" s="74"/>
-      <c r="T69" s="74"/>
-      <c r="U69" s="74"/>
-      <c r="V69" s="74"/>
-      <c r="W69" s="74"/>
-      <c r="X69" s="74"/>
-      <c r="Y69" s="74"/>
-      <c r="Z69" s="74"/>
-      <c r="AA69" s="74"/>
+      <c r="L69" s="61"/>
+      <c r="M69" s="61"/>
+      <c r="N69" s="61"/>
+      <c r="O69" s="61"/>
+      <c r="P69" s="61"/>
+      <c r="Q69" s="61"/>
+      <c r="R69" s="61"/>
+      <c r="S69" s="61"/>
+      <c r="T69" s="61"/>
+      <c r="U69" s="61"/>
+      <c r="V69" s="61"/>
+      <c r="W69" s="61"/>
+      <c r="X69" s="61"/>
+      <c r="Y69" s="61"/>
+      <c r="Z69" s="61"/>
+      <c r="AA69" s="61"/>
     </row>
     <row r="70" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="16" t="s">
-        <v>142</v>
-      </c>
-      <c r="B70" s="49">
+        <v>136</v>
+      </c>
+      <c r="B70" s="47">
         <v>2</v>
       </c>
-      <c r="C70" s="50" t="s">
-        <v>54</v>
+      <c r="C70" s="48" t="s">
+        <v>50</v>
       </c>
       <c r="D70" s="36"/>
       <c r="E70" s="36"/>
@@ -5681,37 +5677,37 @@
       </c>
       <c r="J70" s="15"/>
       <c r="K70" s="15"/>
-      <c r="L70" s="74"/>
-      <c r="M70" s="74"/>
-      <c r="N70" s="74"/>
-      <c r="O70" s="74"/>
-      <c r="P70" s="74"/>
-      <c r="Q70" s="74"/>
-      <c r="R70" s="74"/>
-      <c r="S70" s="74"/>
-      <c r="T70" s="74"/>
-      <c r="U70" s="74"/>
-      <c r="V70" s="74"/>
-      <c r="W70" s="74"/>
-      <c r="X70" s="74"/>
-      <c r="Y70" s="74"/>
-      <c r="Z70" s="74"/>
-      <c r="AA70" s="74"/>
+      <c r="L70" s="61"/>
+      <c r="M70" s="61"/>
+      <c r="N70" s="61"/>
+      <c r="O70" s="61"/>
+      <c r="P70" s="61"/>
+      <c r="Q70" s="61"/>
+      <c r="R70" s="61"/>
+      <c r="S70" s="61"/>
+      <c r="T70" s="61"/>
+      <c r="U70" s="61"/>
+      <c r="V70" s="61"/>
+      <c r="W70" s="61"/>
+      <c r="X70" s="61"/>
+      <c r="Y70" s="61"/>
+      <c r="Z70" s="61"/>
+      <c r="AA70" s="61"/>
     </row>
     <row r="71" spans="1:27" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="B71" s="49">
+        <v>137</v>
+      </c>
+      <c r="B71" s="47">
         <v>3</v>
       </c>
-      <c r="C71" s="51" t="str">
+      <c r="C71" s="49" t="str">
         <f>C27</f>
         <v>Cho vay hộ mới thoát nghèo theo Quyết định số 28/2015/QĐ-TTg</v>
       </c>
-      <c r="D71" s="52"/>
-      <c r="E71" s="52"/>
-      <c r="F71" s="52"/>
+      <c r="D71" s="50"/>
+      <c r="E71" s="50"/>
+      <c r="F71" s="50"/>
       <c r="G71" s="29">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -5722,36 +5718,36 @@
       </c>
       <c r="J71" s="15"/>
       <c r="K71" s="15"/>
-      <c r="L71" s="74"/>
-      <c r="M71" s="74"/>
-      <c r="N71" s="74"/>
-      <c r="O71" s="74"/>
-      <c r="P71" s="74"/>
-      <c r="Q71" s="74"/>
-      <c r="R71" s="74"/>
-      <c r="S71" s="74"/>
-      <c r="T71" s="74"/>
-      <c r="U71" s="74"/>
-      <c r="V71" s="74"/>
-      <c r="W71" s="74"/>
-      <c r="X71" s="74"/>
-      <c r="Y71" s="74"/>
-      <c r="Z71" s="74"/>
-      <c r="AA71" s="74"/>
+      <c r="L71" s="61"/>
+      <c r="M71" s="61"/>
+      <c r="N71" s="61"/>
+      <c r="O71" s="61"/>
+      <c r="P71" s="61"/>
+      <c r="Q71" s="61"/>
+      <c r="R71" s="61"/>
+      <c r="S71" s="61"/>
+      <c r="T71" s="61"/>
+      <c r="U71" s="61"/>
+      <c r="V71" s="61"/>
+      <c r="W71" s="61"/>
+      <c r="X71" s="61"/>
+      <c r="Y71" s="61"/>
+      <c r="Z71" s="61"/>
+      <c r="AA71" s="61"/>
     </row>
     <row r="72" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="B72" s="49">
+        <v>139</v>
+      </c>
+      <c r="B72" s="47">
         <v>4</v>
       </c>
-      <c r="C72" s="51" t="s">
-        <v>137</v>
-      </c>
-      <c r="D72" s="52"/>
-      <c r="E72" s="52"/>
-      <c r="F72" s="52"/>
+      <c r="C72" s="49" t="s">
+        <v>131</v>
+      </c>
+      <c r="D72" s="50"/>
+      <c r="E72" s="50"/>
+      <c r="F72" s="50"/>
       <c r="G72" s="29">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -5762,32 +5758,32 @@
       </c>
       <c r="J72" s="15"/>
       <c r="K72" s="15"/>
-      <c r="L72" s="74"/>
-      <c r="M72" s="74"/>
-      <c r="N72" s="74"/>
-      <c r="O72" s="74"/>
-      <c r="P72" s="74"/>
-      <c r="Q72" s="74"/>
-      <c r="R72" s="74"/>
-      <c r="S72" s="74"/>
-      <c r="T72" s="74"/>
-      <c r="U72" s="74"/>
-      <c r="V72" s="74"/>
-      <c r="W72" s="74"/>
-      <c r="X72" s="74"/>
-      <c r="Y72" s="74"/>
-      <c r="Z72" s="74"/>
-      <c r="AA72" s="74"/>
+      <c r="L72" s="61"/>
+      <c r="M72" s="61"/>
+      <c r="N72" s="61"/>
+      <c r="O72" s="61"/>
+      <c r="P72" s="61"/>
+      <c r="Q72" s="61"/>
+      <c r="R72" s="61"/>
+      <c r="S72" s="61"/>
+      <c r="T72" s="61"/>
+      <c r="U72" s="61"/>
+      <c r="V72" s="61"/>
+      <c r="W72" s="61"/>
+      <c r="X72" s="61"/>
+      <c r="Y72" s="61"/>
+      <c r="Z72" s="61"/>
+      <c r="AA72" s="61"/>
     </row>
     <row r="73" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="B73" s="49">
+        <v>140</v>
+      </c>
+      <c r="B73" s="47">
         <v>5</v>
       </c>
-      <c r="C73" s="53" t="s">
-        <v>139</v>
+      <c r="C73" s="51" t="s">
+        <v>133</v>
       </c>
       <c r="D73" s="36"/>
       <c r="E73" s="36"/>
@@ -5802,36 +5798,36 @@
       </c>
       <c r="J73" s="15"/>
       <c r="K73" s="15"/>
-      <c r="L73" s="74"/>
-      <c r="M73" s="74"/>
-      <c r="N73" s="74"/>
-      <c r="O73" s="74"/>
-      <c r="P73" s="74"/>
-      <c r="Q73" s="74"/>
-      <c r="R73" s="74"/>
-      <c r="S73" s="74"/>
-      <c r="T73" s="74"/>
-      <c r="U73" s="74"/>
-      <c r="V73" s="74"/>
-      <c r="W73" s="74"/>
-      <c r="X73" s="74"/>
-      <c r="Y73" s="74"/>
-      <c r="Z73" s="74"/>
-      <c r="AA73" s="74"/>
+      <c r="L73" s="61"/>
+      <c r="M73" s="61"/>
+      <c r="N73" s="61"/>
+      <c r="O73" s="61"/>
+      <c r="P73" s="61"/>
+      <c r="Q73" s="61"/>
+      <c r="R73" s="61"/>
+      <c r="S73" s="61"/>
+      <c r="T73" s="61"/>
+      <c r="U73" s="61"/>
+      <c r="V73" s="61"/>
+      <c r="W73" s="61"/>
+      <c r="X73" s="61"/>
+      <c r="Y73" s="61"/>
+      <c r="Z73" s="61"/>
+      <c r="AA73" s="61"/>
     </row>
     <row r="74" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="B74" s="75" t="s">
-        <v>33</v>
-      </c>
-      <c r="C74" s="76" t="s">
-        <v>140</v>
-      </c>
-      <c r="D74" s="52"/>
-      <c r="E74" s="52"/>
-      <c r="F74" s="52"/>
+        <v>142</v>
+      </c>
+      <c r="B74" s="62" t="s">
+        <v>29</v>
+      </c>
+      <c r="C74" s="92" t="s">
+        <v>134</v>
+      </c>
+      <c r="D74" s="50"/>
+      <c r="E74" s="50"/>
+      <c r="F74" s="50"/>
       <c r="G74" s="29">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -5842,37 +5838,37 @@
       </c>
       <c r="J74" s="15"/>
       <c r="K74" s="15"/>
-      <c r="L74" s="74"/>
-      <c r="M74" s="74"/>
-      <c r="N74" s="74"/>
-      <c r="O74" s="74"/>
-      <c r="P74" s="74"/>
-      <c r="Q74" s="74"/>
-      <c r="R74" s="74"/>
-      <c r="S74" s="74"/>
-      <c r="T74" s="74"/>
-      <c r="U74" s="74"/>
-      <c r="V74" s="74"/>
-      <c r="W74" s="74"/>
-      <c r="X74" s="74"/>
-      <c r="Y74" s="74"/>
-      <c r="Z74" s="74"/>
-      <c r="AA74" s="74"/>
+      <c r="L74" s="61"/>
+      <c r="M74" s="61"/>
+      <c r="N74" s="61"/>
+      <c r="O74" s="61"/>
+      <c r="P74" s="61"/>
+      <c r="Q74" s="61"/>
+      <c r="R74" s="61"/>
+      <c r="S74" s="61"/>
+      <c r="T74" s="61"/>
+      <c r="U74" s="61"/>
+      <c r="V74" s="61"/>
+      <c r="W74" s="61"/>
+      <c r="X74" s="61"/>
+      <c r="Y74" s="61"/>
+      <c r="Z74" s="61"/>
+      <c r="AA74" s="61"/>
     </row>
     <row r="75" spans="1:27" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="B75" s="49">
+        <v>143</v>
+      </c>
+      <c r="B75" s="47">
         <v>6</v>
       </c>
-      <c r="C75" s="51" t="str">
+      <c r="C75" s="49" t="str">
         <f>C31</f>
         <v>Cho vay người lao động đi làm việc ở nước ngoài theo Quyết định số 365/QĐ-NHNN, Quyết định số 1465/QĐ-TTg, Quyết định số 63/2015/QĐ-TTg và Nghị định số 61/2015/NĐ-CP</v>
       </c>
-      <c r="D75" s="52"/>
-      <c r="E75" s="52"/>
-      <c r="F75" s="52"/>
+      <c r="D75" s="50"/>
+      <c r="E75" s="50"/>
+      <c r="F75" s="50"/>
       <c r="G75" s="29">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -5883,36 +5879,36 @@
       </c>
       <c r="J75" s="15"/>
       <c r="K75" s="15"/>
-      <c r="L75" s="74"/>
-      <c r="M75" s="74"/>
-      <c r="N75" s="74"/>
-      <c r="O75" s="74"/>
-      <c r="P75" s="74"/>
-      <c r="Q75" s="74"/>
-      <c r="R75" s="74"/>
-      <c r="S75" s="74"/>
-      <c r="T75" s="74"/>
-      <c r="U75" s="74"/>
-      <c r="V75" s="74"/>
-      <c r="W75" s="74"/>
-      <c r="X75" s="74"/>
-      <c r="Y75" s="74"/>
-      <c r="Z75" s="74"/>
-      <c r="AA75" s="74"/>
+      <c r="L75" s="61"/>
+      <c r="M75" s="61"/>
+      <c r="N75" s="61"/>
+      <c r="O75" s="61"/>
+      <c r="P75" s="61"/>
+      <c r="Q75" s="61"/>
+      <c r="R75" s="61"/>
+      <c r="S75" s="61"/>
+      <c r="T75" s="61"/>
+      <c r="U75" s="61"/>
+      <c r="V75" s="61"/>
+      <c r="W75" s="61"/>
+      <c r="X75" s="61"/>
+      <c r="Y75" s="61"/>
+      <c r="Z75" s="61"/>
+      <c r="AA75" s="61"/>
     </row>
     <row r="76" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="B76" s="54" t="s">
-        <v>33</v>
-      </c>
-      <c r="C76" s="55" t="s">
-        <v>66</v>
-      </c>
-      <c r="D76" s="52"/>
-      <c r="E76" s="52"/>
-      <c r="F76" s="52"/>
+        <v>145</v>
+      </c>
+      <c r="B76" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="C76" s="53" t="s">
+        <v>62</v>
+      </c>
+      <c r="D76" s="50"/>
+      <c r="E76" s="50"/>
+      <c r="F76" s="50"/>
       <c r="G76" s="29">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -5923,36 +5919,36 @@
       </c>
       <c r="J76" s="15"/>
       <c r="K76" s="15"/>
-      <c r="L76" s="74"/>
-      <c r="M76" s="74"/>
-      <c r="N76" s="74"/>
-      <c r="O76" s="74"/>
-      <c r="P76" s="74"/>
-      <c r="Q76" s="74"/>
-      <c r="R76" s="74"/>
-      <c r="S76" s="74"/>
-      <c r="T76" s="74"/>
-      <c r="U76" s="74"/>
-      <c r="V76" s="74"/>
-      <c r="W76" s="74"/>
-      <c r="X76" s="74"/>
-      <c r="Y76" s="74"/>
-      <c r="Z76" s="74"/>
-      <c r="AA76" s="74"/>
+      <c r="L76" s="61"/>
+      <c r="M76" s="61"/>
+      <c r="N76" s="61"/>
+      <c r="O76" s="61"/>
+      <c r="P76" s="61"/>
+      <c r="Q76" s="61"/>
+      <c r="R76" s="61"/>
+      <c r="S76" s="61"/>
+      <c r="T76" s="61"/>
+      <c r="U76" s="61"/>
+      <c r="V76" s="61"/>
+      <c r="W76" s="61"/>
+      <c r="X76" s="61"/>
+      <c r="Y76" s="61"/>
+      <c r="Z76" s="61"/>
+      <c r="AA76" s="61"/>
     </row>
     <row r="77" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="16" t="s">
-        <v>152</v>
-      </c>
-      <c r="B77" s="49">
+        <v>146</v>
+      </c>
+      <c r="B77" s="47">
         <v>7</v>
       </c>
-      <c r="C77" s="51" t="s">
-        <v>144</v>
-      </c>
-      <c r="D77" s="52"/>
-      <c r="E77" s="52"/>
-      <c r="F77" s="52"/>
+      <c r="C77" s="49" t="s">
+        <v>138</v>
+      </c>
+      <c r="D77" s="50"/>
+      <c r="E77" s="50"/>
+      <c r="F77" s="50"/>
       <c r="G77" s="29">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -5963,37 +5959,37 @@
       </c>
       <c r="J77" s="15"/>
       <c r="K77" s="15"/>
-      <c r="L77" s="74"/>
-      <c r="M77" s="74"/>
-      <c r="N77" s="74"/>
-      <c r="O77" s="74"/>
-      <c r="P77" s="74"/>
-      <c r="Q77" s="74"/>
-      <c r="R77" s="74"/>
-      <c r="S77" s="74"/>
-      <c r="T77" s="74"/>
-      <c r="U77" s="74"/>
-      <c r="V77" s="74"/>
-      <c r="W77" s="74"/>
-      <c r="X77" s="74"/>
-      <c r="Y77" s="74"/>
-      <c r="Z77" s="74"/>
-      <c r="AA77" s="74"/>
+      <c r="L77" s="61"/>
+      <c r="M77" s="61"/>
+      <c r="N77" s="61"/>
+      <c r="O77" s="61"/>
+      <c r="P77" s="61"/>
+      <c r="Q77" s="61"/>
+      <c r="R77" s="61"/>
+      <c r="S77" s="61"/>
+      <c r="T77" s="61"/>
+      <c r="U77" s="61"/>
+      <c r="V77" s="61"/>
+      <c r="W77" s="61"/>
+      <c r="X77" s="61"/>
+      <c r="Y77" s="61"/>
+      <c r="Z77" s="61"/>
+      <c r="AA77" s="61"/>
     </row>
     <row r="78" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="B78" s="49">
+        <v>147</v>
+      </c>
+      <c r="B78" s="47">
         <v>8</v>
       </c>
-      <c r="C78" s="51" t="str">
+      <c r="C78" s="49" t="str">
         <f>C34</f>
         <v>Cho vay Chương trình NS&amp;VSMT nông thôn (QĐ 62/2004/QĐ-TTg)</v>
       </c>
-      <c r="D78" s="52"/>
-      <c r="E78" s="52"/>
-      <c r="F78" s="52"/>
+      <c r="D78" s="50"/>
+      <c r="E78" s="50"/>
+      <c r="F78" s="50"/>
       <c r="G78" s="29">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -6004,36 +6000,36 @@
       </c>
       <c r="J78" s="15"/>
       <c r="K78" s="15"/>
-      <c r="L78" s="74"/>
-      <c r="M78" s="74"/>
-      <c r="N78" s="74"/>
-      <c r="O78" s="74"/>
-      <c r="P78" s="74"/>
-      <c r="Q78" s="74"/>
-      <c r="R78" s="74"/>
-      <c r="S78" s="74"/>
-      <c r="T78" s="74"/>
-      <c r="U78" s="74"/>
-      <c r="V78" s="74"/>
-      <c r="W78" s="74"/>
-      <c r="X78" s="74"/>
-      <c r="Y78" s="74"/>
-      <c r="Z78" s="74"/>
-      <c r="AA78" s="74"/>
+      <c r="L78" s="61"/>
+      <c r="M78" s="61"/>
+      <c r="N78" s="61"/>
+      <c r="O78" s="61"/>
+      <c r="P78" s="61"/>
+      <c r="Q78" s="61"/>
+      <c r="R78" s="61"/>
+      <c r="S78" s="61"/>
+      <c r="T78" s="61"/>
+      <c r="U78" s="61"/>
+      <c r="V78" s="61"/>
+      <c r="W78" s="61"/>
+      <c r="X78" s="61"/>
+      <c r="Y78" s="61"/>
+      <c r="Z78" s="61"/>
+      <c r="AA78" s="61"/>
     </row>
     <row r="79" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="B79" s="49">
+        <v>149</v>
+      </c>
+      <c r="B79" s="47">
         <v>9</v>
       </c>
-      <c r="C79" s="51" t="s">
-        <v>147</v>
-      </c>
-      <c r="D79" s="52"/>
-      <c r="E79" s="52"/>
-      <c r="F79" s="52"/>
+      <c r="C79" s="49" t="s">
+        <v>141</v>
+      </c>
+      <c r="D79" s="50"/>
+      <c r="E79" s="50"/>
+      <c r="F79" s="50"/>
       <c r="G79" s="29">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -6044,37 +6040,37 @@
       </c>
       <c r="J79" s="15"/>
       <c r="K79" s="15"/>
-      <c r="L79" s="74"/>
-      <c r="M79" s="74"/>
-      <c r="N79" s="74"/>
-      <c r="O79" s="74"/>
-      <c r="P79" s="74"/>
-      <c r="Q79" s="74"/>
-      <c r="R79" s="74"/>
-      <c r="S79" s="74"/>
-      <c r="T79" s="74"/>
-      <c r="U79" s="74"/>
-      <c r="V79" s="74"/>
-      <c r="W79" s="74"/>
-      <c r="X79" s="74"/>
-      <c r="Y79" s="74"/>
-      <c r="Z79" s="74"/>
-      <c r="AA79" s="74"/>
+      <c r="L79" s="61"/>
+      <c r="M79" s="61"/>
+      <c r="N79" s="61"/>
+      <c r="O79" s="61"/>
+      <c r="P79" s="61"/>
+      <c r="Q79" s="61"/>
+      <c r="R79" s="61"/>
+      <c r="S79" s="61"/>
+      <c r="T79" s="61"/>
+      <c r="U79" s="61"/>
+      <c r="V79" s="61"/>
+      <c r="W79" s="61"/>
+      <c r="X79" s="61"/>
+      <c r="Y79" s="61"/>
+      <c r="Z79" s="61"/>
+      <c r="AA79" s="61"/>
     </row>
     <row r="80" spans="1:27" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="B80" s="49">
+        <v>150</v>
+      </c>
+      <c r="B80" s="47">
         <v>10</v>
       </c>
-      <c r="C80" s="51" t="str">
+      <c r="C80" s="49" t="str">
         <f>C36</f>
         <v>Cho vay mua trả chậm nhà ở vùng ĐBSCL và Tây Nguyên</v>
       </c>
-      <c r="D80" s="52"/>
-      <c r="E80" s="52"/>
-      <c r="F80" s="52"/>
+      <c r="D80" s="50"/>
+      <c r="E80" s="50"/>
+      <c r="F80" s="50"/>
       <c r="G80" s="29">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -6085,36 +6081,36 @@
       </c>
       <c r="J80" s="15"/>
       <c r="K80" s="15"/>
-      <c r="L80" s="74"/>
-      <c r="M80" s="74"/>
-      <c r="N80" s="74"/>
-      <c r="O80" s="74"/>
-      <c r="P80" s="74"/>
-      <c r="Q80" s="74"/>
-      <c r="R80" s="74"/>
-      <c r="S80" s="74"/>
-      <c r="T80" s="74"/>
-      <c r="U80" s="74"/>
-      <c r="V80" s="74"/>
-      <c r="W80" s="74"/>
-      <c r="X80" s="74"/>
-      <c r="Y80" s="74"/>
-      <c r="Z80" s="74"/>
-      <c r="AA80" s="74"/>
+      <c r="L80" s="61"/>
+      <c r="M80" s="61"/>
+      <c r="N80" s="61"/>
+      <c r="O80" s="61"/>
+      <c r="P80" s="61"/>
+      <c r="Q80" s="61"/>
+      <c r="R80" s="61"/>
+      <c r="S80" s="61"/>
+      <c r="T80" s="61"/>
+      <c r="U80" s="61"/>
+      <c r="V80" s="61"/>
+      <c r="W80" s="61"/>
+      <c r="X80" s="61"/>
+      <c r="Y80" s="61"/>
+      <c r="Z80" s="61"/>
+      <c r="AA80" s="61"/>
     </row>
     <row r="81" spans="1:27" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="B81" s="49">
+        <v>151</v>
+      </c>
+      <c r="B81" s="47">
         <v>11</v>
       </c>
-      <c r="C81" s="51" t="s">
-        <v>150</v>
-      </c>
-      <c r="D81" s="52"/>
-      <c r="E81" s="52"/>
-      <c r="F81" s="52"/>
+      <c r="C81" s="49" t="s">
+        <v>144</v>
+      </c>
+      <c r="D81" s="50"/>
+      <c r="E81" s="50"/>
+      <c r="F81" s="50"/>
       <c r="G81" s="29">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -6125,36 +6121,36 @@
       </c>
       <c r="J81" s="15"/>
       <c r="K81" s="15"/>
-      <c r="L81" s="74"/>
-      <c r="M81" s="74"/>
-      <c r="N81" s="74"/>
-      <c r="O81" s="74"/>
-      <c r="P81" s="74"/>
-      <c r="Q81" s="74"/>
-      <c r="R81" s="74"/>
-      <c r="S81" s="74"/>
-      <c r="T81" s="74"/>
-      <c r="U81" s="74"/>
-      <c r="V81" s="74"/>
-      <c r="W81" s="74"/>
-      <c r="X81" s="74"/>
-      <c r="Y81" s="74"/>
-      <c r="Z81" s="74"/>
-      <c r="AA81" s="74"/>
+      <c r="L81" s="61"/>
+      <c r="M81" s="61"/>
+      <c r="N81" s="61"/>
+      <c r="O81" s="61"/>
+      <c r="P81" s="61"/>
+      <c r="Q81" s="61"/>
+      <c r="R81" s="61"/>
+      <c r="S81" s="61"/>
+      <c r="T81" s="61"/>
+      <c r="U81" s="61"/>
+      <c r="V81" s="61"/>
+      <c r="W81" s="61"/>
+      <c r="X81" s="61"/>
+      <c r="Y81" s="61"/>
+      <c r="Z81" s="61"/>
+      <c r="AA81" s="61"/>
     </row>
     <row r="82" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="B82" s="49">
+        <v>152</v>
+      </c>
+      <c r="B82" s="47">
         <v>12</v>
       </c>
-      <c r="C82" s="51" t="s">
-        <v>78</v>
-      </c>
-      <c r="D82" s="52"/>
-      <c r="E82" s="52"/>
-      <c r="F82" s="52"/>
+      <c r="C82" s="49" t="s">
+        <v>74</v>
+      </c>
+      <c r="D82" s="50"/>
+      <c r="E82" s="50"/>
+      <c r="F82" s="50"/>
       <c r="G82" s="29">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -6165,36 +6161,36 @@
       </c>
       <c r="J82" s="15"/>
       <c r="K82" s="15"/>
-      <c r="L82" s="74"/>
-      <c r="M82" s="74"/>
-      <c r="N82" s="74"/>
-      <c r="O82" s="74"/>
-      <c r="P82" s="74"/>
-      <c r="Q82" s="74"/>
-      <c r="R82" s="74"/>
-      <c r="S82" s="74"/>
-      <c r="T82" s="74"/>
-      <c r="U82" s="74"/>
-      <c r="V82" s="74"/>
-      <c r="W82" s="74"/>
-      <c r="X82" s="74"/>
-      <c r="Y82" s="74"/>
-      <c r="Z82" s="74"/>
-      <c r="AA82" s="74"/>
+      <c r="L82" s="61"/>
+      <c r="M82" s="61"/>
+      <c r="N82" s="61"/>
+      <c r="O82" s="61"/>
+      <c r="P82" s="61"/>
+      <c r="Q82" s="61"/>
+      <c r="R82" s="61"/>
+      <c r="S82" s="61"/>
+      <c r="T82" s="61"/>
+      <c r="U82" s="61"/>
+      <c r="V82" s="61"/>
+      <c r="W82" s="61"/>
+      <c r="X82" s="61"/>
+      <c r="Y82" s="61"/>
+      <c r="Z82" s="61"/>
+      <c r="AA82" s="61"/>
     </row>
     <row r="83" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="B83" s="49">
+        <v>153</v>
+      </c>
+      <c r="B83" s="47">
         <v>13</v>
       </c>
       <c r="C83" s="35" t="s">
-        <v>154</v>
-      </c>
-      <c r="D83" s="52"/>
-      <c r="E83" s="52"/>
-      <c r="F83" s="52"/>
+        <v>148</v>
+      </c>
+      <c r="D83" s="50"/>
+      <c r="E83" s="50"/>
+      <c r="F83" s="50"/>
       <c r="G83" s="29">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -6205,37 +6201,37 @@
       </c>
       <c r="J83" s="15"/>
       <c r="K83" s="15"/>
-      <c r="L83" s="77"/>
-      <c r="M83" s="77"/>
-      <c r="N83" s="77"/>
-      <c r="O83" s="77"/>
-      <c r="P83" s="77"/>
-      <c r="Q83" s="77"/>
-      <c r="R83" s="77"/>
-      <c r="S83" s="77"/>
-      <c r="T83" s="77"/>
-      <c r="U83" s="77"/>
-      <c r="V83" s="77"/>
-      <c r="W83" s="77"/>
-      <c r="X83" s="74"/>
-      <c r="Y83" s="74"/>
-      <c r="Z83" s="74"/>
-      <c r="AA83" s="74"/>
+      <c r="L83" s="63"/>
+      <c r="M83" s="63"/>
+      <c r="N83" s="63"/>
+      <c r="O83" s="63"/>
+      <c r="P83" s="63"/>
+      <c r="Q83" s="63"/>
+      <c r="R83" s="63"/>
+      <c r="S83" s="63"/>
+      <c r="T83" s="63"/>
+      <c r="U83" s="63"/>
+      <c r="V83" s="63"/>
+      <c r="W83" s="63"/>
+      <c r="X83" s="61"/>
+      <c r="Y83" s="61"/>
+      <c r="Z83" s="61"/>
+      <c r="AA83" s="61"/>
     </row>
     <row r="84" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="B84" s="49">
+        <v>154</v>
+      </c>
+      <c r="B84" s="47">
         <v>14</v>
       </c>
-      <c r="C84" s="51" t="str">
+      <c r="C84" s="49" t="str">
         <f>C41</f>
         <v>Cho vay hỗ trợ hộ nghèo về nhà ở (QĐ 167/2008/QĐ-TTg)</v>
       </c>
-      <c r="D84" s="52"/>
-      <c r="E84" s="52"/>
-      <c r="F84" s="52"/>
+      <c r="D84" s="50"/>
+      <c r="E84" s="50"/>
+      <c r="F84" s="50"/>
       <c r="G84" s="29">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -6246,37 +6242,37 @@
       </c>
       <c r="J84" s="15"/>
       <c r="K84" s="15"/>
-      <c r="L84" s="77"/>
-      <c r="M84" s="77"/>
-      <c r="N84" s="77"/>
-      <c r="O84" s="77"/>
-      <c r="P84" s="77"/>
-      <c r="Q84" s="77"/>
-      <c r="R84" s="77"/>
-      <c r="S84" s="77"/>
-      <c r="T84" s="77"/>
-      <c r="U84" s="77"/>
-      <c r="V84" s="77"/>
-      <c r="W84" s="77"/>
-      <c r="X84" s="74"/>
-      <c r="Y84" s="74"/>
-      <c r="Z84" s="74"/>
-      <c r="AA84" s="74"/>
+      <c r="L84" s="63"/>
+      <c r="M84" s="63"/>
+      <c r="N84" s="63"/>
+      <c r="O84" s="63"/>
+      <c r="P84" s="63"/>
+      <c r="Q84" s="63"/>
+      <c r="R84" s="63"/>
+      <c r="S84" s="63"/>
+      <c r="T84" s="63"/>
+      <c r="U84" s="63"/>
+      <c r="V84" s="63"/>
+      <c r="W84" s="63"/>
+      <c r="X84" s="61"/>
+      <c r="Y84" s="61"/>
+      <c r="Z84" s="61"/>
+      <c r="AA84" s="61"/>
     </row>
     <row r="85" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="B85" s="49">
+        <v>157</v>
+      </c>
+      <c r="B85" s="47">
         <v>15</v>
       </c>
-      <c r="C85" s="51" t="str">
+      <c r="C85" s="49" t="str">
         <f>C42</f>
         <v xml:space="preserve">Cho vay hỗ trợ hộ nghèo về nhà ở theo QĐ 33/2015/QĐ-TTg </v>
       </c>
-      <c r="D85" s="52"/>
-      <c r="E85" s="52"/>
-      <c r="F85" s="52"/>
+      <c r="D85" s="50"/>
+      <c r="E85" s="50"/>
+      <c r="F85" s="50"/>
       <c r="G85" s="29">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -6287,36 +6283,36 @@
       </c>
       <c r="J85" s="15"/>
       <c r="K85" s="15"/>
-      <c r="L85" s="77"/>
-      <c r="M85" s="77"/>
-      <c r="N85" s="77"/>
-      <c r="O85" s="77"/>
-      <c r="P85" s="77"/>
-      <c r="Q85" s="77"/>
-      <c r="R85" s="77"/>
-      <c r="S85" s="77"/>
-      <c r="T85" s="77"/>
-      <c r="U85" s="77"/>
-      <c r="V85" s="77"/>
-      <c r="W85" s="77"/>
-      <c r="X85" s="77"/>
-      <c r="Y85" s="77"/>
-      <c r="Z85" s="77"/>
-      <c r="AA85" s="77"/>
+      <c r="L85" s="63"/>
+      <c r="M85" s="63"/>
+      <c r="N85" s="63"/>
+      <c r="O85" s="63"/>
+      <c r="P85" s="63"/>
+      <c r="Q85" s="63"/>
+      <c r="R85" s="63"/>
+      <c r="S85" s="63"/>
+      <c r="T85" s="63"/>
+      <c r="U85" s="63"/>
+      <c r="V85" s="63"/>
+      <c r="W85" s="63"/>
+      <c r="X85" s="63"/>
+      <c r="Y85" s="63"/>
+      <c r="Z85" s="63"/>
+      <c r="AA85" s="63"/>
     </row>
     <row r="86" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="B86" s="49">
+        <v>158</v>
+      </c>
+      <c r="B86" s="47">
         <v>16</v>
       </c>
-      <c r="C86" s="51" t="s">
-        <v>161</v>
-      </c>
-      <c r="D86" s="52"/>
-      <c r="E86" s="52"/>
-      <c r="F86" s="52"/>
+      <c r="C86" s="49" t="s">
+        <v>155</v>
+      </c>
+      <c r="D86" s="50"/>
+      <c r="E86" s="50"/>
+      <c r="F86" s="50"/>
       <c r="G86" s="29">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -6327,36 +6323,36 @@
       </c>
       <c r="J86" s="15"/>
       <c r="K86" s="15"/>
-      <c r="L86" s="74"/>
-      <c r="M86" s="74"/>
-      <c r="N86" s="74"/>
-      <c r="O86" s="74"/>
-      <c r="P86" s="74"/>
-      <c r="Q86" s="74"/>
-      <c r="R86" s="74"/>
-      <c r="S86" s="74"/>
-      <c r="T86" s="74"/>
-      <c r="U86" s="74"/>
-      <c r="V86" s="74"/>
-      <c r="W86" s="74"/>
-      <c r="X86" s="74"/>
-      <c r="Y86" s="74"/>
-      <c r="Z86" s="74"/>
-      <c r="AA86" s="74"/>
+      <c r="L86" s="61"/>
+      <c r="M86" s="61"/>
+      <c r="N86" s="61"/>
+      <c r="O86" s="61"/>
+      <c r="P86" s="61"/>
+      <c r="Q86" s="61"/>
+      <c r="R86" s="61"/>
+      <c r="S86" s="61"/>
+      <c r="T86" s="61"/>
+      <c r="U86" s="61"/>
+      <c r="V86" s="61"/>
+      <c r="W86" s="61"/>
+      <c r="X86" s="61"/>
+      <c r="Y86" s="61"/>
+      <c r="Z86" s="61"/>
+      <c r="AA86" s="61"/>
     </row>
     <row r="87" spans="1:27" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="B87" s="78" t="s">
-        <v>33</v>
-      </c>
-      <c r="C87" s="79" t="s">
-        <v>162</v>
-      </c>
-      <c r="D87" s="52"/>
-      <c r="E87" s="52"/>
-      <c r="F87" s="52"/>
+        <v>159</v>
+      </c>
+      <c r="B87" s="77" t="s">
+        <v>29</v>
+      </c>
+      <c r="C87" s="78" t="s">
+        <v>156</v>
+      </c>
+      <c r="D87" s="50"/>
+      <c r="E87" s="50"/>
+      <c r="F87" s="50"/>
       <c r="G87" s="29">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -6367,34 +6363,34 @@
       </c>
       <c r="J87" s="15"/>
       <c r="K87" s="15"/>
-      <c r="L87" s="74"/>
-      <c r="M87" s="74"/>
-      <c r="N87" s="74"/>
-      <c r="O87" s="74"/>
-      <c r="P87" s="74"/>
-      <c r="Q87" s="74"/>
-      <c r="R87" s="74"/>
-      <c r="S87" s="74"/>
-      <c r="T87" s="74"/>
-      <c r="U87" s="74"/>
-      <c r="V87" s="74"/>
-      <c r="W87" s="74"/>
-      <c r="X87" s="74"/>
-      <c r="Y87" s="74"/>
-      <c r="Z87" s="74"/>
-      <c r="AA87" s="74"/>
+      <c r="L87" s="61"/>
+      <c r="M87" s="61"/>
+      <c r="N87" s="61"/>
+      <c r="O87" s="61"/>
+      <c r="P87" s="61"/>
+      <c r="Q87" s="61"/>
+      <c r="R87" s="61"/>
+      <c r="S87" s="61"/>
+      <c r="T87" s="61"/>
+      <c r="U87" s="61"/>
+      <c r="V87" s="61"/>
+      <c r="W87" s="61"/>
+      <c r="X87" s="61"/>
+      <c r="Y87" s="61"/>
+      <c r="Z87" s="61"/>
+      <c r="AA87" s="61"/>
     </row>
     <row r="88" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="16" t="s">
-        <v>167</v>
-      </c>
-      <c r="B88" s="49"/>
+        <v>160</v>
+      </c>
+      <c r="B88" s="79"/>
       <c r="C88" s="80" t="s">
-        <v>127</v>
-      </c>
-      <c r="D88" s="52"/>
-      <c r="E88" s="52"/>
-      <c r="F88" s="52"/>
+        <v>121</v>
+      </c>
+      <c r="D88" s="50"/>
+      <c r="E88" s="50"/>
+      <c r="F88" s="50"/>
       <c r="G88" s="29">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -6403,36 +6399,34 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="I88" s="57" t="s">
-        <v>164</v>
-      </c>
+      <c r="I88" s="81"/>
       <c r="J88" s="15"/>
       <c r="K88" s="15"/>
-      <c r="L88" s="74"/>
-      <c r="M88" s="74"/>
-      <c r="N88" s="74"/>
-      <c r="O88" s="74"/>
-      <c r="P88" s="74"/>
-      <c r="Q88" s="74"/>
-      <c r="R88" s="74"/>
-      <c r="S88" s="74"/>
-      <c r="T88" s="74"/>
-      <c r="U88" s="74"/>
-      <c r="V88" s="74"/>
-      <c r="W88" s="74"/>
-      <c r="X88" s="74"/>
-      <c r="Y88" s="74"/>
-      <c r="Z88" s="74"/>
-      <c r="AA88" s="74"/>
+      <c r="L88" s="61"/>
+      <c r="M88" s="61"/>
+      <c r="N88" s="61"/>
+      <c r="O88" s="61"/>
+      <c r="P88" s="61"/>
+      <c r="Q88" s="61"/>
+      <c r="R88" s="61"/>
+      <c r="S88" s="61"/>
+      <c r="T88" s="61"/>
+      <c r="U88" s="61"/>
+      <c r="V88" s="61"/>
+      <c r="W88" s="61"/>
+      <c r="X88" s="61"/>
+      <c r="Y88" s="61"/>
+      <c r="Z88" s="61"/>
+      <c r="AA88" s="61"/>
     </row>
     <row r="89" spans="1:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="B89" s="49">
+        <v>162</v>
+      </c>
+      <c r="B89" s="47">
         <v>17</v>
       </c>
-      <c r="C89" s="50" t="str">
+      <c r="C89" s="48" t="str">
         <f>C51</f>
         <v>Cho vay hỗ trợ phát triển kinh tế - xã hội vùng dân tộc thiểu số và miền núi giai đoạn 2017 - 2020 theo Quyết định số 2085/QĐ-TTg</v>
       </c>
@@ -6449,32 +6443,32 @@
       </c>
       <c r="J89" s="15"/>
       <c r="K89" s="15"/>
-      <c r="L89" s="74"/>
-      <c r="M89" s="74"/>
-      <c r="N89" s="74"/>
-      <c r="O89" s="74"/>
-      <c r="P89" s="74"/>
-      <c r="Q89" s="74"/>
-      <c r="R89" s="74"/>
-      <c r="S89" s="74"/>
-      <c r="T89" s="74"/>
-      <c r="U89" s="74"/>
-      <c r="V89" s="74"/>
-      <c r="W89" s="74"/>
-      <c r="X89" s="74"/>
-      <c r="Y89" s="74"/>
-      <c r="Z89" s="74"/>
-      <c r="AA89" s="74"/>
+      <c r="L89" s="61"/>
+      <c r="M89" s="61"/>
+      <c r="N89" s="61"/>
+      <c r="O89" s="61"/>
+      <c r="P89" s="61"/>
+      <c r="Q89" s="61"/>
+      <c r="R89" s="61"/>
+      <c r="S89" s="61"/>
+      <c r="T89" s="61"/>
+      <c r="U89" s="61"/>
+      <c r="V89" s="61"/>
+      <c r="W89" s="61"/>
+      <c r="X89" s="61"/>
+      <c r="Y89" s="61"/>
+      <c r="Z89" s="61"/>
+      <c r="AA89" s="61"/>
     </row>
     <row r="90" spans="1:27" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="B90" s="49">
+        <v>163</v>
+      </c>
+      <c r="B90" s="47">
         <v>18</v>
       </c>
-      <c r="C90" s="81" t="s">
-        <v>128</v>
+      <c r="C90" s="64" t="s">
+        <v>122</v>
       </c>
       <c r="D90" s="36"/>
       <c r="E90" s="36"/>
@@ -6489,32 +6483,32 @@
       </c>
       <c r="J90" s="15"/>
       <c r="K90" s="15"/>
-      <c r="L90" s="74"/>
-      <c r="M90" s="74"/>
-      <c r="N90" s="74"/>
-      <c r="O90" s="74"/>
-      <c r="P90" s="74"/>
-      <c r="Q90" s="74"/>
-      <c r="R90" s="74"/>
-      <c r="S90" s="74"/>
-      <c r="T90" s="74"/>
-      <c r="U90" s="74"/>
-      <c r="V90" s="74"/>
-      <c r="W90" s="74"/>
-      <c r="X90" s="74"/>
-      <c r="Y90" s="74"/>
-      <c r="Z90" s="74"/>
-      <c r="AA90" s="74"/>
+      <c r="L90" s="61"/>
+      <c r="M90" s="61"/>
+      <c r="N90" s="61"/>
+      <c r="O90" s="61"/>
+      <c r="P90" s="61"/>
+      <c r="Q90" s="61"/>
+      <c r="R90" s="61"/>
+      <c r="S90" s="61"/>
+      <c r="T90" s="61"/>
+      <c r="U90" s="61"/>
+      <c r="V90" s="61"/>
+      <c r="W90" s="61"/>
+      <c r="X90" s="61"/>
+      <c r="Y90" s="61"/>
+      <c r="Z90" s="61"/>
+      <c r="AA90" s="61"/>
     </row>
     <row r="91" spans="1:27" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="B91" s="49">
+        <v>166</v>
+      </c>
+      <c r="B91" s="47">
         <v>19</v>
       </c>
-      <c r="C91" s="81" t="s">
-        <v>129</v>
+      <c r="C91" s="64" t="s">
+        <v>123</v>
       </c>
       <c r="D91" s="36"/>
       <c r="E91" s="36"/>
@@ -6529,32 +6523,32 @@
       </c>
       <c r="J91" s="15"/>
       <c r="K91" s="15"/>
-      <c r="L91" s="74"/>
-      <c r="M91" s="74"/>
-      <c r="N91" s="74"/>
-      <c r="O91" s="74"/>
-      <c r="P91" s="74"/>
-      <c r="Q91" s="74"/>
-      <c r="R91" s="74"/>
-      <c r="S91" s="74"/>
-      <c r="T91" s="74"/>
-      <c r="U91" s="74"/>
-      <c r="V91" s="74"/>
-      <c r="W91" s="74"/>
-      <c r="X91" s="74"/>
-      <c r="Y91" s="74"/>
-      <c r="Z91" s="74"/>
-      <c r="AA91" s="74"/>
+      <c r="L91" s="61"/>
+      <c r="M91" s="61"/>
+      <c r="N91" s="61"/>
+      <c r="O91" s="61"/>
+      <c r="P91" s="61"/>
+      <c r="Q91" s="61"/>
+      <c r="R91" s="61"/>
+      <c r="S91" s="61"/>
+      <c r="T91" s="61"/>
+      <c r="U91" s="61"/>
+      <c r="V91" s="61"/>
+      <c r="W91" s="61"/>
+      <c r="X91" s="61"/>
+      <c r="Y91" s="61"/>
+      <c r="Z91" s="61"/>
+      <c r="AA91" s="61"/>
     </row>
     <row r="92" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="16" t="s">
-        <v>175</v>
-      </c>
-      <c r="B92" s="49">
+        <v>168</v>
+      </c>
+      <c r="B92" s="47">
         <v>20</v>
       </c>
-      <c r="C92" s="81" t="s">
-        <v>168</v>
+      <c r="C92" s="64" t="s">
+        <v>161</v>
       </c>
       <c r="D92" s="36"/>
       <c r="E92" s="36"/>
@@ -6569,38 +6563,37 @@
       </c>
       <c r="J92" s="15"/>
       <c r="K92" s="15"/>
-      <c r="L92" s="74"/>
-      <c r="M92" s="74"/>
-      <c r="N92" s="74"/>
-      <c r="O92" s="74"/>
-      <c r="P92" s="74"/>
-      <c r="Q92" s="74"/>
-      <c r="R92" s="74"/>
-      <c r="S92" s="74"/>
-      <c r="T92" s="74"/>
-      <c r="U92" s="74"/>
-      <c r="V92" s="74"/>
-      <c r="W92" s="74"/>
-      <c r="X92" s="74"/>
-      <c r="Y92" s="74"/>
-      <c r="Z92" s="74"/>
-      <c r="AA92" s="74"/>
-    </row>
-    <row r="93" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L92" s="61"/>
+      <c r="M92" s="61"/>
+      <c r="N92" s="61"/>
+      <c r="O92" s="61"/>
+      <c r="P92" s="61"/>
+      <c r="Q92" s="61"/>
+      <c r="R92" s="61"/>
+      <c r="S92" s="61"/>
+      <c r="T92" s="61"/>
+      <c r="U92" s="61"/>
+      <c r="V92" s="61"/>
+      <c r="W92" s="61"/>
+      <c r="X92" s="61"/>
+      <c r="Y92" s="61"/>
+      <c r="Z92" s="61"/>
+      <c r="AA92" s="61"/>
+    </row>
+    <row r="93" spans="1:27" s="93" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="B93" s="49">
+        <v>174</v>
+      </c>
+      <c r="B93" s="47">
         <v>21</v>
       </c>
-      <c r="C93" s="35" t="s">
-        <v>123</v>
+      <c r="C93" s="51" t="s">
+        <v>183</v>
       </c>
       <c r="D93" s="36"/>
       <c r="E93" s="36"/>
       <c r="F93" s="36"/>
       <c r="G93" s="29">
-        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H93" s="25">
@@ -6609,47 +6602,38 @@
       </c>
       <c r="J93" s="15"/>
       <c r="K93" s="15"/>
-      <c r="L93" s="74"/>
-      <c r="M93" s="74"/>
-      <c r="N93" s="74"/>
-      <c r="O93" s="74"/>
-      <c r="P93" s="74"/>
-      <c r="Q93" s="74"/>
-      <c r="R93" s="74"/>
-      <c r="S93" s="74"/>
-      <c r="T93" s="74"/>
-      <c r="U93" s="74"/>
-      <c r="V93" s="74"/>
-      <c r="W93" s="74"/>
-      <c r="X93" s="74"/>
-      <c r="Y93" s="74"/>
-      <c r="Z93" s="74"/>
-      <c r="AA93" s="74"/>
-    </row>
-    <row r="94" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L93" s="61"/>
+      <c r="M93" s="61"/>
+      <c r="N93" s="61"/>
+      <c r="O93" s="61"/>
+      <c r="P93" s="61"/>
+      <c r="Q93" s="61"/>
+      <c r="R93" s="61"/>
+      <c r="S93" s="61"/>
+      <c r="T93" s="61"/>
+      <c r="U93" s="61"/>
+      <c r="V93" s="61"/>
+      <c r="W93" s="61"/>
+      <c r="X93" s="61"/>
+      <c r="Y93" s="61"/>
+      <c r="Z93" s="61"/>
+      <c r="AA93" s="61"/>
+    </row>
+    <row r="94" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="B94" s="82" t="s">
-        <v>171</v>
-      </c>
-      <c r="C94" s="83" t="s">
-        <v>172</v>
-      </c>
-      <c r="D94" s="19">
-        <f t="shared" ref="D94:G94" si="13">D96+D95</f>
-        <v>0</v>
-      </c>
-      <c r="E94" s="19">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="F94" s="19">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="G94" s="19">
-        <f t="shared" si="13"/>
+        <v>170</v>
+      </c>
+      <c r="B94" s="47">
+        <v>22</v>
+      </c>
+      <c r="C94" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="D94" s="36"/>
+      <c r="E94" s="36"/>
+      <c r="F94" s="36"/>
+      <c r="G94" s="29">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H94" s="25">
@@ -6658,38 +6642,47 @@
       </c>
       <c r="J94" s="15"/>
       <c r="K94" s="15"/>
-      <c r="L94" s="45"/>
-      <c r="M94" s="45"/>
-      <c r="N94" s="45"/>
-      <c r="O94" s="45"/>
-      <c r="P94" s="45"/>
-      <c r="Q94" s="45"/>
-      <c r="R94" s="45"/>
-      <c r="S94" s="45"/>
-      <c r="T94" s="45"/>
-      <c r="U94" s="45"/>
-      <c r="V94" s="45"/>
-      <c r="W94" s="45"/>
-      <c r="X94" s="45"/>
-      <c r="Y94" s="45"/>
-      <c r="Z94" s="45"/>
-      <c r="AA94" s="45"/>
-    </row>
-    <row r="95" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L94" s="61"/>
+      <c r="M94" s="61"/>
+      <c r="N94" s="61"/>
+      <c r="O94" s="61"/>
+      <c r="P94" s="61"/>
+      <c r="Q94" s="61"/>
+      <c r="R94" s="61"/>
+      <c r="S94" s="61"/>
+      <c r="T94" s="61"/>
+      <c r="U94" s="61"/>
+      <c r="V94" s="61"/>
+      <c r="W94" s="61"/>
+      <c r="X94" s="61"/>
+      <c r="Y94" s="61"/>
+      <c r="Z94" s="61"/>
+      <c r="AA94" s="61"/>
+    </row>
+    <row r="95" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="B95" s="54" t="s">
-        <v>33</v>
-      </c>
-      <c r="C95" s="55" t="s">
-        <v>174</v>
-      </c>
-      <c r="D95" s="36"/>
-      <c r="E95" s="36"/>
-      <c r="F95" s="36"/>
-      <c r="G95" s="29">
-        <f t="shared" si="12"/>
+        <v>171</v>
+      </c>
+      <c r="B95" s="65" t="s">
+        <v>164</v>
+      </c>
+      <c r="C95" s="66" t="s">
+        <v>165</v>
+      </c>
+      <c r="D95" s="19">
+        <f t="shared" ref="D95:G95" si="13">D97+D96</f>
+        <v>0</v>
+      </c>
+      <c r="E95" s="19">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="F95" s="19">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="G95" s="19">
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="H95" s="25">
@@ -6698,30 +6691,32 @@
       </c>
       <c r="J95" s="15"/>
       <c r="K95" s="15"/>
-      <c r="L95" s="84"/>
-      <c r="M95" s="84"/>
-      <c r="N95" s="84"/>
-      <c r="O95" s="84"/>
-      <c r="P95" s="84"/>
-      <c r="Q95" s="84"/>
-      <c r="R95" s="84"/>
-      <c r="S95" s="84"/>
-      <c r="T95" s="84"/>
-      <c r="U95" s="84"/>
-      <c r="V95" s="84"/>
-      <c r="W95" s="84"/>
-      <c r="X95" s="84"/>
-      <c r="Y95" s="84"/>
-      <c r="Z95" s="84"/>
-      <c r="AA95" s="84"/>
+      <c r="L95" s="45"/>
+      <c r="M95" s="45"/>
+      <c r="N95" s="45"/>
+      <c r="O95" s="45"/>
+      <c r="P95" s="45"/>
+      <c r="Q95" s="45"/>
+      <c r="R95" s="45"/>
+      <c r="S95" s="45"/>
+      <c r="T95" s="45"/>
+      <c r="U95" s="45"/>
+      <c r="V95" s="45"/>
+      <c r="W95" s="45"/>
+      <c r="X95" s="45"/>
+      <c r="Y95" s="45"/>
+      <c r="Z95" s="45"/>
+      <c r="AA95" s="45"/>
     </row>
     <row r="96" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="B96" s="54"/>
-      <c r="C96" s="55" t="s">
-        <v>176</v>
+        <v>172</v>
+      </c>
+      <c r="B96" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="C96" s="53" t="s">
+        <v>167</v>
       </c>
       <c r="D96" s="36"/>
       <c r="E96" s="36"/>
@@ -6736,65 +6731,76 @@
       </c>
       <c r="J96" s="15"/>
       <c r="K96" s="15"/>
-      <c r="L96" s="84"/>
-      <c r="M96" s="84"/>
-      <c r="N96" s="84"/>
-      <c r="O96" s="84"/>
-      <c r="P96" s="84"/>
-      <c r="Q96" s="84"/>
-      <c r="R96" s="84"/>
-      <c r="S96" s="84"/>
-      <c r="T96" s="84"/>
-      <c r="U96" s="84"/>
-      <c r="V96" s="84"/>
-      <c r="W96" s="84"/>
-      <c r="X96" s="84"/>
-      <c r="Y96" s="84"/>
-      <c r="Z96" s="84"/>
-      <c r="AA96" s="84"/>
-    </row>
-    <row r="97" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L96" s="67"/>
+      <c r="M96" s="67"/>
+      <c r="N96" s="67"/>
+      <c r="O96" s="67"/>
+      <c r="P96" s="67"/>
+      <c r="Q96" s="67"/>
+      <c r="R96" s="67"/>
+      <c r="S96" s="67"/>
+      <c r="T96" s="67"/>
+      <c r="U96" s="67"/>
+      <c r="V96" s="67"/>
+      <c r="W96" s="67"/>
+      <c r="X96" s="67"/>
+      <c r="Y96" s="67"/>
+      <c r="Z96" s="67"/>
+      <c r="AA96" s="67"/>
+    </row>
+    <row r="97" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="16" t="s">
-        <v>181</v>
-      </c>
-      <c r="B97" s="101" t="s">
-        <v>182</v>
-      </c>
-      <c r="C97" s="102"/>
-      <c r="D97" s="102"/>
-      <c r="E97" s="102"/>
-      <c r="F97" s="103"/>
-      <c r="G97" s="104" t="s">
-        <v>183</v>
-      </c>
-      <c r="H97" s="105"/>
+        <v>173</v>
+      </c>
+      <c r="B97" s="52"/>
+      <c r="C97" s="53" t="s">
+        <v>169</v>
+      </c>
+      <c r="D97" s="36"/>
+      <c r="E97" s="36"/>
+      <c r="F97" s="36"/>
+      <c r="G97" s="29">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="H97" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="J97" s="15"/>
       <c r="K97" s="15"/>
-      <c r="L97" s="4"/>
-      <c r="M97" s="4"/>
-      <c r="N97" s="4"/>
-      <c r="O97" s="4"/>
-      <c r="P97" s="4"/>
-      <c r="Q97" s="4"/>
-      <c r="R97" s="4"/>
-      <c r="S97" s="4"/>
-      <c r="T97" s="4"/>
-      <c r="U97" s="4"/>
-      <c r="V97" s="4"/>
-      <c r="W97" s="4"/>
-      <c r="X97" s="4"/>
-      <c r="Y97" s="4"/>
-      <c r="Z97" s="4"/>
-      <c r="AA97" s="4"/>
+      <c r="L97" s="67"/>
+      <c r="M97" s="67"/>
+      <c r="N97" s="67"/>
+      <c r="O97" s="67"/>
+      <c r="P97" s="67"/>
+      <c r="Q97" s="67"/>
+      <c r="R97" s="67"/>
+      <c r="S97" s="67"/>
+      <c r="T97" s="67"/>
+      <c r="U97" s="67"/>
+      <c r="V97" s="67"/>
+      <c r="W97" s="67"/>
+      <c r="X97" s="67"/>
+      <c r="Y97" s="67"/>
+      <c r="Z97" s="67"/>
+      <c r="AA97" s="67"/>
     </row>
     <row r="98" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B98" s="85"/>
-      <c r="C98" s="86"/>
-      <c r="D98" s="86"/>
-      <c r="E98" s="86"/>
-      <c r="F98" s="86"/>
-      <c r="G98" s="87"/>
-      <c r="H98" s="88"/>
+      <c r="A98" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="B98" s="94" t="s">
+        <v>175</v>
+      </c>
+      <c r="C98" s="95"/>
+      <c r="D98" s="95"/>
+      <c r="E98" s="95"/>
+      <c r="F98" s="96"/>
+      <c r="G98" s="97" t="s">
+        <v>176</v>
+      </c>
+      <c r="H98" s="98"/>
       <c r="J98" s="15"/>
       <c r="K98" s="15"/>
       <c r="L98" s="4"/>
@@ -6814,19 +6820,16 @@
       <c r="Z98" s="4"/>
       <c r="AA98" s="4"/>
     </row>
-    <row r="99" spans="1:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B99" s="89"/>
-      <c r="C99" s="89"/>
-      <c r="D99" s="89"/>
-      <c r="E99" s="106" t="s">
-        <v>188</v>
-      </c>
-      <c r="F99" s="107"/>
-      <c r="G99" s="107"/>
-      <c r="H99" s="108"/>
-      <c r="I99" s="4"/>
-      <c r="J99" s="4"/>
-      <c r="K99" s="4"/>
+    <row r="99" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B99" s="68"/>
+      <c r="C99" s="69"/>
+      <c r="D99" s="69"/>
+      <c r="E99" s="69"/>
+      <c r="F99" s="69"/>
+      <c r="G99" s="70"/>
+      <c r="H99" s="71"/>
+      <c r="J99" s="15"/>
+      <c r="K99" s="15"/>
       <c r="L99" s="4"/>
       <c r="M99" s="4"/>
       <c r="N99" s="4"/>
@@ -6844,20 +6847,16 @@
       <c r="Z99" s="4"/>
       <c r="AA99" s="4"/>
     </row>
-    <row r="100" spans="1:27" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B100" s="90"/>
-      <c r="C100" s="91" t="s">
-        <v>184</v>
-      </c>
-      <c r="D100" s="92" t="s">
-        <v>185</v>
-      </c>
-      <c r="E100" s="92"/>
-      <c r="F100" s="92"/>
-      <c r="G100" s="92" t="s">
-        <v>186</v>
-      </c>
-      <c r="H100" s="11"/>
+    <row r="100" spans="1:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B100" s="72"/>
+      <c r="C100" s="72"/>
+      <c r="D100" s="72"/>
+      <c r="E100" s="99" t="s">
+        <v>181</v>
+      </c>
+      <c r="F100" s="100"/>
+      <c r="G100" s="100"/>
+      <c r="H100" s="101"/>
       <c r="I100" s="4"/>
       <c r="J100" s="4"/>
       <c r="K100" s="4"/>
@@ -6878,13 +6877,19 @@
       <c r="Z100" s="4"/>
       <c r="AA100" s="4"/>
     </row>
-    <row r="101" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B101" s="93"/>
-      <c r="C101" s="2"/>
-      <c r="D101" s="4"/>
-      <c r="E101" s="4"/>
-      <c r="F101" s="4"/>
-      <c r="G101" s="4"/>
+    <row r="101" spans="1:27" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B101" s="73"/>
+      <c r="C101" s="74" t="s">
+        <v>177</v>
+      </c>
+      <c r="D101" s="75" t="s">
+        <v>178</v>
+      </c>
+      <c r="E101" s="75"/>
+      <c r="F101" s="75"/>
+      <c r="G101" s="75" t="s">
+        <v>179</v>
+      </c>
       <c r="H101" s="11"/>
       <c r="I101" s="4"/>
       <c r="J101" s="4"/>
@@ -6906,8 +6911,8 @@
       <c r="Z101" s="4"/>
       <c r="AA101" s="4"/>
     </row>
-    <row r="102" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B102" s="4"/>
+    <row r="102" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B102" s="76"/>
       <c r="C102" s="2"/>
       <c r="D102" s="4"/>
       <c r="E102" s="4"/>
@@ -31742,26 +31747,60 @@
       <c r="Z988" s="4"/>
       <c r="AA988" s="4"/>
     </row>
-    <row r="989" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="H989" s="88"/>
+    <row r="989" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B989" s="4"/>
+      <c r="C989" s="2"/>
+      <c r="D989" s="4"/>
+      <c r="E989" s="4"/>
+      <c r="F989" s="4"/>
+      <c r="G989" s="4"/>
+      <c r="H989" s="11"/>
+      <c r="I989" s="4"/>
+      <c r="J989" s="4"/>
+      <c r="K989" s="4"/>
+      <c r="L989" s="4"/>
+      <c r="M989" s="4"/>
+      <c r="N989" s="4"/>
+      <c r="O989" s="4"/>
+      <c r="P989" s="4"/>
+      <c r="Q989" s="4"/>
+      <c r="R989" s="4"/>
+      <c r="S989" s="4"/>
+      <c r="T989" s="4"/>
+      <c r="U989" s="4"/>
+      <c r="V989" s="4"/>
+      <c r="W989" s="4"/>
+      <c r="X989" s="4"/>
+      <c r="Y989" s="4"/>
+      <c r="Z989" s="4"/>
+      <c r="AA989" s="4"/>
     </row>
     <row r="990" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="H990" s="88"/>
+      <c r="H990" s="71"/>
     </row>
     <row r="991" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="H991" s="88"/>
+      <c r="H991" s="71"/>
     </row>
     <row r="992" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="H992" s="88"/>
+      <c r="H992" s="71"/>
     </row>
     <row r="993" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H993" s="88"/>
+      <c r="H993" s="71"/>
+    </row>
+    <row r="994" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H994" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="G97:H97"/>
-    <mergeCell ref="E99:H99"/>
+    <mergeCell ref="I9:I11"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="B98:F98"/>
+    <mergeCell ref="G98:H98"/>
+    <mergeCell ref="E100:H100"/>
     <mergeCell ref="B8:H8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="D9:D11"/>
@@ -31772,12 +31811,6 @@
     <mergeCell ref="C9:C11"/>
     <mergeCell ref="G9:G11"/>
     <mergeCell ref="H9:H11"/>
-    <mergeCell ref="I9:I11"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B7:H7"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/web/EXCEL_TEMPLATE/KHNV/NV_QT.xlsx
+++ b/web/EXCEL_TEMPLATE/KHNV/NV_QT.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DucAnh\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\CẬP NHẬT TTBC_APP\IMS_REPORTS_QTKH2024\EXCEL_TEMPLATE\KHNV\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D8C0445-D5BE-4F76-93F1-01FD9978F009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Biểu số 11" sheetId="1" r:id="rId1"/>
@@ -92,7 +93,7 @@
     <definedName name="ZZZ" localSheetId="0">#REF!</definedName>
     <definedName name="ZZZ">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="" roundtripDataSignature="AMtx7miiPYpftlC0kKdav03lF3/fCfpDfg=="/>
@@ -102,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="131">
   <si>
     <t>Biểu số: 11/NHCS-KH</t>
   </si>
@@ -122,33 +123,16 @@
     <t>BÁO CÁO</t>
   </si>
   <si>
-    <t>Đơn vị: Triệu đồng, hộ, người</t>
-  </si>
-  <si>
     <t>STT</t>
   </si>
   <si>
     <t>CHỈ TIÊU</t>
   </si>
   <si>
-    <t>Năm báo cáo</t>
-  </si>
-  <si>
-    <t>Tỷ lệ 
-hoàn thành 
-kế hoạch giao tăng trưởng (%)</t>
-  </si>
-  <si>
-    <t>Số thực hiện đến 31/12/2022</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>6=5-3</t>
-  </si>
-  <si>
-    <t>7=6/4</t>
   </si>
   <si>
     <t>KH0001</t>
@@ -166,16 +150,10 @@
     <t>NGUỒN VỐN CÂN ĐỐI TỪ TRUNG ƯƠNG</t>
   </si>
   <si>
-    <t>KH0003</t>
-  </si>
-  <si>
     <t>I</t>
   </si>
   <si>
     <t>Nguồn vốn cân đối chuyển từ Trung ương</t>
-  </si>
-  <si>
-    <t>KH0004</t>
   </si>
   <si>
     <t>II</t>
@@ -199,12 +177,6 @@
     <t>KH0007</t>
   </si>
   <si>
-    <t>KH0008</t>
-  </si>
-  <si>
-    <t>KH0009</t>
-  </si>
-  <si>
     <t>Tiền gửi của Tổ viên Tổ Tiết kiệm và vay vốn</t>
   </si>
   <si>
@@ -220,15 +192,6 @@
     <t>KH0011</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn vốn nhận ủy thác từ ngân sách địa phương </t>
-  </si>
-  <si>
-    <t>KH0012</t>
-  </si>
-  <si>
-    <t>Nguồn vốn nhận ủy thác của các chủ đầu tư khác</t>
-  </si>
-  <si>
     <t>KH0013</t>
   </si>
   <si>
@@ -241,148 +204,70 @@
     <t>DƯ NỢ NGUỒN VỐN TRUNG ƯƠNG</t>
   </si>
   <si>
-    <t>A1</t>
-  </si>
-  <si>
-    <t>Các chương trình cho vay được TTCP giao hàng năm (không bao gồm cho vay theo Nghị quyết số 11/NQ-CP)</t>
-  </si>
-  <si>
     <t>KH0015</t>
-  </si>
-  <si>
-    <t>Cho vay hộ nghèo theo Nghị định số 78/2002/NĐ-CP</t>
   </si>
   <si>
     <t>KH0016</t>
   </si>
   <si>
-    <t>Cho vay hộ cận nghèo theo QĐ 15/2013/QĐ-TTg</t>
-  </si>
-  <si>
     <t>KH0017</t>
-  </si>
-  <si>
-    <t>Cho vay hộ mới thoát nghèo theo Quyết định số 28/2015/QĐ-TTg</t>
   </si>
   <si>
     <t>KH0018</t>
   </si>
   <si>
-    <t>Cho vay học sinh, sinh viên theo QĐ 157/2007/QĐ-TTg</t>
-  </si>
-  <si>
     <t>KH0019</t>
-  </si>
-  <si>
-    <t>Cho vay hỗ trợ tạo việc làm, duy trì và mở rộng việc làm từ nguồn vốn Quỹ quốc gia về việc làm (NĐ số 61/2015/NĐ-CP; NĐ số 74/2019/NĐ-CP)</t>
-  </si>
-  <si>
-    <t>KH0020</t>
-  </si>
-  <si>
-    <t>Cho vay hỗ trợ tạo việc làm, duy trì và mở rộng việc làm từ nguồn vốn NHCSXH huy động (NĐ số 61/2015/NĐ-CP; NĐ 74/2019/NĐ-CP)</t>
   </si>
   <si>
     <t>KH0021</t>
   </si>
   <si>
-    <t>Cho vay người lao động đi làm việc ở nước ngoài theo Quyết định số 365/QĐ-NHNN, Quyết định số 1465/QĐ-TTg, Quyết định số 63/2015/QĐ-TTg và Nghị định số 61/2015/NĐ-CP</t>
-  </si>
-  <si>
     <t>KH0022</t>
-  </si>
-  <si>
-    <t>Cho vay để ký quỹ đối với người LĐ đi làm việc tại Hàn Quốc</t>
   </si>
   <si>
     <t>KH0023</t>
   </si>
   <si>
-    <t>Cho vay Xuất khẩu lao động tại huyện nghèo (QĐ 71/2009/QĐ-TTg)</t>
-  </si>
-  <si>
     <t>KH0024</t>
-  </si>
-  <si>
-    <t>Cho vay Chương trình NS&amp;VSMT nông thôn (QĐ 62/2004/QĐ-TTg)</t>
   </si>
   <si>
     <t>KH0025</t>
   </si>
   <si>
-    <t>Cho vay hộ gia đình SXKD tại VKK (QĐ 31/2007/QĐ-TTg)</t>
-  </si>
-  <si>
     <t>KH0026</t>
-  </si>
-  <si>
-    <t>Cho vay mua trả chậm nhà ở vùng ĐBSCL và Tây Nguyên</t>
   </si>
   <si>
     <t>KH0027</t>
   </si>
   <si>
-    <t>Cho vay xây dựng cụm tuyến dân cư và nhà ở vùng ngập lũ ĐBSCL giai đoạn 2018-2020 (QĐ 714/QĐ-TTg)</t>
-  </si>
-  <si>
     <t>KH0028</t>
-  </si>
-  <si>
-    <t>Cho vay hộ đồng bào DTTS ĐBKK theo QĐ 32, 54/2012/QĐ-TTg</t>
   </si>
   <si>
     <t>KH0029</t>
   </si>
   <si>
-    <t>Cho vay đồng bào DTTS - ĐBSCL theo QĐ 74, 29/2013/QĐ-TTg</t>
-  </si>
-  <si>
     <t>KH0030</t>
-  </si>
-  <si>
-    <t>Cho vay đồng bào DTTS theo QĐ 755/QĐ-TTg</t>
   </si>
   <si>
     <t>KH0031</t>
   </si>
   <si>
-    <t>Cho vay hỗ trợ hộ nghèo về nhà ở (QĐ 167/2008/QĐ-TTg)</t>
-  </si>
-  <si>
     <t>KH0032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cho vay hỗ trợ hộ nghèo về nhà ở theo QĐ 33/2015/QĐ-TTg </t>
   </si>
   <si>
     <t>KH0033</t>
   </si>
   <si>
-    <t>Cho vay thương nhân tại VKK (QĐ 92/2009/QĐ-TTg)</t>
-  </si>
-  <si>
     <t>KH0034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cho vay hỗ trợ hộ nghèo xây dựng nhà ở phòng, tránh bão, lụt khu vực miền Trung theo QĐ 716, 48/2014/QĐ-TTg </t>
   </si>
   <si>
     <t>KH0035</t>
   </si>
   <si>
-    <t xml:space="preserve">Cho vay đối với hộ gia đình và người nhiễm HIV, người sau cai nghiện ma túy, người điều trị nghiện các chất dạng thuốc phiện bằng thuốc thay thế, người bán dâm hoàn lương theo Quyết định số 29/2014/QĐ-TTg </t>
-  </si>
-  <si>
     <t>KH0036</t>
   </si>
   <si>
-    <t>Cho vay nhà ở xã hội theo NĐ 100/2015/NĐ-CP (không bao gồm cho vay theo Nghị quyết số 11/NQ-CP)</t>
-  </si>
-  <si>
     <t>KH0037</t>
-  </si>
-  <si>
-    <t>Trong đó: nhà ở công nhân trong khu công nghiệp</t>
   </si>
   <si>
     <t>KH0038</t>
@@ -391,212 +276,31 @@
     <t>KH0039</t>
   </si>
   <si>
-    <t>Cho vay hỗ trợ người sử dụng lao động vay vốn trả lương theo QĐ 23/2021/QĐ-TTg và QĐ 33/2021/QĐ-TTg</t>
-  </si>
-  <si>
     <t>KH0040</t>
   </si>
   <si>
     <t xml:space="preserve">Cho vay trồng rừng sản xuất, phát triển chăn nuôi theo NĐ 75/2015/NĐ-CP </t>
   </si>
   <si>
-    <t>KH0041</t>
-  </si>
-  <si>
-    <t>Cho vay hỗ trợ phát triển kinh tế - xã hội vùng dân tộc thiểu số và miền núi giai đoạn 2017 - 2020 theo Quyết định số 2085/QĐ-TTg</t>
-  </si>
-  <si>
-    <t>KH0042</t>
-  </si>
-  <si>
     <t>Cho vay một số dự án vốn nước ngoài khác</t>
-  </si>
-  <si>
-    <t>KH0043</t>
   </si>
   <si>
     <t xml:space="preserve">- Cho vay dự án IFAD </t>
   </si>
   <si>
-    <t>KH0044</t>
-  </si>
-  <si>
-    <t>- Cho vay dự án RIDP</t>
-  </si>
-  <si>
-    <t>KH0045</t>
-  </si>
-  <si>
     <t xml:space="preserve"> - Cho vay Phát triển DN vừa và nhỏ (Dự án KFW)</t>
-  </si>
-  <si>
-    <t>KH0046</t>
   </si>
   <si>
     <t xml:space="preserve"> - Cho vay Phát triển ngành Lâm nghiệp (Dự án FSDP)</t>
   </si>
   <si>
-    <t>KH0047</t>
-  </si>
-  <si>
-    <t>- Cho vay dự án HIV/AIDS</t>
-  </si>
-  <si>
-    <t>KH0048</t>
-  </si>
-  <si>
     <t>- Cho vay dự án NIPPON (Mở rộng tài chính cho người khuyết tật)</t>
-  </si>
-  <si>
-    <t>KH0049</t>
-  </si>
-  <si>
-    <t>- Cho vay dự án CWPD</t>
-  </si>
-  <si>
-    <t>KH0050</t>
   </si>
   <si>
     <t>Cho vay các đối tượng chính sách khác</t>
   </si>
   <si>
-    <t>A2</t>
-  </si>
-  <si>
-    <t>Các chương trình cho vay theo Nghị quyết số 11/NQ-CP của Chính phủ</t>
-  </si>
-  <si>
-    <t>Cho vay nhà ở xã hội theo NĐ 100/2015/NĐ-CP</t>
-  </si>
-  <si>
-    <t>Nhà ở công nhân trong khu công nghiệp</t>
-  </si>
-  <si>
-    <t>Cho vay đối với học sinh, sinh viên có hoàn cảnh gia đình khó khăn để mua máy tính, thiết bị học tập trực tuyến theo Quyết định số 09/2022/QĐ-TTg</t>
-  </si>
-  <si>
-    <t>Cho vay đối với các cơ sở giáo dục mầm non, tiểu học ngoài công lập theo Quyết định số 11/2022/QĐ-TTg</t>
-  </si>
-  <si>
-    <t>Cho vay thực hiện Chương trình mục tiêu quốc gia về phát triển kinh tế - xã hội vùng đồng bào DTTS và miền núi theo Nghị định số 28/2022/NĐ-CP</t>
-  </si>
-  <si>
-    <t>KH0051</t>
-  </si>
-  <si>
     <t>DƯ NỢ NGUỒN VỐN ĐỊA PHƯƠNG</t>
-  </si>
-  <si>
-    <t>KH0052</t>
-  </si>
-  <si>
-    <t>KH0053</t>
-  </si>
-  <si>
-    <t>KH0054</t>
-  </si>
-  <si>
-    <t>KH0055</t>
-  </si>
-  <si>
-    <t>Cho vay HSSV theo QĐ 157/2007/QĐ-TTg</t>
-  </si>
-  <si>
-    <t>KH0056</t>
-  </si>
-  <si>
-    <t>Cho vay hỗ trợ tạo việc làm, duy trì và mở rộng việc làm  (NĐ số 61/2015/NĐ-CP; NĐ số 74/2019/NĐ-CP)</t>
-  </si>
-  <si>
-    <t>Cho vay hỗ trợ tạo việc làm, duy trì và mở rộng việc làm theo Nghị quyết 11/NQ-CP</t>
-  </si>
-  <si>
-    <t>KH0057</t>
-  </si>
-  <si>
-    <t>KH0058</t>
-  </si>
-  <si>
-    <t>KH0059</t>
-  </si>
-  <si>
-    <t>CV XKLĐ tại huyện nghèo theo QĐ 71/2009/QĐ-TTg</t>
-  </si>
-  <si>
-    <t>KH0060</t>
-  </si>
-  <si>
-    <t>KH0061</t>
-  </si>
-  <si>
-    <t>CV hộ gia đình SXKD tại VKK theo QĐ 31/2007/QĐ-TTg</t>
-  </si>
-  <si>
-    <t>KH0062</t>
-  </si>
-  <si>
-    <t>KH0063</t>
-  </si>
-  <si>
-    <t>Cho vay xây dựng cụm tuyến dân cư và nhà ở vùng ngập lũ ĐBSCL giai đoạn 2018-2020
-(QĐ 714/QĐ-TTg)</t>
-  </si>
-  <si>
-    <t>KH0064</t>
-  </si>
-  <si>
-    <t>KH0065</t>
-  </si>
-  <si>
-    <t>KH0066</t>
-  </si>
-  <si>
-    <t>Cho vay đồng bào DTTS theo QĐ 755/QĐ-TTg (QĐ 1592/QĐ-TTg)</t>
-  </si>
-  <si>
-    <t>KH0067</t>
-  </si>
-  <si>
-    <t>KH0068</t>
-  </si>
-  <si>
-    <t>KH0069</t>
-  </si>
-  <si>
-    <t>KH0070</t>
-  </si>
-  <si>
-    <t>KH0071</t>
-  </si>
-  <si>
-    <t>KH0072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cho vay nhà ở xã hội theo NĐ 100/2015/NĐ-CP </t>
-  </si>
-  <si>
-    <t>Cho vay nhà ở xã hội theo NĐ 100/2015/NĐ-CP theo NQ 11/NQ-CP</t>
-  </si>
-  <si>
-    <t>KH0073</t>
-  </si>
-  <si>
-    <t>KH0074</t>
-  </si>
-  <si>
-    <t>KH0075</t>
-  </si>
-  <si>
-    <t>KH0076</t>
-  </si>
-  <si>
-    <t>Cho vay thực hiện Chương trình MTQG về phát triển KT-XH vùng đồng bào DTTS và miền núi theo Nghị định số 28/2022/NĐ-CP</t>
-  </si>
-  <si>
-    <t>KH0077</t>
-  </si>
-  <si>
-    <t>KH0078</t>
   </si>
   <si>
     <t>C</t>
@@ -605,31 +309,10 @@
     <t>QUỸ AN TOÀN CHI TRẢ</t>
   </si>
   <si>
-    <t>KH0079</t>
-  </si>
-  <si>
     <t>Tồn quỹ tiền mặt</t>
   </si>
   <si>
-    <t>KH0080</t>
-  </si>
-  <si>
     <t>Tiền gửi tại NHNN và TCTD</t>
-  </si>
-  <si>
-    <t>KH0081</t>
-  </si>
-  <si>
-    <t>KH0082</t>
-  </si>
-  <si>
-    <t>KH0083</t>
-  </si>
-  <si>
-    <t>KH0084</t>
-  </si>
-  <si>
-    <t>KH0085</t>
   </si>
   <si>
     <t>Người lập biểu</t>
@@ -675,32 +358,180 @@
     </r>
   </si>
   <si>
-    <t>………., ngày       tháng     năm 2023</t>
+    <t>Cho vay hộ nghèo (theo NĐ 78/2002/NĐ-CP)</t>
   </si>
   <si>
-    <t>KH0086</t>
+    <t>Cho vay hộ cận nghèo (theo QĐ 15/2013/QĐ-TTg)</t>
   </si>
   <si>
-    <t>Cho vay đối với người chấp hành xong án phạt tù theo QĐ số 22/2023/QĐ-TTg</t>
+    <t>Cho vay hộ mới thoát nghèo (theo QĐ 28/2015/QĐ-TTg)</t>
   </si>
   <si>
-    <t>KẾT QUẢ THỰC HIỆN  KẾ HOẠCH TÍN DỤNG NĂM 2023</t>
+    <t>Cho vay học sinh, sinh viên (theo QĐ số 157/2007/QĐ-TTg)</t>
   </si>
   <si>
-    <t>Kế hoạch giao tăng trưởng năm 2023</t>
+    <t>Cho vay hỗ trợ tạo việc làm, duy trì và mở rộng việc làm từ nguồn vốn Quỹ quốc gia về việc làm (theo NĐ số 61/2015/NĐ-CP, NĐ 74/2019/NĐ-CP)</t>
   </si>
   <si>
-    <t>Số thực hiện đến 31/12/2023</t>
+    <t>Cho vay hỗ trợ tạo việc làm, duy trì và mở rộng việc làm từ nguồn vốn NHCSXH huy động (theo NĐ số 61/2015/NĐ-CP, NĐ 74/2019/NĐ-CP)</t>
   </si>
   <si>
-    <t>Tăng/giảm so với năm 2022</t>
+    <t>Cho vay người lao động đi làm việc ở nước ngoài (theo QĐ 365/QĐ-NHNN, NĐ 61/2015/NĐ-CP, QĐ 12/2024/QĐ-TTg, QĐ 16/2023/QĐ-TTg…)</t>
+  </si>
+  <si>
+    <t>Cho vay Chương trình NS&amp;VSMT nông thôn (theo QĐ 62/2004/QĐ-TTg, QĐ 10/2024/QĐ-TTg)</t>
+  </si>
+  <si>
+    <t>Cho vay hộ gia đình SXKD tại VKK (theo QĐ 31/2007/QĐ-TTg)</t>
+  </si>
+  <si>
+    <t>Cho vay thương nhân tại VKK (theo QĐ 92/2009/QĐ-TTg)</t>
+  </si>
+  <si>
+    <t>Cho vay nhà ở vùng thường xuyên ngập lũ vùng ĐBSCL</t>
+  </si>
+  <si>
+    <t>Cho vay người chấp hành xong án phạt tù (theo QĐ 22/2023/QĐ-TTg)</t>
+  </si>
+  <si>
+    <t>Cho vay nhà ở xã hội theo (theo NĐ 100/2015/NĐ-CP, NĐ 100/2024/NĐ-CP)</t>
+  </si>
+  <si>
+    <t>Cho vay thực hiện Chương trình mục tiêu quốc gia về phát triển kinh tế - xã hội vùng đồng bào DTTS và miền núi (theo NĐ 28/2022/NĐ-CP)</t>
+  </si>
+  <si>
+    <t>Cho vay hỗ trợ người sử dụng lao động vay vốn trả lương ngừng việc, phục hồi sản xuất (theo QĐ 23/2021/QĐ-TTg, QĐ 33/2021/QĐ-TTg)</t>
+  </si>
+  <si>
+    <t>Cho vay đối với học sinh, sinh viên có hoàn cảnh gia đình khó khăn để mua máy tính, thiết bị học tập trực tuyến (theo QĐ 09/2022/QĐ-TTg)</t>
+  </si>
+  <si>
+    <t>Cho vay đối với các cơ sở giáo dục mầm non, tiểu học ngoài công lập (theo QĐ 11/2022/QĐ-TTg)</t>
+  </si>
+  <si>
+    <t>Cho vay hộ đồng bào dân tộc thiểu số (theo QĐ 32/2007/QĐ-TTg, QĐ 54/2012/QĐ-TTg, QĐ 74/2008/QĐ-TTg, QĐ 29/2013/QĐ-TTg, QĐ 1592/QĐ-TTg, QĐ 755/QĐ-TTg, QĐ 2085/QĐ-TTg</t>
+  </si>
+  <si>
+    <t>Cho vay hỗ trợ hộ nghèo về nhà ở (theo QĐ 167/2008/QĐ-TTg, QĐ 33/2015/QĐ-TTg, QĐ 716/QĐ-TTg, QĐ 48/2014/QĐ-TTg)</t>
+  </si>
+  <si>
+    <t>- Cho vay dự án khác (RIDP, CWPD, HIV/AIDS, khác)</t>
+  </si>
+  <si>
+    <t>Cho vay hỗ trợ tạo việc làm, duy trì và mở rộng việc làm  (NĐ số 61/2015/NĐ-CP, NĐ 74/2019/NĐ-CP)</t>
+  </si>
+  <si>
+    <t>………., ngày       tháng     năm 2024</t>
+  </si>
+  <si>
+    <t>7=6/4 hoặc 5/3</t>
+  </si>
+  <si>
+    <t>Thực hiện đến 31/12/2023</t>
+  </si>
+  <si>
+    <t>Năm 2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kế hoạch giao tăng trưởng </t>
+  </si>
+  <si>
+    <t>Tăng/giảm so với năm 2023</t>
+  </si>
+  <si>
+    <t>Tỷ lệ 
+hoàn thành 
+kế hoạch  (%)</t>
+  </si>
+  <si>
+    <t>Thực hiện đến 31/12/2024</t>
+  </si>
+  <si>
+    <t>KẾT QUẢ THỰC HIỆN  KẾ HOẠCH TÍN DỤNG NĂM 2024</t>
+  </si>
+  <si>
+    <t>Đơn vị: Triệu đồng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lưu ý: </t>
+  </si>
+  <si>
+    <t>- STT 22 mục A - Sử dụng vốn, gồm các chương trình: cho vay XKLĐ tại huyện nghèo theo QĐ 71/2009/QĐ-TTg, 27/2019/QĐ-TTg, chương trình cho vay người nhiễm HIV, người sau cai nghiện ma túy… theo QĐ 29/2014/QĐ-TTg và các chương trình khác (nếu có) bằng nguồn vốn trung ương.</t>
+  </si>
+  <si>
+    <t>- STT 13 mục B - Sử dụng vốn, gồm các chương trình: cho vay hộ nghèo về nhà ở, cho vay hộ dân tộc thiểu số và các chương trình khác (nếu có) bằng nguồn vốn địa phương.</t>
+  </si>
+  <si>
+    <t>Nếu chỉ tiêu không có số dư 2023 thì để ô trống
+Nếu chỉ tiêu không có Kế hoạch tăng trưởng (cột 4) bằng 0, tỷ lệ bằng cột 5 chia cột 3
+Nếu chỉ tiêu có Kế hoạch tăng trưởng (cột 4) khác 0, tỷ lệ bằng cột 6 chia cột 4</t>
+  </si>
+  <si>
+    <t>KH0003</t>
+  </si>
+  <si>
+    <t>KH0004</t>
+  </si>
+  <si>
+    <t>KH0008</t>
+  </si>
+  <si>
+    <t>KH0009</t>
+  </si>
+  <si>
+    <t>KH0012</t>
+  </si>
+  <si>
+    <t>KH0020</t>
+  </si>
+  <si>
+    <t>KH0041</t>
+  </si>
+  <si>
+    <t>KH0042</t>
+  </si>
+  <si>
+    <t>KH0043</t>
+  </si>
+  <si>
+    <t>KH0044</t>
+  </si>
+  <si>
+    <t>KH0045</t>
+  </si>
+  <si>
+    <t>KH0046</t>
+  </si>
+  <si>
+    <t>KH0047</t>
+  </si>
+  <si>
+    <t>KH0048</t>
+  </si>
+  <si>
+    <t>KH0049</t>
+  </si>
+  <si>
+    <t>KH0050</t>
+  </si>
+  <si>
+    <t>KH0051</t>
+  </si>
+  <si>
+    <t>KH0052</t>
+  </si>
+  <si>
+    <t>KH0053</t>
+  </si>
+  <si>
+    <t>KH0054</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="16" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -710,6 +541,7 @@
     <font>
       <sz val="8"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -821,8 +653,48 @@
       <family val="1"/>
       <charset val="163"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="163"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -843,24 +715,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9D9D9"/>
-        <bgColor rgb="FFD9D9D9"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB7B7B7"/>
-        <bgColor rgb="FFB7B7B7"/>
+        <fgColor indexed="9"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="16">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -941,19 +831,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -1029,11 +906,97 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1063,178 +1026,48 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="13" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="13" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1247,112 +1080,203 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="15" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="13" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="21" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="14" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 5" xfId="1" xr:uid="{70C54851-A4B1-4250-B26C-B23591DC2C9F}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1373,7 +1297,7 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1162050</xdr:colOff>
-      <xdr:row>100</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="238125" cy="38100"/>
@@ -1428,7 +1352,7 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>2886075</xdr:colOff>
-      <xdr:row>100</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="38100" cy="38100"/>
@@ -1483,7 +1407,7 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1162050</xdr:colOff>
-      <xdr:row>100</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="238125" cy="38100"/>
@@ -1538,7 +1462,7 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>2886075</xdr:colOff>
-      <xdr:row>100</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="38100" cy="38100"/>
@@ -1593,7 +1517,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1038225</xdr:colOff>
-      <xdr:row>99</xdr:row>
+      <xdr:row>69</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="38100" cy="38100"/>
@@ -1648,7 +1572,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1790700</xdr:colOff>
-      <xdr:row>99</xdr:row>
+      <xdr:row>69</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="38100" cy="38100"/>
@@ -1703,7 +1627,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1038225</xdr:colOff>
-      <xdr:row>99</xdr:row>
+      <xdr:row>69</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="38100" cy="38100"/>
@@ -1758,7 +1682,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1790700</xdr:colOff>
-      <xdr:row>99</xdr:row>
+      <xdr:row>69</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="38100" cy="38100"/>
@@ -1813,7 +1737,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>97</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="85725" cy="238125"/>
@@ -1868,7 +1792,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>97</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="85725" cy="238125"/>
@@ -1923,7 +1847,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>97</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="85725" cy="238125"/>
@@ -1978,7 +1902,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>97</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="85725" cy="238125"/>
@@ -2033,7 +1957,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="85725" cy="171450"/>
@@ -2088,7 +2012,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="85725" cy="171450"/>
@@ -2143,7 +2067,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>97</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="85725" cy="238125"/>
@@ -2198,7 +2122,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>97</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="85725" cy="238125"/>
@@ -2253,7 +2177,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>97</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="85725" cy="238125"/>
@@ -2308,7 +2232,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>97</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="85725" cy="238125"/>
@@ -2363,7 +2287,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>97</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="85725" cy="238125"/>
@@ -2418,7 +2342,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>97</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="85725" cy="238125"/>
@@ -2473,7 +2397,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>97</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="85725" cy="238125"/>
@@ -2528,7 +2452,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>97</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="85725" cy="238125"/>
@@ -2583,7 +2507,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>97</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="85725" cy="238125"/>
@@ -2638,7 +2562,7 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>97</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="85725" cy="238125"/>
@@ -2689,6 +2613,366 @@
     </xdr:sp>
     <xdr:clientData fLocksWithSheet="0"/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1162050</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="Text Box 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C63A901-F97A-46FB-885B-DE1ED9178917}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="590550" y="19459575"/>
+          <a:ext cx="238125" cy="28575"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>2905125</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="Text Box 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CA8AFA5-09F8-4043-BA1E-F6CE9C778626}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="590550" y="19459575"/>
+          <a:ext cx="0" cy="28575"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1162050</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="28" name="Text Box 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D1D8DBC-979B-46BC-B3C4-CE7AAB164C5D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="590550" y="19459575"/>
+          <a:ext cx="238125" cy="28575"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>2905125</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="Text Box 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{871B0396-DFD1-463E-8DD3-92C8A1C8519C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="590550" y="19459575"/>
+          <a:ext cx="0" cy="28575"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1162050</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="30" name="Text Box 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EDDB88D6-6DC3-495A-BD0E-55CF3092B94B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="590550" y="19459575"/>
+          <a:ext cx="238125" cy="28575"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>2905125</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="31" name="Text Box 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F5F6332-D0D8-4847-B95E-F1CED19833AA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="590550" y="19459575"/>
+          <a:ext cx="0" cy="28575"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1162050</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="32" name="Text Box 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6C52CC1-8344-40E6-8AB2-9359642F2E28}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="590550" y="19459575"/>
+          <a:ext cx="238125" cy="28575"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>2905125</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="33" name="Text Box 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6CF84121-2B18-4CF0-AC69-453B74702E01}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1">
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="590550" y="19459575"/>
+          <a:ext cx="0" cy="28575"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2889,19 +3173,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AA994"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AA964"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="3" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" style="3" customWidth="1"/>
     <col min="3" max="3" width="79.5703125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="11.140625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="12" style="3" customWidth="1"/>
-    <col min="8" max="8" width="10.42578125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="12.42578125" style="3" customWidth="1"/>
+    <col min="4" max="7" width="17.7109375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="20.28515625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="44.28515625" style="3" customWidth="1"/>
     <col min="10" max="27" width="10.42578125" style="3" customWidth="1"/>
     <col min="28" max="16384" width="14.42578125" style="3"/>
   </cols>
@@ -2909,13 +3190,13 @@
     <row r="1" spans="1:27" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
-      <c r="D1" s="115" t="s">
+      <c r="D1" s="78" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="114"/>
-      <c r="F1" s="114"/>
-      <c r="G1" s="114"/>
-      <c r="H1" s="114"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
       <c r="I1" s="4"/>
       <c r="J1" s="4"/>
       <c r="K1" s="4"/>
@@ -2940,13 +3221,13 @@
         <v>1</v>
       </c>
       <c r="C2" s="2"/>
-      <c r="D2" s="116" t="s">
+      <c r="D2" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="114"/>
-      <c r="F2" s="114"/>
-      <c r="G2" s="114"/>
-      <c r="H2" s="114"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
       <c r="I2" s="5"/>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
@@ -2974,7 +3255,7 @@
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
       <c r="F3" s="8" t="s">
-        <v>180</v>
+        <v>75</v>
       </c>
       <c r="G3" s="8"/>
       <c r="H3" s="9"/>
@@ -3027,15 +3308,15 @@
       <c r="Z4" s="4"/>
     </row>
     <row r="5" spans="1:27" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="117" t="s">
+      <c r="B5" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="114"/>
-      <c r="D5" s="114"/>
-      <c r="E5" s="114"/>
-      <c r="F5" s="114"/>
-      <c r="G5" s="114"/>
-      <c r="H5" s="114"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
@@ -3056,15 +3337,15 @@
       <c r="Z5" s="4"/>
     </row>
     <row r="6" spans="1:27" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="118" t="s">
-        <v>184</v>
-      </c>
-      <c r="C6" s="119"/>
-      <c r="D6" s="119"/>
-      <c r="E6" s="119"/>
-      <c r="F6" s="119"/>
-      <c r="G6" s="119"/>
-      <c r="H6" s="119"/>
+      <c r="B6" s="81" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" s="79"/>
+      <c r="D6" s="79"/>
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79"/>
+      <c r="H6" s="79"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
@@ -3085,13 +3366,13 @@
       <c r="Z6" s="4"/>
     </row>
     <row r="7" spans="1:27" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="120"/>
-      <c r="C7" s="114"/>
-      <c r="D7" s="114"/>
-      <c r="E7" s="114"/>
-      <c r="F7" s="114"/>
-      <c r="G7" s="114"/>
-      <c r="H7" s="114"/>
+      <c r="B7" s="82"/>
+      <c r="C7" s="79"/>
+      <c r="D7" s="79"/>
+      <c r="E7" s="79"/>
+      <c r="F7" s="79"/>
+      <c r="G7" s="79"/>
+      <c r="H7" s="79"/>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
@@ -3112,15 +3393,15 @@
       <c r="Z7" s="4"/>
     </row>
     <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="102" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="103"/>
-      <c r="D8" s="103"/>
-      <c r="E8" s="103"/>
-      <c r="F8" s="103"/>
-      <c r="G8" s="103"/>
-      <c r="H8" s="103"/>
+      <c r="B8" s="101" t="s">
+        <v>106</v>
+      </c>
+      <c r="C8" s="102"/>
+      <c r="D8" s="102"/>
+      <c r="E8" s="100"/>
+      <c r="F8" s="100"/>
+      <c r="G8" s="100"/>
+      <c r="H8" s="100"/>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
@@ -3141,27 +3422,23 @@
       <c r="Z8" s="4"/>
     </row>
     <row r="9" spans="1:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="104"/>
-      <c r="B9" s="104" t="s">
+      <c r="A9" s="83"/>
+      <c r="B9" s="83" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="104" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="107" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="110" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="111"/>
-      <c r="G9" s="107" t="s">
-        <v>187</v>
-      </c>
-      <c r="H9" s="112" t="s">
-        <v>10</v>
-      </c>
-      <c r="I9" s="113"/>
+      <c r="D9" s="86" t="s">
+        <v>99</v>
+      </c>
+      <c r="E9" s="89" t="s">
+        <v>100</v>
+      </c>
+      <c r="F9" s="89"/>
+      <c r="G9" s="89"/>
+      <c r="H9" s="89"/>
+      <c r="I9" s="105"/>
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -3182,19 +3459,23 @@
       <c r="AA9" s="4"/>
     </row>
     <row r="10" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="105"/>
-      <c r="B10" s="105"/>
-      <c r="C10" s="105"/>
-      <c r="D10" s="108"/>
-      <c r="E10" s="107" t="s">
-        <v>185</v>
-      </c>
-      <c r="F10" s="107" t="s">
-        <v>186</v>
-      </c>
-      <c r="G10" s="108"/>
-      <c r="H10" s="105"/>
-      <c r="I10" s="114"/>
+      <c r="A10" s="84"/>
+      <c r="B10" s="84"/>
+      <c r="C10" s="84"/>
+      <c r="D10" s="87"/>
+      <c r="E10" s="89" t="s">
+        <v>101</v>
+      </c>
+      <c r="F10" s="89" t="s">
+        <v>104</v>
+      </c>
+      <c r="G10" s="89" t="s">
+        <v>102</v>
+      </c>
+      <c r="H10" s="91" t="s">
+        <v>103</v>
+      </c>
+      <c r="I10" s="79"/>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -3215,18 +3496,18 @@
       <c r="AA10" s="4"/>
     </row>
     <row r="11" spans="1:27" ht="120" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="106"/>
-      <c r="B11" s="106"/>
-      <c r="C11" s="106"/>
-      <c r="D11" s="109"/>
-      <c r="E11" s="109"/>
-      <c r="F11" s="109"/>
-      <c r="G11" s="109"/>
-      <c r="H11" s="106"/>
-      <c r="I11" s="114"/>
+      <c r="A11" s="85"/>
+      <c r="B11" s="85"/>
+      <c r="C11" s="85"/>
+      <c r="D11" s="88"/>
+      <c r="E11" s="90"/>
+      <c r="F11" s="90"/>
+      <c r="G11" s="89"/>
+      <c r="H11" s="91"/>
+      <c r="I11" s="79"/>
       <c r="J11" s="4"/>
       <c r="K11" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
@@ -3245,7 +3526,7 @@
       <c r="Z11" s="4"/>
       <c r="AA11" s="4"/>
     </row>
-    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12">
         <v>0</v>
       </c>
@@ -3258,19 +3539,21 @@
       <c r="D12" s="12">
         <v>3</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="55">
         <v>4</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="55">
         <v>5</v>
       </c>
-      <c r="G12" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="H12" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12" s="15"/>
+      <c r="G12" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" s="56" t="s">
+        <v>98</v>
+      </c>
+      <c r="I12" s="92" t="s">
+        <v>110</v>
+      </c>
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -3290,3519 +3573,3108 @@
       <c r="Z12" s="4"/>
       <c r="AA12" s="4"/>
     </row>
-    <row r="13" spans="1:27" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="18">
-        <f>SUM(D14,D19)</f>
+    <row r="13" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="76" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="61"/>
+      <c r="C13" s="61" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="62">
         <v>0</v>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="62">
         <f>SUM(E14,E19)</f>
         <v>0</v>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="62">
         <f>SUM(F14,F19)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="19">
-        <f>SUM(G14,G19)</f>
+      <c r="G13" s="62">
+        <f t="shared" ref="G13:G16" si="0">F13-D13</f>
         <v>0</v>
       </c>
-      <c r="H13" s="20">
-        <f>IFERROR(G13/E13,0)</f>
+      <c r="H13" s="59" t="str">
+        <f>IF(D13=0,"",IF(E13=0,F13/D13,G13/E13)*100)</f>
+        <v/>
+      </c>
+      <c r="I13" s="92"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="14"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="14"/>
+      <c r="P13" s="14"/>
+      <c r="Q13" s="14"/>
+      <c r="R13" s="14"/>
+      <c r="S13" s="14"/>
+      <c r="T13" s="14"/>
+      <c r="U13" s="14"/>
+      <c r="V13" s="14"/>
+      <c r="W13" s="14"/>
+      <c r="X13" s="14"/>
+      <c r="Y13" s="14"/>
+      <c r="Z13" s="14"/>
+      <c r="AA13" s="14"/>
+    </row>
+    <row r="14" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="76" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="61" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="63" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="64">
+        <f t="shared" ref="D14:F14" si="1">D15+D16</f>
         <v>0</v>
       </c>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="21"/>
-      <c r="M13" s="21"/>
-      <c r="N13" s="21"/>
-      <c r="O13" s="21"/>
-      <c r="P13" s="21"/>
-      <c r="Q13" s="21"/>
-      <c r="R13" s="21"/>
-      <c r="S13" s="21"/>
-      <c r="T13" s="21"/>
-      <c r="U13" s="21"/>
-      <c r="V13" s="21"/>
-      <c r="W13" s="21"/>
-      <c r="X13" s="21"/>
-      <c r="Y13" s="21"/>
-      <c r="Z13" s="21"/>
-      <c r="AA13" s="21"/>
-    </row>
-    <row r="14" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="23">
-        <f t="shared" ref="D14:G14" si="0">D15+D16</f>
+      <c r="E14" s="64">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E14" s="23">
+      <c r="F14" s="64">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="64">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F14" s="23">
+      <c r="H14" s="54" t="str">
+        <f t="shared" ref="H14:H62" si="2">IF(D14=0,"",IF(E14=0,F14/D14,G14/E14)*100)</f>
+        <v/>
+      </c>
+      <c r="I14" s="92"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="14"/>
+      <c r="N14" s="14"/>
+      <c r="O14" s="14"/>
+      <c r="P14" s="14"/>
+      <c r="Q14" s="14"/>
+      <c r="R14" s="14"/>
+      <c r="S14" s="14"/>
+      <c r="T14" s="14"/>
+      <c r="U14" s="14"/>
+      <c r="V14" s="14"/>
+      <c r="W14" s="14"/>
+      <c r="X14" s="14"/>
+      <c r="Y14" s="14"/>
+      <c r="Z14" s="14"/>
+      <c r="AA14" s="14"/>
+    </row>
+    <row r="15" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="76" t="s">
+        <v>111</v>
+      </c>
+      <c r="B15" s="65" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="66" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="67">
+        <f>D20-D19-D16</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="67">
+        <f t="shared" ref="E15" si="3">E20-E19-E16</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="67">
+        <f>F20-F19-F16</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="67">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G14" s="24">
+      <c r="H15" s="54" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="I15" s="92"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
+      <c r="L15" s="14"/>
+      <c r="M15" s="14"/>
+      <c r="N15" s="14"/>
+      <c r="O15" s="14"/>
+      <c r="P15" s="14"/>
+      <c r="Q15" s="14"/>
+      <c r="R15" s="14"/>
+      <c r="S15" s="14"/>
+      <c r="T15" s="14"/>
+      <c r="U15" s="14"/>
+      <c r="V15" s="14"/>
+      <c r="W15" s="14"/>
+      <c r="X15" s="14"/>
+      <c r="Y15" s="14"/>
+      <c r="Z15" s="14"/>
+      <c r="AA15" s="14"/>
+    </row>
+    <row r="16" spans="1:27" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="76" t="s">
+        <v>112</v>
+      </c>
+      <c r="B16" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="66" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="67">
+        <f>D17+D18</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="67">
+        <f>E17+E18</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="67">
+        <f>F17+F18</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="67">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H14" s="25">
-        <f t="shared" ref="H14:H46" si="1">IFERROR(G14/E14,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="21"/>
-      <c r="M14" s="21"/>
-      <c r="N14" s="21"/>
-      <c r="O14" s="21"/>
-      <c r="P14" s="21"/>
-      <c r="Q14" s="21"/>
-      <c r="R14" s="21"/>
-      <c r="S14" s="21"/>
-      <c r="T14" s="21"/>
-      <c r="U14" s="21"/>
-      <c r="V14" s="21"/>
-      <c r="W14" s="21"/>
-      <c r="X14" s="21"/>
-      <c r="Y14" s="21"/>
-      <c r="Z14" s="21"/>
-      <c r="AA14" s="21"/>
-    </row>
-    <row r="15" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
+      <c r="H16" s="54" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
+      <c r="L16" s="14"/>
+      <c r="M16" s="14"/>
+      <c r="N16" s="14"/>
+      <c r="O16" s="14"/>
+      <c r="P16" s="14"/>
+      <c r="Q16" s="14"/>
+      <c r="R16" s="14"/>
+      <c r="S16" s="14"/>
+      <c r="T16" s="14"/>
+      <c r="U16" s="14"/>
+      <c r="V16" s="14"/>
+      <c r="W16" s="14"/>
+      <c r="X16" s="14"/>
+      <c r="Y16" s="14"/>
+      <c r="Z16" s="14"/>
+      <c r="AA16" s="14"/>
+    </row>
+    <row r="17" spans="1:27" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="77" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="17">
+        <v>1</v>
+      </c>
+      <c r="C17" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="28">
-        <f>D22-D19-D16</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="28">
-        <f>E22-E19-E16</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="28">
-        <f>F22-F19-F16</f>
-        <v>0</v>
-      </c>
-      <c r="G15" s="29">
-        <f>G22-G19-G16</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="25">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J15" s="15"/>
-      <c r="K15" s="15"/>
-      <c r="L15" s="21"/>
-      <c r="M15" s="21"/>
-      <c r="N15" s="21"/>
-      <c r="O15" s="21"/>
-      <c r="P15" s="21"/>
-      <c r="Q15" s="21"/>
-      <c r="R15" s="21"/>
-      <c r="S15" s="21"/>
-      <c r="T15" s="21"/>
-      <c r="U15" s="21"/>
-      <c r="V15" s="21"/>
-      <c r="W15" s="21"/>
-      <c r="X15" s="21"/>
-      <c r="Y15" s="21"/>
-      <c r="Z15" s="21"/>
-      <c r="AA15" s="21"/>
-    </row>
-    <row r="16" spans="1:27" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" s="28">
-        <f>D17+D18</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="28">
-        <f>E17+E18</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="28">
-        <f>F17+F18</f>
-        <v>0</v>
-      </c>
-      <c r="G16" s="29">
-        <f>G17+G18</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="25">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="21"/>
-      <c r="M16" s="21"/>
-      <c r="N16" s="21"/>
-      <c r="O16" s="21"/>
-      <c r="P16" s="21"/>
-      <c r="Q16" s="21"/>
-      <c r="R16" s="21"/>
-      <c r="S16" s="21"/>
-      <c r="T16" s="21"/>
-      <c r="U16" s="21"/>
-      <c r="V16" s="21"/>
-      <c r="W16" s="21"/>
-      <c r="X16" s="21"/>
-      <c r="Y16" s="21"/>
-      <c r="Z16" s="21"/>
-      <c r="AA16" s="21"/>
-    </row>
-    <row r="17" spans="1:27" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="31">
-        <v>1</v>
-      </c>
-      <c r="C17" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="29">
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="67">
         <f>F17-D17</f>
         <v>0</v>
       </c>
-      <c r="H17" s="25">
-        <f t="shared" si="1"/>
+      <c r="H17" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="14"/>
+      <c r="N17" s="14"/>
+      <c r="O17" s="14"/>
+      <c r="P17" s="14"/>
+      <c r="Q17" s="14"/>
+      <c r="R17" s="14"/>
+      <c r="S17" s="14"/>
+      <c r="T17" s="14"/>
+      <c r="U17" s="14"/>
+      <c r="V17" s="14"/>
+      <c r="W17" s="14"/>
+      <c r="X17" s="14"/>
+      <c r="Y17" s="14"/>
+      <c r="Z17" s="14"/>
+      <c r="AA17" s="14"/>
+    </row>
+    <row r="18" spans="1:27" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="77" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="20">
+        <v>2</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="67">
+        <f t="shared" ref="G18:G65" si="4">F18-D18</f>
         <v>0</v>
       </c>
-      <c r="J17" s="15"/>
-      <c r="K17" s="15"/>
-      <c r="L17" s="21"/>
-      <c r="M17" s="21"/>
-      <c r="N17" s="21"/>
-      <c r="O17" s="21"/>
-      <c r="P17" s="21"/>
-      <c r="Q17" s="21"/>
-      <c r="R17" s="21"/>
-      <c r="S17" s="21"/>
-      <c r="T17" s="21"/>
-      <c r="U17" s="21"/>
-      <c r="V17" s="21"/>
-      <c r="W17" s="21"/>
-      <c r="X17" s="21"/>
-      <c r="Y17" s="21"/>
-      <c r="Z17" s="21"/>
-      <c r="AA17" s="21"/>
-    </row>
-    <row r="18" spans="1:27" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="34">
-        <v>2</v>
-      </c>
-      <c r="C18" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="D18" s="36"/>
-      <c r="E18" s="36"/>
-      <c r="F18" s="36"/>
-      <c r="G18" s="29">
-        <f>F18-D18</f>
-        <v>0</v>
-      </c>
-      <c r="H18" s="25">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J18" s="15"/>
-      <c r="K18" s="15"/>
-      <c r="L18" s="21"/>
-      <c r="M18" s="21"/>
-      <c r="N18" s="21"/>
-      <c r="O18" s="21"/>
-      <c r="P18" s="21"/>
-      <c r="Q18" s="21"/>
-      <c r="R18" s="21"/>
-      <c r="S18" s="21"/>
-      <c r="T18" s="21"/>
-      <c r="U18" s="21"/>
-      <c r="V18" s="21"/>
-      <c r="W18" s="21"/>
-      <c r="X18" s="21"/>
-      <c r="Y18" s="21"/>
-      <c r="Z18" s="21"/>
-      <c r="AA18" s="21"/>
+      <c r="H18" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="14"/>
+      <c r="P18" s="14"/>
+      <c r="Q18" s="14"/>
+      <c r="R18" s="14"/>
+      <c r="S18" s="14"/>
+      <c r="T18" s="14"/>
+      <c r="U18" s="14"/>
+      <c r="V18" s="14"/>
+      <c r="W18" s="14"/>
+      <c r="X18" s="14"/>
+      <c r="Y18" s="14"/>
+      <c r="Z18" s="14"/>
+      <c r="AA18" s="14"/>
     </row>
     <row r="19" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B19" s="37" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="D19" s="23">
-        <f t="shared" ref="D19:G19" si="2">D20+D21</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="23">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F19" s="23">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G19" s="24">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H19" s="25">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J19" s="15"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="21"/>
-      <c r="M19" s="21"/>
-      <c r="N19" s="21"/>
-      <c r="O19" s="21"/>
-      <c r="P19" s="21"/>
-      <c r="Q19" s="21"/>
-      <c r="R19" s="21"/>
-      <c r="S19" s="21"/>
-      <c r="T19" s="21"/>
-      <c r="U19" s="21"/>
-      <c r="V19" s="21"/>
-      <c r="W19" s="21"/>
-      <c r="X19" s="21"/>
-      <c r="Y19" s="21"/>
-      <c r="Z19" s="21"/>
-      <c r="AA19" s="21"/>
-    </row>
-    <row r="20" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20" s="39" t="s">
-        <v>38</v>
-      </c>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="29">
-        <f t="shared" ref="G20:G21" si="3">F20-D20</f>
-        <v>0</v>
-      </c>
-      <c r="H20" s="25">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J20" s="15"/>
-      <c r="K20" s="15"/>
-      <c r="L20" s="21"/>
-      <c r="M20" s="21"/>
-      <c r="N20" s="21"/>
-      <c r="O20" s="21"/>
-      <c r="P20" s="21"/>
-      <c r="Q20" s="21"/>
-      <c r="R20" s="21"/>
-      <c r="S20" s="21"/>
-      <c r="T20" s="21"/>
-      <c r="U20" s="21"/>
-      <c r="V20" s="21"/>
-      <c r="W20" s="21"/>
-      <c r="X20" s="21"/>
-      <c r="Y20" s="21"/>
-      <c r="Z20" s="21"/>
-      <c r="AA20" s="21"/>
-    </row>
-    <row r="21" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" s="38"/>
-      <c r="C21" s="39" t="s">
-        <v>40</v>
-      </c>
-      <c r="D21" s="36"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="29">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H21" s="25">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J21" s="15"/>
-      <c r="K21" s="15"/>
-      <c r="L21" s="21"/>
-      <c r="M21" s="21"/>
-      <c r="N21" s="21"/>
-      <c r="O21" s="21"/>
-      <c r="P21" s="21"/>
-      <c r="Q21" s="21"/>
-      <c r="R21" s="21"/>
-      <c r="S21" s="21"/>
-      <c r="T21" s="21"/>
-      <c r="U21" s="21"/>
-      <c r="V21" s="21"/>
-      <c r="W21" s="21"/>
-      <c r="X21" s="21"/>
-      <c r="Y21" s="21"/>
-      <c r="Z21" s="21"/>
-      <c r="AA21" s="21"/>
-    </row>
-    <row r="22" spans="1:27" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="B22" s="40"/>
-      <c r="C22" s="40" t="s">
-        <v>42</v>
-      </c>
-      <c r="D22" s="41">
-        <f>D23+D68+D95</f>
-        <v>0</v>
-      </c>
-      <c r="E22" s="41">
-        <f>E23+E68+E95</f>
-        <v>0</v>
-      </c>
-      <c r="F22" s="41">
-        <f>F23+F68+F95</f>
-        <v>0</v>
-      </c>
-      <c r="G22" s="41">
-        <f>G23+G68+G95</f>
-        <v>0</v>
-      </c>
-      <c r="H22" s="25">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J22" s="15"/>
-      <c r="K22" s="15"/>
-      <c r="L22" s="21"/>
-      <c r="M22" s="21"/>
-      <c r="N22" s="21"/>
-      <c r="O22" s="21"/>
-      <c r="P22" s="21"/>
-      <c r="Q22" s="21"/>
-      <c r="R22" s="21"/>
-      <c r="S22" s="21"/>
-      <c r="T22" s="21"/>
-      <c r="U22" s="21"/>
-      <c r="V22" s="21"/>
-      <c r="W22" s="21"/>
-      <c r="X22" s="21"/>
-      <c r="Y22" s="21"/>
-      <c r="Z22" s="21"/>
-      <c r="AA22" s="21"/>
-    </row>
-    <row r="23" spans="1:27" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="C23" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="D23" s="44">
-        <f t="shared" ref="D23:G23" si="4">D24+D61</f>
-        <v>0</v>
-      </c>
-      <c r="E23" s="44">
+      <c r="A19" s="76" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="69" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="64">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F23" s="44">
+      <c r="H19" s="54" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="14"/>
+      <c r="N19" s="14"/>
+      <c r="O19" s="14"/>
+      <c r="P19" s="14"/>
+      <c r="Q19" s="14"/>
+      <c r="R19" s="14"/>
+      <c r="S19" s="14"/>
+      <c r="T19" s="14"/>
+      <c r="U19" s="14"/>
+      <c r="V19" s="14"/>
+      <c r="W19" s="14"/>
+      <c r="X19" s="14"/>
+      <c r="Y19" s="14"/>
+      <c r="Z19" s="14"/>
+      <c r="AA19" s="14"/>
+    </row>
+    <row r="20" spans="1:27" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="76" t="s">
+        <v>113</v>
+      </c>
+      <c r="B20" s="61"/>
+      <c r="C20" s="61" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="62">
+        <f>D21+D49+D63</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="62">
+        <f t="shared" ref="E20:F20" si="5">E21+E49+E63</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="62">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G20" s="62">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G23" s="44">
+      <c r="H20" s="54" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="14"/>
+      <c r="N20" s="14"/>
+      <c r="O20" s="14"/>
+      <c r="P20" s="14"/>
+      <c r="Q20" s="14"/>
+      <c r="R20" s="14"/>
+      <c r="S20" s="14"/>
+      <c r="T20" s="14"/>
+      <c r="U20" s="14"/>
+      <c r="V20" s="14"/>
+      <c r="W20" s="14"/>
+      <c r="X20" s="14"/>
+      <c r="Y20" s="14"/>
+      <c r="Z20" s="14"/>
+      <c r="AA20" s="14"/>
+    </row>
+    <row r="21" spans="1:27" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="76" t="s">
+        <v>114</v>
+      </c>
+      <c r="B21" s="70" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="71" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="64">
+        <f>SUM(D22:D42)+D48</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="64">
+        <f t="shared" ref="E21:F21" si="6">SUM(E22:E42)+E48</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="64">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="G21" s="64">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H23" s="25">
-        <f t="shared" si="1"/>
+      <c r="H21" s="54" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
+      <c r="L21" s="58"/>
+      <c r="M21" s="58"/>
+      <c r="N21" s="58"/>
+      <c r="O21" s="58"/>
+      <c r="P21" s="58"/>
+      <c r="Q21" s="58"/>
+      <c r="R21" s="58"/>
+      <c r="S21" s="58"/>
+      <c r="T21" s="58"/>
+      <c r="U21" s="58"/>
+      <c r="V21" s="58"/>
+      <c r="W21" s="58"/>
+      <c r="X21" s="58"/>
+      <c r="Y21" s="58"/>
+      <c r="Z21" s="58"/>
+      <c r="AA21" s="58"/>
+    </row>
+    <row r="22" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="77" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="34">
+        <v>1</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>76</v>
+      </c>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="16">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J23" s="15"/>
-      <c r="K23" s="15"/>
-      <c r="L23" s="45"/>
-      <c r="M23" s="45"/>
-      <c r="N23" s="45"/>
-      <c r="O23" s="45"/>
-      <c r="P23" s="45"/>
-      <c r="Q23" s="45"/>
-      <c r="R23" s="45"/>
-      <c r="S23" s="45"/>
-      <c r="T23" s="45"/>
-      <c r="U23" s="45"/>
-      <c r="V23" s="45"/>
-      <c r="W23" s="45"/>
-      <c r="X23" s="45"/>
-      <c r="Y23" s="45"/>
-      <c r="Z23" s="45"/>
-      <c r="AA23" s="45"/>
-    </row>
-    <row r="24" spans="1:27" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
+      <c r="H22" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J22" s="13"/>
+      <c r="K22" s="13"/>
+      <c r="L22" s="23"/>
+      <c r="M22" s="23"/>
+      <c r="N22" s="23"/>
+      <c r="O22" s="23"/>
+      <c r="P22" s="23"/>
+      <c r="Q22" s="23"/>
+      <c r="R22" s="23"/>
+      <c r="S22" s="23"/>
+      <c r="T22" s="23"/>
+      <c r="U22" s="23"/>
+      <c r="V22" s="23"/>
+      <c r="W22" s="23"/>
+      <c r="X22" s="23"/>
+      <c r="Y22" s="23"/>
+      <c r="Z22" s="23"/>
+      <c r="AA22" s="23"/>
+    </row>
+    <row r="23" spans="1:27" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="77" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="34">
+        <v>2</v>
+      </c>
+      <c r="C23" s="36" t="s">
+        <v>77</v>
+      </c>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H23" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13"/>
+      <c r="L23" s="23"/>
+      <c r="M23" s="23"/>
+      <c r="N23" s="23"/>
+      <c r="O23" s="23"/>
+      <c r="P23" s="23"/>
+      <c r="Q23" s="23"/>
+      <c r="R23" s="23"/>
+      <c r="S23" s="23"/>
+      <c r="T23" s="23"/>
+      <c r="U23" s="23"/>
+      <c r="V23" s="23"/>
+      <c r="W23" s="23"/>
+      <c r="X23" s="23"/>
+      <c r="Y23" s="23"/>
+      <c r="Z23" s="23"/>
+      <c r="AA23" s="23"/>
+    </row>
+    <row r="24" spans="1:27" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="77" t="s">
+        <v>115</v>
+      </c>
+      <c r="B24" s="34">
+        <v>3</v>
+      </c>
+      <c r="C24" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H24" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="23"/>
+      <c r="M24" s="23"/>
+      <c r="N24" s="23"/>
+      <c r="O24" s="23"/>
+      <c r="P24" s="23"/>
+      <c r="Q24" s="23"/>
+      <c r="R24" s="23"/>
+      <c r="S24" s="23"/>
+      <c r="T24" s="23"/>
+      <c r="U24" s="23"/>
+      <c r="V24" s="23"/>
+      <c r="W24" s="23"/>
+      <c r="X24" s="23"/>
+      <c r="Y24" s="23"/>
+      <c r="Z24" s="23"/>
+      <c r="AA24" s="23"/>
+    </row>
+    <row r="25" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="77" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="34">
+        <v>4</v>
+      </c>
+      <c r="C25" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="D25" s="24"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H25" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
+      <c r="L25" s="23"/>
+      <c r="M25" s="23"/>
+      <c r="N25" s="23"/>
+      <c r="O25" s="23"/>
+      <c r="P25" s="23"/>
+      <c r="Q25" s="23"/>
+      <c r="R25" s="23"/>
+      <c r="S25" s="23"/>
+      <c r="T25" s="23"/>
+      <c r="U25" s="23"/>
+      <c r="V25" s="23"/>
+      <c r="W25" s="23"/>
+      <c r="X25" s="23"/>
+      <c r="Y25" s="23"/>
+      <c r="Z25" s="23"/>
+      <c r="AA25" s="23"/>
+    </row>
+    <row r="26" spans="1:27" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="77" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" s="34">
+        <v>5</v>
+      </c>
+      <c r="C26" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" s="24"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H26" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="23"/>
+      <c r="M26" s="23"/>
+      <c r="N26" s="23"/>
+      <c r="O26" s="23"/>
+      <c r="P26" s="23"/>
+      <c r="Q26" s="23"/>
+      <c r="R26" s="23"/>
+      <c r="S26" s="23"/>
+      <c r="T26" s="23"/>
+      <c r="U26" s="23"/>
+      <c r="V26" s="23"/>
+      <c r="W26" s="23"/>
+      <c r="X26" s="23"/>
+      <c r="Y26" s="23"/>
+      <c r="Z26" s="23"/>
+      <c r="AA26" s="23"/>
+    </row>
+    <row r="27" spans="1:27" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="77" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="34">
+        <v>6</v>
+      </c>
+      <c r="C27" s="38" t="s">
+        <v>81</v>
+      </c>
+      <c r="D27" s="24"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H27" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J27" s="13"/>
+      <c r="K27" s="13"/>
+      <c r="L27" s="23"/>
+      <c r="M27" s="23"/>
+      <c r="N27" s="23"/>
+      <c r="O27" s="23"/>
+      <c r="P27" s="23"/>
+      <c r="Q27" s="23"/>
+      <c r="R27" s="23"/>
+      <c r="S27" s="23"/>
+      <c r="T27" s="23"/>
+      <c r="U27" s="23"/>
+      <c r="V27" s="23"/>
+      <c r="W27" s="23"/>
+      <c r="X27" s="23"/>
+      <c r="Y27" s="23"/>
+      <c r="Z27" s="23"/>
+      <c r="AA27" s="23"/>
+    </row>
+    <row r="28" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="77" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="34">
+        <v>7</v>
+      </c>
+      <c r="C28" s="39" t="s">
+        <v>82</v>
+      </c>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H28" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J28" s="13"/>
+      <c r="K28" s="13"/>
+      <c r="L28" s="23"/>
+      <c r="M28" s="23"/>
+      <c r="N28" s="23"/>
+      <c r="O28" s="23"/>
+      <c r="P28" s="23"/>
+      <c r="Q28" s="23"/>
+      <c r="R28" s="23"/>
+      <c r="S28" s="23"/>
+      <c r="T28" s="23"/>
+      <c r="U28" s="23"/>
+      <c r="V28" s="23"/>
+      <c r="W28" s="23"/>
+      <c r="X28" s="23"/>
+      <c r="Y28" s="23"/>
+      <c r="Z28" s="23"/>
+      <c r="AA28" s="23"/>
+    </row>
+    <row r="29" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="77" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="34">
+        <v>8</v>
+      </c>
+      <c r="C29" s="38" t="s">
+        <v>83</v>
+      </c>
+      <c r="D29" s="24"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H29" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
+      <c r="L29" s="23"/>
+      <c r="M29" s="23"/>
+      <c r="N29" s="23"/>
+      <c r="O29" s="23"/>
+      <c r="P29" s="23"/>
+      <c r="Q29" s="23"/>
+      <c r="R29" s="23"/>
+      <c r="S29" s="23"/>
+      <c r="T29" s="23"/>
+      <c r="U29" s="23"/>
+      <c r="V29" s="23"/>
+      <c r="W29" s="23"/>
+      <c r="X29" s="23"/>
+      <c r="Y29" s="23"/>
+      <c r="Z29" s="23"/>
+      <c r="AA29" s="23"/>
+    </row>
+    <row r="30" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="77" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="34">
+        <v>9</v>
+      </c>
+      <c r="C30" s="38" t="s">
+        <v>84</v>
+      </c>
+      <c r="D30" s="24"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H30" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J30" s="13"/>
+      <c r="K30" s="13"/>
+      <c r="L30" s="23"/>
+      <c r="M30" s="23"/>
+      <c r="N30" s="23"/>
+      <c r="O30" s="23"/>
+      <c r="P30" s="23"/>
+      <c r="Q30" s="23"/>
+      <c r="R30" s="23"/>
+      <c r="S30" s="23"/>
+      <c r="T30" s="23"/>
+      <c r="U30" s="23"/>
+      <c r="V30" s="23"/>
+      <c r="W30" s="23"/>
+      <c r="X30" s="23"/>
+      <c r="Y30" s="23"/>
+      <c r="Z30" s="23"/>
+      <c r="AA30" s="23"/>
+    </row>
+    <row r="31" spans="1:27" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="77" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="34">
+        <v>10</v>
+      </c>
+      <c r="C31" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="D31" s="24"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H31" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
+      <c r="L31" s="23"/>
+      <c r="M31" s="23"/>
+      <c r="N31" s="23"/>
+      <c r="O31" s="23"/>
+      <c r="P31" s="23"/>
+      <c r="Q31" s="23"/>
+      <c r="R31" s="23"/>
+      <c r="S31" s="23"/>
+      <c r="T31" s="23"/>
+      <c r="U31" s="23"/>
+      <c r="V31" s="23"/>
+      <c r="W31" s="23"/>
+      <c r="X31" s="23"/>
+      <c r="Y31" s="23"/>
+      <c r="Z31" s="23"/>
+      <c r="AA31" s="23"/>
+    </row>
+    <row r="32" spans="1:27" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="77" t="s">
+        <v>116</v>
+      </c>
+      <c r="B32" s="34">
+        <v>11</v>
+      </c>
+      <c r="C32" s="38" t="s">
+        <v>86</v>
+      </c>
+      <c r="D32" s="24"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H32" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J32" s="13"/>
+      <c r="K32" s="13"/>
+      <c r="L32" s="23"/>
+      <c r="M32" s="23"/>
+      <c r="N32" s="23"/>
+      <c r="O32" s="23"/>
+      <c r="P32" s="23"/>
+      <c r="Q32" s="23"/>
+      <c r="R32" s="23"/>
+      <c r="S32" s="23"/>
+      <c r="T32" s="23"/>
+      <c r="U32" s="23"/>
+      <c r="V32" s="23"/>
+      <c r="W32" s="23"/>
+      <c r="X32" s="23"/>
+      <c r="Y32" s="23"/>
+      <c r="Z32" s="23"/>
+      <c r="AA32" s="23"/>
+    </row>
+    <row r="33" spans="1:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="77" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="34">
+        <v>12</v>
+      </c>
+      <c r="C33" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H33" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J33" s="13"/>
+      <c r="K33" s="13"/>
+      <c r="L33" s="23"/>
+      <c r="M33" s="23"/>
+      <c r="N33" s="23"/>
+      <c r="O33" s="23"/>
+      <c r="P33" s="23"/>
+      <c r="Q33" s="23"/>
+      <c r="R33" s="23"/>
+      <c r="S33" s="23"/>
+      <c r="T33" s="23"/>
+      <c r="U33" s="23"/>
+      <c r="V33" s="23"/>
+      <c r="W33" s="23"/>
+      <c r="X33" s="23"/>
+      <c r="Y33" s="23"/>
+      <c r="Z33" s="23"/>
+      <c r="AA33" s="23"/>
+    </row>
+    <row r="34" spans="1:27" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="77" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="82" t="s">
+      <c r="B34" s="34">
+        <v>13</v>
+      </c>
+      <c r="C34" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="D34" s="24"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H34" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J34" s="13"/>
+      <c r="K34" s="13"/>
+      <c r="L34" s="23"/>
+      <c r="M34" s="23"/>
+      <c r="N34" s="23"/>
+      <c r="O34" s="23"/>
+      <c r="P34" s="23"/>
+      <c r="Q34" s="23"/>
+      <c r="R34" s="23"/>
+      <c r="S34" s="23"/>
+      <c r="T34" s="23"/>
+      <c r="U34" s="23"/>
+      <c r="V34" s="23"/>
+      <c r="W34" s="23"/>
+      <c r="X34" s="23"/>
+      <c r="Y34" s="23"/>
+      <c r="Z34" s="23"/>
+      <c r="AA34" s="23"/>
+    </row>
+    <row r="35" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="77" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="34">
+        <v>14</v>
+      </c>
+      <c r="C35" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D35" s="24"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H35" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J35" s="13"/>
+      <c r="K35" s="13"/>
+      <c r="L35" s="23"/>
+      <c r="M35" s="23"/>
+      <c r="N35" s="23"/>
+      <c r="O35" s="23"/>
+      <c r="P35" s="23"/>
+      <c r="Q35" s="23"/>
+      <c r="R35" s="23"/>
+      <c r="S35" s="23"/>
+      <c r="T35" s="23"/>
+      <c r="U35" s="23"/>
+      <c r="V35" s="23"/>
+      <c r="W35" s="23"/>
+      <c r="X35" s="23"/>
+      <c r="Y35" s="23"/>
+      <c r="Z35" s="23"/>
+      <c r="AA35" s="23"/>
+    </row>
+    <row r="36" spans="1:27" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="77" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="34">
+        <v>15</v>
+      </c>
+      <c r="C36" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H36" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J36" s="13"/>
+      <c r="K36" s="13"/>
+      <c r="L36" s="23"/>
+      <c r="M36" s="23"/>
+      <c r="N36" s="23"/>
+      <c r="O36" s="23"/>
+      <c r="P36" s="23"/>
+      <c r="Q36" s="23"/>
+      <c r="R36" s="23"/>
+      <c r="S36" s="23"/>
+      <c r="T36" s="23"/>
+      <c r="U36" s="23"/>
+      <c r="V36" s="23"/>
+      <c r="W36" s="23"/>
+      <c r="X36" s="23"/>
+      <c r="Y36" s="23"/>
+      <c r="Z36" s="23"/>
+      <c r="AA36" s="23"/>
+    </row>
+    <row r="37" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="77" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" s="34">
+        <v>16</v>
+      </c>
+      <c r="C37" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="D37" s="24"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H37" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J37" s="13"/>
+      <c r="K37" s="13"/>
+      <c r="L37" s="23"/>
+      <c r="M37" s="23"/>
+      <c r="N37" s="23"/>
+      <c r="O37" s="23"/>
+      <c r="P37" s="23"/>
+      <c r="Q37" s="23"/>
+      <c r="R37" s="23"/>
+      <c r="S37" s="23"/>
+      <c r="T37" s="23"/>
+      <c r="U37" s="23"/>
+      <c r="V37" s="23"/>
+      <c r="W37" s="23"/>
+      <c r="X37" s="23"/>
+      <c r="Y37" s="23"/>
+      <c r="Z37" s="23"/>
+      <c r="AA37" s="23"/>
+    </row>
+    <row r="38" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="77" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" s="34">
+        <v>17</v>
+      </c>
+      <c r="C38" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="D38" s="24"/>
+      <c r="E38" s="24"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H38" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J38" s="13"/>
+      <c r="K38" s="13"/>
+      <c r="L38" s="23"/>
+      <c r="M38" s="23"/>
+      <c r="N38" s="23"/>
+      <c r="O38" s="23"/>
+      <c r="P38" s="23"/>
+      <c r="Q38" s="23"/>
+      <c r="R38" s="23"/>
+      <c r="S38" s="23"/>
+      <c r="T38" s="23"/>
+      <c r="U38" s="23"/>
+      <c r="V38" s="23"/>
+      <c r="W38" s="23"/>
+      <c r="X38" s="23"/>
+      <c r="Y38" s="23"/>
+      <c r="Z38" s="23"/>
+      <c r="AA38" s="23"/>
+    </row>
+    <row r="39" spans="1:27" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="77" t="s">
+        <v>44</v>
+      </c>
+      <c r="B39" s="34">
+        <v>18</v>
+      </c>
+      <c r="C39" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="D39" s="24"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H39" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J39" s="13"/>
+      <c r="K39" s="13"/>
+      <c r="L39" s="23"/>
+      <c r="M39" s="23"/>
+      <c r="N39" s="23"/>
+      <c r="O39" s="23"/>
+      <c r="P39" s="23"/>
+      <c r="Q39" s="23"/>
+      <c r="R39" s="23"/>
+      <c r="S39" s="23"/>
+      <c r="T39" s="23"/>
+      <c r="U39" s="23"/>
+      <c r="V39" s="23"/>
+      <c r="W39" s="23"/>
+      <c r="X39" s="23"/>
+      <c r="Y39" s="23"/>
+      <c r="Z39" s="23"/>
+      <c r="AA39" s="23"/>
+    </row>
+    <row r="40" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="77" t="s">
         <v>45</v>
       </c>
-      <c r="C24" s="83" t="s">
+      <c r="B40" s="34">
+        <v>19</v>
+      </c>
+      <c r="C40" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="D40" s="24"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H40" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J40" s="13"/>
+      <c r="K40" s="13"/>
+      <c r="L40" s="23"/>
+      <c r="M40" s="23"/>
+      <c r="N40" s="23"/>
+      <c r="O40" s="23"/>
+      <c r="P40" s="23"/>
+      <c r="Q40" s="23"/>
+      <c r="R40" s="23"/>
+      <c r="S40" s="23"/>
+      <c r="T40" s="23"/>
+      <c r="U40" s="23"/>
+      <c r="V40" s="23"/>
+      <c r="W40" s="23"/>
+      <c r="X40" s="23"/>
+      <c r="Y40" s="23"/>
+      <c r="Z40" s="23"/>
+      <c r="AA40" s="23"/>
+    </row>
+    <row r="41" spans="1:27" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="77" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="41">
-        <f t="shared" ref="D24:G24" si="5">SUM(D25:D52)+D60-D32-D47</f>
+      <c r="B41" s="34">
+        <v>20</v>
+      </c>
+      <c r="C41" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="16">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E24" s="41">
-        <f t="shared" si="5"/>
+      <c r="H41" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J41" s="13"/>
+      <c r="K41" s="13"/>
+      <c r="L41" s="23"/>
+      <c r="M41" s="23"/>
+      <c r="N41" s="23"/>
+      <c r="O41" s="23"/>
+      <c r="P41" s="23"/>
+      <c r="Q41" s="23"/>
+      <c r="R41" s="23"/>
+      <c r="S41" s="23"/>
+      <c r="T41" s="23"/>
+      <c r="U41" s="23"/>
+      <c r="V41" s="23"/>
+      <c r="W41" s="23"/>
+      <c r="X41" s="23"/>
+      <c r="Y41" s="23"/>
+      <c r="Z41" s="23"/>
+      <c r="AA41" s="23"/>
+    </row>
+    <row r="42" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="77" t="s">
+        <v>47</v>
+      </c>
+      <c r="B42" s="72">
+        <v>21</v>
+      </c>
+      <c r="C42" s="73" t="s">
+        <v>59</v>
+      </c>
+      <c r="D42" s="74">
+        <f>SUM(D43:D47)</f>
         <v>0</v>
       </c>
-      <c r="F24" s="41">
-        <f t="shared" si="5"/>
+      <c r="E42" s="74">
+        <f t="shared" ref="E42" si="7">SUM(E43:E47)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="29">
-        <f t="shared" si="5"/>
+      <c r="F42" s="74">
+        <f>SUM(F43:F47)</f>
         <v>0</v>
       </c>
-      <c r="H24" s="25">
-        <f t="shared" si="1"/>
+      <c r="G42" s="16">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J24" s="15"/>
-      <c r="K24" s="15"/>
-      <c r="L24" s="46"/>
-      <c r="M24" s="46"/>
-      <c r="N24" s="46"/>
-      <c r="O24" s="46"/>
-      <c r="P24" s="46"/>
-      <c r="Q24" s="46"/>
-      <c r="R24" s="46"/>
-      <c r="S24" s="46"/>
-      <c r="T24" s="46"/>
-      <c r="U24" s="46"/>
-      <c r="V24" s="46"/>
-      <c r="W24" s="46"/>
-      <c r="X24" s="46"/>
-      <c r="Y24" s="46"/>
-      <c r="Z24" s="46"/>
-      <c r="AA24" s="46"/>
-    </row>
-    <row r="25" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="B25" s="47">
-        <v>1</v>
-      </c>
-      <c r="C25" s="35" t="s">
+      <c r="H42" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J42" s="13"/>
+      <c r="K42" s="13"/>
+      <c r="L42" s="23"/>
+      <c r="M42" s="23"/>
+      <c r="N42" s="23"/>
+      <c r="O42" s="23"/>
+      <c r="P42" s="23"/>
+      <c r="Q42" s="23"/>
+      <c r="R42" s="23"/>
+      <c r="S42" s="23"/>
+      <c r="T42" s="23"/>
+      <c r="U42" s="23"/>
+      <c r="V42" s="23"/>
+      <c r="W42" s="23"/>
+      <c r="X42" s="23"/>
+      <c r="Y42" s="23"/>
+      <c r="Z42" s="23"/>
+      <c r="AA42" s="23"/>
+    </row>
+    <row r="43" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="77" t="s">
         <v>48</v>
       </c>
-      <c r="D25" s="36"/>
-      <c r="E25" s="36"/>
-      <c r="F25" s="36"/>
-      <c r="G25" s="29">
-        <f t="shared" ref="G25:G51" si="6">F25-D25</f>
+      <c r="B43" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="C43" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="D43" s="22"/>
+      <c r="E43" s="22"/>
+      <c r="F43" s="22"/>
+      <c r="G43" s="16">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H25" s="25">
-        <f t="shared" si="1"/>
+      <c r="H43" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J43" s="13"/>
+      <c r="K43" s="13"/>
+      <c r="L43" s="23"/>
+      <c r="M43" s="23"/>
+      <c r="N43" s="23"/>
+      <c r="O43" s="23"/>
+      <c r="P43" s="23"/>
+      <c r="Q43" s="23"/>
+      <c r="R43" s="23"/>
+      <c r="S43" s="23"/>
+      <c r="T43" s="23"/>
+      <c r="U43" s="23"/>
+      <c r="V43" s="23"/>
+      <c r="W43" s="23"/>
+      <c r="X43" s="23"/>
+      <c r="Y43" s="23"/>
+      <c r="Z43" s="23"/>
+      <c r="AA43" s="23"/>
+    </row>
+    <row r="44" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="77" t="s">
+        <v>49</v>
+      </c>
+      <c r="B44" s="40"/>
+      <c r="C44" s="42" t="s">
+        <v>61</v>
+      </c>
+      <c r="D44" s="22"/>
+      <c r="E44" s="22"/>
+      <c r="F44" s="22"/>
+      <c r="G44" s="16">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J25" s="15"/>
-      <c r="K25" s="15"/>
-      <c r="L25" s="46"/>
-      <c r="M25" s="46"/>
-      <c r="N25" s="46"/>
-      <c r="O25" s="46"/>
-      <c r="P25" s="46"/>
-      <c r="Q25" s="46"/>
-      <c r="R25" s="46"/>
-      <c r="S25" s="46"/>
-      <c r="T25" s="46"/>
-      <c r="U25" s="46"/>
-      <c r="V25" s="46"/>
-      <c r="W25" s="46"/>
-      <c r="X25" s="46"/>
-      <c r="Y25" s="46"/>
-      <c r="Z25" s="46"/>
-      <c r="AA25" s="46"/>
-    </row>
-    <row r="26" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="B26" s="47">
-        <v>2</v>
-      </c>
-      <c r="C26" s="48" t="s">
+      <c r="H44" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J44" s="13"/>
+      <c r="K44" s="13"/>
+      <c r="L44" s="23"/>
+      <c r="M44" s="23"/>
+      <c r="N44" s="23"/>
+      <c r="O44" s="23"/>
+      <c r="P44" s="23"/>
+      <c r="Q44" s="23"/>
+      <c r="R44" s="23"/>
+      <c r="S44" s="23"/>
+      <c r="T44" s="23"/>
+      <c r="U44" s="23"/>
+      <c r="V44" s="23"/>
+      <c r="W44" s="23"/>
+      <c r="X44" s="23"/>
+      <c r="Y44" s="23"/>
+      <c r="Z44" s="23"/>
+      <c r="AA44" s="23"/>
+    </row>
+    <row r="45" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="D26" s="36"/>
-      <c r="E26" s="36"/>
-      <c r="F26" s="36"/>
-      <c r="G26" s="29">
-        <f t="shared" si="6"/>
+      <c r="B45" s="40"/>
+      <c r="C45" s="42" t="s">
+        <v>62</v>
+      </c>
+      <c r="D45" s="22"/>
+      <c r="E45" s="22"/>
+      <c r="F45" s="22"/>
+      <c r="G45" s="16">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H26" s="25">
-        <f t="shared" si="1"/>
+      <c r="H45" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J45" s="13"/>
+      <c r="K45" s="13"/>
+      <c r="L45" s="23"/>
+      <c r="M45" s="23"/>
+      <c r="N45" s="23"/>
+      <c r="O45" s="23"/>
+      <c r="P45" s="23"/>
+      <c r="Q45" s="23"/>
+      <c r="R45" s="23"/>
+      <c r="S45" s="23"/>
+      <c r="T45" s="23"/>
+      <c r="U45" s="23"/>
+      <c r="V45" s="23"/>
+      <c r="W45" s="23"/>
+      <c r="X45" s="23"/>
+      <c r="Y45" s="23"/>
+      <c r="Z45" s="23"/>
+      <c r="AA45" s="23"/>
+    </row>
+    <row r="46" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="77" t="s">
+        <v>51</v>
+      </c>
+      <c r="B46" s="40"/>
+      <c r="C46" s="43" t="s">
+        <v>63</v>
+      </c>
+      <c r="D46" s="22"/>
+      <c r="E46" s="22"/>
+      <c r="F46" s="22"/>
+      <c r="G46" s="16">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J26" s="15"/>
-      <c r="K26" s="15"/>
-      <c r="L26" s="46"/>
-      <c r="M26" s="46"/>
-      <c r="N26" s="46"/>
-      <c r="O26" s="46"/>
-      <c r="P26" s="46"/>
-      <c r="Q26" s="46"/>
-      <c r="R26" s="46"/>
-      <c r="S26" s="46"/>
-      <c r="T26" s="46"/>
-      <c r="U26" s="46"/>
-      <c r="V26" s="46"/>
-      <c r="W26" s="46"/>
-      <c r="X26" s="46"/>
-      <c r="Y26" s="46"/>
-      <c r="Z26" s="46"/>
-      <c r="AA26" s="46"/>
-    </row>
-    <row r="27" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="B27" s="47">
-        <v>3</v>
-      </c>
-      <c r="C27" s="49" t="s">
+      <c r="H46" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J46" s="13"/>
+      <c r="K46" s="13"/>
+      <c r="L46" s="23"/>
+      <c r="M46" s="23"/>
+      <c r="N46" s="23"/>
+      <c r="O46" s="23"/>
+      <c r="P46" s="23"/>
+      <c r="Q46" s="23"/>
+      <c r="R46" s="23"/>
+      <c r="S46" s="23"/>
+      <c r="T46" s="23"/>
+      <c r="U46" s="23"/>
+      <c r="V46" s="23"/>
+      <c r="W46" s="23"/>
+      <c r="X46" s="23"/>
+      <c r="Y46" s="23"/>
+      <c r="Z46" s="23"/>
+      <c r="AA46" s="23"/>
+    </row>
+    <row r="47" spans="1:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="77" t="s">
         <v>52</v>
       </c>
-      <c r="D27" s="36"/>
-      <c r="E27" s="36"/>
-      <c r="F27" s="36"/>
-      <c r="G27" s="29">
-        <f t="shared" si="6"/>
+      <c r="B47" s="40"/>
+      <c r="C47" s="44" t="s">
+        <v>95</v>
+      </c>
+      <c r="D47" s="22"/>
+      <c r="E47" s="22"/>
+      <c r="F47" s="22"/>
+      <c r="G47" s="16">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H27" s="25">
-        <f t="shared" si="1"/>
+      <c r="H47" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J47" s="13"/>
+      <c r="K47" s="13"/>
+      <c r="L47" s="23"/>
+      <c r="M47" s="23"/>
+      <c r="N47" s="23"/>
+      <c r="O47" s="23"/>
+      <c r="P47" s="23"/>
+      <c r="Q47" s="23"/>
+      <c r="R47" s="23"/>
+      <c r="S47" s="23"/>
+      <c r="T47" s="23"/>
+      <c r="U47" s="23"/>
+      <c r="V47" s="23"/>
+      <c r="W47" s="23"/>
+      <c r="X47" s="23"/>
+      <c r="Y47" s="23"/>
+      <c r="Z47" s="23"/>
+      <c r="AA47" s="23"/>
+    </row>
+    <row r="48" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="77" t="s">
+        <v>53</v>
+      </c>
+      <c r="B48" s="45">
+        <v>22</v>
+      </c>
+      <c r="C48" s="46" t="s">
+        <v>64</v>
+      </c>
+      <c r="D48" s="22"/>
+      <c r="E48" s="22"/>
+      <c r="F48" s="22"/>
+      <c r="G48" s="16">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J27" s="15"/>
-      <c r="K27" s="15"/>
-      <c r="L27" s="46"/>
-      <c r="M27" s="46"/>
-      <c r="N27" s="46"/>
-      <c r="O27" s="46"/>
-      <c r="P27" s="46"/>
-      <c r="Q27" s="46"/>
-      <c r="R27" s="46"/>
-      <c r="S27" s="46"/>
-      <c r="T27" s="46"/>
-      <c r="U27" s="46"/>
-      <c r="V27" s="46"/>
-      <c r="W27" s="46"/>
-      <c r="X27" s="46"/>
-      <c r="Y27" s="46"/>
-      <c r="Z27" s="46"/>
-      <c r="AA27" s="46"/>
-    </row>
-    <row r="28" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="B28" s="47">
-        <v>4</v>
-      </c>
-      <c r="C28" s="49" t="s">
+      <c r="H48" s="54" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J48" s="13"/>
+      <c r="K48" s="13"/>
+      <c r="L48" s="23"/>
+      <c r="M48" s="23"/>
+      <c r="N48" s="23"/>
+      <c r="O48" s="23"/>
+      <c r="P48" s="23"/>
+      <c r="Q48" s="23"/>
+      <c r="R48" s="23"/>
+      <c r="S48" s="23"/>
+      <c r="T48" s="23"/>
+      <c r="U48" s="23"/>
+      <c r="V48" s="23"/>
+      <c r="W48" s="23"/>
+      <c r="X48" s="23"/>
+      <c r="Y48" s="23"/>
+      <c r="Z48" s="23"/>
+      <c r="AA48" s="23"/>
+    </row>
+    <row r="49" spans="1:27" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="77" t="s">
         <v>54</v>
       </c>
-      <c r="D28" s="50"/>
-      <c r="E28" s="50"/>
-      <c r="F28" s="50"/>
-      <c r="G28" s="29">
-        <f t="shared" si="6"/>
+      <c r="B49" s="70" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" s="75" t="s">
+        <v>65</v>
+      </c>
+      <c r="D49" s="62">
+        <f>SUM(D50:D62)</f>
         <v>0</v>
       </c>
-      <c r="H28" s="25">
-        <f t="shared" si="1"/>
+      <c r="E49" s="62">
+        <f t="shared" ref="E49:F49" si="8">SUM(E50:E62)</f>
         <v>0</v>
       </c>
-      <c r="J28" s="15"/>
-      <c r="K28" s="15"/>
-      <c r="L28" s="46"/>
-      <c r="M28" s="46"/>
-      <c r="N28" s="46"/>
-      <c r="O28" s="46"/>
-      <c r="P28" s="46"/>
-      <c r="Q28" s="46"/>
-      <c r="R28" s="46"/>
-      <c r="S28" s="46"/>
-      <c r="T28" s="46"/>
-      <c r="U28" s="46"/>
-      <c r="V28" s="46"/>
-      <c r="W28" s="46"/>
-      <c r="X28" s="46"/>
-      <c r="Y28" s="46"/>
-      <c r="Z28" s="46"/>
-      <c r="AA28" s="46"/>
-    </row>
-    <row r="29" spans="1:27" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="B29" s="47">
-        <v>5</v>
-      </c>
-      <c r="C29" s="51" t="s">
-        <v>56</v>
-      </c>
-      <c r="D29" s="50"/>
-      <c r="E29" s="50"/>
-      <c r="F29" s="50"/>
-      <c r="G29" s="29">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H29" s="25">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J29" s="15"/>
-      <c r="K29" s="15"/>
-      <c r="L29" s="46"/>
-      <c r="M29" s="46"/>
-      <c r="N29" s="46"/>
-      <c r="O29" s="46"/>
-      <c r="P29" s="46"/>
-      <c r="Q29" s="46"/>
-      <c r="R29" s="46"/>
-      <c r="S29" s="46"/>
-      <c r="T29" s="46"/>
-      <c r="U29" s="46"/>
-      <c r="V29" s="46"/>
-      <c r="W29" s="46"/>
-      <c r="X29" s="46"/>
-      <c r="Y29" s="46"/>
-      <c r="Z29" s="46"/>
-      <c r="AA29" s="46"/>
-    </row>
-    <row r="30" spans="1:27" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="B30" s="47">
-        <v>6</v>
-      </c>
-      <c r="C30" s="51" t="s">
-        <v>58</v>
-      </c>
-      <c r="D30" s="50"/>
-      <c r="E30" s="50"/>
-      <c r="F30" s="50"/>
-      <c r="G30" s="29">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H30" s="25">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J30" s="15"/>
-      <c r="K30" s="15"/>
-      <c r="L30" s="46"/>
-      <c r="M30" s="46"/>
-      <c r="N30" s="46"/>
-      <c r="O30" s="46"/>
-      <c r="P30" s="46"/>
-      <c r="Q30" s="46"/>
-      <c r="R30" s="46"/>
-      <c r="S30" s="46"/>
-      <c r="T30" s="46"/>
-      <c r="U30" s="46"/>
-      <c r="V30" s="46"/>
-      <c r="W30" s="46"/>
-      <c r="X30" s="46"/>
-      <c r="Y30" s="46"/>
-      <c r="Z30" s="46"/>
-      <c r="AA30" s="46"/>
-    </row>
-    <row r="31" spans="1:27" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="B31" s="47">
-        <v>7</v>
-      </c>
-      <c r="C31" s="51" t="s">
-        <v>60</v>
-      </c>
-      <c r="D31" s="50"/>
-      <c r="E31" s="50"/>
-      <c r="F31" s="50"/>
-      <c r="G31" s="29">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H31" s="25">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J31" s="15"/>
-      <c r="K31" s="15"/>
-      <c r="L31" s="46"/>
-      <c r="M31" s="46"/>
-      <c r="N31" s="46"/>
-      <c r="O31" s="46"/>
-      <c r="P31" s="46"/>
-      <c r="Q31" s="46"/>
-      <c r="R31" s="46"/>
-      <c r="S31" s="46"/>
-      <c r="T31" s="46"/>
-      <c r="U31" s="46"/>
-      <c r="V31" s="46"/>
-      <c r="W31" s="46"/>
-      <c r="X31" s="46"/>
-      <c r="Y31" s="46"/>
-      <c r="Z31" s="46"/>
-      <c r="AA31" s="46"/>
-    </row>
-    <row r="32" spans="1:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="B32" s="52" t="s">
-        <v>29</v>
-      </c>
-      <c r="C32" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="D32" s="50"/>
-      <c r="E32" s="50"/>
-      <c r="F32" s="50"/>
-      <c r="G32" s="29">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H32" s="25">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J32" s="15"/>
-      <c r="K32" s="15"/>
-      <c r="L32" s="46"/>
-      <c r="M32" s="46"/>
-      <c r="N32" s="46"/>
-      <c r="O32" s="46"/>
-      <c r="P32" s="46"/>
-      <c r="Q32" s="46"/>
-      <c r="R32" s="46"/>
-      <c r="S32" s="46"/>
-      <c r="T32" s="46"/>
-      <c r="U32" s="46"/>
-      <c r="V32" s="46"/>
-      <c r="W32" s="46"/>
-      <c r="X32" s="46"/>
-      <c r="Y32" s="46"/>
-      <c r="Z32" s="46"/>
-      <c r="AA32" s="46"/>
-    </row>
-    <row r="33" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="B33" s="47">
-        <v>8</v>
-      </c>
-      <c r="C33" s="51" t="s">
-        <v>64</v>
-      </c>
-      <c r="D33" s="50"/>
-      <c r="E33" s="50"/>
-      <c r="F33" s="50"/>
-      <c r="G33" s="29">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H33" s="25">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J33" s="15"/>
-      <c r="K33" s="15"/>
-      <c r="L33" s="46"/>
-      <c r="M33" s="46"/>
-      <c r="N33" s="46"/>
-      <c r="O33" s="46"/>
-      <c r="P33" s="46"/>
-      <c r="Q33" s="46"/>
-      <c r="R33" s="46"/>
-      <c r="S33" s="46"/>
-      <c r="T33" s="46"/>
-      <c r="U33" s="46"/>
-      <c r="V33" s="46"/>
-      <c r="W33" s="46"/>
-      <c r="X33" s="46"/>
-      <c r="Y33" s="46"/>
-      <c r="Z33" s="46"/>
-      <c r="AA33" s="46"/>
-    </row>
-    <row r="34" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="B34" s="47">
-        <v>9</v>
-      </c>
-      <c r="C34" s="51" t="s">
-        <v>66</v>
-      </c>
-      <c r="D34" s="50"/>
-      <c r="E34" s="50"/>
-      <c r="F34" s="50"/>
-      <c r="G34" s="29">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H34" s="25">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J34" s="15"/>
-      <c r="K34" s="15"/>
-      <c r="L34" s="46"/>
-      <c r="M34" s="46"/>
-      <c r="N34" s="46"/>
-      <c r="O34" s="46"/>
-      <c r="P34" s="46"/>
-      <c r="Q34" s="46"/>
-      <c r="R34" s="46"/>
-      <c r="S34" s="46"/>
-      <c r="T34" s="46"/>
-      <c r="U34" s="46"/>
-      <c r="V34" s="46"/>
-      <c r="W34" s="46"/>
-      <c r="X34" s="46"/>
-      <c r="Y34" s="46"/>
-      <c r="Z34" s="46"/>
-      <c r="AA34" s="46"/>
-    </row>
-    <row r="35" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="B35" s="47">
-        <v>10</v>
-      </c>
-      <c r="C35" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="D35" s="50"/>
-      <c r="E35" s="50"/>
-      <c r="F35" s="50"/>
-      <c r="G35" s="29">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H35" s="25">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J35" s="15"/>
-      <c r="K35" s="15"/>
-      <c r="L35" s="46"/>
-      <c r="M35" s="46"/>
-      <c r="N35" s="46"/>
-      <c r="O35" s="46"/>
-      <c r="P35" s="46"/>
-      <c r="Q35" s="46"/>
-      <c r="R35" s="46"/>
-      <c r="S35" s="46"/>
-      <c r="T35" s="46"/>
-      <c r="U35" s="46"/>
-      <c r="V35" s="46"/>
-      <c r="W35" s="46"/>
-      <c r="X35" s="46"/>
-      <c r="Y35" s="46"/>
-      <c r="Z35" s="46"/>
-      <c r="AA35" s="46"/>
-    </row>
-    <row r="36" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="B36" s="47">
-        <v>11</v>
-      </c>
-      <c r="C36" s="51" t="s">
-        <v>70</v>
-      </c>
-      <c r="D36" s="50"/>
-      <c r="E36" s="50"/>
-      <c r="F36" s="50"/>
-      <c r="G36" s="29">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H36" s="25">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J36" s="15"/>
-      <c r="K36" s="15"/>
-      <c r="L36" s="46"/>
-      <c r="M36" s="46"/>
-      <c r="N36" s="46"/>
-      <c r="O36" s="46"/>
-      <c r="P36" s="46"/>
-      <c r="Q36" s="46"/>
-      <c r="R36" s="46"/>
-      <c r="S36" s="46"/>
-      <c r="T36" s="46"/>
-      <c r="U36" s="46"/>
-      <c r="V36" s="46"/>
-      <c r="W36" s="46"/>
-      <c r="X36" s="46"/>
-      <c r="Y36" s="46"/>
-      <c r="Z36" s="46"/>
-      <c r="AA36" s="46"/>
-    </row>
-    <row r="37" spans="1:27" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="B37" s="47">
-        <v>12</v>
-      </c>
-      <c r="C37" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="D37" s="50"/>
-      <c r="E37" s="50"/>
-      <c r="F37" s="50"/>
-      <c r="G37" s="29">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H37" s="25">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J37" s="15"/>
-      <c r="K37" s="15"/>
-      <c r="L37" s="46"/>
-      <c r="M37" s="46"/>
-      <c r="N37" s="46"/>
-      <c r="O37" s="46"/>
-      <c r="P37" s="46"/>
-      <c r="Q37" s="46"/>
-      <c r="R37" s="46"/>
-      <c r="S37" s="46"/>
-      <c r="T37" s="46"/>
-      <c r="U37" s="46"/>
-      <c r="V37" s="46"/>
-      <c r="W37" s="46"/>
-      <c r="X37" s="46"/>
-      <c r="Y37" s="46"/>
-      <c r="Z37" s="46"/>
-      <c r="AA37" s="46"/>
-    </row>
-    <row r="38" spans="1:27" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="B38" s="47">
-        <v>13</v>
-      </c>
-      <c r="C38" s="49" t="s">
-        <v>74</v>
-      </c>
-      <c r="D38" s="50"/>
-      <c r="E38" s="50"/>
-      <c r="F38" s="50"/>
-      <c r="G38" s="29">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H38" s="25">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J38" s="15"/>
-      <c r="K38" s="15"/>
-      <c r="L38" s="46"/>
-      <c r="M38" s="46"/>
-      <c r="N38" s="46"/>
-      <c r="O38" s="46"/>
-      <c r="P38" s="46"/>
-      <c r="Q38" s="46"/>
-      <c r="R38" s="46"/>
-      <c r="S38" s="46"/>
-      <c r="T38" s="46"/>
-      <c r="U38" s="46"/>
-      <c r="V38" s="46"/>
-      <c r="W38" s="46"/>
-      <c r="X38" s="46"/>
-      <c r="Y38" s="46"/>
-      <c r="Z38" s="46"/>
-      <c r="AA38" s="46"/>
-    </row>
-    <row r="39" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="B39" s="47">
-        <v>14</v>
-      </c>
-      <c r="C39" s="49" t="s">
-        <v>76</v>
-      </c>
-      <c r="D39" s="50"/>
-      <c r="E39" s="50"/>
-      <c r="F39" s="50"/>
-      <c r="G39" s="29">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H39" s="25">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J39" s="15"/>
-      <c r="K39" s="15"/>
-      <c r="L39" s="46"/>
-      <c r="M39" s="46"/>
-      <c r="N39" s="46"/>
-      <c r="O39" s="46"/>
-      <c r="P39" s="46"/>
-      <c r="Q39" s="46"/>
-      <c r="R39" s="46"/>
-      <c r="S39" s="46"/>
-      <c r="T39" s="46"/>
-      <c r="U39" s="46"/>
-      <c r="V39" s="46"/>
-      <c r="W39" s="46"/>
-      <c r="X39" s="46"/>
-      <c r="Y39" s="46"/>
-      <c r="Z39" s="46"/>
-      <c r="AA39" s="46"/>
-    </row>
-    <row r="40" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="B40" s="47">
-        <v>15</v>
-      </c>
-      <c r="C40" s="51" t="s">
-        <v>78</v>
-      </c>
-      <c r="D40" s="36"/>
-      <c r="E40" s="36"/>
-      <c r="F40" s="36"/>
-      <c r="G40" s="29">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H40" s="25">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J40" s="15"/>
-      <c r="K40" s="15"/>
-      <c r="L40" s="46"/>
-      <c r="M40" s="46"/>
-      <c r="N40" s="46"/>
-      <c r="O40" s="46"/>
-      <c r="P40" s="46"/>
-      <c r="Q40" s="46"/>
-      <c r="R40" s="46"/>
-      <c r="S40" s="46"/>
-      <c r="T40" s="46"/>
-      <c r="U40" s="46"/>
-      <c r="V40" s="46"/>
-      <c r="W40" s="46"/>
-      <c r="X40" s="46"/>
-      <c r="Y40" s="46"/>
-      <c r="Z40" s="46"/>
-      <c r="AA40" s="46"/>
-    </row>
-    <row r="41" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="B41" s="47">
-        <v>16</v>
-      </c>
-      <c r="C41" s="51" t="s">
-        <v>80</v>
-      </c>
-      <c r="D41" s="50"/>
-      <c r="E41" s="50"/>
-      <c r="F41" s="50"/>
-      <c r="G41" s="29">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H41" s="25">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J41" s="15"/>
-      <c r="K41" s="15"/>
-      <c r="L41" s="46"/>
-      <c r="M41" s="46"/>
-      <c r="N41" s="46"/>
-      <c r="O41" s="46"/>
-      <c r="P41" s="46"/>
-      <c r="Q41" s="46"/>
-      <c r="R41" s="46"/>
-      <c r="S41" s="46"/>
-      <c r="T41" s="46"/>
-      <c r="U41" s="46"/>
-      <c r="V41" s="46"/>
-      <c r="W41" s="46"/>
-      <c r="X41" s="46"/>
-      <c r="Y41" s="46"/>
-      <c r="Z41" s="46"/>
-      <c r="AA41" s="46"/>
-    </row>
-    <row r="42" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="B42" s="47">
-        <v>17</v>
-      </c>
-      <c r="C42" s="49" t="s">
-        <v>82</v>
-      </c>
-      <c r="D42" s="50"/>
-      <c r="E42" s="50"/>
-      <c r="F42" s="50"/>
-      <c r="G42" s="29">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H42" s="25">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J42" s="15"/>
-      <c r="K42" s="15"/>
-      <c r="L42" s="46"/>
-      <c r="M42" s="46"/>
-      <c r="N42" s="46"/>
-      <c r="O42" s="46"/>
-      <c r="P42" s="46"/>
-      <c r="Q42" s="46"/>
-      <c r="R42" s="46"/>
-      <c r="S42" s="46"/>
-      <c r="T42" s="46"/>
-      <c r="U42" s="46"/>
-      <c r="V42" s="46"/>
-      <c r="W42" s="46"/>
-      <c r="X42" s="46"/>
-      <c r="Y42" s="46"/>
-      <c r="Z42" s="46"/>
-      <c r="AA42" s="46"/>
-    </row>
-    <row r="43" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="B43" s="47">
-        <v>18</v>
-      </c>
-      <c r="C43" s="51" t="s">
-        <v>84</v>
-      </c>
-      <c r="D43" s="50"/>
-      <c r="E43" s="50"/>
-      <c r="F43" s="50"/>
-      <c r="G43" s="29">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H43" s="25">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J43" s="15"/>
-      <c r="K43" s="15"/>
-      <c r="L43" s="46"/>
-      <c r="M43" s="46"/>
-      <c r="N43" s="46"/>
-      <c r="O43" s="46"/>
-      <c r="P43" s="46"/>
-      <c r="Q43" s="46"/>
-      <c r="R43" s="46"/>
-      <c r="S43" s="46"/>
-      <c r="T43" s="46"/>
-      <c r="U43" s="46"/>
-      <c r="V43" s="46"/>
-      <c r="W43" s="46"/>
-      <c r="X43" s="46"/>
-      <c r="Y43" s="46"/>
-      <c r="Z43" s="46"/>
-      <c r="AA43" s="46"/>
-    </row>
-    <row r="44" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="B44" s="47">
-        <v>19</v>
-      </c>
-      <c r="C44" s="49" t="s">
-        <v>86</v>
-      </c>
-      <c r="D44" s="50"/>
-      <c r="E44" s="50"/>
-      <c r="F44" s="50"/>
-      <c r="G44" s="29">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H44" s="25">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J44" s="15"/>
-      <c r="K44" s="15"/>
-      <c r="L44" s="46"/>
-      <c r="M44" s="46"/>
-      <c r="N44" s="46"/>
-      <c r="O44" s="46"/>
-      <c r="P44" s="46"/>
-      <c r="Q44" s="46"/>
-      <c r="R44" s="46"/>
-      <c r="S44" s="46"/>
-      <c r="T44" s="46"/>
-      <c r="U44" s="46"/>
-      <c r="V44" s="46"/>
-      <c r="W44" s="46"/>
-      <c r="X44" s="46"/>
-      <c r="Y44" s="46"/>
-      <c r="Z44" s="46"/>
-      <c r="AA44" s="46"/>
-    </row>
-    <row r="45" spans="1:27" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="B45" s="47">
-        <v>20</v>
-      </c>
-      <c r="C45" s="48" t="s">
-        <v>88</v>
-      </c>
-      <c r="D45" s="36"/>
-      <c r="E45" s="36"/>
-      <c r="F45" s="36"/>
-      <c r="G45" s="29">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H45" s="25">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J45" s="15"/>
-      <c r="K45" s="15"/>
-      <c r="L45" s="46"/>
-      <c r="M45" s="46"/>
-      <c r="N45" s="46"/>
-      <c r="O45" s="46"/>
-      <c r="P45" s="46"/>
-      <c r="Q45" s="46"/>
-      <c r="R45" s="46"/>
-      <c r="S45" s="46"/>
-      <c r="T45" s="46"/>
-      <c r="U45" s="46"/>
-      <c r="V45" s="46"/>
-      <c r="W45" s="46"/>
-      <c r="X45" s="46"/>
-      <c r="Y45" s="46"/>
-      <c r="Z45" s="46"/>
-      <c r="AA45" s="46"/>
-    </row>
-    <row r="46" spans="1:27" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="B46" s="79">
-        <v>21</v>
-      </c>
-      <c r="C46" s="84" t="s">
-        <v>90</v>
-      </c>
-      <c r="D46" s="50"/>
-      <c r="E46" s="50"/>
-      <c r="F46" s="50"/>
-      <c r="G46" s="29">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H46" s="25">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I46" s="81"/>
-      <c r="J46" s="15"/>
-      <c r="K46" s="15"/>
-      <c r="L46" s="46"/>
-      <c r="M46" s="46"/>
-      <c r="N46" s="46"/>
-      <c r="O46" s="46"/>
-      <c r="P46" s="46"/>
-      <c r="Q46" s="46"/>
-      <c r="R46" s="46"/>
-      <c r="S46" s="46"/>
-      <c r="T46" s="46"/>
-      <c r="U46" s="46"/>
-      <c r="V46" s="46"/>
-      <c r="W46" s="46"/>
-      <c r="X46" s="46"/>
-      <c r="Y46" s="46"/>
-      <c r="Z46" s="46"/>
-      <c r="AA46" s="46"/>
-    </row>
-    <row r="47" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="B47" s="79"/>
-      <c r="C47" s="80" t="s">
-        <v>92</v>
-      </c>
-      <c r="D47" s="36"/>
-      <c r="E47" s="36"/>
-      <c r="F47" s="36"/>
-      <c r="G47" s="29">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H47" s="25">
-        <f t="shared" ref="H47:H97" si="7">IFERROR(G47/E47,0)</f>
-        <v>0</v>
-      </c>
-      <c r="I47" s="81"/>
-      <c r="J47" s="15"/>
-      <c r="K47" s="15"/>
-      <c r="L47" s="46"/>
-      <c r="M47" s="46"/>
-      <c r="N47" s="46"/>
-      <c r="O47" s="46"/>
-      <c r="P47" s="46"/>
-      <c r="Q47" s="46"/>
-      <c r="R47" s="46"/>
-      <c r="S47" s="46"/>
-      <c r="T47" s="46"/>
-      <c r="U47" s="46"/>
-      <c r="V47" s="46"/>
-      <c r="W47" s="46"/>
-      <c r="X47" s="46"/>
-      <c r="Y47" s="46"/>
-      <c r="Z47" s="46"/>
-      <c r="AA47" s="46"/>
-    </row>
-    <row r="48" spans="1:27" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="B48" s="79">
-        <v>22</v>
-      </c>
-      <c r="C48" s="121" t="s">
-        <v>183</v>
-      </c>
-      <c r="D48" s="36"/>
-      <c r="E48" s="36"/>
-      <c r="F48" s="36"/>
-      <c r="G48" s="29">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H48" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="I48" s="81"/>
-      <c r="J48" s="15"/>
-      <c r="K48" s="15"/>
-      <c r="L48" s="46"/>
-      <c r="M48" s="46"/>
-      <c r="N48" s="46"/>
-      <c r="O48" s="46"/>
-      <c r="P48" s="46"/>
-      <c r="Q48" s="46"/>
-      <c r="R48" s="46"/>
-      <c r="S48" s="46"/>
-      <c r="T48" s="46"/>
-      <c r="U48" s="46"/>
-      <c r="V48" s="46"/>
-      <c r="W48" s="46"/>
-      <c r="X48" s="46"/>
-      <c r="Y48" s="46"/>
-      <c r="Z48" s="46"/>
-      <c r="AA48" s="46"/>
-    </row>
-    <row r="49" spans="1:27" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="B49" s="79">
-        <v>23</v>
-      </c>
-      <c r="C49" s="85" t="s">
-        <v>95</v>
-      </c>
-      <c r="D49" s="36"/>
-      <c r="E49" s="36"/>
-      <c r="F49" s="36"/>
-      <c r="G49" s="29">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H49" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="I49" s="81"/>
-      <c r="J49" s="15"/>
-      <c r="K49" s="15"/>
-      <c r="L49" s="46"/>
-      <c r="M49" s="46"/>
-      <c r="N49" s="46"/>
-      <c r="O49" s="46"/>
-      <c r="P49" s="46"/>
-      <c r="Q49" s="46"/>
-      <c r="R49" s="46"/>
-      <c r="S49" s="46"/>
-      <c r="T49" s="46"/>
-      <c r="U49" s="46"/>
-      <c r="V49" s="46"/>
-      <c r="W49" s="46"/>
-      <c r="X49" s="46"/>
-      <c r="Y49" s="46"/>
-      <c r="Z49" s="46"/>
-      <c r="AA49" s="46"/>
-    </row>
-    <row r="50" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="B50" s="47">
-        <v>24</v>
-      </c>
-      <c r="C50" s="48" t="s">
-        <v>97</v>
-      </c>
-      <c r="D50" s="36"/>
-      <c r="E50" s="36"/>
-      <c r="F50" s="36"/>
-      <c r="G50" s="29">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H50" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J50" s="15"/>
-      <c r="K50" s="15"/>
-      <c r="L50" s="46"/>
-      <c r="M50" s="46"/>
-      <c r="N50" s="46"/>
-      <c r="O50" s="46"/>
-      <c r="P50" s="46"/>
-      <c r="Q50" s="46"/>
-      <c r="R50" s="46"/>
-      <c r="S50" s="46"/>
-      <c r="T50" s="46"/>
-      <c r="U50" s="46"/>
-      <c r="V50" s="46"/>
-      <c r="W50" s="46"/>
-      <c r="X50" s="46"/>
-      <c r="Y50" s="46"/>
-      <c r="Z50" s="46"/>
-      <c r="AA50" s="46"/>
-    </row>
-    <row r="51" spans="1:27" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A51" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="B51" s="47">
-        <v>25</v>
-      </c>
-      <c r="C51" s="48" t="s">
-        <v>99</v>
-      </c>
-      <c r="D51" s="36"/>
-      <c r="E51" s="36"/>
-      <c r="F51" s="36"/>
-      <c r="G51" s="29">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H51" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J51" s="15"/>
-      <c r="K51" s="15"/>
-      <c r="L51" s="46"/>
-      <c r="M51" s="46"/>
-      <c r="N51" s="46"/>
-      <c r="O51" s="46"/>
-      <c r="P51" s="46"/>
-      <c r="Q51" s="46"/>
-      <c r="R51" s="46"/>
-      <c r="S51" s="46"/>
-      <c r="T51" s="46"/>
-      <c r="U51" s="46"/>
-      <c r="V51" s="46"/>
-      <c r="W51" s="46"/>
-      <c r="X51" s="46"/>
-      <c r="Y51" s="46"/>
-      <c r="Z51" s="46"/>
-      <c r="AA51" s="46"/>
-    </row>
-    <row r="52" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B52" s="55">
-        <v>26</v>
-      </c>
-      <c r="C52" s="56" t="s">
-        <v>101</v>
-      </c>
-      <c r="D52" s="28">
-        <f t="shared" ref="D52:G52" si="8">SUM(D53:D59)</f>
-        <v>0</v>
-      </c>
-      <c r="E52" s="28">
+      <c r="F49" s="62">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F52" s="28">
-        <f t="shared" si="8"/>
+      <c r="G49" s="67">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G52" s="28">
-        <f t="shared" si="8"/>
+      <c r="H49" s="54" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J49" s="13"/>
+      <c r="K49" s="13"/>
+      <c r="L49" s="58"/>
+      <c r="M49" s="58"/>
+      <c r="N49" s="58"/>
+      <c r="O49" s="58"/>
+      <c r="P49" s="58"/>
+      <c r="Q49" s="58"/>
+      <c r="R49" s="58"/>
+      <c r="S49" s="58"/>
+      <c r="T49" s="58"/>
+      <c r="U49" s="58"/>
+      <c r="V49" s="58"/>
+      <c r="W49" s="58"/>
+      <c r="X49" s="58"/>
+      <c r="Y49" s="58"/>
+      <c r="Z49" s="58"/>
+      <c r="AA49" s="58"/>
+    </row>
+    <row r="50" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="B50" s="34">
+        <v>1</v>
+      </c>
+      <c r="C50" s="47" t="str">
+        <f>C22</f>
+        <v>Cho vay hộ nghèo (theo NĐ 78/2002/NĐ-CP)</v>
+      </c>
+      <c r="D50" s="22"/>
+      <c r="E50" s="22"/>
+      <c r="F50" s="22"/>
+      <c r="G50" s="16">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H52" s="25">
-        <f t="shared" si="7"/>
+      <c r="H50" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J50" s="13"/>
+      <c r="K50" s="13"/>
+      <c r="L50" s="25"/>
+      <c r="M50" s="25"/>
+      <c r="N50" s="25"/>
+      <c r="O50" s="25"/>
+      <c r="P50" s="25"/>
+      <c r="Q50" s="25"/>
+      <c r="R50" s="25"/>
+      <c r="S50" s="25"/>
+      <c r="T50" s="25"/>
+      <c r="U50" s="25"/>
+      <c r="V50" s="25"/>
+      <c r="W50" s="25"/>
+      <c r="X50" s="25"/>
+      <c r="Y50" s="25"/>
+      <c r="Z50" s="25"/>
+      <c r="AA50" s="25"/>
+    </row>
+    <row r="51" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="77" t="s">
+        <v>56</v>
+      </c>
+      <c r="B51" s="34">
+        <v>2</v>
+      </c>
+      <c r="C51" s="36" t="s">
+        <v>77</v>
+      </c>
+      <c r="D51" s="22"/>
+      <c r="E51" s="22"/>
+      <c r="F51" s="22"/>
+      <c r="G51" s="16">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J52" s="15"/>
-      <c r="K52" s="15"/>
-      <c r="L52" s="46"/>
-      <c r="M52" s="46"/>
-      <c r="N52" s="46"/>
-      <c r="O52" s="46"/>
-      <c r="P52" s="46"/>
-      <c r="Q52" s="46"/>
-      <c r="R52" s="46"/>
-      <c r="S52" s="46"/>
-      <c r="T52" s="46"/>
-      <c r="U52" s="46"/>
-      <c r="V52" s="46"/>
-      <c r="W52" s="46"/>
-      <c r="X52" s="46"/>
-      <c r="Y52" s="46"/>
-      <c r="Z52" s="46"/>
-      <c r="AA52" s="46"/>
-    </row>
-    <row r="53" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="B53" s="52" t="s">
-        <v>29</v>
-      </c>
-      <c r="C53" s="57" t="s">
-        <v>103</v>
-      </c>
-      <c r="D53" s="36"/>
-      <c r="E53" s="36"/>
-      <c r="F53" s="36"/>
-      <c r="G53" s="29">
-        <f t="shared" ref="G53:G60" si="9">F53-D53</f>
+      <c r="H51" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J51" s="13"/>
+      <c r="K51" s="13"/>
+      <c r="L51" s="25"/>
+      <c r="M51" s="25"/>
+      <c r="N51" s="25"/>
+      <c r="O51" s="25"/>
+      <c r="P51" s="25"/>
+      <c r="Q51" s="25"/>
+      <c r="R51" s="25"/>
+      <c r="S51" s="25"/>
+      <c r="T51" s="25"/>
+      <c r="U51" s="25"/>
+      <c r="V51" s="25"/>
+      <c r="W51" s="25"/>
+      <c r="X51" s="25"/>
+      <c r="Y51" s="25"/>
+      <c r="Z51" s="25"/>
+      <c r="AA51" s="25"/>
+    </row>
+    <row r="52" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="77" t="s">
+        <v>57</v>
+      </c>
+      <c r="B52" s="34">
+        <v>3</v>
+      </c>
+      <c r="C52" s="37" t="str">
+        <f>C24</f>
+        <v>Cho vay hộ mới thoát nghèo (theo QĐ 28/2015/QĐ-TTg)</v>
+      </c>
+      <c r="D52" s="24"/>
+      <c r="E52" s="24"/>
+      <c r="F52" s="24"/>
+      <c r="G52" s="16">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H53" s="25">
-        <f t="shared" si="7"/>
+      <c r="H52" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J52" s="13"/>
+      <c r="K52" s="13"/>
+      <c r="L52" s="25"/>
+      <c r="M52" s="25"/>
+      <c r="N52" s="25"/>
+      <c r="O52" s="25"/>
+      <c r="P52" s="25"/>
+      <c r="Q52" s="25"/>
+      <c r="R52" s="25"/>
+      <c r="S52" s="25"/>
+      <c r="T52" s="25"/>
+      <c r="U52" s="25"/>
+      <c r="V52" s="25"/>
+      <c r="W52" s="25"/>
+      <c r="X52" s="25"/>
+      <c r="Y52" s="25"/>
+      <c r="Z52" s="25"/>
+      <c r="AA52" s="25"/>
+    </row>
+    <row r="53" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="77" t="s">
+        <v>117</v>
+      </c>
+      <c r="B53" s="34">
+        <v>4</v>
+      </c>
+      <c r="C53" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="D53" s="24"/>
+      <c r="E53" s="24"/>
+      <c r="F53" s="24"/>
+      <c r="G53" s="16">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J53" s="15"/>
-      <c r="K53" s="15"/>
-      <c r="L53" s="58"/>
-      <c r="M53" s="58"/>
-      <c r="N53" s="58"/>
-      <c r="O53" s="58"/>
-      <c r="P53" s="58"/>
-      <c r="Q53" s="58"/>
-      <c r="R53" s="58"/>
-      <c r="S53" s="58"/>
-      <c r="T53" s="58"/>
-      <c r="U53" s="58"/>
-      <c r="V53" s="58"/>
-      <c r="W53" s="58"/>
-      <c r="X53" s="58"/>
-      <c r="Y53" s="58"/>
-      <c r="Z53" s="58"/>
-      <c r="AA53" s="58"/>
-    </row>
-    <row r="54" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="B54" s="52"/>
-      <c r="C54" s="57" t="s">
-        <v>105</v>
-      </c>
-      <c r="D54" s="36"/>
-      <c r="E54" s="36"/>
-      <c r="F54" s="36"/>
-      <c r="G54" s="29">
-        <f t="shared" si="9"/>
+      <c r="H53" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J53" s="13"/>
+      <c r="K53" s="13"/>
+      <c r="L53" s="25"/>
+      <c r="M53" s="25"/>
+      <c r="N53" s="25"/>
+      <c r="O53" s="25"/>
+      <c r="P53" s="25"/>
+      <c r="Q53" s="25"/>
+      <c r="R53" s="25"/>
+      <c r="S53" s="25"/>
+      <c r="T53" s="25"/>
+      <c r="U53" s="25"/>
+      <c r="V53" s="25"/>
+      <c r="W53" s="25"/>
+      <c r="X53" s="25"/>
+      <c r="Y53" s="25"/>
+      <c r="Z53" s="25"/>
+      <c r="AA53" s="25"/>
+    </row>
+    <row r="54" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="77" t="s">
+        <v>118</v>
+      </c>
+      <c r="B54" s="34">
+        <v>5</v>
+      </c>
+      <c r="C54" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="D54" s="22"/>
+      <c r="E54" s="22"/>
+      <c r="F54" s="22"/>
+      <c r="G54" s="16">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H54" s="25">
-        <f t="shared" si="7"/>
+      <c r="H54" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J54" s="13"/>
+      <c r="K54" s="13"/>
+      <c r="L54" s="25"/>
+      <c r="M54" s="25"/>
+      <c r="N54" s="25"/>
+      <c r="O54" s="25"/>
+      <c r="P54" s="25"/>
+      <c r="Q54" s="25"/>
+      <c r="R54" s="25"/>
+      <c r="S54" s="25"/>
+      <c r="T54" s="25"/>
+      <c r="U54" s="25"/>
+      <c r="V54" s="25"/>
+      <c r="W54" s="25"/>
+      <c r="X54" s="25"/>
+      <c r="Y54" s="25"/>
+      <c r="Z54" s="25"/>
+      <c r="AA54" s="25"/>
+    </row>
+    <row r="55" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="77" t="s">
+        <v>119</v>
+      </c>
+      <c r="B55" s="34">
+        <v>6</v>
+      </c>
+      <c r="C55" s="37" t="str">
+        <f>C28</f>
+        <v>Cho vay người lao động đi làm việc ở nước ngoài (theo QĐ 365/QĐ-NHNN, NĐ 61/2015/NĐ-CP, QĐ 12/2024/QĐ-TTg, QĐ 16/2023/QĐ-TTg…)</v>
+      </c>
+      <c r="D55" s="24"/>
+      <c r="E55" s="24"/>
+      <c r="F55" s="24"/>
+      <c r="G55" s="16">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J54" s="15"/>
-      <c r="K54" s="15"/>
-      <c r="L54" s="58"/>
-      <c r="M54" s="58"/>
-      <c r="N54" s="58"/>
-      <c r="O54" s="58"/>
-      <c r="P54" s="58"/>
-      <c r="Q54" s="58"/>
-      <c r="R54" s="58"/>
-      <c r="S54" s="58"/>
-      <c r="T54" s="58"/>
-      <c r="U54" s="58"/>
-      <c r="V54" s="58"/>
-      <c r="W54" s="58"/>
-      <c r="X54" s="58"/>
-      <c r="Y54" s="58"/>
-      <c r="Z54" s="58"/>
-      <c r="AA54" s="58"/>
-    </row>
-    <row r="55" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="B55" s="52"/>
-      <c r="C55" s="54" t="s">
+      <c r="H55" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J55" s="13"/>
+      <c r="K55" s="13"/>
+      <c r="L55" s="25"/>
+      <c r="M55" s="25"/>
+      <c r="N55" s="25"/>
+      <c r="O55" s="25"/>
+      <c r="P55" s="25"/>
+      <c r="Q55" s="25"/>
+      <c r="R55" s="25"/>
+      <c r="S55" s="25"/>
+      <c r="T55" s="25"/>
+      <c r="U55" s="25"/>
+      <c r="V55" s="25"/>
+      <c r="W55" s="25"/>
+      <c r="X55" s="25"/>
+      <c r="Y55" s="25"/>
+      <c r="Z55" s="25"/>
+      <c r="AA55" s="25"/>
+    </row>
+    <row r="56" spans="1:27" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="77" t="s">
+        <v>120</v>
+      </c>
+      <c r="B56" s="34">
+        <v>7</v>
+      </c>
+      <c r="C56" s="38" t="s">
+        <v>83</v>
+      </c>
+      <c r="D56" s="24"/>
+      <c r="E56" s="24"/>
+      <c r="F56" s="24"/>
+      <c r="G56" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H56" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J56" s="13"/>
+      <c r="K56" s="13"/>
+      <c r="L56" s="25"/>
+      <c r="M56" s="25"/>
+      <c r="N56" s="25"/>
+      <c r="O56" s="25"/>
+      <c r="P56" s="25"/>
+      <c r="Q56" s="25"/>
+      <c r="R56" s="25"/>
+      <c r="S56" s="25"/>
+      <c r="T56" s="25"/>
+      <c r="U56" s="25"/>
+      <c r="V56" s="25"/>
+      <c r="W56" s="25"/>
+      <c r="X56" s="25"/>
+      <c r="Y56" s="25"/>
+      <c r="Z56" s="25"/>
+      <c r="AA56" s="25"/>
+    </row>
+    <row r="57" spans="1:27" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="77" t="s">
+        <v>121</v>
+      </c>
+      <c r="B57" s="34">
+        <v>8</v>
+      </c>
+      <c r="C57" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="D57" s="24"/>
+      <c r="E57" s="24"/>
+      <c r="F57" s="24"/>
+      <c r="G57" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H57" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J57" s="13"/>
+      <c r="K57" s="13"/>
+      <c r="L57" s="25"/>
+      <c r="M57" s="25"/>
+      <c r="N57" s="25"/>
+      <c r="O57" s="25"/>
+      <c r="P57" s="25"/>
+      <c r="Q57" s="25"/>
+      <c r="R57" s="25"/>
+      <c r="S57" s="25"/>
+      <c r="T57" s="25"/>
+      <c r="U57" s="25"/>
+      <c r="V57" s="25"/>
+      <c r="W57" s="25"/>
+      <c r="X57" s="25"/>
+      <c r="Y57" s="25"/>
+      <c r="Z57" s="25"/>
+      <c r="AA57" s="25"/>
+    </row>
+    <row r="58" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="77" t="s">
+        <v>122</v>
+      </c>
+      <c r="B58" s="34">
+        <v>9</v>
+      </c>
+      <c r="C58" s="38" t="str">
+        <f>C32</f>
+        <v>Cho vay nhà ở vùng thường xuyên ngập lũ vùng ĐBSCL</v>
+      </c>
+      <c r="D58" s="24"/>
+      <c r="E58" s="24"/>
+      <c r="F58" s="24"/>
+      <c r="G58" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H58" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J58" s="13"/>
+      <c r="K58" s="13"/>
+      <c r="L58" s="25"/>
+      <c r="M58" s="25"/>
+      <c r="N58" s="25"/>
+      <c r="O58" s="25"/>
+      <c r="P58" s="25"/>
+      <c r="Q58" s="25"/>
+      <c r="R58" s="25"/>
+      <c r="S58" s="25"/>
+      <c r="T58" s="25"/>
+      <c r="U58" s="25"/>
+      <c r="V58" s="25"/>
+      <c r="W58" s="25"/>
+      <c r="X58" s="25"/>
+      <c r="Y58" s="25"/>
+      <c r="Z58" s="25"/>
+      <c r="AA58" s="25"/>
+    </row>
+    <row r="59" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="77" t="s">
+        <v>123</v>
+      </c>
+      <c r="B59" s="34">
+        <v>10</v>
+      </c>
+      <c r="C59" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="D59" s="24"/>
+      <c r="E59" s="24"/>
+      <c r="F59" s="24"/>
+      <c r="G59" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H59" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J59" s="13"/>
+      <c r="K59" s="13"/>
+      <c r="L59" s="25"/>
+      <c r="M59" s="25"/>
+      <c r="N59" s="25"/>
+      <c r="O59" s="25"/>
+      <c r="P59" s="25"/>
+      <c r="Q59" s="25"/>
+      <c r="R59" s="25"/>
+      <c r="S59" s="25"/>
+      <c r="T59" s="25"/>
+      <c r="U59" s="25"/>
+      <c r="V59" s="25"/>
+      <c r="W59" s="25"/>
+      <c r="X59" s="25"/>
+      <c r="Y59" s="25"/>
+      <c r="Z59" s="25"/>
+      <c r="AA59" s="25"/>
+    </row>
+    <row r="60" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="77" t="s">
+        <v>124</v>
+      </c>
+      <c r="B60" s="34">
+        <v>11</v>
+      </c>
+      <c r="C60" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="D60" s="24"/>
+      <c r="E60" s="24"/>
+      <c r="F60" s="24"/>
+      <c r="G60" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H60" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J60" s="13"/>
+      <c r="K60" s="13"/>
+      <c r="L60" s="25"/>
+      <c r="M60" s="25"/>
+      <c r="N60" s="25"/>
+      <c r="O60" s="25"/>
+      <c r="P60" s="25"/>
+      <c r="Q60" s="25"/>
+      <c r="R60" s="25"/>
+      <c r="S60" s="25"/>
+      <c r="T60" s="25"/>
+      <c r="U60" s="25"/>
+      <c r="V60" s="25"/>
+      <c r="W60" s="25"/>
+      <c r="X60" s="25"/>
+      <c r="Y60" s="25"/>
+      <c r="Z60" s="25"/>
+      <c r="AA60" s="25"/>
+    </row>
+    <row r="61" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="77" t="s">
+        <v>125</v>
+      </c>
+      <c r="B61" s="34">
+        <v>12</v>
+      </c>
+      <c r="C61" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="D61" s="24"/>
+      <c r="E61" s="24"/>
+      <c r="F61" s="24"/>
+      <c r="G61" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H61" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J61" s="13"/>
+      <c r="K61" s="13"/>
+      <c r="L61" s="25"/>
+      <c r="M61" s="25"/>
+      <c r="N61" s="25"/>
+      <c r="O61" s="25"/>
+      <c r="P61" s="25"/>
+      <c r="Q61" s="25"/>
+      <c r="R61" s="25"/>
+      <c r="S61" s="25"/>
+      <c r="T61" s="25"/>
+      <c r="U61" s="25"/>
+      <c r="V61" s="25"/>
+      <c r="W61" s="25"/>
+      <c r="X61" s="25"/>
+      <c r="Y61" s="25"/>
+      <c r="Z61" s="25"/>
+      <c r="AA61" s="25"/>
+    </row>
+    <row r="62" spans="1:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="77" t="s">
+        <v>126</v>
+      </c>
+      <c r="B62" s="34">
+        <v>13</v>
+      </c>
+      <c r="C62" s="46" t="s">
+        <v>64</v>
+      </c>
+      <c r="D62" s="24"/>
+      <c r="E62" s="24"/>
+      <c r="F62" s="24"/>
+      <c r="G62" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H62" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J62" s="13"/>
+      <c r="K62" s="13"/>
+      <c r="L62" s="25"/>
+      <c r="M62" s="25"/>
+      <c r="N62" s="25"/>
+      <c r="O62" s="25"/>
+      <c r="P62" s="25"/>
+      <c r="Q62" s="25"/>
+      <c r="R62" s="25"/>
+      <c r="S62" s="25"/>
+      <c r="T62" s="25"/>
+      <c r="U62" s="25"/>
+      <c r="V62" s="25"/>
+      <c r="W62" s="25"/>
+      <c r="X62" s="25"/>
+      <c r="Y62" s="25"/>
+      <c r="Z62" s="25"/>
+      <c r="AA62" s="25"/>
+    </row>
+    <row r="63" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="77" t="s">
+        <v>127</v>
+      </c>
+      <c r="B63" s="48" t="s">
+        <v>66</v>
+      </c>
+      <c r="C63" s="49" t="s">
+        <v>67</v>
+      </c>
+      <c r="D63" s="24"/>
+      <c r="E63" s="24"/>
+      <c r="F63" s="24"/>
+      <c r="G63" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H63" s="15"/>
+      <c r="J63" s="13"/>
+      <c r="K63" s="13"/>
+      <c r="L63" s="25"/>
+      <c r="M63" s="25"/>
+      <c r="N63" s="25"/>
+      <c r="O63" s="25"/>
+      <c r="P63" s="25"/>
+      <c r="Q63" s="25"/>
+      <c r="R63" s="25"/>
+      <c r="S63" s="25"/>
+      <c r="T63" s="25"/>
+      <c r="U63" s="25"/>
+      <c r="V63" s="25"/>
+      <c r="W63" s="25"/>
+      <c r="X63" s="25"/>
+      <c r="Y63" s="25"/>
+      <c r="Z63" s="25"/>
+      <c r="AA63" s="25"/>
+    </row>
+    <row r="64" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="77" t="s">
+        <v>128</v>
+      </c>
+      <c r="B64" s="50" t="s">
+        <v>22</v>
+      </c>
+      <c r="C64" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D64" s="24"/>
+      <c r="E64" s="24"/>
+      <c r="F64" s="24"/>
+      <c r="G64" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H64" s="15"/>
+      <c r="J64" s="13"/>
+      <c r="K64" s="13"/>
+      <c r="L64" s="26"/>
+      <c r="M64" s="26"/>
+      <c r="N64" s="26"/>
+      <c r="O64" s="26"/>
+      <c r="P64" s="26"/>
+      <c r="Q64" s="26"/>
+      <c r="R64" s="26"/>
+      <c r="S64" s="26"/>
+      <c r="T64" s="26"/>
+      <c r="U64" s="26"/>
+      <c r="V64" s="26"/>
+      <c r="W64" s="26"/>
+      <c r="X64" s="25"/>
+      <c r="Y64" s="25"/>
+      <c r="Z64" s="25"/>
+      <c r="AA64" s="25"/>
+    </row>
+    <row r="65" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="77" t="s">
+        <v>129</v>
+      </c>
+      <c r="B65" s="52"/>
+      <c r="C65" s="53" t="s">
+        <v>69</v>
+      </c>
+      <c r="D65" s="24"/>
+      <c r="E65" s="24"/>
+      <c r="F65" s="24"/>
+      <c r="G65" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H65" s="15"/>
+      <c r="J65" s="13"/>
+      <c r="K65" s="13"/>
+      <c r="L65" s="26"/>
+      <c r="M65" s="26"/>
+      <c r="N65" s="26"/>
+      <c r="O65" s="26"/>
+      <c r="P65" s="26"/>
+      <c r="Q65" s="26"/>
+      <c r="R65" s="26"/>
+      <c r="S65" s="26"/>
+      <c r="T65" s="26"/>
+      <c r="U65" s="26"/>
+      <c r="V65" s="26"/>
+      <c r="W65" s="26"/>
+      <c r="X65" s="25"/>
+      <c r="Y65" s="25"/>
+      <c r="Z65" s="25"/>
+      <c r="AA65" s="25"/>
+    </row>
+    <row r="66" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="77" t="s">
+        <v>130</v>
+      </c>
+      <c r="B66" s="93" t="s">
+        <v>70</v>
+      </c>
+      <c r="C66" s="94"/>
+      <c r="D66" s="94"/>
+      <c r="E66" s="94"/>
+      <c r="F66" s="95"/>
+      <c r="G66" s="96" t="s">
+        <v>71</v>
+      </c>
+      <c r="H66" s="97"/>
+      <c r="J66" s="13"/>
+      <c r="K66" s="13"/>
+      <c r="L66" s="4"/>
+      <c r="M66" s="4"/>
+      <c r="N66" s="4"/>
+      <c r="O66" s="4"/>
+      <c r="P66" s="4"/>
+      <c r="Q66" s="4"/>
+      <c r="R66" s="4"/>
+      <c r="S66" s="4"/>
+      <c r="T66" s="4"/>
+      <c r="U66" s="4"/>
+      <c r="V66" s="4"/>
+      <c r="W66" s="4"/>
+      <c r="X66" s="4"/>
+      <c r="Y66" s="4"/>
+      <c r="Z66" s="4"/>
+      <c r="AA66" s="4"/>
+    </row>
+    <row r="67" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="103" t="s">
         <v>107</v>
       </c>
-      <c r="D55" s="36"/>
-      <c r="E55" s="36"/>
-      <c r="F55" s="36"/>
-      <c r="G55" s="29">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H55" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J55" s="15"/>
-      <c r="K55" s="15"/>
-      <c r="L55" s="58"/>
-      <c r="M55" s="58"/>
-      <c r="N55" s="58"/>
-      <c r="O55" s="58"/>
-      <c r="P55" s="58"/>
-      <c r="Q55" s="58"/>
-      <c r="R55" s="58"/>
-      <c r="S55" s="58"/>
-      <c r="T55" s="58"/>
-      <c r="U55" s="58"/>
-      <c r="V55" s="58"/>
-      <c r="W55" s="58"/>
-      <c r="X55" s="58"/>
-      <c r="Y55" s="58"/>
-      <c r="Z55" s="58"/>
-      <c r="AA55" s="58"/>
-    </row>
-    <row r="56" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="B56" s="52"/>
-      <c r="C56" s="54" t="s">
+      <c r="B67" s="103"/>
+      <c r="C67" s="103"/>
+      <c r="D67" s="103"/>
+      <c r="E67" s="103"/>
+      <c r="F67" s="103"/>
+      <c r="G67" s="103"/>
+      <c r="H67" s="33"/>
+      <c r="J67" s="13"/>
+      <c r="K67" s="13"/>
+      <c r="L67" s="4"/>
+      <c r="M67" s="4"/>
+      <c r="N67" s="4"/>
+      <c r="O67" s="4"/>
+      <c r="P67" s="4"/>
+      <c r="Q67" s="4"/>
+      <c r="R67" s="4"/>
+      <c r="S67" s="4"/>
+      <c r="T67" s="4"/>
+      <c r="U67" s="4"/>
+      <c r="V67" s="4"/>
+      <c r="W67" s="4"/>
+      <c r="X67" s="4"/>
+      <c r="Y67" s="4"/>
+      <c r="Z67" s="4"/>
+      <c r="AA67" s="4"/>
+    </row>
+    <row r="68" spans="1:27" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="104" t="s">
+        <v>108</v>
+      </c>
+      <c r="B68" s="104"/>
+      <c r="C68" s="104"/>
+      <c r="D68" s="104"/>
+      <c r="E68" s="104"/>
+      <c r="F68" s="104"/>
+      <c r="G68" s="104"/>
+      <c r="H68" s="33"/>
+      <c r="J68" s="13"/>
+      <c r="K68" s="13"/>
+      <c r="L68" s="4"/>
+      <c r="M68" s="4"/>
+      <c r="N68" s="4"/>
+      <c r="O68" s="4"/>
+      <c r="P68" s="4"/>
+      <c r="Q68" s="4"/>
+      <c r="R68" s="4"/>
+      <c r="S68" s="4"/>
+      <c r="T68" s="4"/>
+      <c r="U68" s="4"/>
+      <c r="V68" s="4"/>
+      <c r="W68" s="4"/>
+      <c r="X68" s="4"/>
+      <c r="Y68" s="4"/>
+      <c r="Z68" s="4"/>
+      <c r="AA68" s="4"/>
+    </row>
+    <row r="69" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="104" t="s">
         <v>109</v>
       </c>
-      <c r="D56" s="36"/>
-      <c r="E56" s="36"/>
-      <c r="F56" s="36"/>
-      <c r="G56" s="29">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H56" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J56" s="15"/>
-      <c r="K56" s="15"/>
-      <c r="L56" s="58"/>
-      <c r="M56" s="58"/>
-      <c r="N56" s="58"/>
-      <c r="O56" s="58"/>
-      <c r="P56" s="58"/>
-      <c r="Q56" s="58"/>
-      <c r="R56" s="58"/>
-      <c r="S56" s="58"/>
-      <c r="T56" s="58"/>
-      <c r="U56" s="58"/>
-      <c r="V56" s="58"/>
-      <c r="W56" s="58"/>
-      <c r="X56" s="58"/>
-      <c r="Y56" s="58"/>
-      <c r="Z56" s="58"/>
-      <c r="AA56" s="58"/>
-    </row>
-    <row r="57" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="B57" s="52"/>
-      <c r="C57" s="59" t="s">
-        <v>111</v>
-      </c>
-      <c r="D57" s="50"/>
-      <c r="E57" s="50"/>
-      <c r="F57" s="50"/>
-      <c r="G57" s="29">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H57" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J57" s="15"/>
-      <c r="K57" s="15"/>
-      <c r="L57" s="58"/>
-      <c r="M57" s="58"/>
-      <c r="N57" s="58"/>
-      <c r="O57" s="58"/>
-      <c r="P57" s="58"/>
-      <c r="Q57" s="58"/>
-      <c r="R57" s="58"/>
-      <c r="S57" s="58"/>
-      <c r="T57" s="58"/>
-      <c r="U57" s="58"/>
-      <c r="V57" s="58"/>
-      <c r="W57" s="58"/>
-      <c r="X57" s="58"/>
-      <c r="Y57" s="58"/>
-      <c r="Z57" s="58"/>
-      <c r="AA57" s="58"/>
-    </row>
-    <row r="58" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="B58" s="52"/>
-      <c r="C58" s="59" t="s">
-        <v>113</v>
-      </c>
-      <c r="D58" s="50"/>
-      <c r="E58" s="50"/>
-      <c r="F58" s="50"/>
-      <c r="G58" s="29">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H58" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J58" s="15"/>
-      <c r="K58" s="15"/>
-      <c r="L58" s="58"/>
-      <c r="M58" s="58"/>
-      <c r="N58" s="58"/>
-      <c r="O58" s="58"/>
-      <c r="P58" s="58"/>
-      <c r="Q58" s="58"/>
-      <c r="R58" s="58"/>
-      <c r="S58" s="58"/>
-      <c r="T58" s="58"/>
-      <c r="U58" s="58"/>
-      <c r="V58" s="58"/>
-      <c r="W58" s="58"/>
-      <c r="X58" s="58"/>
-      <c r="Y58" s="58"/>
-      <c r="Z58" s="58"/>
-      <c r="AA58" s="58"/>
-    </row>
-    <row r="59" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="B59" s="52"/>
-      <c r="C59" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="D59" s="50"/>
-      <c r="E59" s="50"/>
-      <c r="F59" s="50"/>
-      <c r="G59" s="29">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H59" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J59" s="15"/>
-      <c r="K59" s="15"/>
-      <c r="L59" s="58"/>
-      <c r="M59" s="58"/>
-      <c r="N59" s="58"/>
-      <c r="O59" s="58"/>
-      <c r="P59" s="58"/>
-      <c r="Q59" s="58"/>
-      <c r="R59" s="58"/>
-      <c r="S59" s="58"/>
-      <c r="T59" s="58"/>
-      <c r="U59" s="58"/>
-      <c r="V59" s="58"/>
-      <c r="W59" s="58"/>
-      <c r="X59" s="58"/>
-      <c r="Y59" s="58"/>
-      <c r="Z59" s="58"/>
-      <c r="AA59" s="58"/>
-    </row>
-    <row r="60" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="B60" s="47">
-        <v>27</v>
-      </c>
-      <c r="C60" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="D60" s="36"/>
-      <c r="E60" s="36"/>
-      <c r="F60" s="36"/>
-      <c r="G60" s="29">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H60" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J60" s="15"/>
-      <c r="K60" s="15"/>
-      <c r="L60" s="58"/>
-      <c r="M60" s="58"/>
-      <c r="N60" s="58"/>
-      <c r="O60" s="58"/>
-      <c r="P60" s="58"/>
-      <c r="Q60" s="58"/>
-      <c r="R60" s="58"/>
-      <c r="S60" s="58"/>
-      <c r="T60" s="58"/>
-      <c r="U60" s="58"/>
-      <c r="V60" s="58"/>
-      <c r="W60" s="58"/>
-      <c r="X60" s="58"/>
-      <c r="Y60" s="58"/>
-      <c r="Z60" s="58"/>
-      <c r="AA60" s="58"/>
-    </row>
-    <row r="61" spans="1:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="B61" s="82" t="s">
-        <v>118</v>
-      </c>
-      <c r="C61" s="86" t="s">
-        <v>119</v>
-      </c>
-      <c r="D61" s="87">
-        <f>D62+D63+D65+D66+D67</f>
-        <v>0</v>
-      </c>
-      <c r="E61" s="87">
-        <f t="shared" ref="E61:G61" si="10">E62+E63+E65+E66+E67</f>
-        <v>0</v>
-      </c>
-      <c r="F61" s="87">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="G61" s="87">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="H61" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J61" s="15"/>
-      <c r="K61" s="15"/>
-      <c r="L61" s="45"/>
-      <c r="M61" s="45"/>
-      <c r="N61" s="45"/>
-      <c r="O61" s="45"/>
-      <c r="P61" s="45"/>
-      <c r="Q61" s="45"/>
-      <c r="R61" s="45"/>
-      <c r="S61" s="45"/>
-      <c r="T61" s="45"/>
-      <c r="U61" s="45"/>
-      <c r="V61" s="45"/>
-      <c r="W61" s="45"/>
-      <c r="X61" s="45"/>
-      <c r="Y61" s="45"/>
-      <c r="Z61" s="45"/>
-      <c r="AA61" s="45"/>
-    </row>
-    <row r="62" spans="1:27" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="B62" s="79">
-        <v>1</v>
-      </c>
-      <c r="C62" s="85" t="s">
-        <v>58</v>
-      </c>
-      <c r="D62" s="88"/>
-      <c r="E62" s="88"/>
-      <c r="F62" s="88"/>
-      <c r="G62" s="19">
-        <f t="shared" ref="G62:G67" si="11">F62-D62</f>
-        <v>0</v>
-      </c>
-      <c r="H62" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J62" s="15"/>
-      <c r="K62" s="15"/>
-      <c r="L62" s="45"/>
-      <c r="M62" s="45"/>
-      <c r="N62" s="45"/>
-      <c r="O62" s="45"/>
-      <c r="P62" s="45"/>
-      <c r="Q62" s="45"/>
-      <c r="R62" s="45"/>
-      <c r="S62" s="45"/>
-      <c r="T62" s="45"/>
-      <c r="U62" s="45"/>
-      <c r="V62" s="45"/>
-      <c r="W62" s="45"/>
-      <c r="X62" s="45"/>
-      <c r="Y62" s="45"/>
-      <c r="Z62" s="45"/>
-      <c r="AA62" s="45"/>
-    </row>
-    <row r="63" spans="1:27" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="B63" s="79">
-        <v>2</v>
-      </c>
-      <c r="C63" s="89" t="s">
-        <v>120</v>
-      </c>
-      <c r="D63" s="88"/>
-      <c r="E63" s="88"/>
-      <c r="F63" s="88"/>
-      <c r="G63" s="19">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H63" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J63" s="15"/>
-      <c r="K63" s="15"/>
-      <c r="L63" s="45"/>
-      <c r="M63" s="45"/>
-      <c r="N63" s="45"/>
-      <c r="O63" s="45"/>
-      <c r="P63" s="45"/>
-      <c r="Q63" s="45"/>
-      <c r="R63" s="45"/>
-      <c r="S63" s="45"/>
-      <c r="T63" s="45"/>
-      <c r="U63" s="45"/>
-      <c r="V63" s="45"/>
-      <c r="W63" s="45"/>
-      <c r="X63" s="45"/>
-      <c r="Y63" s="45"/>
-      <c r="Z63" s="45"/>
-      <c r="AA63" s="45"/>
-    </row>
-    <row r="64" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="16" t="s">
-        <v>127</v>
-      </c>
-      <c r="B64" s="90" t="s">
-        <v>29</v>
-      </c>
-      <c r="C64" s="91" t="s">
-        <v>121</v>
-      </c>
-      <c r="D64" s="88"/>
-      <c r="E64" s="88"/>
-      <c r="F64" s="88"/>
-      <c r="G64" s="19">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H64" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J64" s="15"/>
-      <c r="K64" s="15"/>
-      <c r="L64" s="45"/>
-      <c r="M64" s="45"/>
-      <c r="N64" s="45"/>
-      <c r="O64" s="45"/>
-      <c r="P64" s="45"/>
-      <c r="Q64" s="45"/>
-      <c r="R64" s="45"/>
-      <c r="S64" s="45"/>
-      <c r="T64" s="45"/>
-      <c r="U64" s="45"/>
-      <c r="V64" s="45"/>
-      <c r="W64" s="45"/>
-      <c r="X64" s="45"/>
-      <c r="Y64" s="45"/>
-      <c r="Z64" s="45"/>
-      <c r="AA64" s="45"/>
-    </row>
-    <row r="65" spans="1:27" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="B65" s="79">
-        <v>3</v>
-      </c>
-      <c r="C65" s="85" t="s">
-        <v>122</v>
-      </c>
-      <c r="D65" s="88"/>
-      <c r="E65" s="88"/>
-      <c r="F65" s="88"/>
-      <c r="G65" s="19">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H65" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J65" s="15"/>
-      <c r="K65" s="15"/>
-      <c r="L65" s="45"/>
-      <c r="M65" s="45"/>
-      <c r="N65" s="45"/>
-      <c r="O65" s="45"/>
-      <c r="P65" s="45"/>
-      <c r="Q65" s="45"/>
-      <c r="R65" s="45"/>
-      <c r="S65" s="45"/>
-      <c r="T65" s="45"/>
-      <c r="U65" s="45"/>
-      <c r="V65" s="45"/>
-      <c r="W65" s="45"/>
-      <c r="X65" s="45"/>
-      <c r="Y65" s="45"/>
-      <c r="Z65" s="45"/>
-      <c r="AA65" s="45"/>
-    </row>
-    <row r="66" spans="1:27" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="B66" s="79">
-        <v>4</v>
-      </c>
-      <c r="C66" s="89" t="s">
-        <v>123</v>
-      </c>
-      <c r="D66" s="88"/>
-      <c r="E66" s="88"/>
-      <c r="F66" s="88"/>
-      <c r="G66" s="19">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H66" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J66" s="15"/>
-      <c r="K66" s="15"/>
-      <c r="L66" s="45"/>
-      <c r="M66" s="45"/>
-      <c r="N66" s="45"/>
-      <c r="O66" s="45"/>
-      <c r="P66" s="45"/>
-      <c r="Q66" s="45"/>
-      <c r="R66" s="45"/>
-      <c r="S66" s="45"/>
-      <c r="T66" s="45"/>
-      <c r="U66" s="45"/>
-      <c r="V66" s="45"/>
-      <c r="W66" s="45"/>
-      <c r="X66" s="45"/>
-      <c r="Y66" s="45"/>
-      <c r="Z66" s="45"/>
-      <c r="AA66" s="45"/>
-    </row>
-    <row r="67" spans="1:27" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="16" t="s">
-        <v>130</v>
-      </c>
-      <c r="B67" s="79">
-        <v>5</v>
-      </c>
-      <c r="C67" s="89" t="s">
-        <v>124</v>
-      </c>
-      <c r="D67" s="88"/>
-      <c r="E67" s="88"/>
-      <c r="F67" s="88"/>
-      <c r="G67" s="19">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H67" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J67" s="15"/>
-      <c r="K67" s="15"/>
-      <c r="L67" s="45"/>
-      <c r="M67" s="45"/>
-      <c r="N67" s="45"/>
-      <c r="O67" s="45"/>
-      <c r="P67" s="45"/>
-      <c r="Q67" s="45"/>
-      <c r="R67" s="45"/>
-      <c r="S67" s="45"/>
-      <c r="T67" s="45"/>
-      <c r="U67" s="45"/>
-      <c r="V67" s="45"/>
-      <c r="W67" s="45"/>
-      <c r="X67" s="45"/>
-      <c r="Y67" s="45"/>
-      <c r="Z67" s="45"/>
-      <c r="AA67" s="45"/>
-    </row>
-    <row r="68" spans="1:27" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="B68" s="42" t="s">
-        <v>35</v>
-      </c>
-      <c r="C68" s="60" t="s">
-        <v>126</v>
-      </c>
-      <c r="D68" s="41">
-        <f>SUM(D69:D94)-D74-D76-D87-D88</f>
-        <v>0</v>
-      </c>
-      <c r="E68" s="41">
-        <f>SUM(E69:E94)-E74-E76-E87-E88</f>
-        <v>0</v>
-      </c>
-      <c r="F68" s="41">
-        <f>SUM(F69:F94)-F74-F76-F87-F88</f>
-        <v>0</v>
-      </c>
-      <c r="G68" s="41">
-        <f>SUM(G69:G94)-G74-G76-G87-G88</f>
-        <v>0</v>
-      </c>
-      <c r="H68" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J68" s="15"/>
-      <c r="K68" s="15"/>
-      <c r="L68" s="45"/>
-      <c r="M68" s="45"/>
-      <c r="N68" s="45"/>
-      <c r="O68" s="45"/>
-      <c r="P68" s="45"/>
-      <c r="Q68" s="45"/>
-      <c r="R68" s="45"/>
-      <c r="S68" s="45"/>
-      <c r="T68" s="45"/>
-      <c r="U68" s="45"/>
-      <c r="V68" s="45"/>
-      <c r="W68" s="45"/>
-      <c r="X68" s="45"/>
-      <c r="Y68" s="45"/>
-      <c r="Z68" s="45"/>
-      <c r="AA68" s="45"/>
-    </row>
-    <row r="69" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="B69" s="47">
-        <v>1</v>
-      </c>
-      <c r="C69" s="35" t="str">
-        <f>C25</f>
-        <v>Cho vay hộ nghèo theo Nghị định số 78/2002/NĐ-CP</v>
-      </c>
-      <c r="D69" s="36"/>
-      <c r="E69" s="36"/>
-      <c r="F69" s="36"/>
-      <c r="G69" s="29">
-        <f t="shared" ref="G69:G97" si="12">F69-D69</f>
-        <v>0</v>
-      </c>
-      <c r="H69" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J69" s="15"/>
-      <c r="K69" s="15"/>
-      <c r="L69" s="61"/>
-      <c r="M69" s="61"/>
-      <c r="N69" s="61"/>
-      <c r="O69" s="61"/>
-      <c r="P69" s="61"/>
-      <c r="Q69" s="61"/>
-      <c r="R69" s="61"/>
-      <c r="S69" s="61"/>
-      <c r="T69" s="61"/>
-      <c r="U69" s="61"/>
-      <c r="V69" s="61"/>
-      <c r="W69" s="61"/>
-      <c r="X69" s="61"/>
-      <c r="Y69" s="61"/>
-      <c r="Z69" s="61"/>
-      <c r="AA69" s="61"/>
-    </row>
-    <row r="70" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="B70" s="47">
-        <v>2</v>
-      </c>
-      <c r="C70" s="48" t="s">
-        <v>50</v>
-      </c>
-      <c r="D70" s="36"/>
-      <c r="E70" s="36"/>
-      <c r="F70" s="36"/>
-      <c r="G70" s="29">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H70" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J70" s="15"/>
-      <c r="K70" s="15"/>
-      <c r="L70" s="61"/>
-      <c r="M70" s="61"/>
-      <c r="N70" s="61"/>
-      <c r="O70" s="61"/>
-      <c r="P70" s="61"/>
-      <c r="Q70" s="61"/>
-      <c r="R70" s="61"/>
-      <c r="S70" s="61"/>
-      <c r="T70" s="61"/>
-      <c r="U70" s="61"/>
-      <c r="V70" s="61"/>
-      <c r="W70" s="61"/>
-      <c r="X70" s="61"/>
-      <c r="Y70" s="61"/>
-      <c r="Z70" s="61"/>
-      <c r="AA70" s="61"/>
-    </row>
-    <row r="71" spans="1:27" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="B71" s="47">
-        <v>3</v>
-      </c>
-      <c r="C71" s="49" t="str">
-        <f>C27</f>
-        <v>Cho vay hộ mới thoát nghèo theo Quyết định số 28/2015/QĐ-TTg</v>
-      </c>
-      <c r="D71" s="50"/>
-      <c r="E71" s="50"/>
-      <c r="F71" s="50"/>
-      <c r="G71" s="29">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H71" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J71" s="15"/>
-      <c r="K71" s="15"/>
-      <c r="L71" s="61"/>
-      <c r="M71" s="61"/>
-      <c r="N71" s="61"/>
-      <c r="O71" s="61"/>
-      <c r="P71" s="61"/>
-      <c r="Q71" s="61"/>
-      <c r="R71" s="61"/>
-      <c r="S71" s="61"/>
-      <c r="T71" s="61"/>
-      <c r="U71" s="61"/>
-      <c r="V71" s="61"/>
-      <c r="W71" s="61"/>
-      <c r="X71" s="61"/>
-      <c r="Y71" s="61"/>
-      <c r="Z71" s="61"/>
-      <c r="AA71" s="61"/>
-    </row>
-    <row r="72" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="B72" s="47">
-        <v>4</v>
-      </c>
-      <c r="C72" s="49" t="s">
-        <v>131</v>
-      </c>
-      <c r="D72" s="50"/>
-      <c r="E72" s="50"/>
-      <c r="F72" s="50"/>
-      <c r="G72" s="29">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H72" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J72" s="15"/>
-      <c r="K72" s="15"/>
-      <c r="L72" s="61"/>
-      <c r="M72" s="61"/>
-      <c r="N72" s="61"/>
-      <c r="O72" s="61"/>
-      <c r="P72" s="61"/>
-      <c r="Q72" s="61"/>
-      <c r="R72" s="61"/>
-      <c r="S72" s="61"/>
-      <c r="T72" s="61"/>
-      <c r="U72" s="61"/>
-      <c r="V72" s="61"/>
-      <c r="W72" s="61"/>
-      <c r="X72" s="61"/>
-      <c r="Y72" s="61"/>
-      <c r="Z72" s="61"/>
-      <c r="AA72" s="61"/>
-    </row>
-    <row r="73" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="16" t="s">
-        <v>140</v>
-      </c>
-      <c r="B73" s="47">
-        <v>5</v>
-      </c>
-      <c r="C73" s="51" t="s">
-        <v>133</v>
-      </c>
-      <c r="D73" s="36"/>
-      <c r="E73" s="36"/>
-      <c r="F73" s="36"/>
-      <c r="G73" s="29">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H73" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J73" s="15"/>
-      <c r="K73" s="15"/>
-      <c r="L73" s="61"/>
-      <c r="M73" s="61"/>
-      <c r="N73" s="61"/>
-      <c r="O73" s="61"/>
-      <c r="P73" s="61"/>
-      <c r="Q73" s="61"/>
-      <c r="R73" s="61"/>
-      <c r="S73" s="61"/>
-      <c r="T73" s="61"/>
-      <c r="U73" s="61"/>
-      <c r="V73" s="61"/>
-      <c r="W73" s="61"/>
-      <c r="X73" s="61"/>
-      <c r="Y73" s="61"/>
-      <c r="Z73" s="61"/>
-      <c r="AA73" s="61"/>
-    </row>
-    <row r="74" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="16" t="s">
-        <v>142</v>
-      </c>
-      <c r="B74" s="62" t="s">
-        <v>29</v>
-      </c>
-      <c r="C74" s="92" t="s">
-        <v>134</v>
-      </c>
-      <c r="D74" s="50"/>
-      <c r="E74" s="50"/>
-      <c r="F74" s="50"/>
-      <c r="G74" s="29">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H74" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J74" s="15"/>
-      <c r="K74" s="15"/>
-      <c r="L74" s="61"/>
-      <c r="M74" s="61"/>
-      <c r="N74" s="61"/>
-      <c r="O74" s="61"/>
-      <c r="P74" s="61"/>
-      <c r="Q74" s="61"/>
-      <c r="R74" s="61"/>
-      <c r="S74" s="61"/>
-      <c r="T74" s="61"/>
-      <c r="U74" s="61"/>
-      <c r="V74" s="61"/>
-      <c r="W74" s="61"/>
-      <c r="X74" s="61"/>
-      <c r="Y74" s="61"/>
-      <c r="Z74" s="61"/>
-      <c r="AA74" s="61"/>
-    </row>
-    <row r="75" spans="1:27" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="B75" s="47">
-        <v>6</v>
-      </c>
-      <c r="C75" s="49" t="str">
-        <f>C31</f>
-        <v>Cho vay người lao động đi làm việc ở nước ngoài theo Quyết định số 365/QĐ-NHNN, Quyết định số 1465/QĐ-TTg, Quyết định số 63/2015/QĐ-TTg và Nghị định số 61/2015/NĐ-CP</v>
-      </c>
-      <c r="D75" s="50"/>
-      <c r="E75" s="50"/>
-      <c r="F75" s="50"/>
-      <c r="G75" s="29">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H75" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J75" s="15"/>
-      <c r="K75" s="15"/>
-      <c r="L75" s="61"/>
-      <c r="M75" s="61"/>
-      <c r="N75" s="61"/>
-      <c r="O75" s="61"/>
-      <c r="P75" s="61"/>
-      <c r="Q75" s="61"/>
-      <c r="R75" s="61"/>
-      <c r="S75" s="61"/>
-      <c r="T75" s="61"/>
-      <c r="U75" s="61"/>
-      <c r="V75" s="61"/>
-      <c r="W75" s="61"/>
-      <c r="X75" s="61"/>
-      <c r="Y75" s="61"/>
-      <c r="Z75" s="61"/>
-      <c r="AA75" s="61"/>
-    </row>
-    <row r="76" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="B76" s="52" t="s">
-        <v>29</v>
-      </c>
-      <c r="C76" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="D76" s="50"/>
-      <c r="E76" s="50"/>
-      <c r="F76" s="50"/>
-      <c r="G76" s="29">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H76" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J76" s="15"/>
-      <c r="K76" s="15"/>
-      <c r="L76" s="61"/>
-      <c r="M76" s="61"/>
-      <c r="N76" s="61"/>
-      <c r="O76" s="61"/>
-      <c r="P76" s="61"/>
-      <c r="Q76" s="61"/>
-      <c r="R76" s="61"/>
-      <c r="S76" s="61"/>
-      <c r="T76" s="61"/>
-      <c r="U76" s="61"/>
-      <c r="V76" s="61"/>
-      <c r="W76" s="61"/>
-      <c r="X76" s="61"/>
-      <c r="Y76" s="61"/>
-      <c r="Z76" s="61"/>
-      <c r="AA76" s="61"/>
-    </row>
-    <row r="77" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="B77" s="47">
-        <v>7</v>
-      </c>
-      <c r="C77" s="49" t="s">
-        <v>138</v>
-      </c>
-      <c r="D77" s="50"/>
-      <c r="E77" s="50"/>
-      <c r="F77" s="50"/>
-      <c r="G77" s="29">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H77" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J77" s="15"/>
-      <c r="K77" s="15"/>
-      <c r="L77" s="61"/>
-      <c r="M77" s="61"/>
-      <c r="N77" s="61"/>
-      <c r="O77" s="61"/>
-      <c r="P77" s="61"/>
-      <c r="Q77" s="61"/>
-      <c r="R77" s="61"/>
-      <c r="S77" s="61"/>
-      <c r="T77" s="61"/>
-      <c r="U77" s="61"/>
-      <c r="V77" s="61"/>
-      <c r="W77" s="61"/>
-      <c r="X77" s="61"/>
-      <c r="Y77" s="61"/>
-      <c r="Z77" s="61"/>
-      <c r="AA77" s="61"/>
-    </row>
-    <row r="78" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="B78" s="47">
-        <v>8</v>
-      </c>
-      <c r="C78" s="49" t="str">
-        <f>C34</f>
-        <v>Cho vay Chương trình NS&amp;VSMT nông thôn (QĐ 62/2004/QĐ-TTg)</v>
-      </c>
-      <c r="D78" s="50"/>
-      <c r="E78" s="50"/>
-      <c r="F78" s="50"/>
-      <c r="G78" s="29">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H78" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J78" s="15"/>
-      <c r="K78" s="15"/>
-      <c r="L78" s="61"/>
-      <c r="M78" s="61"/>
-      <c r="N78" s="61"/>
-      <c r="O78" s="61"/>
-      <c r="P78" s="61"/>
-      <c r="Q78" s="61"/>
-      <c r="R78" s="61"/>
-      <c r="S78" s="61"/>
-      <c r="T78" s="61"/>
-      <c r="U78" s="61"/>
-      <c r="V78" s="61"/>
-      <c r="W78" s="61"/>
-      <c r="X78" s="61"/>
-      <c r="Y78" s="61"/>
-      <c r="Z78" s="61"/>
-      <c r="AA78" s="61"/>
-    </row>
-    <row r="79" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="B79" s="47">
-        <v>9</v>
-      </c>
-      <c r="C79" s="49" t="s">
-        <v>141</v>
-      </c>
-      <c r="D79" s="50"/>
-      <c r="E79" s="50"/>
-      <c r="F79" s="50"/>
-      <c r="G79" s="29">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H79" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J79" s="15"/>
-      <c r="K79" s="15"/>
-      <c r="L79" s="61"/>
-      <c r="M79" s="61"/>
-      <c r="N79" s="61"/>
-      <c r="O79" s="61"/>
-      <c r="P79" s="61"/>
-      <c r="Q79" s="61"/>
-      <c r="R79" s="61"/>
-      <c r="S79" s="61"/>
-      <c r="T79" s="61"/>
-      <c r="U79" s="61"/>
-      <c r="V79" s="61"/>
-      <c r="W79" s="61"/>
-      <c r="X79" s="61"/>
-      <c r="Y79" s="61"/>
-      <c r="Z79" s="61"/>
-      <c r="AA79" s="61"/>
-    </row>
-    <row r="80" spans="1:27" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="B80" s="47">
-        <v>10</v>
-      </c>
-      <c r="C80" s="49" t="str">
-        <f>C36</f>
-        <v>Cho vay mua trả chậm nhà ở vùng ĐBSCL và Tây Nguyên</v>
-      </c>
-      <c r="D80" s="50"/>
-      <c r="E80" s="50"/>
-      <c r="F80" s="50"/>
-      <c r="G80" s="29">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H80" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J80" s="15"/>
-      <c r="K80" s="15"/>
-      <c r="L80" s="61"/>
-      <c r="M80" s="61"/>
-      <c r="N80" s="61"/>
-      <c r="O80" s="61"/>
-      <c r="P80" s="61"/>
-      <c r="Q80" s="61"/>
-      <c r="R80" s="61"/>
-      <c r="S80" s="61"/>
-      <c r="T80" s="61"/>
-      <c r="U80" s="61"/>
-      <c r="V80" s="61"/>
-      <c r="W80" s="61"/>
-      <c r="X80" s="61"/>
-      <c r="Y80" s="61"/>
-      <c r="Z80" s="61"/>
-      <c r="AA80" s="61"/>
-    </row>
-    <row r="81" spans="1:27" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="B81" s="47">
-        <v>11</v>
-      </c>
-      <c r="C81" s="49" t="s">
-        <v>144</v>
-      </c>
-      <c r="D81" s="50"/>
-      <c r="E81" s="50"/>
-      <c r="F81" s="50"/>
-      <c r="G81" s="29">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H81" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J81" s="15"/>
-      <c r="K81" s="15"/>
-      <c r="L81" s="61"/>
-      <c r="M81" s="61"/>
-      <c r="N81" s="61"/>
-      <c r="O81" s="61"/>
-      <c r="P81" s="61"/>
-      <c r="Q81" s="61"/>
-      <c r="R81" s="61"/>
-      <c r="S81" s="61"/>
-      <c r="T81" s="61"/>
-      <c r="U81" s="61"/>
-      <c r="V81" s="61"/>
-      <c r="W81" s="61"/>
-      <c r="X81" s="61"/>
-      <c r="Y81" s="61"/>
-      <c r="Z81" s="61"/>
-      <c r="AA81" s="61"/>
-    </row>
-    <row r="82" spans="1:27" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="16" t="s">
-        <v>152</v>
-      </c>
-      <c r="B82" s="47">
-        <v>12</v>
-      </c>
-      <c r="C82" s="49" t="s">
+      <c r="B69" s="104"/>
+      <c r="C69" s="104"/>
+      <c r="D69" s="104"/>
+      <c r="E69" s="104"/>
+      <c r="F69" s="104"/>
+      <c r="G69" s="104"/>
+      <c r="H69" s="27"/>
+      <c r="J69" s="13"/>
+      <c r="K69" s="13"/>
+      <c r="L69" s="4"/>
+      <c r="M69" s="4"/>
+      <c r="N69" s="4"/>
+      <c r="O69" s="4"/>
+      <c r="P69" s="4"/>
+      <c r="Q69" s="4"/>
+      <c r="R69" s="4"/>
+      <c r="S69" s="4"/>
+      <c r="T69" s="4"/>
+      <c r="U69" s="4"/>
+      <c r="V69" s="4"/>
+      <c r="W69" s="4"/>
+      <c r="X69" s="4"/>
+      <c r="Y69" s="4"/>
+      <c r="Z69" s="4"/>
+      <c r="AA69" s="4"/>
+    </row>
+    <row r="70" spans="1:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B70" s="28"/>
+      <c r="C70" s="28"/>
+      <c r="D70" s="28"/>
+      <c r="E70" s="98" t="s">
+        <v>97</v>
+      </c>
+      <c r="F70" s="99"/>
+      <c r="G70" s="99"/>
+      <c r="H70" s="100"/>
+      <c r="I70" s="4"/>
+      <c r="J70" s="4"/>
+      <c r="K70" s="4"/>
+      <c r="L70" s="4"/>
+      <c r="M70" s="4"/>
+      <c r="N70" s="4"/>
+      <c r="O70" s="4"/>
+      <c r="P70" s="4"/>
+      <c r="Q70" s="4"/>
+      <c r="R70" s="4"/>
+      <c r="S70" s="4"/>
+      <c r="T70" s="4"/>
+      <c r="U70" s="4"/>
+      <c r="V70" s="4"/>
+      <c r="W70" s="4"/>
+      <c r="X70" s="4"/>
+      <c r="Y70" s="4"/>
+      <c r="Z70" s="4"/>
+      <c r="AA70" s="4"/>
+    </row>
+    <row r="71" spans="1:27" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B71" s="29"/>
+      <c r="C71" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="D71" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="E71" s="31"/>
+      <c r="F71" s="31"/>
+      <c r="G71" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="D82" s="50"/>
-      <c r="E82" s="50"/>
-      <c r="F82" s="50"/>
-      <c r="G82" s="29">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H82" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J82" s="15"/>
-      <c r="K82" s="15"/>
-      <c r="L82" s="61"/>
-      <c r="M82" s="61"/>
-      <c r="N82" s="61"/>
-      <c r="O82" s="61"/>
-      <c r="P82" s="61"/>
-      <c r="Q82" s="61"/>
-      <c r="R82" s="61"/>
-      <c r="S82" s="61"/>
-      <c r="T82" s="61"/>
-      <c r="U82" s="61"/>
-      <c r="V82" s="61"/>
-      <c r="W82" s="61"/>
-      <c r="X82" s="61"/>
-      <c r="Y82" s="61"/>
-      <c r="Z82" s="61"/>
-      <c r="AA82" s="61"/>
-    </row>
-    <row r="83" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="B83" s="47">
-        <v>13</v>
-      </c>
-      <c r="C83" s="35" t="s">
-        <v>148</v>
-      </c>
-      <c r="D83" s="50"/>
-      <c r="E83" s="50"/>
-      <c r="F83" s="50"/>
-      <c r="G83" s="29">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H83" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J83" s="15"/>
-      <c r="K83" s="15"/>
-      <c r="L83" s="63"/>
-      <c r="M83" s="63"/>
-      <c r="N83" s="63"/>
-      <c r="O83" s="63"/>
-      <c r="P83" s="63"/>
-      <c r="Q83" s="63"/>
-      <c r="R83" s="63"/>
-      <c r="S83" s="63"/>
-      <c r="T83" s="63"/>
-      <c r="U83" s="63"/>
-      <c r="V83" s="63"/>
-      <c r="W83" s="63"/>
-      <c r="X83" s="61"/>
-      <c r="Y83" s="61"/>
-      <c r="Z83" s="61"/>
-      <c r="AA83" s="61"/>
-    </row>
-    <row r="84" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="B84" s="47">
-        <v>14</v>
-      </c>
-      <c r="C84" s="49" t="str">
-        <f>C41</f>
-        <v>Cho vay hỗ trợ hộ nghèo về nhà ở (QĐ 167/2008/QĐ-TTg)</v>
-      </c>
-      <c r="D84" s="50"/>
-      <c r="E84" s="50"/>
-      <c r="F84" s="50"/>
-      <c r="G84" s="29">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H84" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J84" s="15"/>
-      <c r="K84" s="15"/>
-      <c r="L84" s="63"/>
-      <c r="M84" s="63"/>
-      <c r="N84" s="63"/>
-      <c r="O84" s="63"/>
-      <c r="P84" s="63"/>
-      <c r="Q84" s="63"/>
-      <c r="R84" s="63"/>
-      <c r="S84" s="63"/>
-      <c r="T84" s="63"/>
-      <c r="U84" s="63"/>
-      <c r="V84" s="63"/>
-      <c r="W84" s="63"/>
-      <c r="X84" s="61"/>
-      <c r="Y84" s="61"/>
-      <c r="Z84" s="61"/>
-      <c r="AA84" s="61"/>
-    </row>
-    <row r="85" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="B85" s="47">
-        <v>15</v>
-      </c>
-      <c r="C85" s="49" t="str">
-        <f>C42</f>
-        <v xml:space="preserve">Cho vay hỗ trợ hộ nghèo về nhà ở theo QĐ 33/2015/QĐ-TTg </v>
-      </c>
-      <c r="D85" s="50"/>
-      <c r="E85" s="50"/>
-      <c r="F85" s="50"/>
-      <c r="G85" s="29">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H85" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J85" s="15"/>
-      <c r="K85" s="15"/>
-      <c r="L85" s="63"/>
-      <c r="M85" s="63"/>
-      <c r="N85" s="63"/>
-      <c r="O85" s="63"/>
-      <c r="P85" s="63"/>
-      <c r="Q85" s="63"/>
-      <c r="R85" s="63"/>
-      <c r="S85" s="63"/>
-      <c r="T85" s="63"/>
-      <c r="U85" s="63"/>
-      <c r="V85" s="63"/>
-      <c r="W85" s="63"/>
-      <c r="X85" s="63"/>
-      <c r="Y85" s="63"/>
-      <c r="Z85" s="63"/>
-      <c r="AA85" s="63"/>
-    </row>
-    <row r="86" spans="1:27" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="B86" s="47">
-        <v>16</v>
-      </c>
-      <c r="C86" s="49" t="s">
-        <v>155</v>
-      </c>
-      <c r="D86" s="50"/>
-      <c r="E86" s="50"/>
-      <c r="F86" s="50"/>
-      <c r="G86" s="29">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H86" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J86" s="15"/>
-      <c r="K86" s="15"/>
-      <c r="L86" s="61"/>
-      <c r="M86" s="61"/>
-      <c r="N86" s="61"/>
-      <c r="O86" s="61"/>
-      <c r="P86" s="61"/>
-      <c r="Q86" s="61"/>
-      <c r="R86" s="61"/>
-      <c r="S86" s="61"/>
-      <c r="T86" s="61"/>
-      <c r="U86" s="61"/>
-      <c r="V86" s="61"/>
-      <c r="W86" s="61"/>
-      <c r="X86" s="61"/>
-      <c r="Y86" s="61"/>
-      <c r="Z86" s="61"/>
-      <c r="AA86" s="61"/>
-    </row>
-    <row r="87" spans="1:27" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="B87" s="77" t="s">
-        <v>29</v>
-      </c>
-      <c r="C87" s="78" t="s">
-        <v>156</v>
-      </c>
-      <c r="D87" s="50"/>
-      <c r="E87" s="50"/>
-      <c r="F87" s="50"/>
-      <c r="G87" s="29">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H87" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J87" s="15"/>
-      <c r="K87" s="15"/>
-      <c r="L87" s="61"/>
-      <c r="M87" s="61"/>
-      <c r="N87" s="61"/>
-      <c r="O87" s="61"/>
-      <c r="P87" s="61"/>
-      <c r="Q87" s="61"/>
-      <c r="R87" s="61"/>
-      <c r="S87" s="61"/>
-      <c r="T87" s="61"/>
-      <c r="U87" s="61"/>
-      <c r="V87" s="61"/>
-      <c r="W87" s="61"/>
-      <c r="X87" s="61"/>
-      <c r="Y87" s="61"/>
-      <c r="Z87" s="61"/>
-      <c r="AA87" s="61"/>
-    </row>
-    <row r="88" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="B88" s="79"/>
-      <c r="C88" s="80" t="s">
-        <v>121</v>
-      </c>
-      <c r="D88" s="50"/>
-      <c r="E88" s="50"/>
-      <c r="F88" s="50"/>
-      <c r="G88" s="29">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H88" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="I88" s="81"/>
-      <c r="J88" s="15"/>
-      <c r="K88" s="15"/>
-      <c r="L88" s="61"/>
-      <c r="M88" s="61"/>
-      <c r="N88" s="61"/>
-      <c r="O88" s="61"/>
-      <c r="P88" s="61"/>
-      <c r="Q88" s="61"/>
-      <c r="R88" s="61"/>
-      <c r="S88" s="61"/>
-      <c r="T88" s="61"/>
-      <c r="U88" s="61"/>
-      <c r="V88" s="61"/>
-      <c r="W88" s="61"/>
-      <c r="X88" s="61"/>
-      <c r="Y88" s="61"/>
-      <c r="Z88" s="61"/>
-      <c r="AA88" s="61"/>
-    </row>
-    <row r="89" spans="1:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="B89" s="47">
-        <v>17</v>
-      </c>
-      <c r="C89" s="48" t="str">
-        <f>C51</f>
-        <v>Cho vay hỗ trợ phát triển kinh tế - xã hội vùng dân tộc thiểu số và miền núi giai đoạn 2017 - 2020 theo Quyết định số 2085/QĐ-TTg</v>
-      </c>
-      <c r="D89" s="36"/>
-      <c r="E89" s="36"/>
-      <c r="F89" s="36"/>
-      <c r="G89" s="29">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H89" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J89" s="15"/>
-      <c r="K89" s="15"/>
-      <c r="L89" s="61"/>
-      <c r="M89" s="61"/>
-      <c r="N89" s="61"/>
-      <c r="O89" s="61"/>
-      <c r="P89" s="61"/>
-      <c r="Q89" s="61"/>
-      <c r="R89" s="61"/>
-      <c r="S89" s="61"/>
-      <c r="T89" s="61"/>
-      <c r="U89" s="61"/>
-      <c r="V89" s="61"/>
-      <c r="W89" s="61"/>
-      <c r="X89" s="61"/>
-      <c r="Y89" s="61"/>
-      <c r="Z89" s="61"/>
-      <c r="AA89" s="61"/>
-    </row>
-    <row r="90" spans="1:27" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="B90" s="47">
-        <v>18</v>
-      </c>
-      <c r="C90" s="64" t="s">
-        <v>122</v>
-      </c>
-      <c r="D90" s="36"/>
-      <c r="E90" s="36"/>
-      <c r="F90" s="36"/>
-      <c r="G90" s="29">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H90" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J90" s="15"/>
-      <c r="K90" s="15"/>
-      <c r="L90" s="61"/>
-      <c r="M90" s="61"/>
-      <c r="N90" s="61"/>
-      <c r="O90" s="61"/>
-      <c r="P90" s="61"/>
-      <c r="Q90" s="61"/>
-      <c r="R90" s="61"/>
-      <c r="S90" s="61"/>
-      <c r="T90" s="61"/>
-      <c r="U90" s="61"/>
-      <c r="V90" s="61"/>
-      <c r="W90" s="61"/>
-      <c r="X90" s="61"/>
-      <c r="Y90" s="61"/>
-      <c r="Z90" s="61"/>
-      <c r="AA90" s="61"/>
-    </row>
-    <row r="91" spans="1:27" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="B91" s="47">
-        <v>19</v>
-      </c>
-      <c r="C91" s="64" t="s">
-        <v>123</v>
-      </c>
-      <c r="D91" s="36"/>
-      <c r="E91" s="36"/>
-      <c r="F91" s="36"/>
-      <c r="G91" s="29">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H91" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J91" s="15"/>
-      <c r="K91" s="15"/>
-      <c r="L91" s="61"/>
-      <c r="M91" s="61"/>
-      <c r="N91" s="61"/>
-      <c r="O91" s="61"/>
-      <c r="P91" s="61"/>
-      <c r="Q91" s="61"/>
-      <c r="R91" s="61"/>
-      <c r="S91" s="61"/>
-      <c r="T91" s="61"/>
-      <c r="U91" s="61"/>
-      <c r="V91" s="61"/>
-      <c r="W91" s="61"/>
-      <c r="X91" s="61"/>
-      <c r="Y91" s="61"/>
-      <c r="Z91" s="61"/>
-      <c r="AA91" s="61"/>
-    </row>
-    <row r="92" spans="1:27" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="16" t="s">
-        <v>168</v>
-      </c>
-      <c r="B92" s="47">
-        <v>20</v>
-      </c>
-      <c r="C92" s="64" t="s">
-        <v>161</v>
-      </c>
-      <c r="D92" s="36"/>
-      <c r="E92" s="36"/>
-      <c r="F92" s="36"/>
-      <c r="G92" s="29">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H92" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J92" s="15"/>
-      <c r="K92" s="15"/>
-      <c r="L92" s="61"/>
-      <c r="M92" s="61"/>
-      <c r="N92" s="61"/>
-      <c r="O92" s="61"/>
-      <c r="P92" s="61"/>
-      <c r="Q92" s="61"/>
-      <c r="R92" s="61"/>
-      <c r="S92" s="61"/>
-      <c r="T92" s="61"/>
-      <c r="U92" s="61"/>
-      <c r="V92" s="61"/>
-      <c r="W92" s="61"/>
-      <c r="X92" s="61"/>
-      <c r="Y92" s="61"/>
-      <c r="Z92" s="61"/>
-      <c r="AA92" s="61"/>
-    </row>
-    <row r="93" spans="1:27" s="93" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="B93" s="47">
-        <v>21</v>
-      </c>
-      <c r="C93" s="51" t="s">
-        <v>183</v>
-      </c>
-      <c r="D93" s="36"/>
-      <c r="E93" s="36"/>
-      <c r="F93" s="36"/>
-      <c r="G93" s="29">
-        <v>0</v>
-      </c>
-      <c r="H93" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J93" s="15"/>
-      <c r="K93" s="15"/>
-      <c r="L93" s="61"/>
-      <c r="M93" s="61"/>
-      <c r="N93" s="61"/>
-      <c r="O93" s="61"/>
-      <c r="P93" s="61"/>
-      <c r="Q93" s="61"/>
-      <c r="R93" s="61"/>
-      <c r="S93" s="61"/>
-      <c r="T93" s="61"/>
-      <c r="U93" s="61"/>
-      <c r="V93" s="61"/>
-      <c r="W93" s="61"/>
-      <c r="X93" s="61"/>
-      <c r="Y93" s="61"/>
-      <c r="Z93" s="61"/>
-      <c r="AA93" s="61"/>
-    </row>
-    <row r="94" spans="1:27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="B94" s="47">
-        <v>22</v>
-      </c>
-      <c r="C94" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="D94" s="36"/>
-      <c r="E94" s="36"/>
-      <c r="F94" s="36"/>
-      <c r="G94" s="29">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H94" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J94" s="15"/>
-      <c r="K94" s="15"/>
-      <c r="L94" s="61"/>
-      <c r="M94" s="61"/>
-      <c r="N94" s="61"/>
-      <c r="O94" s="61"/>
-      <c r="P94" s="61"/>
-      <c r="Q94" s="61"/>
-      <c r="R94" s="61"/>
-      <c r="S94" s="61"/>
-      <c r="T94" s="61"/>
-      <c r="U94" s="61"/>
-      <c r="V94" s="61"/>
-      <c r="W94" s="61"/>
-      <c r="X94" s="61"/>
-      <c r="Y94" s="61"/>
-      <c r="Z94" s="61"/>
-      <c r="AA94" s="61"/>
-    </row>
-    <row r="95" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="B95" s="65" t="s">
-        <v>164</v>
-      </c>
-      <c r="C95" s="66" t="s">
-        <v>165</v>
-      </c>
-      <c r="D95" s="19">
-        <f t="shared" ref="D95:G95" si="13">D97+D96</f>
-        <v>0</v>
-      </c>
-      <c r="E95" s="19">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="F95" s="19">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="G95" s="19">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="H95" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J95" s="15"/>
-      <c r="K95" s="15"/>
-      <c r="L95" s="45"/>
-      <c r="M95" s="45"/>
-      <c r="N95" s="45"/>
-      <c r="O95" s="45"/>
-      <c r="P95" s="45"/>
-      <c r="Q95" s="45"/>
-      <c r="R95" s="45"/>
-      <c r="S95" s="45"/>
-      <c r="T95" s="45"/>
-      <c r="U95" s="45"/>
-      <c r="V95" s="45"/>
-      <c r="W95" s="45"/>
-      <c r="X95" s="45"/>
-      <c r="Y95" s="45"/>
-      <c r="Z95" s="45"/>
-      <c r="AA95" s="45"/>
-    </row>
-    <row r="96" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="16" t="s">
-        <v>172</v>
-      </c>
-      <c r="B96" s="52" t="s">
-        <v>29</v>
-      </c>
-      <c r="C96" s="53" t="s">
-        <v>167</v>
-      </c>
-      <c r="D96" s="36"/>
-      <c r="E96" s="36"/>
-      <c r="F96" s="36"/>
-      <c r="G96" s="29">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H96" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J96" s="15"/>
-      <c r="K96" s="15"/>
-      <c r="L96" s="67"/>
-      <c r="M96" s="67"/>
-      <c r="N96" s="67"/>
-      <c r="O96" s="67"/>
-      <c r="P96" s="67"/>
-      <c r="Q96" s="67"/>
-      <c r="R96" s="67"/>
-      <c r="S96" s="67"/>
-      <c r="T96" s="67"/>
-      <c r="U96" s="67"/>
-      <c r="V96" s="67"/>
-      <c r="W96" s="67"/>
-      <c r="X96" s="67"/>
-      <c r="Y96" s="67"/>
-      <c r="Z96" s="67"/>
-      <c r="AA96" s="67"/>
-    </row>
-    <row r="97" spans="1:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="B97" s="52"/>
-      <c r="C97" s="53" t="s">
-        <v>169</v>
-      </c>
-      <c r="D97" s="36"/>
-      <c r="E97" s="36"/>
-      <c r="F97" s="36"/>
-      <c r="G97" s="29">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H97" s="25">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J97" s="15"/>
-      <c r="K97" s="15"/>
-      <c r="L97" s="67"/>
-      <c r="M97" s="67"/>
-      <c r="N97" s="67"/>
-      <c r="O97" s="67"/>
-      <c r="P97" s="67"/>
-      <c r="Q97" s="67"/>
-      <c r="R97" s="67"/>
-      <c r="S97" s="67"/>
-      <c r="T97" s="67"/>
-      <c r="U97" s="67"/>
-      <c r="V97" s="67"/>
-      <c r="W97" s="67"/>
-      <c r="X97" s="67"/>
-      <c r="Y97" s="67"/>
-      <c r="Z97" s="67"/>
-      <c r="AA97" s="67"/>
-    </row>
-    <row r="98" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="16" t="s">
-        <v>182</v>
-      </c>
-      <c r="B98" s="94" t="s">
-        <v>175</v>
-      </c>
-      <c r="C98" s="95"/>
-      <c r="D98" s="95"/>
-      <c r="E98" s="95"/>
-      <c r="F98" s="96"/>
-      <c r="G98" s="97" t="s">
-        <v>176</v>
-      </c>
-      <c r="H98" s="98"/>
-      <c r="J98" s="15"/>
-      <c r="K98" s="15"/>
+      <c r="H71" s="11"/>
+      <c r="I71" s="4"/>
+      <c r="J71" s="4"/>
+      <c r="K71" s="4"/>
+      <c r="L71" s="4"/>
+      <c r="M71" s="4"/>
+      <c r="N71" s="4"/>
+      <c r="O71" s="4"/>
+      <c r="P71" s="4"/>
+      <c r="Q71" s="4"/>
+      <c r="R71" s="4"/>
+      <c r="S71" s="4"/>
+      <c r="T71" s="4"/>
+      <c r="U71" s="4"/>
+      <c r="V71" s="4"/>
+      <c r="W71" s="4"/>
+      <c r="X71" s="4"/>
+      <c r="Y71" s="4"/>
+      <c r="Z71" s="4"/>
+      <c r="AA71" s="4"/>
+    </row>
+    <row r="72" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B72" s="32"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="11"/>
+      <c r="I72" s="4"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="4"/>
+      <c r="L72" s="4"/>
+      <c r="M72" s="4"/>
+      <c r="N72" s="4"/>
+      <c r="O72" s="4"/>
+      <c r="P72" s="4"/>
+      <c r="Q72" s="4"/>
+      <c r="R72" s="4"/>
+      <c r="S72" s="4"/>
+      <c r="T72" s="4"/>
+      <c r="U72" s="4"/>
+      <c r="V72" s="4"/>
+      <c r="W72" s="4"/>
+      <c r="X72" s="4"/>
+      <c r="Y72" s="4"/>
+      <c r="Z72" s="4"/>
+      <c r="AA72" s="4"/>
+    </row>
+    <row r="73" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B73" s="4"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="4"/>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
+      <c r="G73" s="4"/>
+      <c r="H73" s="11"/>
+      <c r="I73" s="4"/>
+      <c r="J73" s="4"/>
+      <c r="K73" s="4"/>
+      <c r="L73" s="4"/>
+      <c r="M73" s="4"/>
+      <c r="N73" s="4"/>
+      <c r="O73" s="4"/>
+      <c r="P73" s="4"/>
+      <c r="Q73" s="4"/>
+      <c r="R73" s="4"/>
+      <c r="S73" s="4"/>
+      <c r="T73" s="4"/>
+      <c r="U73" s="4"/>
+      <c r="V73" s="4"/>
+      <c r="W73" s="4"/>
+      <c r="X73" s="4"/>
+      <c r="Y73" s="4"/>
+      <c r="Z73" s="4"/>
+      <c r="AA73" s="4"/>
+    </row>
+    <row r="74" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B74" s="4"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="4"/>
+      <c r="H74" s="11"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="4"/>
+      <c r="L74" s="4"/>
+      <c r="M74" s="4"/>
+      <c r="N74" s="4"/>
+      <c r="O74" s="4"/>
+      <c r="P74" s="4"/>
+      <c r="Q74" s="4"/>
+      <c r="R74" s="4"/>
+      <c r="S74" s="4"/>
+      <c r="T74" s="4"/>
+      <c r="U74" s="4"/>
+      <c r="V74" s="4"/>
+      <c r="W74" s="4"/>
+      <c r="X74" s="4"/>
+      <c r="Y74" s="4"/>
+      <c r="Z74" s="4"/>
+      <c r="AA74" s="4"/>
+    </row>
+    <row r="75" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B75" s="4"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="4"/>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4"/>
+      <c r="G75" s="4"/>
+      <c r="H75" s="11"/>
+      <c r="I75" s="4"/>
+      <c r="J75" s="4"/>
+      <c r="K75" s="4"/>
+      <c r="L75" s="4"/>
+      <c r="M75" s="4"/>
+      <c r="N75" s="4"/>
+      <c r="O75" s="4"/>
+      <c r="P75" s="4"/>
+      <c r="Q75" s="4"/>
+      <c r="R75" s="4"/>
+      <c r="S75" s="4"/>
+      <c r="T75" s="4"/>
+      <c r="U75" s="4"/>
+      <c r="V75" s="4"/>
+      <c r="W75" s="4"/>
+      <c r="X75" s="4"/>
+      <c r="Y75" s="4"/>
+      <c r="Z75" s="4"/>
+      <c r="AA75" s="4"/>
+    </row>
+    <row r="76" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B76" s="4"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="4"/>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
+      <c r="G76" s="4"/>
+      <c r="H76" s="11"/>
+      <c r="I76" s="4"/>
+      <c r="J76" s="4"/>
+      <c r="K76" s="4"/>
+      <c r="L76" s="4"/>
+      <c r="M76" s="4"/>
+      <c r="N76" s="4"/>
+      <c r="O76" s="4"/>
+      <c r="P76" s="4"/>
+      <c r="Q76" s="4"/>
+      <c r="R76" s="4"/>
+      <c r="S76" s="4"/>
+      <c r="T76" s="4"/>
+      <c r="U76" s="4"/>
+      <c r="V76" s="4"/>
+      <c r="W76" s="4"/>
+      <c r="X76" s="4"/>
+      <c r="Y76" s="4"/>
+      <c r="Z76" s="4"/>
+      <c r="AA76" s="4"/>
+    </row>
+    <row r="77" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B77" s="4"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+      <c r="G77" s="4"/>
+      <c r="H77" s="11"/>
+      <c r="I77" s="4"/>
+      <c r="J77" s="4"/>
+      <c r="K77" s="4"/>
+      <c r="L77" s="4"/>
+      <c r="M77" s="4"/>
+      <c r="N77" s="4"/>
+      <c r="O77" s="4"/>
+      <c r="P77" s="4"/>
+      <c r="Q77" s="4"/>
+      <c r="R77" s="4"/>
+      <c r="S77" s="4"/>
+      <c r="T77" s="4"/>
+      <c r="U77" s="4"/>
+      <c r="V77" s="4"/>
+      <c r="W77" s="4"/>
+      <c r="X77" s="4"/>
+      <c r="Y77" s="4"/>
+      <c r="Z77" s="4"/>
+      <c r="AA77" s="4"/>
+    </row>
+    <row r="78" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B78" s="4"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4"/>
+      <c r="H78" s="11"/>
+      <c r="I78" s="4"/>
+      <c r="J78" s="4"/>
+      <c r="K78" s="4"/>
+      <c r="L78" s="4"/>
+      <c r="M78" s="4"/>
+      <c r="N78" s="4"/>
+      <c r="O78" s="4"/>
+      <c r="P78" s="4"/>
+      <c r="Q78" s="4"/>
+      <c r="R78" s="4"/>
+      <c r="S78" s="4"/>
+      <c r="T78" s="4"/>
+      <c r="U78" s="4"/>
+      <c r="V78" s="4"/>
+      <c r="W78" s="4"/>
+      <c r="X78" s="4"/>
+      <c r="Y78" s="4"/>
+      <c r="Z78" s="4"/>
+      <c r="AA78" s="4"/>
+    </row>
+    <row r="79" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B79" s="4"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="11"/>
+      <c r="I79" s="4"/>
+      <c r="J79" s="4"/>
+      <c r="K79" s="4"/>
+      <c r="L79" s="4"/>
+      <c r="M79" s="4"/>
+      <c r="N79" s="4"/>
+      <c r="O79" s="4"/>
+      <c r="P79" s="4"/>
+      <c r="Q79" s="4"/>
+      <c r="R79" s="4"/>
+      <c r="S79" s="4"/>
+      <c r="T79" s="4"/>
+      <c r="U79" s="4"/>
+      <c r="V79" s="4"/>
+      <c r="W79" s="4"/>
+      <c r="X79" s="4"/>
+      <c r="Y79" s="4"/>
+      <c r="Z79" s="4"/>
+      <c r="AA79" s="4"/>
+    </row>
+    <row r="80" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B80" s="4"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="4"/>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
+      <c r="G80" s="4"/>
+      <c r="H80" s="11"/>
+      <c r="I80" s="4"/>
+      <c r="J80" s="4"/>
+      <c r="K80" s="4"/>
+      <c r="L80" s="4"/>
+      <c r="M80" s="4"/>
+      <c r="N80" s="4"/>
+      <c r="O80" s="4"/>
+      <c r="P80" s="4"/>
+      <c r="Q80" s="4"/>
+      <c r="R80" s="4"/>
+      <c r="S80" s="4"/>
+      <c r="T80" s="4"/>
+      <c r="U80" s="4"/>
+      <c r="V80" s="4"/>
+      <c r="W80" s="4"/>
+      <c r="X80" s="4"/>
+      <c r="Y80" s="4"/>
+      <c r="Z80" s="4"/>
+      <c r="AA80" s="4"/>
+    </row>
+    <row r="81" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B81" s="4"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="4"/>
+      <c r="E81" s="4"/>
+      <c r="F81" s="4"/>
+      <c r="G81" s="4"/>
+      <c r="H81" s="11"/>
+      <c r="I81" s="4"/>
+      <c r="J81" s="4"/>
+      <c r="K81" s="4"/>
+      <c r="L81" s="4"/>
+      <c r="M81" s="4"/>
+      <c r="N81" s="4"/>
+      <c r="O81" s="4"/>
+      <c r="P81" s="4"/>
+      <c r="Q81" s="4"/>
+      <c r="R81" s="4"/>
+      <c r="S81" s="4"/>
+      <c r="T81" s="4"/>
+      <c r="U81" s="4"/>
+      <c r="V81" s="4"/>
+      <c r="W81" s="4"/>
+      <c r="X81" s="4"/>
+      <c r="Y81" s="4"/>
+      <c r="Z81" s="4"/>
+      <c r="AA81" s="4"/>
+    </row>
+    <row r="82" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B82" s="4"/>
+      <c r="C82" s="2"/>
+      <c r="D82" s="4"/>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
+      <c r="G82" s="4"/>
+      <c r="H82" s="11"/>
+      <c r="I82" s="4"/>
+      <c r="J82" s="4"/>
+      <c r="K82" s="4"/>
+      <c r="L82" s="4"/>
+      <c r="M82" s="4"/>
+      <c r="N82" s="4"/>
+      <c r="O82" s="4"/>
+      <c r="P82" s="4"/>
+      <c r="Q82" s="4"/>
+      <c r="R82" s="4"/>
+      <c r="S82" s="4"/>
+      <c r="T82" s="4"/>
+      <c r="U82" s="4"/>
+      <c r="V82" s="4"/>
+      <c r="W82" s="4"/>
+      <c r="X82" s="4"/>
+      <c r="Y82" s="4"/>
+      <c r="Z82" s="4"/>
+      <c r="AA82" s="4"/>
+    </row>
+    <row r="83" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B83" s="4"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="4"/>
+      <c r="E83" s="4"/>
+      <c r="F83" s="4"/>
+      <c r="G83" s="4"/>
+      <c r="H83" s="11"/>
+      <c r="I83" s="4"/>
+      <c r="J83" s="4"/>
+      <c r="K83" s="4"/>
+      <c r="L83" s="4"/>
+      <c r="M83" s="4"/>
+      <c r="N83" s="4"/>
+      <c r="O83" s="4"/>
+      <c r="P83" s="4"/>
+      <c r="Q83" s="4"/>
+      <c r="R83" s="4"/>
+      <c r="S83" s="4"/>
+      <c r="T83" s="4"/>
+      <c r="U83" s="4"/>
+      <c r="V83" s="4"/>
+      <c r="W83" s="4"/>
+      <c r="X83" s="4"/>
+      <c r="Y83" s="4"/>
+      <c r="Z83" s="4"/>
+      <c r="AA83" s="4"/>
+    </row>
+    <row r="84" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B84" s="4"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="4"/>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+      <c r="G84" s="4"/>
+      <c r="H84" s="11"/>
+      <c r="I84" s="4"/>
+      <c r="J84" s="4"/>
+      <c r="K84" s="4"/>
+      <c r="L84" s="4"/>
+      <c r="M84" s="4"/>
+      <c r="N84" s="4"/>
+      <c r="O84" s="4"/>
+      <c r="P84" s="4"/>
+      <c r="Q84" s="4"/>
+      <c r="R84" s="4"/>
+      <c r="S84" s="4"/>
+      <c r="T84" s="4"/>
+      <c r="U84" s="4"/>
+      <c r="V84" s="4"/>
+      <c r="W84" s="4"/>
+      <c r="X84" s="4"/>
+      <c r="Y84" s="4"/>
+      <c r="Z84" s="4"/>
+      <c r="AA84" s="4"/>
+    </row>
+    <row r="85" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B85" s="4"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="4"/>
+      <c r="E85" s="4"/>
+      <c r="F85" s="4"/>
+      <c r="G85" s="4"/>
+      <c r="H85" s="11"/>
+      <c r="I85" s="4"/>
+      <c r="J85" s="4"/>
+      <c r="K85" s="4"/>
+      <c r="L85" s="4"/>
+      <c r="M85" s="4"/>
+      <c r="N85" s="4"/>
+      <c r="O85" s="4"/>
+      <c r="P85" s="4"/>
+      <c r="Q85" s="4"/>
+      <c r="R85" s="4"/>
+      <c r="S85" s="4"/>
+      <c r="T85" s="4"/>
+      <c r="U85" s="4"/>
+      <c r="V85" s="4"/>
+      <c r="W85" s="4"/>
+      <c r="X85" s="4"/>
+      <c r="Y85" s="4"/>
+      <c r="Z85" s="4"/>
+      <c r="AA85" s="4"/>
+    </row>
+    <row r="86" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B86" s="4"/>
+      <c r="C86" s="2"/>
+      <c r="D86" s="4"/>
+      <c r="E86" s="4"/>
+      <c r="F86" s="4"/>
+      <c r="G86" s="4"/>
+      <c r="H86" s="11"/>
+      <c r="I86" s="4"/>
+      <c r="J86" s="4"/>
+      <c r="K86" s="4"/>
+      <c r="L86" s="4"/>
+      <c r="M86" s="4"/>
+      <c r="N86" s="4"/>
+      <c r="O86" s="4"/>
+      <c r="P86" s="4"/>
+      <c r="Q86" s="4"/>
+      <c r="R86" s="4"/>
+      <c r="S86" s="4"/>
+      <c r="T86" s="4"/>
+      <c r="U86" s="4"/>
+      <c r="V86" s="4"/>
+      <c r="W86" s="4"/>
+      <c r="X86" s="4"/>
+      <c r="Y86" s="4"/>
+      <c r="Z86" s="4"/>
+      <c r="AA86" s="4"/>
+    </row>
+    <row r="87" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B87" s="4"/>
+      <c r="C87" s="2"/>
+      <c r="D87" s="4"/>
+      <c r="E87" s="4"/>
+      <c r="F87" s="4"/>
+      <c r="G87" s="4"/>
+      <c r="H87" s="11"/>
+      <c r="I87" s="4"/>
+      <c r="J87" s="4"/>
+      <c r="K87" s="4"/>
+      <c r="L87" s="4"/>
+      <c r="M87" s="4"/>
+      <c r="N87" s="4"/>
+      <c r="O87" s="4"/>
+      <c r="P87" s="4"/>
+      <c r="Q87" s="4"/>
+      <c r="R87" s="4"/>
+      <c r="S87" s="4"/>
+      <c r="T87" s="4"/>
+      <c r="U87" s="4"/>
+      <c r="V87" s="4"/>
+      <c r="W87" s="4"/>
+      <c r="X87" s="4"/>
+      <c r="Y87" s="4"/>
+      <c r="Z87" s="4"/>
+      <c r="AA87" s="4"/>
+    </row>
+    <row r="88" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B88" s="4"/>
+      <c r="C88" s="2"/>
+      <c r="D88" s="4"/>
+      <c r="E88" s="4"/>
+      <c r="F88" s="4"/>
+      <c r="G88" s="4"/>
+      <c r="H88" s="11"/>
+      <c r="I88" s="4"/>
+      <c r="J88" s="4"/>
+      <c r="K88" s="4"/>
+      <c r="L88" s="4"/>
+      <c r="M88" s="4"/>
+      <c r="N88" s="4"/>
+      <c r="O88" s="4"/>
+      <c r="P88" s="4"/>
+      <c r="Q88" s="4"/>
+      <c r="R88" s="4"/>
+      <c r="S88" s="4"/>
+      <c r="T88" s="4"/>
+      <c r="U88" s="4"/>
+      <c r="V88" s="4"/>
+      <c r="W88" s="4"/>
+      <c r="X88" s="4"/>
+      <c r="Y88" s="4"/>
+      <c r="Z88" s="4"/>
+      <c r="AA88" s="4"/>
+    </row>
+    <row r="89" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B89" s="4"/>
+      <c r="C89" s="2"/>
+      <c r="D89" s="4"/>
+      <c r="E89" s="4"/>
+      <c r="F89" s="4"/>
+      <c r="G89" s="4"/>
+      <c r="H89" s="11"/>
+      <c r="I89" s="4"/>
+      <c r="J89" s="4"/>
+      <c r="K89" s="4"/>
+      <c r="L89" s="4"/>
+      <c r="M89" s="4"/>
+      <c r="N89" s="4"/>
+      <c r="O89" s="4"/>
+      <c r="P89" s="4"/>
+      <c r="Q89" s="4"/>
+      <c r="R89" s="4"/>
+      <c r="S89" s="4"/>
+      <c r="T89" s="4"/>
+      <c r="U89" s="4"/>
+      <c r="V89" s="4"/>
+      <c r="W89" s="4"/>
+      <c r="X89" s="4"/>
+      <c r="Y89" s="4"/>
+      <c r="Z89" s="4"/>
+      <c r="AA89" s="4"/>
+    </row>
+    <row r="90" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B90" s="4"/>
+      <c r="C90" s="2"/>
+      <c r="D90" s="4"/>
+      <c r="E90" s="4"/>
+      <c r="F90" s="4"/>
+      <c r="G90" s="4"/>
+      <c r="H90" s="11"/>
+      <c r="I90" s="4"/>
+      <c r="J90" s="4"/>
+      <c r="K90" s="4"/>
+      <c r="L90" s="4"/>
+      <c r="M90" s="4"/>
+      <c r="N90" s="4"/>
+      <c r="O90" s="4"/>
+      <c r="P90" s="4"/>
+      <c r="Q90" s="4"/>
+      <c r="R90" s="4"/>
+      <c r="S90" s="4"/>
+      <c r="T90" s="4"/>
+      <c r="U90" s="4"/>
+      <c r="V90" s="4"/>
+      <c r="W90" s="4"/>
+      <c r="X90" s="4"/>
+      <c r="Y90" s="4"/>
+      <c r="Z90" s="4"/>
+      <c r="AA90" s="4"/>
+    </row>
+    <row r="91" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B91" s="4"/>
+      <c r="C91" s="2"/>
+      <c r="D91" s="4"/>
+      <c r="E91" s="4"/>
+      <c r="F91" s="4"/>
+      <c r="G91" s="4"/>
+      <c r="H91" s="11"/>
+      <c r="I91" s="4"/>
+      <c r="J91" s="4"/>
+      <c r="K91" s="4"/>
+      <c r="L91" s="4"/>
+      <c r="M91" s="4"/>
+      <c r="N91" s="4"/>
+      <c r="O91" s="4"/>
+      <c r="P91" s="4"/>
+      <c r="Q91" s="4"/>
+      <c r="R91" s="4"/>
+      <c r="S91" s="4"/>
+      <c r="T91" s="4"/>
+      <c r="U91" s="4"/>
+      <c r="V91" s="4"/>
+      <c r="W91" s="4"/>
+      <c r="X91" s="4"/>
+      <c r="Y91" s="4"/>
+      <c r="Z91" s="4"/>
+      <c r="AA91" s="4"/>
+    </row>
+    <row r="92" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B92" s="4"/>
+      <c r="C92" s="2"/>
+      <c r="D92" s="4"/>
+      <c r="E92" s="4"/>
+      <c r="F92" s="4"/>
+      <c r="G92" s="4"/>
+      <c r="H92" s="11"/>
+      <c r="I92" s="4"/>
+      <c r="J92" s="4"/>
+      <c r="K92" s="4"/>
+      <c r="L92" s="4"/>
+      <c r="M92" s="4"/>
+      <c r="N92" s="4"/>
+      <c r="O92" s="4"/>
+      <c r="P92" s="4"/>
+      <c r="Q92" s="4"/>
+      <c r="R92" s="4"/>
+      <c r="S92" s="4"/>
+      <c r="T92" s="4"/>
+      <c r="U92" s="4"/>
+      <c r="V92" s="4"/>
+      <c r="W92" s="4"/>
+      <c r="X92" s="4"/>
+      <c r="Y92" s="4"/>
+      <c r="Z92" s="4"/>
+      <c r="AA92" s="4"/>
+    </row>
+    <row r="93" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B93" s="4"/>
+      <c r="C93" s="2"/>
+      <c r="D93" s="4"/>
+      <c r="E93" s="4"/>
+      <c r="F93" s="4"/>
+      <c r="G93" s="4"/>
+      <c r="H93" s="11"/>
+      <c r="I93" s="4"/>
+      <c r="J93" s="4"/>
+      <c r="K93" s="4"/>
+      <c r="L93" s="4"/>
+      <c r="M93" s="4"/>
+      <c r="N93" s="4"/>
+      <c r="O93" s="4"/>
+      <c r="P93" s="4"/>
+      <c r="Q93" s="4"/>
+      <c r="R93" s="4"/>
+      <c r="S93" s="4"/>
+      <c r="T93" s="4"/>
+      <c r="U93" s="4"/>
+      <c r="V93" s="4"/>
+      <c r="W93" s="4"/>
+      <c r="X93" s="4"/>
+      <c r="Y93" s="4"/>
+      <c r="Z93" s="4"/>
+      <c r="AA93" s="4"/>
+    </row>
+    <row r="94" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B94" s="4"/>
+      <c r="C94" s="2"/>
+      <c r="D94" s="4"/>
+      <c r="E94" s="4"/>
+      <c r="F94" s="4"/>
+      <c r="G94" s="4"/>
+      <c r="H94" s="11"/>
+      <c r="I94" s="4"/>
+      <c r="J94" s="4"/>
+      <c r="K94" s="4"/>
+      <c r="L94" s="4"/>
+      <c r="M94" s="4"/>
+      <c r="N94" s="4"/>
+      <c r="O94" s="4"/>
+      <c r="P94" s="4"/>
+      <c r="Q94" s="4"/>
+      <c r="R94" s="4"/>
+      <c r="S94" s="4"/>
+      <c r="T94" s="4"/>
+      <c r="U94" s="4"/>
+      <c r="V94" s="4"/>
+      <c r="W94" s="4"/>
+      <c r="X94" s="4"/>
+      <c r="Y94" s="4"/>
+      <c r="Z94" s="4"/>
+      <c r="AA94" s="4"/>
+    </row>
+    <row r="95" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B95" s="4"/>
+      <c r="C95" s="2"/>
+      <c r="D95" s="4"/>
+      <c r="E95" s="4"/>
+      <c r="F95" s="4"/>
+      <c r="G95" s="4"/>
+      <c r="H95" s="11"/>
+      <c r="I95" s="4"/>
+      <c r="J95" s="4"/>
+      <c r="K95" s="4"/>
+      <c r="L95" s="4"/>
+      <c r="M95" s="4"/>
+      <c r="N95" s="4"/>
+      <c r="O95" s="4"/>
+      <c r="P95" s="4"/>
+      <c r="Q95" s="4"/>
+      <c r="R95" s="4"/>
+      <c r="S95" s="4"/>
+      <c r="T95" s="4"/>
+      <c r="U95" s="4"/>
+      <c r="V95" s="4"/>
+      <c r="W95" s="4"/>
+      <c r="X95" s="4"/>
+      <c r="Y95" s="4"/>
+      <c r="Z95" s="4"/>
+      <c r="AA95" s="4"/>
+    </row>
+    <row r="96" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B96" s="4"/>
+      <c r="C96" s="2"/>
+      <c r="D96" s="4"/>
+      <c r="E96" s="4"/>
+      <c r="F96" s="4"/>
+      <c r="G96" s="4"/>
+      <c r="H96" s="11"/>
+      <c r="I96" s="4"/>
+      <c r="J96" s="4"/>
+      <c r="K96" s="4"/>
+      <c r="L96" s="4"/>
+      <c r="M96" s="4"/>
+      <c r="N96" s="4"/>
+      <c r="O96" s="4"/>
+      <c r="P96" s="4"/>
+      <c r="Q96" s="4"/>
+      <c r="R96" s="4"/>
+      <c r="S96" s="4"/>
+      <c r="T96" s="4"/>
+      <c r="U96" s="4"/>
+      <c r="V96" s="4"/>
+      <c r="W96" s="4"/>
+      <c r="X96" s="4"/>
+      <c r="Y96" s="4"/>
+      <c r="Z96" s="4"/>
+      <c r="AA96" s="4"/>
+    </row>
+    <row r="97" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B97" s="4"/>
+      <c r="C97" s="2"/>
+      <c r="D97" s="4"/>
+      <c r="E97" s="4"/>
+      <c r="F97" s="4"/>
+      <c r="G97" s="4"/>
+      <c r="H97" s="11"/>
+      <c r="I97" s="4"/>
+      <c r="J97" s="4"/>
+      <c r="K97" s="4"/>
+      <c r="L97" s="4"/>
+      <c r="M97" s="4"/>
+      <c r="N97" s="4"/>
+      <c r="O97" s="4"/>
+      <c r="P97" s="4"/>
+      <c r="Q97" s="4"/>
+      <c r="R97" s="4"/>
+      <c r="S97" s="4"/>
+      <c r="T97" s="4"/>
+      <c r="U97" s="4"/>
+      <c r="V97" s="4"/>
+      <c r="W97" s="4"/>
+      <c r="X97" s="4"/>
+      <c r="Y97" s="4"/>
+      <c r="Z97" s="4"/>
+      <c r="AA97" s="4"/>
+    </row>
+    <row r="98" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B98" s="4"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="4"/>
+      <c r="E98" s="4"/>
+      <c r="F98" s="4"/>
+      <c r="G98" s="4"/>
+      <c r="H98" s="11"/>
+      <c r="I98" s="4"/>
+      <c r="J98" s="4"/>
+      <c r="K98" s="4"/>
       <c r="L98" s="4"/>
       <c r="M98" s="4"/>
       <c r="N98" s="4"/>
@@ -6820,16 +6692,17 @@
       <c r="Z98" s="4"/>
       <c r="AA98" s="4"/>
     </row>
-    <row r="99" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B99" s="68"/>
-      <c r="C99" s="69"/>
-      <c r="D99" s="69"/>
-      <c r="E99" s="69"/>
-      <c r="F99" s="69"/>
-      <c r="G99" s="70"/>
-      <c r="H99" s="71"/>
-      <c r="J99" s="15"/>
-      <c r="K99" s="15"/>
+    <row r="99" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B99" s="4"/>
+      <c r="C99" s="2"/>
+      <c r="D99" s="4"/>
+      <c r="E99" s="4"/>
+      <c r="F99" s="4"/>
+      <c r="G99" s="4"/>
+      <c r="H99" s="11"/>
+      <c r="I99" s="4"/>
+      <c r="J99" s="4"/>
+      <c r="K99" s="4"/>
       <c r="L99" s="4"/>
       <c r="M99" s="4"/>
       <c r="N99" s="4"/>
@@ -6847,16 +6720,14 @@
       <c r="Z99" s="4"/>
       <c r="AA99" s="4"/>
     </row>
-    <row r="100" spans="1:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B100" s="72"/>
-      <c r="C100" s="72"/>
-      <c r="D100" s="72"/>
-      <c r="E100" s="99" t="s">
-        <v>181</v>
-      </c>
-      <c r="F100" s="100"/>
-      <c r="G100" s="100"/>
-      <c r="H100" s="101"/>
+    <row r="100" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B100" s="4"/>
+      <c r="C100" s="2"/>
+      <c r="D100" s="4"/>
+      <c r="E100" s="4"/>
+      <c r="F100" s="4"/>
+      <c r="G100" s="4"/>
+      <c r="H100" s="11"/>
       <c r="I100" s="4"/>
       <c r="J100" s="4"/>
       <c r="K100" s="4"/>
@@ -6877,19 +6748,13 @@
       <c r="Z100" s="4"/>
       <c r="AA100" s="4"/>
     </row>
-    <row r="101" spans="1:27" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B101" s="73"/>
-      <c r="C101" s="74" t="s">
-        <v>177</v>
-      </c>
-      <c r="D101" s="75" t="s">
-        <v>178</v>
-      </c>
-      <c r="E101" s="75"/>
-      <c r="F101" s="75"/>
-      <c r="G101" s="75" t="s">
-        <v>179</v>
-      </c>
+    <row r="101" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B101" s="4"/>
+      <c r="C101" s="2"/>
+      <c r="D101" s="4"/>
+      <c r="E101" s="4"/>
+      <c r="F101" s="4"/>
+      <c r="G101" s="4"/>
       <c r="H101" s="11"/>
       <c r="I101" s="4"/>
       <c r="J101" s="4"/>
@@ -6911,8 +6776,8 @@
       <c r="Z101" s="4"/>
       <c r="AA101" s="4"/>
     </row>
-    <row r="102" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B102" s="76"/>
+    <row r="102" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B102" s="4"/>
       <c r="C102" s="2"/>
       <c r="D102" s="4"/>
       <c r="E102" s="4"/>
@@ -6939,7 +6804,7 @@
       <c r="Z102" s="4"/>
       <c r="AA102" s="4"/>
     </row>
-    <row r="103" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B103" s="4"/>
       <c r="C103" s="2"/>
       <c r="D103" s="4"/>
@@ -6967,7 +6832,7 @@
       <c r="Z103" s="4"/>
       <c r="AA103" s="4"/>
     </row>
-    <row r="104" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B104" s="4"/>
       <c r="C104" s="2"/>
       <c r="D104" s="4"/>
@@ -6995,7 +6860,7 @@
       <c r="Z104" s="4"/>
       <c r="AA104" s="4"/>
     </row>
-    <row r="105" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B105" s="4"/>
       <c r="C105" s="2"/>
       <c r="D105" s="4"/>
@@ -7023,7 +6888,7 @@
       <c r="Z105" s="4"/>
       <c r="AA105" s="4"/>
     </row>
-    <row r="106" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B106" s="4"/>
       <c r="C106" s="2"/>
       <c r="D106" s="4"/>
@@ -7051,7 +6916,7 @@
       <c r="Z106" s="4"/>
       <c r="AA106" s="4"/>
     </row>
-    <row r="107" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B107" s="4"/>
       <c r="C107" s="2"/>
       <c r="D107" s="4"/>
@@ -7079,7 +6944,7 @@
       <c r="Z107" s="4"/>
       <c r="AA107" s="4"/>
     </row>
-    <row r="108" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B108" s="4"/>
       <c r="C108" s="2"/>
       <c r="D108" s="4"/>
@@ -7107,7 +6972,7 @@
       <c r="Z108" s="4"/>
       <c r="AA108" s="4"/>
     </row>
-    <row r="109" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B109" s="4"/>
       <c r="C109" s="2"/>
       <c r="D109" s="4"/>
@@ -7135,7 +7000,7 @@
       <c r="Z109" s="4"/>
       <c r="AA109" s="4"/>
     </row>
-    <row r="110" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B110" s="4"/>
       <c r="C110" s="2"/>
       <c r="D110" s="4"/>
@@ -7163,7 +7028,7 @@
       <c r="Z110" s="4"/>
       <c r="AA110" s="4"/>
     </row>
-    <row r="111" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B111" s="4"/>
       <c r="C111" s="2"/>
       <c r="D111" s="4"/>
@@ -7191,7 +7056,7 @@
       <c r="Z111" s="4"/>
       <c r="AA111" s="4"/>
     </row>
-    <row r="112" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B112" s="4"/>
       <c r="C112" s="2"/>
       <c r="D112" s="4"/>
@@ -30935,882 +30800,46 @@
       <c r="Z959" s="4"/>
       <c r="AA959" s="4"/>
     </row>
-    <row r="960" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B960" s="4"/>
-      <c r="C960" s="2"/>
-      <c r="D960" s="4"/>
-      <c r="E960" s="4"/>
-      <c r="F960" s="4"/>
-      <c r="G960" s="4"/>
-      <c r="H960" s="11"/>
-      <c r="I960" s="4"/>
-      <c r="J960" s="4"/>
-      <c r="K960" s="4"/>
-      <c r="L960" s="4"/>
-      <c r="M960" s="4"/>
-      <c r="N960" s="4"/>
-      <c r="O960" s="4"/>
-      <c r="P960" s="4"/>
-      <c r="Q960" s="4"/>
-      <c r="R960" s="4"/>
-      <c r="S960" s="4"/>
-      <c r="T960" s="4"/>
-      <c r="U960" s="4"/>
-      <c r="V960" s="4"/>
-      <c r="W960" s="4"/>
-      <c r="X960" s="4"/>
-      <c r="Y960" s="4"/>
-      <c r="Z960" s="4"/>
-      <c r="AA960" s="4"/>
-    </row>
-    <row r="961" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B961" s="4"/>
-      <c r="C961" s="2"/>
-      <c r="D961" s="4"/>
-      <c r="E961" s="4"/>
-      <c r="F961" s="4"/>
-      <c r="G961" s="4"/>
-      <c r="H961" s="11"/>
-      <c r="I961" s="4"/>
-      <c r="J961" s="4"/>
-      <c r="K961" s="4"/>
-      <c r="L961" s="4"/>
-      <c r="M961" s="4"/>
-      <c r="N961" s="4"/>
-      <c r="O961" s="4"/>
-      <c r="P961" s="4"/>
-      <c r="Q961" s="4"/>
-      <c r="R961" s="4"/>
-      <c r="S961" s="4"/>
-      <c r="T961" s="4"/>
-      <c r="U961" s="4"/>
-      <c r="V961" s="4"/>
-      <c r="W961" s="4"/>
-      <c r="X961" s="4"/>
-      <c r="Y961" s="4"/>
-      <c r="Z961" s="4"/>
-      <c r="AA961" s="4"/>
-    </row>
-    <row r="962" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B962" s="4"/>
-      <c r="C962" s="2"/>
-      <c r="D962" s="4"/>
-      <c r="E962" s="4"/>
-      <c r="F962" s="4"/>
-      <c r="G962" s="4"/>
-      <c r="H962" s="11"/>
-      <c r="I962" s="4"/>
-      <c r="J962" s="4"/>
-      <c r="K962" s="4"/>
-      <c r="L962" s="4"/>
-      <c r="M962" s="4"/>
-      <c r="N962" s="4"/>
-      <c r="O962" s="4"/>
-      <c r="P962" s="4"/>
-      <c r="Q962" s="4"/>
-      <c r="R962" s="4"/>
-      <c r="S962" s="4"/>
-      <c r="T962" s="4"/>
-      <c r="U962" s="4"/>
-      <c r="V962" s="4"/>
-      <c r="W962" s="4"/>
-      <c r="X962" s="4"/>
-      <c r="Y962" s="4"/>
-      <c r="Z962" s="4"/>
-      <c r="AA962" s="4"/>
-    </row>
-    <row r="963" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B963" s="4"/>
-      <c r="C963" s="2"/>
-      <c r="D963" s="4"/>
-      <c r="E963" s="4"/>
-      <c r="F963" s="4"/>
-      <c r="G963" s="4"/>
-      <c r="H963" s="11"/>
-      <c r="I963" s="4"/>
-      <c r="J963" s="4"/>
-      <c r="K963" s="4"/>
-      <c r="L963" s="4"/>
-      <c r="M963" s="4"/>
-      <c r="N963" s="4"/>
-      <c r="O963" s="4"/>
-      <c r="P963" s="4"/>
-      <c r="Q963" s="4"/>
-      <c r="R963" s="4"/>
-      <c r="S963" s="4"/>
-      <c r="T963" s="4"/>
-      <c r="U963" s="4"/>
-      <c r="V963" s="4"/>
-      <c r="W963" s="4"/>
-      <c r="X963" s="4"/>
-      <c r="Y963" s="4"/>
-      <c r="Z963" s="4"/>
-      <c r="AA963" s="4"/>
-    </row>
-    <row r="964" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B964" s="4"/>
-      <c r="C964" s="2"/>
-      <c r="D964" s="4"/>
-      <c r="E964" s="4"/>
-      <c r="F964" s="4"/>
-      <c r="G964" s="4"/>
-      <c r="H964" s="11"/>
-      <c r="I964" s="4"/>
-      <c r="J964" s="4"/>
-      <c r="K964" s="4"/>
-      <c r="L964" s="4"/>
-      <c r="M964" s="4"/>
-      <c r="N964" s="4"/>
-      <c r="O964" s="4"/>
-      <c r="P964" s="4"/>
-      <c r="Q964" s="4"/>
-      <c r="R964" s="4"/>
-      <c r="S964" s="4"/>
-      <c r="T964" s="4"/>
-      <c r="U964" s="4"/>
-      <c r="V964" s="4"/>
-      <c r="W964" s="4"/>
-      <c r="X964" s="4"/>
-      <c r="Y964" s="4"/>
-      <c r="Z964" s="4"/>
-      <c r="AA964" s="4"/>
-    </row>
-    <row r="965" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B965" s="4"/>
-      <c r="C965" s="2"/>
-      <c r="D965" s="4"/>
-      <c r="E965" s="4"/>
-      <c r="F965" s="4"/>
-      <c r="G965" s="4"/>
-      <c r="H965" s="11"/>
-      <c r="I965" s="4"/>
-      <c r="J965" s="4"/>
-      <c r="K965" s="4"/>
-      <c r="L965" s="4"/>
-      <c r="M965" s="4"/>
-      <c r="N965" s="4"/>
-      <c r="O965" s="4"/>
-      <c r="P965" s="4"/>
-      <c r="Q965" s="4"/>
-      <c r="R965" s="4"/>
-      <c r="S965" s="4"/>
-      <c r="T965" s="4"/>
-      <c r="U965" s="4"/>
-      <c r="V965" s="4"/>
-      <c r="W965" s="4"/>
-      <c r="X965" s="4"/>
-      <c r="Y965" s="4"/>
-      <c r="Z965" s="4"/>
-      <c r="AA965" s="4"/>
-    </row>
-    <row r="966" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B966" s="4"/>
-      <c r="C966" s="2"/>
-      <c r="D966" s="4"/>
-      <c r="E966" s="4"/>
-      <c r="F966" s="4"/>
-      <c r="G966" s="4"/>
-      <c r="H966" s="11"/>
-      <c r="I966" s="4"/>
-      <c r="J966" s="4"/>
-      <c r="K966" s="4"/>
-      <c r="L966" s="4"/>
-      <c r="M966" s="4"/>
-      <c r="N966" s="4"/>
-      <c r="O966" s="4"/>
-      <c r="P966" s="4"/>
-      <c r="Q966" s="4"/>
-      <c r="R966" s="4"/>
-      <c r="S966" s="4"/>
-      <c r="T966" s="4"/>
-      <c r="U966" s="4"/>
-      <c r="V966" s="4"/>
-      <c r="W966" s="4"/>
-      <c r="X966" s="4"/>
-      <c r="Y966" s="4"/>
-      <c r="Z966" s="4"/>
-      <c r="AA966" s="4"/>
-    </row>
-    <row r="967" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B967" s="4"/>
-      <c r="C967" s="2"/>
-      <c r="D967" s="4"/>
-      <c r="E967" s="4"/>
-      <c r="F967" s="4"/>
-      <c r="G967" s="4"/>
-      <c r="H967" s="11"/>
-      <c r="I967" s="4"/>
-      <c r="J967" s="4"/>
-      <c r="K967" s="4"/>
-      <c r="L967" s="4"/>
-      <c r="M967" s="4"/>
-      <c r="N967" s="4"/>
-      <c r="O967" s="4"/>
-      <c r="P967" s="4"/>
-      <c r="Q967" s="4"/>
-      <c r="R967" s="4"/>
-      <c r="S967" s="4"/>
-      <c r="T967" s="4"/>
-      <c r="U967" s="4"/>
-      <c r="V967" s="4"/>
-      <c r="W967" s="4"/>
-      <c r="X967" s="4"/>
-      <c r="Y967" s="4"/>
-      <c r="Z967" s="4"/>
-      <c r="AA967" s="4"/>
-    </row>
-    <row r="968" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B968" s="4"/>
-      <c r="C968" s="2"/>
-      <c r="D968" s="4"/>
-      <c r="E968" s="4"/>
-      <c r="F968" s="4"/>
-      <c r="G968" s="4"/>
-      <c r="H968" s="11"/>
-      <c r="I968" s="4"/>
-      <c r="J968" s="4"/>
-      <c r="K968" s="4"/>
-      <c r="L968" s="4"/>
-      <c r="M968" s="4"/>
-      <c r="N968" s="4"/>
-      <c r="O968" s="4"/>
-      <c r="P968" s="4"/>
-      <c r="Q968" s="4"/>
-      <c r="R968" s="4"/>
-      <c r="S968" s="4"/>
-      <c r="T968" s="4"/>
-      <c r="U968" s="4"/>
-      <c r="V968" s="4"/>
-      <c r="W968" s="4"/>
-      <c r="X968" s="4"/>
-      <c r="Y968" s="4"/>
-      <c r="Z968" s="4"/>
-      <c r="AA968" s="4"/>
-    </row>
-    <row r="969" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B969" s="4"/>
-      <c r="C969" s="2"/>
-      <c r="D969" s="4"/>
-      <c r="E969" s="4"/>
-      <c r="F969" s="4"/>
-      <c r="G969" s="4"/>
-      <c r="H969" s="11"/>
-      <c r="I969" s="4"/>
-      <c r="J969" s="4"/>
-      <c r="K969" s="4"/>
-      <c r="L969" s="4"/>
-      <c r="M969" s="4"/>
-      <c r="N969" s="4"/>
-      <c r="O969" s="4"/>
-      <c r="P969" s="4"/>
-      <c r="Q969" s="4"/>
-      <c r="R969" s="4"/>
-      <c r="S969" s="4"/>
-      <c r="T969" s="4"/>
-      <c r="U969" s="4"/>
-      <c r="V969" s="4"/>
-      <c r="W969" s="4"/>
-      <c r="X969" s="4"/>
-      <c r="Y969" s="4"/>
-      <c r="Z969" s="4"/>
-      <c r="AA969" s="4"/>
-    </row>
-    <row r="970" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B970" s="4"/>
-      <c r="C970" s="2"/>
-      <c r="D970" s="4"/>
-      <c r="E970" s="4"/>
-      <c r="F970" s="4"/>
-      <c r="G970" s="4"/>
-      <c r="H970" s="11"/>
-      <c r="I970" s="4"/>
-      <c r="J970" s="4"/>
-      <c r="K970" s="4"/>
-      <c r="L970" s="4"/>
-      <c r="M970" s="4"/>
-      <c r="N970" s="4"/>
-      <c r="O970" s="4"/>
-      <c r="P970" s="4"/>
-      <c r="Q970" s="4"/>
-      <c r="R970" s="4"/>
-      <c r="S970" s="4"/>
-      <c r="T970" s="4"/>
-      <c r="U970" s="4"/>
-      <c r="V970" s="4"/>
-      <c r="W970" s="4"/>
-      <c r="X970" s="4"/>
-      <c r="Y970" s="4"/>
-      <c r="Z970" s="4"/>
-      <c r="AA970" s="4"/>
-    </row>
-    <row r="971" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B971" s="4"/>
-      <c r="C971" s="2"/>
-      <c r="D971" s="4"/>
-      <c r="E971" s="4"/>
-      <c r="F971" s="4"/>
-      <c r="G971" s="4"/>
-      <c r="H971" s="11"/>
-      <c r="I971" s="4"/>
-      <c r="J971" s="4"/>
-      <c r="K971" s="4"/>
-      <c r="L971" s="4"/>
-      <c r="M971" s="4"/>
-      <c r="N971" s="4"/>
-      <c r="O971" s="4"/>
-      <c r="P971" s="4"/>
-      <c r="Q971" s="4"/>
-      <c r="R971" s="4"/>
-      <c r="S971" s="4"/>
-      <c r="T971" s="4"/>
-      <c r="U971" s="4"/>
-      <c r="V971" s="4"/>
-      <c r="W971" s="4"/>
-      <c r="X971" s="4"/>
-      <c r="Y971" s="4"/>
-      <c r="Z971" s="4"/>
-      <c r="AA971" s="4"/>
-    </row>
-    <row r="972" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B972" s="4"/>
-      <c r="C972" s="2"/>
-      <c r="D972" s="4"/>
-      <c r="E972" s="4"/>
-      <c r="F972" s="4"/>
-      <c r="G972" s="4"/>
-      <c r="H972" s="11"/>
-      <c r="I972" s="4"/>
-      <c r="J972" s="4"/>
-      <c r="K972" s="4"/>
-      <c r="L972" s="4"/>
-      <c r="M972" s="4"/>
-      <c r="N972" s="4"/>
-      <c r="O972" s="4"/>
-      <c r="P972" s="4"/>
-      <c r="Q972" s="4"/>
-      <c r="R972" s="4"/>
-      <c r="S972" s="4"/>
-      <c r="T972" s="4"/>
-      <c r="U972" s="4"/>
-      <c r="V972" s="4"/>
-      <c r="W972" s="4"/>
-      <c r="X972" s="4"/>
-      <c r="Y972" s="4"/>
-      <c r="Z972" s="4"/>
-      <c r="AA972" s="4"/>
-    </row>
-    <row r="973" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B973" s="4"/>
-      <c r="C973" s="2"/>
-      <c r="D973" s="4"/>
-      <c r="E973" s="4"/>
-      <c r="F973" s="4"/>
-      <c r="G973" s="4"/>
-      <c r="H973" s="11"/>
-      <c r="I973" s="4"/>
-      <c r="J973" s="4"/>
-      <c r="K973" s="4"/>
-      <c r="L973" s="4"/>
-      <c r="M973" s="4"/>
-      <c r="N973" s="4"/>
-      <c r="O973" s="4"/>
-      <c r="P973" s="4"/>
-      <c r="Q973" s="4"/>
-      <c r="R973" s="4"/>
-      <c r="S973" s="4"/>
-      <c r="T973" s="4"/>
-      <c r="U973" s="4"/>
-      <c r="V973" s="4"/>
-      <c r="W973" s="4"/>
-      <c r="X973" s="4"/>
-      <c r="Y973" s="4"/>
-      <c r="Z973" s="4"/>
-      <c r="AA973" s="4"/>
-    </row>
-    <row r="974" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B974" s="4"/>
-      <c r="C974" s="2"/>
-      <c r="D974" s="4"/>
-      <c r="E974" s="4"/>
-      <c r="F974" s="4"/>
-      <c r="G974" s="4"/>
-      <c r="H974" s="11"/>
-      <c r="I974" s="4"/>
-      <c r="J974" s="4"/>
-      <c r="K974" s="4"/>
-      <c r="L974" s="4"/>
-      <c r="M974" s="4"/>
-      <c r="N974" s="4"/>
-      <c r="O974" s="4"/>
-      <c r="P974" s="4"/>
-      <c r="Q974" s="4"/>
-      <c r="R974" s="4"/>
-      <c r="S974" s="4"/>
-      <c r="T974" s="4"/>
-      <c r="U974" s="4"/>
-      <c r="V974" s="4"/>
-      <c r="W974" s="4"/>
-      <c r="X974" s="4"/>
-      <c r="Y974" s="4"/>
-      <c r="Z974" s="4"/>
-      <c r="AA974" s="4"/>
-    </row>
-    <row r="975" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B975" s="4"/>
-      <c r="C975" s="2"/>
-      <c r="D975" s="4"/>
-      <c r="E975" s="4"/>
-      <c r="F975" s="4"/>
-      <c r="G975" s="4"/>
-      <c r="H975" s="11"/>
-      <c r="I975" s="4"/>
-      <c r="J975" s="4"/>
-      <c r="K975" s="4"/>
-      <c r="L975" s="4"/>
-      <c r="M975" s="4"/>
-      <c r="N975" s="4"/>
-      <c r="O975" s="4"/>
-      <c r="P975" s="4"/>
-      <c r="Q975" s="4"/>
-      <c r="R975" s="4"/>
-      <c r="S975" s="4"/>
-      <c r="T975" s="4"/>
-      <c r="U975" s="4"/>
-      <c r="V975" s="4"/>
-      <c r="W975" s="4"/>
-      <c r="X975" s="4"/>
-      <c r="Y975" s="4"/>
-      <c r="Z975" s="4"/>
-      <c r="AA975" s="4"/>
-    </row>
-    <row r="976" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B976" s="4"/>
-      <c r="C976" s="2"/>
-      <c r="D976" s="4"/>
-      <c r="E976" s="4"/>
-      <c r="F976" s="4"/>
-      <c r="G976" s="4"/>
-      <c r="H976" s="11"/>
-      <c r="I976" s="4"/>
-      <c r="J976" s="4"/>
-      <c r="K976" s="4"/>
-      <c r="L976" s="4"/>
-      <c r="M976" s="4"/>
-      <c r="N976" s="4"/>
-      <c r="O976" s="4"/>
-      <c r="P976" s="4"/>
-      <c r="Q976" s="4"/>
-      <c r="R976" s="4"/>
-      <c r="S976" s="4"/>
-      <c r="T976" s="4"/>
-      <c r="U976" s="4"/>
-      <c r="V976" s="4"/>
-      <c r="W976" s="4"/>
-      <c r="X976" s="4"/>
-      <c r="Y976" s="4"/>
-      <c r="Z976" s="4"/>
-      <c r="AA976" s="4"/>
-    </row>
-    <row r="977" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B977" s="4"/>
-      <c r="C977" s="2"/>
-      <c r="D977" s="4"/>
-      <c r="E977" s="4"/>
-      <c r="F977" s="4"/>
-      <c r="G977" s="4"/>
-      <c r="H977" s="11"/>
-      <c r="I977" s="4"/>
-      <c r="J977" s="4"/>
-      <c r="K977" s="4"/>
-      <c r="L977" s="4"/>
-      <c r="M977" s="4"/>
-      <c r="N977" s="4"/>
-      <c r="O977" s="4"/>
-      <c r="P977" s="4"/>
-      <c r="Q977" s="4"/>
-      <c r="R977" s="4"/>
-      <c r="S977" s="4"/>
-      <c r="T977" s="4"/>
-      <c r="U977" s="4"/>
-      <c r="V977" s="4"/>
-      <c r="W977" s="4"/>
-      <c r="X977" s="4"/>
-      <c r="Y977" s="4"/>
-      <c r="Z977" s="4"/>
-      <c r="AA977" s="4"/>
-    </row>
-    <row r="978" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B978" s="4"/>
-      <c r="C978" s="2"/>
-      <c r="D978" s="4"/>
-      <c r="E978" s="4"/>
-      <c r="F978" s="4"/>
-      <c r="G978" s="4"/>
-      <c r="H978" s="11"/>
-      <c r="I978" s="4"/>
-      <c r="J978" s="4"/>
-      <c r="K978" s="4"/>
-      <c r="L978" s="4"/>
-      <c r="M978" s="4"/>
-      <c r="N978" s="4"/>
-      <c r="O978" s="4"/>
-      <c r="P978" s="4"/>
-      <c r="Q978" s="4"/>
-      <c r="R978" s="4"/>
-      <c r="S978" s="4"/>
-      <c r="T978" s="4"/>
-      <c r="U978" s="4"/>
-      <c r="V978" s="4"/>
-      <c r="W978" s="4"/>
-      <c r="X978" s="4"/>
-      <c r="Y978" s="4"/>
-      <c r="Z978" s="4"/>
-      <c r="AA978" s="4"/>
-    </row>
-    <row r="979" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B979" s="4"/>
-      <c r="C979" s="2"/>
-      <c r="D979" s="4"/>
-      <c r="E979" s="4"/>
-      <c r="F979" s="4"/>
-      <c r="G979" s="4"/>
-      <c r="H979" s="11"/>
-      <c r="I979" s="4"/>
-      <c r="J979" s="4"/>
-      <c r="K979" s="4"/>
-      <c r="L979" s="4"/>
-      <c r="M979" s="4"/>
-      <c r="N979" s="4"/>
-      <c r="O979" s="4"/>
-      <c r="P979" s="4"/>
-      <c r="Q979" s="4"/>
-      <c r="R979" s="4"/>
-      <c r="S979" s="4"/>
-      <c r="T979" s="4"/>
-      <c r="U979" s="4"/>
-      <c r="V979" s="4"/>
-      <c r="W979" s="4"/>
-      <c r="X979" s="4"/>
-      <c r="Y979" s="4"/>
-      <c r="Z979" s="4"/>
-      <c r="AA979" s="4"/>
-    </row>
-    <row r="980" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B980" s="4"/>
-      <c r="C980" s="2"/>
-      <c r="D980" s="4"/>
-      <c r="E980" s="4"/>
-      <c r="F980" s="4"/>
-      <c r="G980" s="4"/>
-      <c r="H980" s="11"/>
-      <c r="I980" s="4"/>
-      <c r="J980" s="4"/>
-      <c r="K980" s="4"/>
-      <c r="L980" s="4"/>
-      <c r="M980" s="4"/>
-      <c r="N980" s="4"/>
-      <c r="O980" s="4"/>
-      <c r="P980" s="4"/>
-      <c r="Q980" s="4"/>
-      <c r="R980" s="4"/>
-      <c r="S980" s="4"/>
-      <c r="T980" s="4"/>
-      <c r="U980" s="4"/>
-      <c r="V980" s="4"/>
-      <c r="W980" s="4"/>
-      <c r="X980" s="4"/>
-      <c r="Y980" s="4"/>
-      <c r="Z980" s="4"/>
-      <c r="AA980" s="4"/>
-    </row>
-    <row r="981" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B981" s="4"/>
-      <c r="C981" s="2"/>
-      <c r="D981" s="4"/>
-      <c r="E981" s="4"/>
-      <c r="F981" s="4"/>
-      <c r="G981" s="4"/>
-      <c r="H981" s="11"/>
-      <c r="I981" s="4"/>
-      <c r="J981" s="4"/>
-      <c r="K981" s="4"/>
-      <c r="L981" s="4"/>
-      <c r="M981" s="4"/>
-      <c r="N981" s="4"/>
-      <c r="O981" s="4"/>
-      <c r="P981" s="4"/>
-      <c r="Q981" s="4"/>
-      <c r="R981" s="4"/>
-      <c r="S981" s="4"/>
-      <c r="T981" s="4"/>
-      <c r="U981" s="4"/>
-      <c r="V981" s="4"/>
-      <c r="W981" s="4"/>
-      <c r="X981" s="4"/>
-      <c r="Y981" s="4"/>
-      <c r="Z981" s="4"/>
-      <c r="AA981" s="4"/>
-    </row>
-    <row r="982" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B982" s="4"/>
-      <c r="C982" s="2"/>
-      <c r="D982" s="4"/>
-      <c r="E982" s="4"/>
-      <c r="F982" s="4"/>
-      <c r="G982" s="4"/>
-      <c r="H982" s="11"/>
-      <c r="I982" s="4"/>
-      <c r="J982" s="4"/>
-      <c r="K982" s="4"/>
-      <c r="L982" s="4"/>
-      <c r="M982" s="4"/>
-      <c r="N982" s="4"/>
-      <c r="O982" s="4"/>
-      <c r="P982" s="4"/>
-      <c r="Q982" s="4"/>
-      <c r="R982" s="4"/>
-      <c r="S982" s="4"/>
-      <c r="T982" s="4"/>
-      <c r="U982" s="4"/>
-      <c r="V982" s="4"/>
-      <c r="W982" s="4"/>
-      <c r="X982" s="4"/>
-      <c r="Y982" s="4"/>
-      <c r="Z982" s="4"/>
-      <c r="AA982" s="4"/>
-    </row>
-    <row r="983" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B983" s="4"/>
-      <c r="C983" s="2"/>
-      <c r="D983" s="4"/>
-      <c r="E983" s="4"/>
-      <c r="F983" s="4"/>
-      <c r="G983" s="4"/>
-      <c r="H983" s="11"/>
-      <c r="I983" s="4"/>
-      <c r="J983" s="4"/>
-      <c r="K983" s="4"/>
-      <c r="L983" s="4"/>
-      <c r="M983" s="4"/>
-      <c r="N983" s="4"/>
-      <c r="O983" s="4"/>
-      <c r="P983" s="4"/>
-      <c r="Q983" s="4"/>
-      <c r="R983" s="4"/>
-      <c r="S983" s="4"/>
-      <c r="T983" s="4"/>
-      <c r="U983" s="4"/>
-      <c r="V983" s="4"/>
-      <c r="W983" s="4"/>
-      <c r="X983" s="4"/>
-      <c r="Y983" s="4"/>
-      <c r="Z983" s="4"/>
-      <c r="AA983" s="4"/>
-    </row>
-    <row r="984" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B984" s="4"/>
-      <c r="C984" s="2"/>
-      <c r="D984" s="4"/>
-      <c r="E984" s="4"/>
-      <c r="F984" s="4"/>
-      <c r="G984" s="4"/>
-      <c r="H984" s="11"/>
-      <c r="I984" s="4"/>
-      <c r="J984" s="4"/>
-      <c r="K984" s="4"/>
-      <c r="L984" s="4"/>
-      <c r="M984" s="4"/>
-      <c r="N984" s="4"/>
-      <c r="O984" s="4"/>
-      <c r="P984" s="4"/>
-      <c r="Q984" s="4"/>
-      <c r="R984" s="4"/>
-      <c r="S984" s="4"/>
-      <c r="T984" s="4"/>
-      <c r="U984" s="4"/>
-      <c r="V984" s="4"/>
-      <c r="W984" s="4"/>
-      <c r="X984" s="4"/>
-      <c r="Y984" s="4"/>
-      <c r="Z984" s="4"/>
-      <c r="AA984" s="4"/>
-    </row>
-    <row r="985" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B985" s="4"/>
-      <c r="C985" s="2"/>
-      <c r="D985" s="4"/>
-      <c r="E985" s="4"/>
-      <c r="F985" s="4"/>
-      <c r="G985" s="4"/>
-      <c r="H985" s="11"/>
-      <c r="I985" s="4"/>
-      <c r="J985" s="4"/>
-      <c r="K985" s="4"/>
-      <c r="L985" s="4"/>
-      <c r="M985" s="4"/>
-      <c r="N985" s="4"/>
-      <c r="O985" s="4"/>
-      <c r="P985" s="4"/>
-      <c r="Q985" s="4"/>
-      <c r="R985" s="4"/>
-      <c r="S985" s="4"/>
-      <c r="T985" s="4"/>
-      <c r="U985" s="4"/>
-      <c r="V985" s="4"/>
-      <c r="W985" s="4"/>
-      <c r="X985" s="4"/>
-      <c r="Y985" s="4"/>
-      <c r="Z985" s="4"/>
-      <c r="AA985" s="4"/>
-    </row>
-    <row r="986" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B986" s="4"/>
-      <c r="C986" s="2"/>
-      <c r="D986" s="4"/>
-      <c r="E986" s="4"/>
-      <c r="F986" s="4"/>
-      <c r="G986" s="4"/>
-      <c r="H986" s="11"/>
-      <c r="I986" s="4"/>
-      <c r="J986" s="4"/>
-      <c r="K986" s="4"/>
-      <c r="L986" s="4"/>
-      <c r="M986" s="4"/>
-      <c r="N986" s="4"/>
-      <c r="O986" s="4"/>
-      <c r="P986" s="4"/>
-      <c r="Q986" s="4"/>
-      <c r="R986" s="4"/>
-      <c r="S986" s="4"/>
-      <c r="T986" s="4"/>
-      <c r="U986" s="4"/>
-      <c r="V986" s="4"/>
-      <c r="W986" s="4"/>
-      <c r="X986" s="4"/>
-      <c r="Y986" s="4"/>
-      <c r="Z986" s="4"/>
-      <c r="AA986" s="4"/>
-    </row>
-    <row r="987" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B987" s="4"/>
-      <c r="C987" s="2"/>
-      <c r="D987" s="4"/>
-      <c r="E987" s="4"/>
-      <c r="F987" s="4"/>
-      <c r="G987" s="4"/>
-      <c r="H987" s="11"/>
-      <c r="I987" s="4"/>
-      <c r="J987" s="4"/>
-      <c r="K987" s="4"/>
-      <c r="L987" s="4"/>
-      <c r="M987" s="4"/>
-      <c r="N987" s="4"/>
-      <c r="O987" s="4"/>
-      <c r="P987" s="4"/>
-      <c r="Q987" s="4"/>
-      <c r="R987" s="4"/>
-      <c r="S987" s="4"/>
-      <c r="T987" s="4"/>
-      <c r="U987" s="4"/>
-      <c r="V987" s="4"/>
-      <c r="W987" s="4"/>
-      <c r="X987" s="4"/>
-      <c r="Y987" s="4"/>
-      <c r="Z987" s="4"/>
-      <c r="AA987" s="4"/>
-    </row>
-    <row r="988" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B988" s="4"/>
-      <c r="C988" s="2"/>
-      <c r="D988" s="4"/>
-      <c r="E988" s="4"/>
-      <c r="F988" s="4"/>
-      <c r="G988" s="4"/>
-      <c r="H988" s="11"/>
-      <c r="I988" s="4"/>
-      <c r="J988" s="4"/>
-      <c r="K988" s="4"/>
-      <c r="L988" s="4"/>
-      <c r="M988" s="4"/>
-      <c r="N988" s="4"/>
-      <c r="O988" s="4"/>
-      <c r="P988" s="4"/>
-      <c r="Q988" s="4"/>
-      <c r="R988" s="4"/>
-      <c r="S988" s="4"/>
-      <c r="T988" s="4"/>
-      <c r="U988" s="4"/>
-      <c r="V988" s="4"/>
-      <c r="W988" s="4"/>
-      <c r="X988" s="4"/>
-      <c r="Y988" s="4"/>
-      <c r="Z988" s="4"/>
-      <c r="AA988" s="4"/>
-    </row>
-    <row r="989" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B989" s="4"/>
-      <c r="C989" s="2"/>
-      <c r="D989" s="4"/>
-      <c r="E989" s="4"/>
-      <c r="F989" s="4"/>
-      <c r="G989" s="4"/>
-      <c r="H989" s="11"/>
-      <c r="I989" s="4"/>
-      <c r="J989" s="4"/>
-      <c r="K989" s="4"/>
-      <c r="L989" s="4"/>
-      <c r="M989" s="4"/>
-      <c r="N989" s="4"/>
-      <c r="O989" s="4"/>
-      <c r="P989" s="4"/>
-      <c r="Q989" s="4"/>
-      <c r="R989" s="4"/>
-      <c r="S989" s="4"/>
-      <c r="T989" s="4"/>
-      <c r="U989" s="4"/>
-      <c r="V989" s="4"/>
-      <c r="W989" s="4"/>
-      <c r="X989" s="4"/>
-      <c r="Y989" s="4"/>
-      <c r="Z989" s="4"/>
-      <c r="AA989" s="4"/>
-    </row>
-    <row r="990" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="H990" s="71"/>
-    </row>
-    <row r="991" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="H991" s="71"/>
-    </row>
-    <row r="992" spans="2:27" x14ac:dyDescent="0.25">
-      <c r="H992" s="71"/>
-    </row>
-    <row r="993" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H993" s="71"/>
-    </row>
-    <row r="994" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H994" s="71"/>
+    <row r="960" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="H960" s="27"/>
+    </row>
+    <row r="961" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H961" s="27"/>
+    </row>
+    <row r="962" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H962" s="27"/>
+    </row>
+    <row r="963" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H963" s="27"/>
+    </row>
+    <row r="964" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H964" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="23">
+    <mergeCell ref="I12:I15"/>
+    <mergeCell ref="B66:F66"/>
+    <mergeCell ref="G66:H66"/>
+    <mergeCell ref="E70:H70"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="A67:G67"/>
+    <mergeCell ref="A68:G68"/>
+    <mergeCell ref="A69:G69"/>
     <mergeCell ref="I9:I11"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="D9:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="H10:H11"/>
     <mergeCell ref="D1:H1"/>
     <mergeCell ref="D2:H2"/>
     <mergeCell ref="B5:H5"/>
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="B7:H7"/>
-    <mergeCell ref="B98:F98"/>
-    <mergeCell ref="G98:H98"/>
-    <mergeCell ref="E100:H100"/>
-    <mergeCell ref="B8:H8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="D9:D11"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="G9:G11"/>
-    <mergeCell ref="H9:H11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
